--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC641F7-218F-4018-BD66-D039C0D7EC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC8C18F-6AE8-4758-9004-F606A731E541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>correo</t>
   </si>
@@ -59,6 +59,12 @@
   </si>
   <si>
     <t>Negocios</t>
+  </si>
+  <si>
+    <t>Ing.</t>
+  </si>
+  <si>
+    <t>guerrerofranco1429@outlook.com</t>
   </si>
 </sst>
 </file>
@@ -432,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
@@ -493,12 +499,24 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" xr:uid="{2A9A9881-DC05-4B41-B8AC-A7F869B852C1}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{6C5EF15F-64E8-489C-A283-845D7B404C80}"/>
     <hyperlink ref="A2" r:id="rId3" xr:uid="{2A1BEA8C-C04A-401C-89F3-2BD68897AA7D}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{7BD4971A-DDA1-48E3-8ED4-519D9D26EA61}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{9065DADE-A1C3-4E71-BF87-DEF8A616FFFB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC8C18F-6AE8-4758-9004-F606A731E541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F70F39-2784-47BC-A124-210138B5AB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,7 +441,7 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F70F39-2784-47BC-A124-210138B5AB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5BE089-9872-4817-B8C2-388A52D99FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>correo</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>guerrerofranco1429@outlook.com</t>
+  </si>
+  <si>
+    <t>ale00528@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -438,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -510,6 +513,17 @@
         <v>13</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" xr:uid="{2A9A9881-DC05-4B41-B8AC-A7F869B852C1}"/>
@@ -517,6 +531,7 @@
     <hyperlink ref="A2" r:id="rId3" xr:uid="{2A1BEA8C-C04A-401C-89F3-2BD68897AA7D}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{7BD4971A-DDA1-48E3-8ED4-519D9D26EA61}"/>
     <hyperlink ref="A6" r:id="rId5" xr:uid="{9065DADE-A1C3-4E71-BF87-DEF8A616FFFB}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{A86CE147-B6E5-45AB-8800-08EE4B6B0414}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5BE089-9872-4817-B8C2-388A52D99FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646E2DD7-C4D7-46DB-8582-F1FB596AD773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>correo</t>
   </si>
@@ -68,13 +68,22 @@
   </si>
   <si>
     <t>ale00528@gmail.com</t>
+  </si>
+  <si>
+    <t>sfrkaiserf@gmail.com</t>
+  </si>
+  <si>
+    <t>Kaiser</t>
+  </si>
+  <si>
+    <t>sfrkaiser@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,11 +95,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -132,12 +150,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -441,13 +460,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,80 +477,105 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" xr:uid="{2A9A9881-DC05-4B41-B8AC-A7F869B852C1}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{6C5EF15F-64E8-489C-A283-845D7B404C80}"/>
-    <hyperlink ref="A2" r:id="rId3" xr:uid="{2A1BEA8C-C04A-401C-89F3-2BD68897AA7D}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{7BD4971A-DDA1-48E3-8ED4-519D9D26EA61}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{9065DADE-A1C3-4E71-BF87-DEF8A616FFFB}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{A86CE147-B6E5-45AB-8800-08EE4B6B0414}"/>
+    <hyperlink ref="A5" r:id="rId1" xr:uid="{2A9A9881-DC05-4B41-B8AC-A7F869B852C1}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{6C5EF15F-64E8-489C-A283-845D7B404C80}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{2A1BEA8C-C04A-401C-89F3-2BD68897AA7D}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{7BD4971A-DDA1-48E3-8ED4-519D9D26EA61}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{9065DADE-A1C3-4E71-BF87-DEF8A616FFFB}"/>
+    <hyperlink ref="A8" r:id="rId6" xr:uid="{A86CE147-B6E5-45AB-8800-08EE4B6B0414}"/>
+    <hyperlink ref="A9" r:id="rId7" xr:uid="{46DAF42B-BA7D-494A-A5A1-6E45ED5C5A96}"/>
+    <hyperlink ref="A2" r:id="rId8" xr:uid="{EF517B94-34D6-4A6E-9AB3-381D0842451D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646E2DD7-C4D7-46DB-8582-F1FB596AD773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75951606-5991-458D-B9D9-127853FFA693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>correo</t>
   </si>
@@ -31,59 +31,17 @@
     <t>tratamiento</t>
   </si>
   <si>
-    <t>fguerrero@partnertech.pe</t>
-  </si>
-  <si>
-    <t>Franco</t>
-  </si>
-  <si>
-    <t>Sr.</t>
-  </si>
-  <si>
-    <t>Srta.</t>
-  </si>
-  <si>
-    <t>Helio</t>
-  </si>
-  <si>
-    <t>hmelgarejo@partnertech.pe</t>
-  </si>
-  <si>
-    <t>acardozo@partnertech.pe</t>
-  </si>
-  <si>
-    <t>Alexandra</t>
-  </si>
-  <si>
     <t>negocios@partnertech.pe</t>
   </si>
   <si>
-    <t>Negocios</t>
-  </si>
-  <si>
-    <t>Ing.</t>
-  </si>
-  <si>
-    <t>guerrerofranco1429@outlook.com</t>
-  </si>
-  <si>
-    <t>ale00528@gmail.com</t>
-  </si>
-  <si>
-    <t>sfrkaiserf@gmail.com</t>
-  </si>
-  <si>
-    <t>Kaiser</t>
-  </si>
-  <si>
-    <t>sfrkaiser@gmail.com</t>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,14 +59,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -150,13 +100,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -460,13 +409,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,105 +426,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" xr:uid="{2A9A9881-DC05-4B41-B8AC-A7F869B852C1}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{6C5EF15F-64E8-489C-A283-845D7B404C80}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{2A1BEA8C-C04A-401C-89F3-2BD68897AA7D}"/>
-    <hyperlink ref="A6" r:id="rId4" xr:uid="{7BD4971A-DDA1-48E3-8ED4-519D9D26EA61}"/>
-    <hyperlink ref="A7" r:id="rId5" xr:uid="{9065DADE-A1C3-4E71-BF87-DEF8A616FFFB}"/>
-    <hyperlink ref="A8" r:id="rId6" xr:uid="{A86CE147-B6E5-45AB-8800-08EE4B6B0414}"/>
-    <hyperlink ref="A9" r:id="rId7" xr:uid="{46DAF42B-BA7D-494A-A5A1-6E45ED5C5A96}"/>
-    <hyperlink ref="A2" r:id="rId8" xr:uid="{EF517B94-34D6-4A6E-9AB3-381D0842451D}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{280767C9-3621-46D1-909F-43A1929E105E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75951606-5991-458D-B9D9-127853FFA693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB795FA-BCC3-406A-8D06-7687F6FDFFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3612" yWindow="1716" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>correo</t>
   </si>
   <si>
     <t>nombre</t>
-  </si>
-  <si>
-    <t>tratamiento</t>
   </si>
   <si>
     <t>negocios@partnertech.pe</t>
@@ -409,32 +406,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB795FA-BCC3-406A-8D06-7687F6FDFFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545AD4A-85DE-4701-93C0-6271F3D70568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3612" yWindow="1716" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>correo</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>test-qtkbj0x0k@srv1.mail-tester.com</t>
   </si>
 </sst>
 </file>
@@ -406,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -428,9 +431,18 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{280767C9-3621-46D1-909F-43A1929E105E}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{B86295BB-C93E-45CD-B9DD-C0CBA1FEAC0D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545AD4A-85DE-4701-93C0-6271F3D70568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7CB1EE-5861-4E48-A27D-AA80487EDA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="1716" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="160">
   <si>
     <t>correo</t>
   </si>
@@ -28,13 +41,478 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>negocios@partnertech.pe</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>test-qtkbj0x0k@srv1.mail-tester.com</t>
+    <t>jcefferino@spesac.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>mpon@spesac.com</t>
+  </si>
+  <si>
+    <t>Marisol</t>
+  </si>
+  <si>
+    <t>jruiz@agroindustriallaredo.com</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>pgarzon@agroindustriallaredo.com</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>gcardenas@kallpagas.com</t>
+  </si>
+  <si>
+    <t>Glicia</t>
+  </si>
+  <si>
+    <t>msuarez@kallpagas.com</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>huroma0207@gmail.com</t>
+  </si>
+  <si>
+    <t>Huber</t>
+  </si>
+  <si>
+    <t>manuel.26.gt@gmail.com</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>henri.borit@serfi.pe</t>
+  </si>
+  <si>
+    <t>Henri</t>
+  </si>
+  <si>
+    <t>liliana.benavides@serfi.pe</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>admin@renbikemotors.com</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>juancsc20111@hotmail.com</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>anabella.lar@gmail.com</t>
+  </si>
+  <si>
+    <t>esanchezherrera@gmail.com</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>univenpvc@gmail.com</t>
+  </si>
+  <si>
+    <t>Keskin</t>
+  </si>
+  <si>
+    <t>ventasunivenpvc@gmail.com</t>
+  </si>
+  <si>
+    <t>Abraham</t>
+  </si>
+  <si>
+    <t>gerencia@mefico.com.pe</t>
+  </si>
+  <si>
+    <t>Leoncio</t>
+  </si>
+  <si>
+    <t>pbeas@hotmail.com</t>
+  </si>
+  <si>
+    <t>carlos.rubina@corpessa.com.pe</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>josue.gamarra@corpessa.com.pe</t>
+  </si>
+  <si>
+    <t>Josue</t>
+  </si>
+  <si>
+    <t>fsuclupe@serrature.com.pe</t>
+  </si>
+  <si>
+    <t>Fiorella</t>
+  </si>
+  <si>
+    <t>ls@serrature.com.pe</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>alexanderadm28@gmail.com</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>royalalpacadelperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Rober</t>
+  </si>
+  <si>
+    <t>amalejo@isamisa.com.pe</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>falejo@isamisa.com.pe</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
+    <t>carlosenriquealvarezlecaros@gmail.com</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>marycruzalvarosinca@gmail.com</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>amyd.import@gmail.com</t>
+  </si>
+  <si>
+    <t>Wiler</t>
+  </si>
+  <si>
+    <t>info@leds1108.pe</t>
+  </si>
+  <si>
+    <t>adirectorio@ladrillospiramide.com</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>wugarte@ladrillospiramide.com</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>administracion@appesca.pe</t>
+  </si>
+  <si>
+    <t>Erick</t>
+  </si>
+  <si>
+    <t>pesquera_tevimar_sa@hotmail.com</t>
+  </si>
+  <si>
+    <t>Benny</t>
+  </si>
+  <si>
+    <t>lukabf@zadar.com.pe</t>
+  </si>
+  <si>
+    <t>Luka</t>
+  </si>
+  <si>
+    <t>manliopiana@gmail.com</t>
+  </si>
+  <si>
+    <t>Manlio</t>
+  </si>
+  <si>
+    <t>jparrue@gt.com.pe</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>lrodriguez@gt.com.pe</t>
+  </si>
+  <si>
+    <t>Luciana</t>
+  </si>
+  <si>
+    <t>cristisuare@gmail.com</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>hugorey86@gmail.com</t>
+  </si>
+  <si>
+    <t>contabilidad@jvgenergy.pe</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>rpalacios@jvgenergy.pe</t>
+  </si>
+  <si>
+    <t>Roxana</t>
+  </si>
+  <si>
+    <t>barteaga@cmbenly.com.pe</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>contabilidad@cmbenly.com.pe</t>
+  </si>
+  <si>
+    <t>Joselyn</t>
+  </si>
+  <si>
+    <t>adrianavar99@hotmail.com</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>arc@armr.com.pe</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>lvtianshi@xiaomi.com</t>
+  </si>
+  <si>
+    <t>Lv</t>
+  </si>
+  <si>
+    <t>mfpr@xiaomi.com</t>
+  </si>
+  <si>
+    <t>María</t>
+  </si>
+  <si>
+    <t>artifum@gmail.com</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>julioarti@hotmail.com</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>jose.callalle@arwii.com</t>
+  </si>
+  <si>
+    <t>josseph.callalle@arwii.com</t>
+  </si>
+  <si>
+    <t>Josseph</t>
+  </si>
+  <si>
+    <t>calderos@calderospiedra.com</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>calderospiedra@gmail.com</t>
+  </si>
+  <si>
+    <t>evargas@grupovargas-na.com</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>juanllatas@maderasamerica.com</t>
+  </si>
+  <si>
+    <t>monersosa123@gmail.com</t>
+  </si>
+  <si>
+    <t>sosaoliva123@gmail.com</t>
+  </si>
+  <si>
+    <t>juan.landeo@lharqts.com</t>
+  </si>
+  <si>
+    <t>yuliana.ponce@lharqts.com</t>
+  </si>
+  <si>
+    <t>Yuliana</t>
+  </si>
+  <si>
+    <t>condezosamuel@gmail.com</t>
+  </si>
+  <si>
+    <t>pauladeamat@gmail.com</t>
+  </si>
+  <si>
+    <t>Paula</t>
+  </si>
+  <si>
+    <t>cufalsrl@gmail.com</t>
+  </si>
+  <si>
+    <t>rexchemicalandserviceeirl@gmail.com</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>carolina@vodevil.pe</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>gailee@vodevil.pe</t>
+  </si>
+  <si>
+    <t>Gailee</t>
+  </si>
+  <si>
+    <t>administracion@celltronicperu.com</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>administracion@sotravelpe.com</t>
+  </si>
+  <si>
+    <t>Amanda</t>
+  </si>
+  <si>
+    <t>juantumbap@hotmail.com</t>
+  </si>
+  <si>
+    <t>josmell.importaciones@gmail.com</t>
+  </si>
+  <si>
+    <t>Josmell</t>
+  </si>
+  <si>
+    <t>papeleravalen@hotmail.com</t>
+  </si>
+  <si>
+    <t>Eugenio</t>
+  </si>
+  <si>
+    <t>studio3@studio3peru.com</t>
+  </si>
+  <si>
+    <t>marissa@newsmonitor.pe</t>
+  </si>
+  <si>
+    <t>Marissa</t>
+  </si>
+  <si>
+    <t>luzmila.cardenas@hotmail.com</t>
+  </si>
+  <si>
+    <t>Luzmila</t>
+  </si>
+  <si>
+    <t>paola.salas@genesis7.pe</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>christianvillanueva@savia.school</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>condugasperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Edy</t>
+  </si>
+  <si>
+    <t>industriasfiberjassac@hotmail.com</t>
+  </si>
+  <si>
+    <t>hugo@barcoderfid.pe</t>
+  </si>
+  <si>
+    <t>luistalledo1128@gmail.com</t>
+  </si>
+  <si>
+    <t>patricia.ancosolorzano@gmail.com</t>
+  </si>
+  <si>
+    <t>j.castro@peruprintrm.com</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>jqueirolo@labocer.com.pe</t>
+  </si>
+  <si>
+    <t>ventas@metalglass.com.pe</t>
+  </si>
+  <si>
+    <t>gallardogonzalesjesusalberto@gmail.com</t>
+  </si>
+  <si>
+    <t>ludicusplayground@gmail.com</t>
+  </si>
+  <si>
+    <t>Ludwing</t>
+  </si>
+  <si>
+    <t>alpiespejos@gmail.com</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Anabella</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>Moner</t>
+  </si>
+  <si>
+    <t>Samuel</t>
   </si>
 </sst>
 </file>
@@ -409,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -424,7 +902,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -432,18 +910,697 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>110</v>
+      </c>
+      <c r="B61" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>116</v>
+      </c>
+      <c r="B65" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>118</v>
+      </c>
+      <c r="B66" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>122</v>
+      </c>
+      <c r="B68" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>132</v>
+      </c>
+      <c r="B74" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>134</v>
+      </c>
+      <c r="B75" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>140</v>
+      </c>
+      <c r="B78" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>142</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>143</v>
+      </c>
+      <c r="B80" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>144</v>
+      </c>
+      <c r="B81" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>145</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>148</v>
+      </c>
+      <c r="B84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>149</v>
+      </c>
+      <c r="B85" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>151</v>
+      </c>
+      <c r="B87" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="2"/>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{280767C9-3621-46D1-909F-43A1929E105E}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{B86295BB-C93E-45CD-B9DD-C0CBA1FEAC0D}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21A8553-0E45-430C-8E47-1032054CD4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686684C7-516B-4CD3-9824-3390B777FEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="169">
   <si>
     <t>correo</t>
   </si>
@@ -45,6 +45,501 @@
   </si>
   <si>
     <t>negocios@partnertech.pe</t>
+  </si>
+  <si>
+    <t>p.marketing@asclaboral.com</t>
+  </si>
+  <si>
+    <t>Cesia</t>
+  </si>
+  <si>
+    <t>secretaria@asclaboral.com</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>vandia@asclaboral.com</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>rsarmiento@ventia.pe</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>tzolezzi@ventia.pe</t>
+  </si>
+  <si>
+    <t>Tulio</t>
+  </si>
+  <si>
+    <t>yllanos@ventia.pe</t>
+  </si>
+  <si>
+    <t>Yliana</t>
+  </si>
+  <si>
+    <t>gmarin@asi-group.com</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>rvillagran@asi-group.com</t>
+  </si>
+  <si>
+    <t>sergioql@gmail.com</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>dfonseca@idearkperu.com</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>iaguilar@idearkperu.com</t>
+  </si>
+  <si>
+    <t>Elard</t>
+  </si>
+  <si>
+    <t>mfonseca@idearkperu.com</t>
+  </si>
+  <si>
+    <t>Marisol</t>
+  </si>
+  <si>
+    <t>acbrigs@hotmail.com</t>
+  </si>
+  <si>
+    <t>Giannina</t>
+  </si>
+  <si>
+    <t>monicaayllon.diezcanseco@gmail.com</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>peru@cortes-moldes.com</t>
+  </si>
+  <si>
+    <t>Emilio</t>
+  </si>
+  <si>
+    <t>cynthia.zegarra@gim-peru.com</t>
+  </si>
+  <si>
+    <t>Cynthia</t>
+  </si>
+  <si>
+    <t>gerencia.valfhesigroup@gmail.com</t>
+  </si>
+  <si>
+    <t>Clara</t>
+  </si>
+  <si>
+    <t>gestioninmobiliaria@gmail.com</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>administracion@refsupplysac.com</t>
+  </si>
+  <si>
+    <t>Irene</t>
+  </si>
+  <si>
+    <t>al.efer5@hotmail.com</t>
+  </si>
+  <si>
+    <t>Alfonsa</t>
+  </si>
+  <si>
+    <t>pantera_galia@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jhonny</t>
+  </si>
+  <si>
+    <t>lcamacho@cayman.com.pe</t>
+  </si>
+  <si>
+    <t>Marisa</t>
+  </si>
+  <si>
+    <t>makibacontabilidad@gmail.com</t>
+  </si>
+  <si>
+    <t>Melina</t>
+  </si>
+  <si>
+    <t>oscar@makiba.pe</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>econgache@edgecompany.com.pe</t>
+  </si>
+  <si>
+    <t>Edison</t>
+  </si>
+  <si>
+    <t>jlopez@edgecompany.com.pe</t>
+  </si>
+  <si>
+    <t>Justina</t>
+  </si>
+  <si>
+    <t>rconde@edgecompany.com.pe</t>
+  </si>
+  <si>
+    <t>Ruther</t>
+  </si>
+  <si>
+    <t>info@queensdeco.pe</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>multidecor_centro@hotmail.com</t>
+  </si>
+  <si>
+    <t>Reynaldo</t>
+  </si>
+  <si>
+    <t>ventas@queensdeco.pe</t>
+  </si>
+  <si>
+    <t>Elodia</t>
+  </si>
+  <si>
+    <t>enicoll@peruviancolors.com.pe</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>perucolor@peruviancolors.com.pe</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>rguillen@peruviancolors.com.pe</t>
+  </si>
+  <si>
+    <t>Walter</t>
+  </si>
+  <si>
+    <t>antony.tolentino@stifgroup.com</t>
+  </si>
+  <si>
+    <t>Antony</t>
+  </si>
+  <si>
+    <t>gerencia@decorstone.com.pe</t>
+  </si>
+  <si>
+    <t>Rudy</t>
+  </si>
+  <si>
+    <t>jpena@disal.cl</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>georgina.olarte@egolartesac.com</t>
+  </si>
+  <si>
+    <t>Georgina</t>
+  </si>
+  <si>
+    <t>lenin.rengifo@egolartesac.com</t>
+  </si>
+  <si>
+    <t>Lenin</t>
+  </si>
+  <si>
+    <t>victor.egoavil@egolartesac.com</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>jespinoza@fiorellarepre.com.pe</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>mgomero@fiorellarepre.com.pe</t>
+  </si>
+  <si>
+    <t>Hindelber</t>
+  </si>
+  <si>
+    <t>tesoreria@fiorellarepre.com.pe</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>alopez@arcrodin.com.pe</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>contabilidad@arcrodin.com.pe</t>
+  </si>
+  <si>
+    <t>Rosaura</t>
+  </si>
+  <si>
+    <t>ventas@arcrodin.com.pe</t>
+  </si>
+  <si>
+    <t>Leisdy</t>
+  </si>
+  <si>
+    <t>administracion@inmetal.com.pe</t>
+  </si>
+  <si>
+    <t>Dayana</t>
+  </si>
+  <si>
+    <t>p.martinez@inmetal.com.pe</t>
+  </si>
+  <si>
+    <t>Pepe</t>
+  </si>
+  <si>
+    <t>ventas@inmetal.com.pe</t>
+  </si>
+  <si>
+    <t>claudia.chipoco@tdpcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>recepcion@tdcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>silvia.vidal@tdpcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>ggrimaldim@aygajustadores.com</t>
+  </si>
+  <si>
+    <t>Guido</t>
+  </si>
+  <si>
+    <t>rvillavicencio@aygajustadores.com</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>vaguirre@silpousa.com</t>
+  </si>
+  <si>
+    <t>leyter.sandoval@travexperu.com</t>
+  </si>
+  <si>
+    <t>Leyter</t>
+  </si>
+  <si>
+    <t>rafael.larco@travexperu.com</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>virginia.azabache@travexperu.com</t>
+  </si>
+  <si>
+    <t>carmen.gartner@international.gc.ca</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>glen.mcpherson@international.gc.ca</t>
+  </si>
+  <si>
+    <t>Jo-Hanna</t>
+  </si>
+  <si>
+    <t>rvaldivieso@produccion.gob.ec</t>
+  </si>
+  <si>
+    <t>jraya@sissac.com</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>jrayap@sissac.com</t>
+  </si>
+  <si>
+    <t>proyectos@sissac.com</t>
+  </si>
+  <si>
+    <t>Jhazmin</t>
+  </si>
+  <si>
+    <t>info@bavariamining.com</t>
+  </si>
+  <si>
+    <t>Carmelo</t>
+  </si>
+  <si>
+    <t>isilva@cdm.pe</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>pepekar4x4@gmail.com</t>
+  </si>
+  <si>
+    <t>gerencia@mundotecnologico.pe</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>lourdes.velasquez@mundotecnologico.pe</t>
+  </si>
+  <si>
+    <t>lourdes.zevallos@intecniacorp.pe</t>
+  </si>
+  <si>
+    <t>Lourdes</t>
+  </si>
+  <si>
+    <t>k.steigleder@germaineperu.com</t>
+  </si>
+  <si>
+    <t>Katia</t>
+  </si>
+  <si>
+    <t>mangonegeri@gmail.com</t>
+  </si>
+  <si>
+    <t>Geri</t>
+  </si>
+  <si>
+    <t>newbodygerencianb@gmail.com</t>
+  </si>
+  <si>
+    <t>Elio</t>
+  </si>
+  <si>
+    <t>carla.rios@alsglobal.com</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>lcanturin@coopetro.com</t>
+  </si>
+  <si>
+    <t>Leonor</t>
+  </si>
+  <si>
+    <t>mcalderon@coopetro.com</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>elizabethqg26@gmail.com</t>
+  </si>
+  <si>
+    <t>jesamegu26@hotmail.com</t>
+  </si>
+  <si>
+    <t>miva_2817@hotmail.com</t>
+  </si>
+  <si>
+    <t>Janet</t>
+  </si>
+  <si>
+    <t>dsalaverry@jaro.pe</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>imacosa@imacosa.com</t>
+  </si>
+  <si>
+    <t>mhuerta@imacosa.com</t>
+  </si>
+  <si>
+    <t>Fanny</t>
+  </si>
+  <si>
+    <t>hncapitalsac@gmail.com</t>
+  </si>
+  <si>
+    <t>ivancito79@gmail.com</t>
+  </si>
+  <si>
+    <t>jorge.grados.coach@gmail.com</t>
+  </si>
+  <si>
+    <t>bgallesi.entertaiment@gmail.com</t>
+  </si>
+  <si>
+    <t>Brando</t>
+  </si>
+  <si>
+    <t>gomez_joseluis18@outlook.es</t>
+  </si>
+  <si>
+    <t>info@mastergamesperu.com</t>
+  </si>
+  <si>
+    <t>Alvaro</t>
+  </si>
+  <si>
+    <t>ccedron@optometriaperu.org</t>
+  </si>
+  <si>
+    <t>Cesibel</t>
+  </si>
+  <si>
+    <t>contacto@detallesinfin.com</t>
+  </si>
+  <si>
+    <t>Giovanna</t>
+  </si>
+  <si>
+    <t>ssanchez@eurohispano.pe</t>
+  </si>
+  <si>
+    <t>Severo</t>
   </si>
 </sst>
 </file>
@@ -419,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -435,18 +930,737 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>122</v>
+      </c>
+      <c r="B64" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>134</v>
+      </c>
+      <c r="B71" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>136</v>
+      </c>
+      <c r="B72" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>138</v>
+      </c>
+      <c r="B73" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>142</v>
+      </c>
+      <c r="B75" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>146</v>
+      </c>
+      <c r="B77" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B78" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>153</v>
+      </c>
+      <c r="B82" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>156</v>
+      </c>
+      <c r="B84" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>157</v>
+      </c>
+      <c r="B85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>160</v>
+      </c>
+      <c r="B87" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>161</v>
+      </c>
+      <c r="B88" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B89" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>165</v>
+      </c>
+      <c r="B90" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>167</v>
+      </c>
+      <c r="B91" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B92" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{03D0B70B-CA3D-42A4-AB8B-090799BA5F82}"/>
+    <hyperlink ref="A2" r:id="rId1" display="negocios@partnertech.pe" xr:uid="{03D0B70B-CA3D-42A4-AB8B-090799BA5F82}"/>
+    <hyperlink ref="A3" r:id="rId2" display="negocios@partnertech.pe" xr:uid="{68520335-2678-4B43-8BF3-94271BC5C19F}"/>
+    <hyperlink ref="A92" r:id="rId3" xr:uid="{DEC3824D-1AA3-4DE4-BA28-4866CD128EB1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686684C7-516B-4CD3-9824-3390B777FEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F046C6D-1AF0-42A7-BBE3-57B2F48FC743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="188">
   <si>
     <t>correo</t>
   </si>
@@ -47,499 +47,556 @@
     <t>negocios@partnertech.pe</t>
   </si>
   <si>
-    <t>p.marketing@asclaboral.com</t>
-  </si>
-  <si>
-    <t>Cesia</t>
-  </si>
-  <si>
-    <t>secretaria@asclaboral.com</t>
-  </si>
-  <si>
-    <t>Angel</t>
-  </si>
-  <si>
-    <t>vandia@asclaboral.com</t>
-  </si>
-  <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>rsarmiento@ventia.pe</t>
-  </si>
-  <si>
     <t>Ricardo</t>
   </si>
   <si>
-    <t>tzolezzi@ventia.pe</t>
-  </si>
-  <si>
     <t>Tulio</t>
   </si>
   <si>
-    <t>yllanos@ventia.pe</t>
-  </si>
-  <si>
-    <t>Yliana</t>
-  </si>
-  <si>
-    <t>gmarin@asi-group.com</t>
-  </si>
-  <si>
-    <t>Gonzalo</t>
-  </si>
-  <si>
-    <t>rvillagran@asi-group.com</t>
-  </si>
-  <si>
-    <t>sergioql@gmail.com</t>
-  </si>
-  <si>
-    <t>Sergio</t>
-  </si>
-  <si>
-    <t>dfonseca@idearkperu.com</t>
-  </si>
-  <si>
-    <t>Diana</t>
-  </si>
-  <si>
-    <t>iaguilar@idearkperu.com</t>
-  </si>
-  <si>
-    <t>Elard</t>
-  </si>
-  <si>
-    <t>mfonseca@idearkperu.com</t>
-  </si>
-  <si>
-    <t>Marisol</t>
-  </si>
-  <si>
-    <t>acbrigs@hotmail.com</t>
-  </si>
-  <si>
-    <t>Giannina</t>
-  </si>
-  <si>
-    <t>monicaayllon.diezcanseco@gmail.com</t>
-  </si>
-  <si>
-    <t>Monica</t>
-  </si>
-  <si>
-    <t>peru@cortes-moldes.com</t>
-  </si>
-  <si>
-    <t>Emilio</t>
-  </si>
-  <si>
-    <t>cynthia.zegarra@gim-peru.com</t>
-  </si>
-  <si>
-    <t>Cynthia</t>
-  </si>
-  <si>
-    <t>gerencia.valfhesigroup@gmail.com</t>
-  </si>
-  <si>
-    <t>Clara</t>
-  </si>
-  <si>
-    <t>gestioninmobiliaria@gmail.com</t>
-  </si>
-  <si>
-    <t>Liliana</t>
-  </si>
-  <si>
-    <t>administracion@refsupplysac.com</t>
-  </si>
-  <si>
-    <t>Irene</t>
-  </si>
-  <si>
-    <t>al.efer5@hotmail.com</t>
-  </si>
-  <si>
-    <t>Alfonsa</t>
-  </si>
-  <si>
-    <t>pantera_galia@hotmail.com</t>
-  </si>
-  <si>
-    <t>Jhonny</t>
-  </si>
-  <si>
-    <t>lcamacho@cayman.com.pe</t>
-  </si>
-  <si>
-    <t>Marisa</t>
-  </si>
-  <si>
-    <t>makibacontabilidad@gmail.com</t>
-  </si>
-  <si>
     <t>Melina</t>
   </si>
   <si>
-    <t>oscar@makiba.pe</t>
-  </si>
-  <si>
     <t>Oscar</t>
   </si>
   <si>
-    <t>econgache@edgecompany.com.pe</t>
-  </si>
-  <si>
-    <t>Edison</t>
-  </si>
-  <si>
-    <t>jlopez@edgecompany.com.pe</t>
-  </si>
-  <si>
-    <t>Justina</t>
-  </si>
-  <si>
-    <t>rconde@edgecompany.com.pe</t>
-  </si>
-  <si>
-    <t>Ruther</t>
-  </si>
-  <si>
-    <t>info@queensdeco.pe</t>
-  </si>
-  <si>
     <t>Jorge</t>
   </si>
   <si>
-    <t>multidecor_centro@hotmail.com</t>
-  </si>
-  <si>
-    <t>Reynaldo</t>
-  </si>
-  <si>
-    <t>ventas@queensdeco.pe</t>
-  </si>
-  <si>
-    <t>Elodia</t>
-  </si>
-  <si>
-    <t>enicoll@peruviancolors.com.pe</t>
-  </si>
-  <si>
-    <t>Rosa</t>
-  </si>
-  <si>
-    <t>perucolor@peruviancolors.com.pe</t>
-  </si>
-  <si>
-    <t>Andrea</t>
-  </si>
-  <si>
-    <t>rguillen@peruviancolors.com.pe</t>
-  </si>
-  <si>
-    <t>Walter</t>
-  </si>
-  <si>
-    <t>antony.tolentino@stifgroup.com</t>
-  </si>
-  <si>
-    <t>Antony</t>
-  </si>
-  <si>
-    <t>gerencia@decorstone.com.pe</t>
-  </si>
-  <si>
-    <t>Rudy</t>
-  </si>
-  <si>
-    <t>jpena@disal.cl</t>
-  </si>
-  <si>
-    <t>Jose</t>
-  </si>
-  <si>
-    <t>georgina.olarte@egolartesac.com</t>
-  </si>
-  <si>
-    <t>Georgina</t>
-  </si>
-  <si>
-    <t>lenin.rengifo@egolartesac.com</t>
-  </si>
-  <si>
-    <t>Lenin</t>
-  </si>
-  <si>
-    <t>victor.egoavil@egolartesac.com</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>jespinoza@fiorellarepre.com.pe</t>
-  </si>
-  <si>
-    <t>Javier</t>
-  </si>
-  <si>
-    <t>mgomero@fiorellarepre.com.pe</t>
-  </si>
-  <si>
-    <t>Hindelber</t>
-  </si>
-  <si>
-    <t>tesoreria@fiorellarepre.com.pe</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>alopez@arcrodin.com.pe</t>
-  </si>
-  <si>
-    <t>Abel</t>
-  </si>
-  <si>
-    <t>contabilidad@arcrodin.com.pe</t>
-  </si>
-  <si>
-    <t>Rosaura</t>
-  </si>
-  <si>
-    <t>ventas@arcrodin.com.pe</t>
-  </si>
-  <si>
-    <t>Leisdy</t>
-  </si>
-  <si>
-    <t>administracion@inmetal.com.pe</t>
-  </si>
-  <si>
-    <t>Dayana</t>
-  </si>
-  <si>
-    <t>p.martinez@inmetal.com.pe</t>
-  </si>
-  <si>
-    <t>Pepe</t>
-  </si>
-  <si>
-    <t>ventas@inmetal.com.pe</t>
-  </si>
-  <si>
-    <t>claudia.chipoco@tdpcorp.com.pe</t>
-  </si>
-  <si>
-    <t>Claudia</t>
-  </si>
-  <si>
-    <t>recepcion@tdcorp.com.pe</t>
-  </si>
-  <si>
-    <t>Angelica</t>
-  </si>
-  <si>
-    <t>silvia.vidal@tdpcorp.com.pe</t>
-  </si>
-  <si>
-    <t>Silvia</t>
-  </si>
-  <si>
-    <t>ggrimaldim@aygajustadores.com</t>
-  </si>
-  <si>
-    <t>Guido</t>
-  </si>
-  <si>
-    <t>rvillavicencio@aygajustadores.com</t>
-  </si>
-  <si>
     <t>Maria</t>
   </si>
   <si>
-    <t>vaguirre@silpousa.com</t>
-  </si>
-  <si>
-    <t>leyter.sandoval@travexperu.com</t>
-  </si>
-  <si>
-    <t>Leyter</t>
-  </si>
-  <si>
-    <t>rafael.larco@travexperu.com</t>
-  </si>
-  <si>
     <t>Luis</t>
   </si>
   <si>
-    <t>virginia.azabache@travexperu.com</t>
-  </si>
-  <si>
-    <t>carmen.gartner@international.gc.ca</t>
-  </si>
-  <si>
     <t>Carmen</t>
   </si>
   <si>
-    <t>glen.mcpherson@international.gc.ca</t>
-  </si>
-  <si>
-    <t>Jo-Hanna</t>
-  </si>
-  <si>
-    <t>rvaldivieso@produccion.gob.ec</t>
-  </si>
-  <si>
-    <t>jraya@sissac.com</t>
-  </si>
-  <si>
     <t>Jaime</t>
   </si>
   <si>
-    <t>jrayap@sissac.com</t>
-  </si>
-  <si>
-    <t>proyectos@sissac.com</t>
-  </si>
-  <si>
-    <t>Jhazmin</t>
-  </si>
-  <si>
-    <t>info@bavariamining.com</t>
-  </si>
-  <si>
-    <t>Carmelo</t>
-  </si>
-  <si>
-    <t>isilva@cdm.pe</t>
-  </si>
-  <si>
-    <t>Ivan</t>
-  </si>
-  <si>
-    <t>pepekar4x4@gmail.com</t>
-  </si>
-  <si>
-    <t>gerencia@mundotecnologico.pe</t>
-  </si>
-  <si>
     <t>Carlos</t>
   </si>
   <si>
-    <t>lourdes.velasquez@mundotecnologico.pe</t>
-  </si>
-  <si>
-    <t>lourdes.zevallos@intecniacorp.pe</t>
-  </si>
-  <si>
     <t>Lourdes</t>
   </si>
   <si>
-    <t>k.steigleder@germaineperu.com</t>
-  </si>
-  <si>
-    <t>Katia</t>
-  </si>
-  <si>
-    <t>mangonegeri@gmail.com</t>
-  </si>
-  <si>
-    <t>Geri</t>
-  </si>
-  <si>
-    <t>newbodygerencianb@gmail.com</t>
-  </si>
-  <si>
-    <t>Elio</t>
-  </si>
-  <si>
-    <t>carla.rios@alsglobal.com</t>
-  </si>
-  <si>
-    <t>Carla</t>
-  </si>
-  <si>
-    <t>lcanturin@coopetro.com</t>
-  </si>
-  <si>
-    <t>Leonor</t>
-  </si>
-  <si>
-    <t>mcalderon@coopetro.com</t>
-  </si>
-  <si>
     <t>Juan</t>
   </si>
   <si>
-    <t>elizabethqg26@gmail.com</t>
-  </si>
-  <si>
-    <t>jesamegu26@hotmail.com</t>
-  </si>
-  <si>
-    <t>miva_2817@hotmail.com</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
-    <t>dsalaverry@jaro.pe</t>
-  </si>
-  <si>
     <t>Diego</t>
   </si>
   <si>
-    <t>imacosa@imacosa.com</t>
-  </si>
-  <si>
-    <t>mhuerta@imacosa.com</t>
-  </si>
-  <si>
-    <t>Fanny</t>
-  </si>
-  <si>
-    <t>hncapitalsac@gmail.com</t>
-  </si>
-  <si>
-    <t>ivancito79@gmail.com</t>
-  </si>
-  <si>
-    <t>jorge.grados.coach@gmail.com</t>
-  </si>
-  <si>
-    <t>bgallesi.entertaiment@gmail.com</t>
-  </si>
-  <si>
-    <t>Brando</t>
-  </si>
-  <si>
-    <t>gomez_joseluis18@outlook.es</t>
-  </si>
-  <si>
-    <t>info@mastergamesperu.com</t>
-  </si>
-  <si>
     <t>Alvaro</t>
   </si>
   <si>
-    <t>ccedron@optometriaperu.org</t>
-  </si>
-  <si>
-    <t>Cesibel</t>
-  </si>
-  <si>
-    <t>contacto@detallesinfin.com</t>
-  </si>
-  <si>
-    <t>Giovanna</t>
-  </si>
-  <si>
-    <t>ssanchez@eurohispano.pe</t>
-  </si>
-  <si>
-    <t>Severo</t>
+    <t>bryangabrielm@gmail.com</t>
+  </si>
+  <si>
+    <t>Bryan</t>
+  </si>
+  <si>
+    <t>contabilidad@peruparadisetravel.com</t>
+  </si>
+  <si>
+    <t>Thalia</t>
+  </si>
+  <si>
+    <t>michele@peruparadisetravel.com</t>
+  </si>
+  <si>
+    <t>Michele</t>
+  </si>
+  <si>
+    <t>nancy@peruparadisetravel.com</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>dsalazarp@sigma-alimentos.com</t>
+  </si>
+  <si>
+    <t>Romy</t>
+  </si>
+  <si>
+    <t>fmilla@sigma-alimentos.com</t>
+  </si>
+  <si>
+    <t>Fedra</t>
+  </si>
+  <si>
+    <t>juan.iturria@spsa.pe</t>
+  </si>
+  <si>
+    <t>rcanepa@sigma-alimentos.com</t>
+  </si>
+  <si>
+    <t>Roxana</t>
+  </si>
+  <si>
+    <t>alberto.silvestre@creditomype.com</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>cgonzaleslorenzo@gmail.com</t>
+  </si>
+  <si>
+    <t>jeus.echeverre.rd@gmail.com</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>melanie.samaniego@creditomype.com</t>
+  </si>
+  <si>
+    <t>Melanie</t>
+  </si>
+  <si>
+    <t>plavera@mebolsite.com</t>
+  </si>
+  <si>
+    <t>rcortijo@solimar.com.pe</t>
+  </si>
+  <si>
+    <t>Rodolfo</t>
+  </si>
+  <si>
+    <t>sales@solimar.com.pe</t>
+  </si>
+  <si>
+    <t>Jessica</t>
+  </si>
+  <si>
+    <t>tania.nb11@gmail.com</t>
+  </si>
+  <si>
+    <t>Rocio</t>
+  </si>
+  <si>
+    <t>ana.ricci@ciplast.biz</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>duribe@ciplast.biz</t>
+  </si>
+  <si>
+    <t>Rebeca</t>
+  </si>
+  <si>
+    <t>enovak@ciplast.biz</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>finanzas@ciplast.biz</t>
+  </si>
+  <si>
+    <t>Liz</t>
+  </si>
+  <si>
+    <t>dcherrepano@rd.com.pe</t>
+  </si>
+  <si>
+    <t>Nestor</t>
+  </si>
+  <si>
+    <t>metacperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Rusbelht</t>
+  </si>
+  <si>
+    <t>rmosquera@rd.com.pe</t>
+  </si>
+  <si>
+    <t>taccamartin@gmail.com</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>jjuan1calixto2moron4@gmail.com</t>
+  </si>
+  <si>
+    <t>kpaicoe@gmail.com</t>
+  </si>
+  <si>
+    <t>Kalev</t>
+  </si>
+  <si>
+    <t>mrivas@ckf.pe</t>
+  </si>
+  <si>
+    <t>yalzamora@ckf.pe</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>administracion@jrgse.com</t>
+  </si>
+  <si>
+    <t>gerenciacomercial@jrgse.com</t>
+  </si>
+  <si>
+    <t>Milagros</t>
+  </si>
+  <si>
+    <t>jrosas@jrgse.com</t>
+  </si>
+  <si>
+    <t>Justo</t>
+  </si>
+  <si>
+    <t>milagroscustodio@jrgse.com</t>
+  </si>
+  <si>
+    <t>administracion@cheirl.com</t>
+  </si>
+  <si>
+    <t>Esteicy</t>
+  </si>
+  <si>
+    <t>carla.campos@heinz-glas.com</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>gerencia@cheirl.com</t>
+  </si>
+  <si>
+    <t>sandra.davila@heinz-glas.com</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>cflorescosmos@gmail.com</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>diegoaguilarromero@gmail.com</t>
+  </si>
+  <si>
+    <t>oscarcasimirof@gmail.com</t>
+  </si>
+  <si>
+    <t>wmarquez@cosmosgames.com.pe</t>
+  </si>
+  <si>
+    <t>Wilmer</t>
+  </si>
+  <si>
+    <t>info@keramglass.com</t>
+  </si>
+  <si>
+    <t>Clever</t>
+  </si>
+  <si>
+    <t>keramglass@gmail.com</t>
+  </si>
+  <si>
+    <t>Deywi</t>
+  </si>
+  <si>
+    <t>trapex_carlosquispe@hotmail.com</t>
+  </si>
+  <si>
+    <t>ventas@bitoka.pe</t>
+  </si>
+  <si>
+    <t>evelynobrien@pacpac.com</t>
+  </si>
+  <si>
+    <t>Evelyn</t>
+  </si>
+  <si>
+    <t>mariacrovetto@romipack.pe</t>
+  </si>
+  <si>
+    <t>mariellagonzalez@romipack.pe</t>
+  </si>
+  <si>
+    <t>Mariella</t>
+  </si>
+  <si>
+    <t>mpamez@pacpac.com</t>
+  </si>
+  <si>
+    <t>contabilidad@southshipping.com</t>
+  </si>
+  <si>
+    <t>Soledad</t>
+  </si>
+  <si>
+    <t>gerencia@goldcargo.pe</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>gtumanikarmy@gmail.com</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>main@southshipping.pe</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>alourbe@hotmail.com</t>
+  </si>
+  <si>
+    <t>etcojesa@hotmail.com</t>
+  </si>
+  <si>
+    <t>Eugenio</t>
+  </si>
+  <si>
+    <t>eugeniobenitest5@gmail.com</t>
+  </si>
+  <si>
+    <t>patthykaften@gmail.com</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>contabilidad1@dorichywatkin.com</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>dorichfa@dorichywatkin.com</t>
+  </si>
+  <si>
+    <t>elisa.rodriguez@dorichywatkin.com</t>
+  </si>
+  <si>
+    <t>Elisa</t>
+  </si>
+  <si>
+    <t>fabioladorich@dorichywatkin.com</t>
+  </si>
+  <si>
+    <t>Fabiola</t>
+  </si>
+  <si>
+    <t>decofesac2007@hotmail.com</t>
+  </si>
+  <si>
+    <t>detectivesescuadronfemenino007@hotmail.com</t>
+  </si>
+  <si>
+    <t>escuadronfemenino007@hotmail.com</t>
+  </si>
+  <si>
+    <t>menaranimage@hotmail.com</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>carnesdelvalle3hc@gmail.com</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>condezo976@gmail.com</t>
+  </si>
+  <si>
+    <t>Belu</t>
+  </si>
+  <si>
+    <t>elianaruiz189@gmail.com</t>
+  </si>
+  <si>
+    <t>Juana</t>
+  </si>
+  <si>
+    <t>sixmaru@gmail.com</t>
+  </si>
+  <si>
+    <t>Sixto</t>
+  </si>
+  <si>
+    <t>alan.martinezc@gmail.com</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>misarimartinez852@gmail.com</t>
+  </si>
+  <si>
+    <t>Mabel</t>
+  </si>
+  <si>
+    <t>oldren_unico@hotmail.com</t>
+  </si>
+  <si>
+    <t>Oldren</t>
+  </si>
+  <si>
+    <t>ptoulier@jardines.pe</t>
+  </si>
+  <si>
+    <t>Priscilla</t>
+  </si>
+  <si>
+    <t>frannsjesus@gmail.com</t>
+  </si>
+  <si>
+    <t>Franns</t>
+  </si>
+  <si>
+    <t>joaquin_servat@inkapebblesandtiles.com</t>
+  </si>
+  <si>
+    <t>Joaquin</t>
+  </si>
+  <si>
+    <t>juaquin_servat@inkapebblesandtiles.com</t>
+  </si>
+  <si>
+    <t>leandramayhuasca@gmail.com</t>
+  </si>
+  <si>
+    <t>Leandra</t>
+  </si>
+  <si>
+    <t>blancablass027@gmail.com</t>
+  </si>
+  <si>
+    <t>Blanca</t>
+  </si>
+  <si>
+    <t>contacto@dizayninteriors.com</t>
+  </si>
+  <si>
+    <t>Yaneisy</t>
+  </si>
+  <si>
+    <t>luciamariafernandafarfansalaza@gmail.com</t>
+  </si>
+  <si>
+    <t>Lucia</t>
+  </si>
+  <si>
+    <t>multiservicioroja@hotmail.com</t>
+  </si>
+  <si>
+    <t>Moises</t>
+  </si>
+  <si>
+    <t>dferrer@fervalgroup.com</t>
+  </si>
+  <si>
+    <t>importacioneswiljob@hotmail.com</t>
+  </si>
+  <si>
+    <t>Nayeli</t>
+  </si>
+  <si>
+    <t>margoth8311@gmail.com</t>
+  </si>
+  <si>
+    <t>Cinthia</t>
+  </si>
+  <si>
+    <t>rcerpa@fervalperu.com</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>amira.salazr@gmail.com</t>
+  </si>
+  <si>
+    <t>Amira</t>
+  </si>
+  <si>
+    <t>cheerperu@yahoo.com</t>
+  </si>
+  <si>
+    <t>direccion@escuelaenda.com</t>
+  </si>
+  <si>
+    <t>Lilian</t>
+  </si>
+  <si>
+    <t>gymmegaforce.gerencia@gmail.com</t>
+  </si>
+  <si>
+    <t>cguerrero@glintglobal.com</t>
+  </si>
+  <si>
+    <t>diazcelso10@gmail.com</t>
+  </si>
+  <si>
+    <t>Celso</t>
+  </si>
+  <si>
+    <t>gabrielamanriquesalinas@gmail.ocm</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>manriqueb_om@hotmail.com</t>
+  </si>
+  <si>
+    <t>Omar</t>
+  </si>
+  <si>
+    <t>achuquipiondo@companiaamericana.com</t>
+  </si>
+  <si>
+    <t>carmen.abad@companiaamericana.com</t>
+  </si>
+  <si>
+    <t>naor@gmail.com</t>
+  </si>
+  <si>
+    <t>Nicolas</t>
+  </si>
+  <si>
+    <t>tnoscorpca@gmail.com</t>
+  </si>
+  <si>
+    <t>jcancino518528@gmail.com</t>
+  </si>
+  <si>
+    <t>pcornejo@serviciosquma.com</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>soporte@serviciosquma.com</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>ymallma@magicamagica.com</t>
+  </si>
+  <si>
+    <t>Yanina</t>
   </si>
 </sst>
 </file>
@@ -914,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -930,426 +987,426 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1357,15 +1414,15 @@
         <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
         <v>109</v>
-      </c>
-      <c r="B56" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1381,15 +1438,15 @@
         <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>115</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1405,15 +1462,15 @@
         <v>118</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -1421,7 +1478,7 @@
         <v>121</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1429,31 +1486,31 @@
         <v>122</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" t="s">
         <v>124</v>
-      </c>
-      <c r="B65" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" t="s">
         <v>126</v>
-      </c>
-      <c r="B66" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>127</v>
+      </c>
+      <c r="B67" t="s">
         <v>128</v>
-      </c>
-      <c r="B67" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -1469,63 +1526,63 @@
         <v>131</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B70" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B74" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B75" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B76" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -1533,126 +1590,206 @@
         <v>146</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B79" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B81" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B83" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B84" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>166</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B92" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>174</v>
+      </c>
+      <c r="B93" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>177</v>
+      </c>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>178</v>
+      </c>
+      <c r="B96" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>180</v>
+      </c>
+      <c r="B97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>181</v>
+      </c>
+      <c r="B98" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>182</v>
+      </c>
+      <c r="B99" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>184</v>
+      </c>
+      <c r="B100" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>186</v>
+      </c>
+      <c r="B101" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B102" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1660,7 +1797,8 @@
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="negocios@partnertech.pe" xr:uid="{03D0B70B-CA3D-42A4-AB8B-090799BA5F82}"/>
     <hyperlink ref="A3" r:id="rId2" display="negocios@partnertech.pe" xr:uid="{68520335-2678-4B43-8BF3-94271BC5C19F}"/>
-    <hyperlink ref="A92" r:id="rId3" xr:uid="{DEC3824D-1AA3-4DE4-BA28-4866CD128EB1}"/>
+    <hyperlink ref="A92" r:id="rId3" display="negocios@partnertech.pe" xr:uid="{DEC3824D-1AA3-4DE4-BA28-4866CD128EB1}"/>
+    <hyperlink ref="A102" r:id="rId4" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F046C6D-1AF0-42A7-BBE3-57B2F48FC743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4EF898-171E-4CC5-A3C8-A7EB8C56406D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="182">
   <si>
     <t>correo</t>
   </si>
@@ -50,12 +50,6 @@
     <t>Ricardo</t>
   </si>
   <si>
-    <t>Tulio</t>
-  </si>
-  <si>
-    <t>Melina</t>
-  </si>
-  <si>
     <t>Oscar</t>
   </si>
   <si>
@@ -71,9 +65,6 @@
     <t>Carmen</t>
   </si>
   <si>
-    <t>Jaime</t>
-  </si>
-  <si>
     <t>Carlos</t>
   </si>
   <si>
@@ -89,514 +80,505 @@
     <t>Alvaro</t>
   </si>
   <si>
-    <t>bryangabrielm@gmail.com</t>
-  </si>
-  <si>
-    <t>Bryan</t>
-  </si>
-  <si>
-    <t>contabilidad@peruparadisetravel.com</t>
-  </si>
-  <si>
-    <t>Thalia</t>
-  </si>
-  <si>
-    <t>michele@peruparadisetravel.com</t>
-  </si>
-  <si>
-    <t>Michele</t>
-  </si>
-  <si>
-    <t>nancy@peruparadisetravel.com</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>dsalazarp@sigma-alimentos.com</t>
-  </si>
-  <si>
-    <t>Romy</t>
-  </si>
-  <si>
-    <t>fmilla@sigma-alimentos.com</t>
-  </si>
-  <si>
-    <t>Fedra</t>
-  </si>
-  <si>
-    <t>juan.iturria@spsa.pe</t>
-  </si>
-  <si>
-    <t>rcanepa@sigma-alimentos.com</t>
-  </si>
-  <si>
     <t>Roxana</t>
   </si>
   <si>
-    <t>alberto.silvestre@creditomype.com</t>
-  </si>
-  <si>
-    <t>Alberto</t>
-  </si>
-  <si>
-    <t>cgonzaleslorenzo@gmail.com</t>
-  </si>
-  <si>
-    <t>jeus.echeverre.rd@gmail.com</t>
-  </si>
-  <si>
-    <t>Jesus</t>
-  </si>
-  <si>
-    <t>melanie.samaniego@creditomype.com</t>
-  </si>
-  <si>
-    <t>Melanie</t>
-  </si>
-  <si>
-    <t>plavera@mebolsite.com</t>
-  </si>
-  <si>
-    <t>rcortijo@solimar.com.pe</t>
-  </si>
-  <si>
-    <t>Rodolfo</t>
-  </si>
-  <si>
-    <t>sales@solimar.com.pe</t>
-  </si>
-  <si>
-    <t>Jessica</t>
-  </si>
-  <si>
-    <t>tania.nb11@gmail.com</t>
-  </si>
-  <si>
-    <t>Rocio</t>
-  </si>
-  <si>
-    <t>ana.ricci@ciplast.biz</t>
-  </si>
-  <si>
     <t>Ana</t>
   </si>
   <si>
-    <t>duribe@ciplast.biz</t>
-  </si>
-  <si>
-    <t>Rebeca</t>
-  </si>
-  <si>
-    <t>enovak@ciplast.biz</t>
-  </si>
-  <si>
     <t>Enrique</t>
   </si>
   <si>
-    <t>finanzas@ciplast.biz</t>
-  </si>
-  <si>
-    <t>Liz</t>
-  </si>
-  <si>
-    <t>dcherrepano@rd.com.pe</t>
-  </si>
-  <si>
-    <t>Nestor</t>
-  </si>
-  <si>
-    <t>metacperu@gmail.com</t>
-  </si>
-  <si>
-    <t>Rusbelht</t>
-  </si>
-  <si>
-    <t>rmosquera@rd.com.pe</t>
-  </si>
-  <si>
-    <t>taccamartin@gmail.com</t>
-  </si>
-  <si>
     <t>Martin</t>
   </si>
   <si>
-    <t>jjuan1calixto2moron4@gmail.com</t>
-  </si>
-  <si>
-    <t>kpaicoe@gmail.com</t>
-  </si>
-  <si>
-    <t>Kalev</t>
-  </si>
-  <si>
-    <t>mrivas@ckf.pe</t>
-  </si>
-  <si>
-    <t>yalzamora@ckf.pe</t>
-  </si>
-  <si>
-    <t>Fernando</t>
-  </si>
-  <si>
-    <t>administracion@jrgse.com</t>
-  </si>
-  <si>
-    <t>gerenciacomercial@jrgse.com</t>
-  </si>
-  <si>
-    <t>Milagros</t>
-  </si>
-  <si>
-    <t>jrosas@jrgse.com</t>
-  </si>
-  <si>
-    <t>Justo</t>
-  </si>
-  <si>
-    <t>milagroscustodio@jrgse.com</t>
-  </si>
-  <si>
-    <t>administracion@cheirl.com</t>
-  </si>
-  <si>
-    <t>Esteicy</t>
-  </si>
-  <si>
-    <t>carla.campos@heinz-glas.com</t>
-  </si>
-  <si>
-    <t>Roberto</t>
-  </si>
-  <si>
-    <t>gerencia@cheirl.com</t>
-  </si>
-  <si>
-    <t>sandra.davila@heinz-glas.com</t>
-  </si>
-  <si>
-    <t>Sandra</t>
-  </si>
-  <si>
-    <t>cflorescosmos@gmail.com</t>
-  </si>
-  <si>
     <t>Cesar</t>
   </si>
   <si>
-    <t>diegoaguilarromero@gmail.com</t>
-  </si>
-  <si>
-    <t>oscarcasimirof@gmail.com</t>
-  </si>
-  <si>
-    <t>wmarquez@cosmosgames.com.pe</t>
-  </si>
-  <si>
-    <t>Wilmer</t>
-  </si>
-  <si>
-    <t>info@keramglass.com</t>
-  </si>
-  <si>
-    <t>Clever</t>
-  </si>
-  <si>
-    <t>keramglass@gmail.com</t>
-  </si>
-  <si>
-    <t>Deywi</t>
-  </si>
-  <si>
-    <t>trapex_carlosquispe@hotmail.com</t>
-  </si>
-  <si>
-    <t>ventas@bitoka.pe</t>
-  </si>
-  <si>
-    <t>evelynobrien@pacpac.com</t>
-  </si>
-  <si>
-    <t>Evelyn</t>
-  </si>
-  <si>
-    <t>mariacrovetto@romipack.pe</t>
-  </si>
-  <si>
-    <t>mariellagonzalez@romipack.pe</t>
-  </si>
-  <si>
-    <t>Mariella</t>
-  </si>
-  <si>
-    <t>mpamez@pacpac.com</t>
-  </si>
-  <si>
-    <t>contabilidad@southshipping.com</t>
-  </si>
-  <si>
-    <t>Soledad</t>
-  </si>
-  <si>
-    <t>gerencia@goldcargo.pe</t>
-  </si>
-  <si>
-    <t>Jean</t>
-  </si>
-  <si>
-    <t>gtumanikarmy@gmail.com</t>
-  </si>
-  <si>
-    <t>Gabriel</t>
-  </si>
-  <si>
-    <t>main@southshipping.pe</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>alourbe@hotmail.com</t>
-  </si>
-  <si>
-    <t>etcojesa@hotmail.com</t>
-  </si>
-  <si>
-    <t>Eugenio</t>
-  </si>
-  <si>
-    <t>eugeniobenitest5@gmail.com</t>
-  </si>
-  <si>
-    <t>patthykaften@gmail.com</t>
-  </si>
-  <si>
     <t>Patricia</t>
   </si>
   <si>
-    <t>contabilidad1@dorichywatkin.com</t>
-  </si>
-  <si>
-    <t>José</t>
-  </si>
-  <si>
-    <t>dorichfa@dorichywatkin.com</t>
-  </si>
-  <si>
-    <t>elisa.rodriguez@dorichywatkin.com</t>
-  </si>
-  <si>
-    <t>Elisa</t>
-  </si>
-  <si>
-    <t>fabioladorich@dorichywatkin.com</t>
-  </si>
-  <si>
-    <t>Fabiola</t>
-  </si>
-  <si>
-    <t>decofesac2007@hotmail.com</t>
-  </si>
-  <si>
-    <t>detectivesescuadronfemenino007@hotmail.com</t>
-  </si>
-  <si>
-    <t>escuadronfemenino007@hotmail.com</t>
-  </si>
-  <si>
-    <t>menaranimage@hotmail.com</t>
-  </si>
-  <si>
-    <t>Pedro</t>
-  </si>
-  <si>
-    <t>carnesdelvalle3hc@gmail.com</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>condezo976@gmail.com</t>
-  </si>
-  <si>
-    <t>Belu</t>
-  </si>
-  <si>
-    <t>elianaruiz189@gmail.com</t>
-  </si>
-  <si>
     <t>Juana</t>
   </si>
   <si>
-    <t>sixmaru@gmail.com</t>
-  </si>
-  <si>
-    <t>Sixto</t>
-  </si>
-  <si>
-    <t>alan.martinezc@gmail.com</t>
-  </si>
-  <si>
-    <t>Alan</t>
-  </si>
-  <si>
-    <t>misarimartinez852@gmail.com</t>
-  </si>
-  <si>
-    <t>Mabel</t>
-  </si>
-  <si>
-    <t>oldren_unico@hotmail.com</t>
-  </si>
-  <si>
-    <t>Oldren</t>
-  </si>
-  <si>
-    <t>ptoulier@jardines.pe</t>
-  </si>
-  <si>
-    <t>Priscilla</t>
-  </si>
-  <si>
-    <t>frannsjesus@gmail.com</t>
-  </si>
-  <si>
-    <t>Franns</t>
-  </si>
-  <si>
-    <t>joaquin_servat@inkapebblesandtiles.com</t>
-  </si>
-  <si>
-    <t>Joaquin</t>
-  </si>
-  <si>
-    <t>juaquin_servat@inkapebblesandtiles.com</t>
-  </si>
-  <si>
-    <t>leandramayhuasca@gmail.com</t>
-  </si>
-  <si>
-    <t>Leandra</t>
-  </si>
-  <si>
-    <t>blancablass027@gmail.com</t>
-  </si>
-  <si>
-    <t>Blanca</t>
-  </si>
-  <si>
-    <t>contacto@dizayninteriors.com</t>
-  </si>
-  <si>
-    <t>Yaneisy</t>
-  </si>
-  <si>
-    <t>luciamariafernandafarfansalaza@gmail.com</t>
-  </si>
-  <si>
     <t>Lucia</t>
   </si>
   <si>
-    <t>multiservicioroja@hotmail.com</t>
-  </si>
-  <si>
-    <t>Moises</t>
-  </si>
-  <si>
-    <t>dferrer@fervalgroup.com</t>
-  </si>
-  <si>
-    <t>importacioneswiljob@hotmail.com</t>
-  </si>
-  <si>
-    <t>Nayeli</t>
-  </si>
-  <si>
-    <t>margoth8311@gmail.com</t>
-  </si>
-  <si>
-    <t>Cinthia</t>
-  </si>
-  <si>
-    <t>rcerpa@fervalperu.com</t>
-  </si>
-  <si>
-    <t>Rosario</t>
-  </si>
-  <si>
-    <t>amira.salazr@gmail.com</t>
-  </si>
-  <si>
-    <t>Amira</t>
-  </si>
-  <si>
-    <t>cheerperu@yahoo.com</t>
-  </si>
-  <si>
-    <t>direccion@escuelaenda.com</t>
-  </si>
-  <si>
-    <t>Lilian</t>
-  </si>
-  <si>
-    <t>gymmegaforce.gerencia@gmail.com</t>
-  </si>
-  <si>
-    <t>cguerrero@glintglobal.com</t>
-  </si>
-  <si>
-    <t>diazcelso10@gmail.com</t>
-  </si>
-  <si>
-    <t>Celso</t>
-  </si>
-  <si>
-    <t>gabrielamanriquesalinas@gmail.ocm</t>
-  </si>
-  <si>
     <t>Gabriela</t>
   </si>
   <si>
-    <t>manriqueb_om@hotmail.com</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>achuquipiondo@companiaamericana.com</t>
-  </si>
-  <si>
-    <t>carmen.abad@companiaamericana.com</t>
-  </si>
-  <si>
-    <t>naor@gmail.com</t>
-  </si>
-  <si>
-    <t>Nicolas</t>
-  </si>
-  <si>
-    <t>tnoscorpca@gmail.com</t>
-  </si>
-  <si>
-    <t>jcancino518528@gmail.com</t>
-  </si>
-  <si>
-    <t>pcornejo@serviciosquma.com</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>soporte@serviciosquma.com</t>
-  </si>
-  <si>
-    <t>Kelly</t>
-  </si>
-  <si>
-    <t>ymallma@magicamagica.com</t>
-  </si>
-  <si>
-    <t>Yanina</t>
+    <t>finanzas@hacsa-peru.com</t>
+  </si>
+  <si>
+    <t>Janet</t>
+  </si>
+  <si>
+    <t>hacsa2005@hotmail.com</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>joel.zuta@jwclogistic.com</t>
+  </si>
+  <si>
+    <t>Joel</t>
+  </si>
+  <si>
+    <t>sgestion@hacsa-peru.com</t>
+  </si>
+  <si>
+    <t>Evelin</t>
+  </si>
+  <si>
+    <t>yvonne.pinto@jwclogistic.com</t>
+  </si>
+  <si>
+    <t>Yvonne</t>
+  </si>
+  <si>
+    <t>gerencia@corporacionorluma.com</t>
+  </si>
+  <si>
+    <t>Luzmila</t>
+  </si>
+  <si>
+    <t>luisortiz15@gmail.com</t>
+  </si>
+  <si>
+    <t>mobiliariabarboza@gmail.com</t>
+  </si>
+  <si>
+    <t>Brayan</t>
+  </si>
+  <si>
+    <t>rui.valcarce@miguelez.com</t>
+  </si>
+  <si>
+    <t>Rui</t>
+  </si>
+  <si>
+    <t>valeria.canales@miguelez.com</t>
+  </si>
+  <si>
+    <t>Valeria</t>
+  </si>
+  <si>
+    <t>drossello@rossello.com.pe</t>
+  </si>
+  <si>
+    <t>gabriela.monar@unacem.pe</t>
+  </si>
+  <si>
+    <t>lromero@comacsa.com.pe</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>mbarrios@calidra.com.mx</t>
+  </si>
+  <si>
+    <t>rossana.tonussi@unacem.pe</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>fanofordi@hotmail.com</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>ingrid-fano@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ingrid</t>
+  </si>
+  <si>
+    <t>jamesfano@negociosjordi.com</t>
+  </si>
+  <si>
+    <t>lvargas@corporacionjordi.com</t>
+  </si>
+  <si>
+    <t>negociosjordi@hotmail.com</t>
+  </si>
+  <si>
+    <t>amendoza@nutesa.com.pe</t>
+  </si>
+  <si>
+    <t>Adelaida</t>
+  </si>
+  <si>
+    <t>arcowayta@gmail.com</t>
+  </si>
+  <si>
+    <t>Maricielo</t>
+  </si>
+  <si>
+    <t>ecd@kp.pe</t>
+  </si>
+  <si>
+    <t>marketing@nutesa.com.pe</t>
+  </si>
+  <si>
+    <t>Fiorella</t>
+  </si>
+  <si>
+    <t>mcrosas@nutesa.com.pe</t>
+  </si>
+  <si>
+    <t>ledesma.am@pg.com</t>
+  </si>
+  <si>
+    <t>moran.er@pg.com</t>
+  </si>
+  <si>
+    <t>Elva</t>
+  </si>
+  <si>
+    <t>muniz.g@pg.com</t>
+  </si>
+  <si>
+    <t>reyes.h@pg.com</t>
+  </si>
+  <si>
+    <t>Román</t>
+  </si>
+  <si>
+    <t>villalobos.n.3@pg.com</t>
+  </si>
+  <si>
+    <t>Nury</t>
+  </si>
+  <si>
+    <t>abravo@corkperu.com</t>
+  </si>
+  <si>
+    <t>Fiorela</t>
+  </si>
+  <si>
+    <t>daysi.montenegro.salazar@gmail.com</t>
+  </si>
+  <si>
+    <t>Daysi</t>
+  </si>
+  <si>
+    <t>eduardo.monzon.rondon@gmail.com</t>
+  </si>
+  <si>
+    <t>negocios@amfa.com.pe</t>
+  </si>
+  <si>
+    <t>operaciones@amfa.com.pe</t>
+  </si>
+  <si>
+    <t>diego.rincon@experian.com</t>
+  </si>
+  <si>
+    <t>efrain.aquino@experian.com</t>
+  </si>
+  <si>
+    <t>Efrain</t>
+  </si>
+  <si>
+    <t>fuyumi.noda@experian.com</t>
+  </si>
+  <si>
+    <t>Fuyumi</t>
+  </si>
+  <si>
+    <t>hpeirano@addvalora-wmoller.com</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>juancarlos.veturo@experian.com</t>
+  </si>
+  <si>
+    <t>francojbulnes@eaton.com</t>
+  </si>
+  <si>
+    <t>jorgelmorales@eaton.com</t>
+  </si>
+  <si>
+    <t>keikolaos@eaton.com</t>
+  </si>
+  <si>
+    <t>Keiko</t>
+  </si>
+  <si>
+    <t>mnunez@mgp.com.pe</t>
+  </si>
+  <si>
+    <t>Mariela</t>
+  </si>
+  <si>
+    <t>nohaycorreo@gmail.com</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>administracion@cbm.pe</t>
+  </si>
+  <si>
+    <t>ana.bar@cbm.pe</t>
+  </si>
+  <si>
+    <t>carlos.ruiz@cbm.pe</t>
+  </si>
+  <si>
+    <t>dvera0306@gmail.com</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>noemitj26@gmail.com</t>
+  </si>
+  <si>
+    <t>Ruth</t>
+  </si>
+  <si>
+    <t>alaserperu@hotmail.com</t>
+  </si>
+  <si>
+    <t>alfonsomatos82@yahoo.com</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>maxmetalserviciosgenerales@gmail.com</t>
+  </si>
+  <si>
+    <t>Flor</t>
+  </si>
+  <si>
+    <t>omerjuncog@gmail.com</t>
+  </si>
+  <si>
+    <t>Omer</t>
+  </si>
+  <si>
+    <t>vierochka.santander@gmail.com</t>
+  </si>
+  <si>
+    <t>Vierochka</t>
+  </si>
+  <si>
+    <t>implemaq.adm2@gmail.com</t>
+  </si>
+  <si>
+    <t>implemaqdelperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Lenin</t>
+  </si>
+  <si>
+    <t>j.guerrero@motopits.pe</t>
+  </si>
+  <si>
+    <t>Johanna</t>
+  </si>
+  <si>
+    <t>martin.rodriguez@motopits.pe</t>
+  </si>
+  <si>
+    <t>rosy.kanaffo@motopits.pe</t>
+  </si>
+  <si>
+    <t>Rosy</t>
+  </si>
+  <si>
+    <t>alex.fernandez@resefer.com</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>isaias.guerrero@resefer.com</t>
+  </si>
+  <si>
+    <t>Isaias</t>
+  </si>
+  <si>
+    <t>mugarte@neumopack.com</t>
+  </si>
+  <si>
+    <t>Mauricio</t>
+  </si>
+  <si>
+    <t>ruben.lavado@resefer.com</t>
+  </si>
+  <si>
+    <t>Ruben</t>
+  </si>
+  <si>
+    <t>apana.lucio@gmail.com</t>
+  </si>
+  <si>
+    <t>Lucio</t>
+  </si>
+  <si>
+    <t>ernesto.l@electrodunas.com</t>
+  </si>
+  <si>
+    <t>Ernesto</t>
+  </si>
+  <si>
+    <t>gerencia@syrconge.com</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>vjayo@electrodunas.com</t>
+  </si>
+  <si>
+    <t>carmenlopezalb84@gmail.com</t>
+  </si>
+  <si>
+    <t>isaac.lopez@grupocaarein.com.pe</t>
+  </si>
+  <si>
+    <t>Isaac</t>
+  </si>
+  <si>
+    <t>manuel.torres@grupocaarein.com.pe</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>marino@grupocaarein.com.pe</t>
+  </si>
+  <si>
+    <t>Leidin</t>
+  </si>
+  <si>
+    <t>bjm@mahecor.com</t>
+  </si>
+  <si>
+    <t>Bernardo</t>
+  </si>
+  <si>
+    <t>jenny.ingaruca@tlr.com.pe</t>
+  </si>
+  <si>
+    <t>Jenny</t>
+  </si>
+  <si>
+    <t>luis.carbajal@tlr.com.pe</t>
+  </si>
+  <si>
+    <t>ricardo.rodriguez@tlr.com.pe</t>
+  </si>
+  <si>
+    <t>cristina.peralta@gruposcp.com</t>
+  </si>
+  <si>
+    <t>gperalta@socpur.com</t>
+  </si>
+  <si>
+    <t>kelly.loza@gruposcp.com</t>
+  </si>
+  <si>
+    <t>miriam.murakami@gruposcp.com</t>
+  </si>
+  <si>
+    <t>Miriam</t>
+  </si>
+  <si>
+    <t>info@fullbusinessglobal.com</t>
+  </si>
+  <si>
+    <t>mgirano@rey.pe</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>olanatta@perugoldtrade.com.pe</t>
+  </si>
+  <si>
+    <t>ssilva@perugoldtrade.com.pe</t>
+  </si>
+  <si>
+    <t>genaro.amaya@ferretoolssac.com</t>
+  </si>
+  <si>
+    <t>Genaro</t>
+  </si>
+  <si>
+    <t>luis.monroy@ferretoolssac.com</t>
+  </si>
+  <si>
+    <t>pablotineo@azchemical.pe</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>veronica.avalos@azchemical.pe</t>
+  </si>
+  <si>
+    <t>ddivos@solpack.com.pe</t>
+  </si>
+  <si>
+    <t>hugomhf14@gmail.com</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>jcabero@solpack.com.pe</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>ptippe@solpack.com.pe</t>
+  </si>
+  <si>
+    <t>admi.cicoplas@gmail.com</t>
+  </si>
+  <si>
+    <t>Noemy</t>
+  </si>
+  <si>
+    <t>cirodelrio@agro-gestion.com</t>
+  </si>
+  <si>
+    <t>Ciro</t>
+  </si>
+  <si>
+    <t>g.laupa@agro-gestion.com</t>
+  </si>
+  <si>
+    <t>Galich</t>
+  </si>
+  <si>
+    <t>heidi.chero@tigre.com</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>carla.melendez@husqvarnagroup.com</t>
+  </si>
+  <si>
+    <t>erika.hurtado@husqvarnagroup.com</t>
+  </si>
+  <si>
+    <t>liliana.vargas@husqvarnagroup.com</t>
+  </si>
+  <si>
+    <t>mariaclaudia.urbina@husqvarnagroup.com</t>
   </si>
 </sst>
 </file>
@@ -987,290 +969,290 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1286,31 +1268,31 @@
         <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1318,15 +1300,15 @@
         <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s">
         <v>91</v>
-      </c>
-      <c r="B44" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -1334,31 +1316,31 @@
         <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1366,7 +1348,7 @@
         <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1390,23 +1372,23 @@
         <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
         <v>105</v>
-      </c>
-      <c r="B53" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
         <v>107</v>
-      </c>
-      <c r="B54" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1422,15 +1404,15 @@
         <v>110</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1446,15 +1428,15 @@
         <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>117</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1470,127 +1452,127 @@
         <v>120</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B73" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B74" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B76" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B77" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -1598,191 +1580,191 @@
         <v>148</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B80" t="s">
-        <v>153</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B81" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B82" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B83" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B84" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B85" t="s">
-        <v>162</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B86" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B87" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B88" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B89" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B92" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B93" t="s">
-        <v>175</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B94" t="s">
-        <v>17</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B96" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>5</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>183</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
-        <v>185</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
-        <v>187</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4EF898-171E-4CC5-A3C8-A7EB8C56406D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D70B35-976C-4EF6-8A55-3D9D49E7D67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="182">
   <si>
     <t>correo</t>
   </si>
@@ -47,12 +47,6 @@
     <t>negocios@partnertech.pe</t>
   </si>
   <si>
-    <t>Ricardo</t>
-  </si>
-  <si>
-    <t>Oscar</t>
-  </si>
-  <si>
     <t>Jorge</t>
   </si>
   <si>
@@ -68,24 +62,12 @@
     <t>Carlos</t>
   </si>
   <si>
-    <t>Lourdes</t>
-  </si>
-  <si>
     <t>Juan</t>
   </si>
   <si>
     <t>Diego</t>
   </si>
   <si>
-    <t>Alvaro</t>
-  </si>
-  <si>
-    <t>Roxana</t>
-  </si>
-  <si>
-    <t>Ana</t>
-  </si>
-  <si>
     <t>Enrique</t>
   </si>
   <si>
@@ -95,490 +77,508 @@
     <t>Cesar</t>
   </si>
   <si>
-    <t>Patricia</t>
-  </si>
-  <si>
     <t>Juana</t>
   </si>
   <si>
-    <t>Lucia</t>
-  </si>
-  <si>
-    <t>Gabriela</t>
-  </si>
-  <si>
-    <t>finanzas@hacsa-peru.com</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
-    <t>hacsa2005@hotmail.com</t>
-  </si>
-  <si>
-    <t>Anthony</t>
-  </si>
-  <si>
-    <t>joel.zuta@jwclogistic.com</t>
-  </si>
-  <si>
-    <t>Joel</t>
-  </si>
-  <si>
-    <t>sgestion@hacsa-peru.com</t>
-  </si>
-  <si>
-    <t>Evelin</t>
-  </si>
-  <si>
-    <t>yvonne.pinto@jwclogistic.com</t>
-  </si>
-  <si>
-    <t>Yvonne</t>
-  </si>
-  <si>
-    <t>gerencia@corporacionorluma.com</t>
-  </si>
-  <si>
-    <t>Luzmila</t>
-  </si>
-  <si>
-    <t>luisortiz15@gmail.com</t>
-  </si>
-  <si>
-    <t>mobiliariabarboza@gmail.com</t>
-  </si>
-  <si>
-    <t>Brayan</t>
-  </si>
-  <si>
-    <t>rui.valcarce@miguelez.com</t>
-  </si>
-  <si>
-    <t>Rui</t>
-  </si>
-  <si>
-    <t>valeria.canales@miguelez.com</t>
-  </si>
-  <si>
-    <t>Valeria</t>
-  </si>
-  <si>
-    <t>drossello@rossello.com.pe</t>
-  </si>
-  <si>
-    <t>gabriela.monar@unacem.pe</t>
-  </si>
-  <si>
-    <t>lromero@comacsa.com.pe</t>
-  </si>
-  <si>
-    <t>Liliana</t>
-  </si>
-  <si>
-    <t>mbarrios@calidra.com.mx</t>
-  </si>
-  <si>
-    <t>rossana.tonussi@unacem.pe</t>
-  </si>
-  <si>
-    <t>Eduardo</t>
-  </si>
-  <si>
-    <t>fanofordi@hotmail.com</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>ingrid-fano@hotmail.com</t>
-  </si>
-  <si>
     <t>Ingrid</t>
   </si>
   <si>
-    <t>jamesfano@negociosjordi.com</t>
-  </si>
-  <si>
-    <t>lvargas@corporacionjordi.com</t>
-  </si>
-  <si>
-    <t>negociosjordi@hotmail.com</t>
-  </si>
-  <si>
-    <t>amendoza@nutesa.com.pe</t>
-  </si>
-  <si>
-    <t>Adelaida</t>
-  </si>
-  <si>
-    <t>arcowayta@gmail.com</t>
-  </si>
-  <si>
-    <t>Maricielo</t>
-  </si>
-  <si>
-    <t>ecd@kp.pe</t>
-  </si>
-  <si>
-    <t>marketing@nutesa.com.pe</t>
-  </si>
-  <si>
-    <t>Fiorella</t>
-  </si>
-  <si>
-    <t>mcrosas@nutesa.com.pe</t>
-  </si>
-  <si>
-    <t>ledesma.am@pg.com</t>
-  </si>
-  <si>
-    <t>moran.er@pg.com</t>
-  </si>
-  <si>
-    <t>Elva</t>
-  </si>
-  <si>
-    <t>muniz.g@pg.com</t>
-  </si>
-  <si>
-    <t>reyes.h@pg.com</t>
-  </si>
-  <si>
-    <t>Román</t>
-  </si>
-  <si>
-    <t>villalobos.n.3@pg.com</t>
-  </si>
-  <si>
-    <t>Nury</t>
-  </si>
-  <si>
-    <t>abravo@corkperu.com</t>
-  </si>
-  <si>
-    <t>Fiorela</t>
-  </si>
-  <si>
-    <t>daysi.montenegro.salazar@gmail.com</t>
-  </si>
-  <si>
-    <t>Daysi</t>
-  </si>
-  <si>
-    <t>eduardo.monzon.rondon@gmail.com</t>
-  </si>
-  <si>
-    <t>negocios@amfa.com.pe</t>
-  </si>
-  <si>
-    <t>operaciones@amfa.com.pe</t>
-  </si>
-  <si>
-    <t>diego.rincon@experian.com</t>
-  </si>
-  <si>
-    <t>efrain.aquino@experian.com</t>
-  </si>
-  <si>
-    <t>Efrain</t>
-  </si>
-  <si>
-    <t>fuyumi.noda@experian.com</t>
-  </si>
-  <si>
-    <t>Fuyumi</t>
-  </si>
-  <si>
-    <t>hpeirano@addvalora-wmoller.com</t>
-  </si>
-  <si>
-    <t>Laura</t>
-  </si>
-  <si>
-    <t>juancarlos.veturo@experian.com</t>
-  </si>
-  <si>
-    <t>francojbulnes@eaton.com</t>
-  </si>
-  <si>
-    <t>jorgelmorales@eaton.com</t>
-  </si>
-  <si>
-    <t>keikolaos@eaton.com</t>
-  </si>
-  <si>
-    <t>Keiko</t>
-  </si>
-  <si>
-    <t>mnunez@mgp.com.pe</t>
-  </si>
-  <si>
-    <t>Mariela</t>
-  </si>
-  <si>
-    <t>nohaycorreo@gmail.com</t>
-  </si>
-  <si>
-    <t>Carolina</t>
-  </si>
-  <si>
-    <t>administracion@cbm.pe</t>
-  </si>
-  <si>
-    <t>ana.bar@cbm.pe</t>
-  </si>
-  <si>
-    <t>carlos.ruiz@cbm.pe</t>
-  </si>
-  <si>
-    <t>dvera0306@gmail.com</t>
-  </si>
-  <si>
     <t>Daniel</t>
   </si>
   <si>
-    <t>noemitj26@gmail.com</t>
-  </si>
-  <si>
-    <t>Ruth</t>
-  </si>
-  <si>
-    <t>alaserperu@hotmail.com</t>
-  </si>
-  <si>
-    <t>alfonsomatos82@yahoo.com</t>
-  </si>
-  <si>
     <t>Alfonso</t>
   </si>
   <si>
-    <t>maxmetalserviciosgenerales@gmail.com</t>
-  </si>
-  <si>
-    <t>Flor</t>
-  </si>
-  <si>
-    <t>omerjuncog@gmail.com</t>
-  </si>
-  <si>
-    <t>Omer</t>
-  </si>
-  <si>
-    <t>vierochka.santander@gmail.com</t>
-  </si>
-  <si>
-    <t>Vierochka</t>
-  </si>
-  <si>
-    <t>implemaq.adm2@gmail.com</t>
-  </si>
-  <si>
-    <t>implemaqdelperu@gmail.com</t>
-  </si>
-  <si>
-    <t>Lenin</t>
-  </si>
-  <si>
-    <t>j.guerrero@motopits.pe</t>
-  </si>
-  <si>
-    <t>Johanna</t>
-  </si>
-  <si>
-    <t>martin.rodriguez@motopits.pe</t>
-  </si>
-  <si>
-    <t>rosy.kanaffo@motopits.pe</t>
-  </si>
-  <si>
-    <t>Rosy</t>
-  </si>
-  <si>
-    <t>alex.fernandez@resefer.com</t>
-  </si>
-  <si>
-    <t>Alex</t>
-  </si>
-  <si>
-    <t>isaias.guerrero@resefer.com</t>
-  </si>
-  <si>
-    <t>Isaias</t>
-  </si>
-  <si>
-    <t>mugarte@neumopack.com</t>
-  </si>
-  <si>
-    <t>Mauricio</t>
-  </si>
-  <si>
-    <t>ruben.lavado@resefer.com</t>
-  </si>
-  <si>
-    <t>Ruben</t>
-  </si>
-  <si>
-    <t>apana.lucio@gmail.com</t>
-  </si>
-  <si>
-    <t>Lucio</t>
-  </si>
-  <si>
-    <t>ernesto.l@electrodunas.com</t>
-  </si>
-  <si>
-    <t>Ernesto</t>
-  </si>
-  <si>
-    <t>gerencia@syrconge.com</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>vjayo@electrodunas.com</t>
-  </si>
-  <si>
-    <t>carmenlopezalb84@gmail.com</t>
-  </si>
-  <si>
-    <t>isaac.lopez@grupocaarein.com.pe</t>
-  </si>
-  <si>
-    <t>Isaac</t>
-  </si>
-  <si>
-    <t>manuel.torres@grupocaarein.com.pe</t>
-  </si>
-  <si>
-    <t>Manuel</t>
-  </si>
-  <si>
-    <t>marino@grupocaarein.com.pe</t>
-  </si>
-  <si>
-    <t>Leidin</t>
-  </si>
-  <si>
-    <t>bjm@mahecor.com</t>
-  </si>
-  <si>
-    <t>Bernardo</t>
-  </si>
-  <si>
-    <t>jenny.ingaruca@tlr.com.pe</t>
-  </si>
-  <si>
     <t>Jenny</t>
   </si>
   <si>
-    <t>luis.carbajal@tlr.com.pe</t>
-  </si>
-  <si>
-    <t>ricardo.rodriguez@tlr.com.pe</t>
-  </si>
-  <si>
-    <t>cristina.peralta@gruposcp.com</t>
-  </si>
-  <si>
-    <t>gperalta@socpur.com</t>
-  </si>
-  <si>
-    <t>kelly.loza@gruposcp.com</t>
-  </si>
-  <si>
-    <t>miriam.murakami@gruposcp.com</t>
-  </si>
-  <si>
-    <t>Miriam</t>
-  </si>
-  <si>
-    <t>info@fullbusinessglobal.com</t>
-  </si>
-  <si>
-    <t>mgirano@rey.pe</t>
-  </si>
-  <si>
-    <t>Alexander</t>
-  </si>
-  <si>
-    <t>olanatta@perugoldtrade.com.pe</t>
-  </si>
-  <si>
-    <t>ssilva@perugoldtrade.com.pe</t>
-  </si>
-  <si>
-    <t>genaro.amaya@ferretoolssac.com</t>
-  </si>
-  <si>
-    <t>Genaro</t>
-  </si>
-  <si>
-    <t>luis.monroy@ferretoolssac.com</t>
-  </si>
-  <si>
-    <t>pablotineo@azchemical.pe</t>
-  </si>
-  <si>
     <t>Pablo</t>
   </si>
   <si>
-    <t>veronica.avalos@azchemical.pe</t>
-  </si>
-  <si>
-    <t>ddivos@solpack.com.pe</t>
-  </si>
-  <si>
-    <t>hugomhf14@gmail.com</t>
-  </si>
-  <si>
-    <t>Hugo</t>
-  </si>
-  <si>
-    <t>jcabero@solpack.com.pe</t>
-  </si>
-  <si>
     <t>Jose</t>
   </si>
   <si>
-    <t>ptippe@solpack.com.pe</t>
-  </si>
-  <si>
-    <t>admi.cicoplas@gmail.com</t>
-  </si>
-  <si>
-    <t>Noemy</t>
-  </si>
-  <si>
-    <t>cirodelrio@agro-gestion.com</t>
-  </si>
-  <si>
-    <t>Ciro</t>
-  </si>
-  <si>
-    <t>g.laupa@agro-gestion.com</t>
-  </si>
-  <si>
-    <t>Galich</t>
-  </si>
-  <si>
-    <t>heidi.chero@tigre.com</t>
-  </si>
-  <si>
-    <t>Carla</t>
-  </si>
-  <si>
-    <t>carla.melendez@husqvarnagroup.com</t>
-  </si>
-  <si>
-    <t>erika.hurtado@husqvarnagroup.com</t>
-  </si>
-  <si>
-    <t>liliana.vargas@husqvarnagroup.com</t>
-  </si>
-  <si>
-    <t>mariaclaudia.urbina@husqvarnagroup.com</t>
+    <t>achirinos@quimand.com.pe</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>administracion@novaprint.com.pe</t>
+  </si>
+  <si>
+    <t>Margarita</t>
+  </si>
+  <si>
+    <t>apinillos@quimand.com.pe</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>carllt234@gmail.com</t>
+  </si>
+  <si>
+    <t>innovaingenieros@gmail.com</t>
+  </si>
+  <si>
+    <t>munoz@quimand.com.pe</t>
+  </si>
+  <si>
+    <t>carlos.saba.6@gmail.com</t>
+  </si>
+  <si>
+    <t>jazminhuamanchura@gmail.com</t>
+  </si>
+  <si>
+    <t>Reyna</t>
+  </si>
+  <si>
+    <t>jjazmin227@hotmail.com</t>
+  </si>
+  <si>
+    <t>Yobana</t>
+  </si>
+  <si>
+    <t>lopezsaba10@gmail.com</t>
+  </si>
+  <si>
+    <t>Gustavo</t>
+  </si>
+  <si>
+    <t>martincb1965@gmail.com</t>
+  </si>
+  <si>
+    <t>martincb1965@hotmail.com</t>
+  </si>
+  <si>
+    <t>arianicmk@gmail.com</t>
+  </si>
+  <si>
+    <t>Justina</t>
+  </si>
+  <si>
+    <t>contact@comchi.com.cn</t>
+  </si>
+  <si>
+    <t>Jiawei</t>
+  </si>
+  <si>
+    <t>dmontanonina@gmail.com</t>
+  </si>
+  <si>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>fchang@comchi.com.cn</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>montagnoperu07@hotmail.com</t>
+  </si>
+  <si>
+    <t>Tito</t>
+  </si>
+  <si>
+    <t>olivosenator@gmail.com</t>
+  </si>
+  <si>
+    <t>cesarlari@cilsaperu.com</t>
+  </si>
+  <si>
+    <t>eliza-lari@cilsaperu.com</t>
+  </si>
+  <si>
+    <t>Liza</t>
+  </si>
+  <si>
+    <t>emendoza@lubricantespremium.com.pe</t>
+  </si>
+  <si>
+    <t>lari@cilsapereu.com</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>ventas@lubricantespremium.com.pe</t>
+  </si>
+  <si>
+    <t>cecilia.urrutia@linde.com</t>
+  </si>
+  <si>
+    <t>Cecilia</t>
+  </si>
+  <si>
+    <t>jose_moran@praxair.com</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>julio.caceres@linde.com</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>paola_vera@praxair.com</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>vanessa_kianman@praxair.com</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>admin@burbujaverde.com</t>
+  </si>
+  <si>
+    <t>André</t>
+  </si>
+  <si>
+    <t>administration@feelingboardco.com</t>
+  </si>
+  <si>
+    <t>amelendez@feelingboardco.com</t>
+  </si>
+  <si>
+    <t>Alexanda</t>
+  </si>
+  <si>
+    <t>becquerkayac@hotmail.com</t>
+  </si>
+  <si>
+    <t>Becquer</t>
+  </si>
+  <si>
+    <t>sales.manager@feelingboardco.com</t>
+  </si>
+  <si>
+    <t>aadministracion@barbacci.pe</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>contabilidad@barbacci.pe</t>
+  </si>
+  <si>
+    <t>Katherine</t>
+  </si>
+  <si>
+    <t>francisco.vargas@credivargas.pe</t>
+  </si>
+  <si>
+    <t>giuliana.vargas@credivargas.pe</t>
+  </si>
+  <si>
+    <t>Giuliana</t>
+  </si>
+  <si>
+    <t>lorena.perez@credivargas.pe</t>
+  </si>
+  <si>
+    <t>Lorena</t>
+  </si>
+  <si>
+    <t>contabilidad@isetek.com.pe</t>
+  </si>
+  <si>
+    <t>gerencia@isetek.com.pe</t>
+  </si>
+  <si>
+    <t>Alejandro</t>
+  </si>
+  <si>
+    <t>rpiedra@georya.com</t>
+  </si>
+  <si>
+    <t>Ramiro</t>
+  </si>
+  <si>
+    <t>smolleapaza@myrserviplast.com</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>yparipanca@georys.com</t>
+  </si>
+  <si>
+    <t>Yris</t>
+  </si>
+  <si>
+    <t>administracion@audiomax.com.pe</t>
+  </si>
+  <si>
+    <t>audiologia@hotmail.com</t>
+  </si>
+  <si>
+    <t>julioswayne@audiomax.com.pe</t>
+  </si>
+  <si>
+    <t>nancyaguilar@audiomax.com.pe</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>pmartel@petcoaudicion.com</t>
+  </si>
+  <si>
+    <t>antonilia@live.com</t>
+  </si>
+  <si>
+    <t>Antonia</t>
+  </si>
+  <si>
+    <t>ivonneinga@iccperu.com</t>
+  </si>
+  <si>
+    <t>Ivonne</t>
+  </si>
+  <si>
+    <t>mrabelo@iccperu.com</t>
+  </si>
+  <si>
+    <t>Marina</t>
+  </si>
+  <si>
+    <t>slastreto@iccperu.com</t>
+  </si>
+  <si>
+    <t>Silvana</t>
+  </si>
+  <si>
+    <t>ventas@iccperu.com</t>
+  </si>
+  <si>
+    <t>crusurach@graco.com.pe</t>
+  </si>
+  <si>
+    <t>Crusura</t>
+  </si>
+  <si>
+    <t>gerencia@graco.com.pe</t>
+  </si>
+  <si>
+    <t>ingeniera@graco.com.pe</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>marketing@grupoere.com.pe</t>
+  </si>
+  <si>
+    <t>Kiara</t>
+  </si>
+  <si>
+    <t>vramirez@grupoere.com.pe</t>
+  </si>
+  <si>
+    <t>Vladimir</t>
+  </si>
+  <si>
+    <t>factoriareymotorssac@gmail.com</t>
+  </si>
+  <si>
+    <t>gabriela4643@gmail.com</t>
+  </si>
+  <si>
+    <t>Gabriela.</t>
+  </si>
+  <si>
+    <t>logistica@gavelgroup.com.pe</t>
+  </si>
+  <si>
+    <t>Joseline</t>
+  </si>
+  <si>
+    <t>mtorres@arifeperu.com</t>
+  </si>
+  <si>
+    <t>Dani</t>
+  </si>
+  <si>
+    <t>neria.velasquez@gavelgroup.com.pe</t>
+  </si>
+  <si>
+    <t>Neria</t>
+  </si>
+  <si>
+    <t>contabilidad@fnjones.com</t>
+  </si>
+  <si>
+    <t>fnjones@fnjones.com</t>
+  </si>
+  <si>
+    <t>fnjones@snjones.com</t>
+  </si>
+  <si>
+    <t>Sandy</t>
+  </si>
+  <si>
+    <t>leonlauli@hotmail.com</t>
+  </si>
+  <si>
+    <t>Leon</t>
+  </si>
+  <si>
+    <t>marco.poma@tkambio.com</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>administracion@radiotrans.com.pe</t>
+  </si>
+  <si>
+    <t>energesa@energesa.com</t>
+  </si>
+  <si>
+    <t>maria.yanca@2m.pe</t>
+  </si>
+  <si>
+    <t>mreyes@radiotrans.com.pe</t>
+  </si>
+  <si>
+    <t>Mabel</t>
+  </si>
+  <si>
+    <t>nmoises_g@hotmail.com</t>
+  </si>
+  <si>
+    <t>Nelver</t>
+  </si>
+  <si>
+    <t>comprasconicsa@gmail.com</t>
+  </si>
+  <si>
+    <t>comprasconvicsa@gmail.com</t>
+  </si>
+  <si>
+    <t>Wilmer</t>
+  </si>
+  <si>
+    <t>convicsa_@hotmail.com</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>creditosycobranzasconvicsa@gmail.com</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>ventas01@nazcainnovation.com</t>
+  </si>
+  <si>
+    <t>jeanette.yanez@gfk.com</t>
+  </si>
+  <si>
+    <t>Jeanette</t>
+  </si>
+  <si>
+    <t>jeanluis.vargas@gfk.com</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>jeanluis.vargas@nielseniq.com</t>
+  </si>
+  <si>
+    <t>karen.doig@gfk.com</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>nancy.jaen@gfk.com</t>
+  </si>
+  <si>
+    <t>amc@amc-gaskets.com</t>
+  </si>
+  <si>
+    <t>Martha</t>
+  </si>
+  <si>
+    <t>inflores.jaless@gmail.com</t>
+  </si>
+  <si>
+    <t>jean.franco.fs@gmail.com</t>
+  </si>
+  <si>
+    <t>luis_flores_diaz@hotmail.com</t>
+  </si>
+  <si>
+    <t>tesoreria@amc-gaskets.com</t>
+  </si>
+  <si>
+    <t>Shayuri</t>
+  </si>
+  <si>
+    <t>fcentral@fcentral.com.pe</t>
+  </si>
+  <si>
+    <t>jbenavides@fcentral.com.pe</t>
+  </si>
+  <si>
+    <t>mdongo@fcentral.com.pe</t>
+  </si>
+  <si>
+    <t>Marianella</t>
+  </si>
+  <si>
+    <t>mmorales@fcentral.com.pe</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>rcumapa@fcentral.com.pe</t>
+  </si>
+  <si>
+    <t>Roger</t>
+  </si>
+  <si>
+    <t>eguerreroleyva1998@gmail.com</t>
+  </si>
+  <si>
+    <t>Edinson</t>
+  </si>
+  <si>
+    <t>kmarcos@beltsfashion.com</t>
+  </si>
+  <si>
+    <t>Kathering</t>
+  </si>
+  <si>
+    <t>ntorres@arseguinperu.com</t>
+  </si>
+  <si>
+    <t>Nashely</t>
+  </si>
+  <si>
+    <t>valery.shoes2016@gmail.com</t>
+  </si>
+  <si>
+    <t>Maribel</t>
+  </si>
+  <si>
+    <t>zafra282828@gmail.com</t>
+  </si>
+  <si>
+    <t>Placido</t>
   </si>
 </sst>
 </file>
@@ -953,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -969,55 +969,55 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -1025,274 +1025,274 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" t="s">
         <v>81</v>
-      </c>
-      <c r="B38" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" t="s">
         <v>83</v>
-      </c>
-      <c r="B39" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" t="s">
         <v>88</v>
-      </c>
-      <c r="B42" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1300,23 +1300,23 @@
         <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1324,23 +1324,23 @@
         <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" t="s">
         <v>97</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1348,7 +1348,7 @@
         <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1372,23 +1372,23 @@
         <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1404,15 +1404,15 @@
         <v>110</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" t="s">
         <v>112</v>
-      </c>
-      <c r="B57" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1436,7 +1436,7 @@
         <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1476,127 +1476,127 @@
         <v>126</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B69" t="s">
-        <v>6</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B72" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B74" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B75" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B76" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B77" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>149</v>
+      </c>
+      <c r="B80" t="s">
         <v>150</v>
-      </c>
-      <c r="B80" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -1612,7 +1612,7 @@
         <v>153</v>
       </c>
       <c r="B82" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -1628,7 +1628,7 @@
         <v>156</v>
       </c>
       <c r="B84" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -1636,15 +1636,15 @@
         <v>157</v>
       </c>
       <c r="B85" t="s">
-        <v>7</v>
+        <v>158</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -1652,7 +1652,7 @@
         <v>160</v>
       </c>
       <c r="B87" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -1660,15 +1660,15 @@
         <v>161</v>
       </c>
       <c r="B88" t="s">
-        <v>162</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B89" t="s">
         <v>163</v>
-      </c>
-      <c r="B89" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -1676,7 +1676,7 @@
         <v>164</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -1684,23 +1684,23 @@
         <v>165</v>
       </c>
       <c r="B91" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B92" t="s">
         <v>167</v>
-      </c>
-      <c r="B92" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>168</v>
+      </c>
+      <c r="B93" t="s">
         <v>169</v>
-      </c>
-      <c r="B93" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -1740,38 +1740,22 @@
         <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B99" t="s">
-        <v>10</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>180</v>
+      <c r="A100" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B100" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>181</v>
-      </c>
-      <c r="B101" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B102" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1780,7 +1764,7 @@
     <hyperlink ref="A2" r:id="rId1" display="negocios@partnertech.pe" xr:uid="{03D0B70B-CA3D-42A4-AB8B-090799BA5F82}"/>
     <hyperlink ref="A3" r:id="rId2" display="negocios@partnertech.pe" xr:uid="{68520335-2678-4B43-8BF3-94271BC5C19F}"/>
     <hyperlink ref="A92" r:id="rId3" display="negocios@partnertech.pe" xr:uid="{DEC3824D-1AA3-4DE4-BA28-4866CD128EB1}"/>
-    <hyperlink ref="A102" r:id="rId4" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
+    <hyperlink ref="A100" r:id="rId4" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402F87D4-2BDB-4AD5-88E6-E0A99F9A4057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64BF481-A4A5-4DC9-A042-C554153D64DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="185">
   <si>
     <t>correo</t>
   </si>
@@ -45,6 +45,549 @@
   </si>
   <si>
     <t>negocios@partnertech.pe</t>
+  </si>
+  <si>
+    <t>amayanec77@gmail.com</t>
+  </si>
+  <si>
+    <t>Amanda</t>
+  </si>
+  <si>
+    <t>dveliz@velzar.com.pe</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>emory@ormaquinarias.com.pe</t>
+  </si>
+  <si>
+    <t>Emali</t>
+  </si>
+  <si>
+    <t>hveliz@velzar.com.pe</t>
+  </si>
+  <si>
+    <t>Hernan</t>
+  </si>
+  <si>
+    <t>joteprin29@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>orlando@ormaquinarias.com.pe</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>velzar@telefonica.net.pe</t>
+  </si>
+  <si>
+    <t>Carthac</t>
+  </si>
+  <si>
+    <t>contabilidad@elpescador.biz</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>cportilla@elpescador.biz</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>eprb@elpescador.biz</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>eprbz@elpescador.biz</t>
+  </si>
+  <si>
+    <t>fimar@fimar.com.pe</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>oportilla@elpescador.biz</t>
+  </si>
+  <si>
+    <t>Oriele</t>
+  </si>
+  <si>
+    <t>rmherreralachira@gmail.com</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>andrescrosby@peruvianalliance.pe</t>
+  </si>
+  <si>
+    <t>Andres</t>
+  </si>
+  <si>
+    <t>malumerlo@peruvianalliance.com</t>
+  </si>
+  <si>
+    <t>mpajueloescobar@gmail.com</t>
+  </si>
+  <si>
+    <t>Martha</t>
+  </si>
+  <si>
+    <t>nrcadm2023@gmail.com</t>
+  </si>
+  <si>
+    <t>Alexandra</t>
+  </si>
+  <si>
+    <t>terranovaceramica@gmail.com</t>
+  </si>
+  <si>
+    <t>Alessandra</t>
+  </si>
+  <si>
+    <t>ventas@rymsolucionesgenerales.com</t>
+  </si>
+  <si>
+    <t>Magaly</t>
+  </si>
+  <si>
+    <t>filiberto.terrazos@sotrami.com.pe</t>
+  </si>
+  <si>
+    <t>Filiberto</t>
+  </si>
+  <si>
+    <t>gemrockperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Stefan</t>
+  </si>
+  <si>
+    <t>german.sapillado@sotrami.com.pe</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>juan.mejia@sotrami.com.pe</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>porfirio.pena@sotrami.com.pe</t>
+  </si>
+  <si>
+    <t>Porfirio</t>
+  </si>
+  <si>
+    <t>sotrami@hotmail.com</t>
+  </si>
+  <si>
+    <t>Eugenio</t>
+  </si>
+  <si>
+    <t>alfonsohrh@gmail.com</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>cdgutierrez25@hotmail.com</t>
+  </si>
+  <si>
+    <t>luisa.roque.huaman@gmail.com</t>
+  </si>
+  <si>
+    <t>Luisa</t>
+  </si>
+  <si>
+    <t>pieromatias14@gmail.com</t>
+  </si>
+  <si>
+    <t>Piero</t>
+  </si>
+  <si>
+    <t>studiobecan@gmail.com</t>
+  </si>
+  <si>
+    <t>Mireya</t>
+  </si>
+  <si>
+    <t>vmatias_marquez@hotmail.com</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>aprovet@aprovet.pe</t>
+  </si>
+  <si>
+    <t>Gretta</t>
+  </si>
+  <si>
+    <t>asimon@invetsa.com</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>dramos@invetsa.com</t>
+  </si>
+  <si>
+    <t>Dany</t>
+  </si>
+  <si>
+    <t>grettalazo@aprovet.pe</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>jruiz@invetsa.com</t>
+  </si>
+  <si>
+    <t>Jessica</t>
+  </si>
+  <si>
+    <t>wwhittembury@invetsa.com</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>carlos.mayday25@gmail.com</t>
+  </si>
+  <si>
+    <t>dollypaquita@yahoo.com</t>
+  </si>
+  <si>
+    <t>Dolly</t>
+  </si>
+  <si>
+    <t>grosminet98@gmail.com</t>
+  </si>
+  <si>
+    <t>Vieillard</t>
+  </si>
+  <si>
+    <t>intitaregalos@gmail.com</t>
+  </si>
+  <si>
+    <t>mafv1020@gmail.com</t>
+  </si>
+  <si>
+    <t>Mayra</t>
+  </si>
+  <si>
+    <t>veromontoro82@gmail.com</t>
+  </si>
+  <si>
+    <t>Veronica</t>
+  </si>
+  <si>
+    <t>cgan@diacorsa.com</t>
+  </si>
+  <si>
+    <t>Cecilia</t>
+  </si>
+  <si>
+    <t>gerencia@filtermedia.com.pe</t>
+  </si>
+  <si>
+    <t>kgonzales@diacorsa.com</t>
+  </si>
+  <si>
+    <t>Katia</t>
+  </si>
+  <si>
+    <t>miguellanza@diacorsa.com</t>
+  </si>
+  <si>
+    <t>Michelangelo</t>
+  </si>
+  <si>
+    <t>mlanza@diacorsa.com</t>
+  </si>
+  <si>
+    <t>ventas@filtermedia.com.pe</t>
+  </si>
+  <si>
+    <t>bcoarite@gmail.com</t>
+  </si>
+  <si>
+    <t>Betsabe</t>
+  </si>
+  <si>
+    <t>hdiaz@soloperusac.com</t>
+  </si>
+  <si>
+    <t>Henderson</t>
+  </si>
+  <si>
+    <t>mgarcia@soloperusac.com</t>
+  </si>
+  <si>
+    <t>Malena</t>
+  </si>
+  <si>
+    <t>mpuerta@soloperusac.com.pe</t>
+  </si>
+  <si>
+    <t>Moises</t>
+  </si>
+  <si>
+    <t>rcastro@soloperusac.com</t>
+  </si>
+  <si>
+    <t>Rocìo</t>
+  </si>
+  <si>
+    <t>williancoarite@gmail.com</t>
+  </si>
+  <si>
+    <t>Willian</t>
+  </si>
+  <si>
+    <t>contacto@libut.pe</t>
+  </si>
+  <si>
+    <t>Melissa</t>
+  </si>
+  <si>
+    <t>crodriguez@libut.pe</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>gabriela.lopez@crisol.com.pe</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>jaime.rivera@crisol.com.pe</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>rvergara.contadora@gmail.com</t>
+  </si>
+  <si>
+    <t>Rudith</t>
+  </si>
+  <si>
+    <t>sergio.venancio@crisol.com.pe</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>camarenabezares@gmail.com</t>
+  </si>
+  <si>
+    <t>copiadoraperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>fiorella.valderrama@arclad.com</t>
+  </si>
+  <si>
+    <t>Fiorella</t>
+  </si>
+  <si>
+    <t>ggutierrez@design-printings.com</t>
+  </si>
+  <si>
+    <t>Caroline</t>
+  </si>
+  <si>
+    <t>ines.huamani@arclad.com</t>
+  </si>
+  <si>
+    <t>Ines</t>
+  </si>
+  <si>
+    <t>nelly.lozada@arclad.com</t>
+  </si>
+  <si>
+    <t>Nelly</t>
+  </si>
+  <si>
+    <t>administracion@ecoservicios.pe</t>
+  </si>
+  <si>
+    <t>Maricielo</t>
+  </si>
+  <si>
+    <t>auxiliar.rrhh@solandra.pe</t>
+  </si>
+  <si>
+    <t>Kenyi</t>
+  </si>
+  <si>
+    <t>csaldana@cidelco.com</t>
+  </si>
+  <si>
+    <t>César</t>
+  </si>
+  <si>
+    <t>rcamargo@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ruben</t>
+  </si>
+  <si>
+    <t>rrhh@ecoservicios.pe</t>
+  </si>
+  <si>
+    <t>Nidia</t>
+  </si>
+  <si>
+    <t>zonalyss11@gmail.com</t>
+  </si>
+  <si>
+    <t>Zonaly</t>
+  </si>
+  <si>
+    <t>administracion@innpackperu.com</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>administracion@potenciaindustrial.com.pe</t>
+  </si>
+  <si>
+    <t>Pamela</t>
+  </si>
+  <si>
+    <t>anaguplastinversiones@gmail.com</t>
+  </si>
+  <si>
+    <t>Freddy</t>
+  </si>
+  <si>
+    <t>ccjc_15@yahoo.com</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>czamudio@potenciaindustrial.com.pe</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>jgutierrez@potenciaindustrial.com.pe</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>abocanegra@consultoriaabg.com</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>administracion@carp.pe</t>
+  </si>
+  <si>
+    <t>Yudith</t>
+  </si>
+  <si>
+    <t>bellcox_safety@hotmail.com</t>
+  </si>
+  <si>
+    <t>fermateo@yahoo.com</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>jc-acosta@hotmail.com</t>
+  </si>
+  <si>
+    <t>jdelgado@carpyasociados.com</t>
+  </si>
+  <si>
+    <t>bocanegrasantillan@gmail.com</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>danielsgl.18.99@gmail.com</t>
+  </si>
+  <si>
+    <t>Daniels</t>
+  </si>
+  <si>
+    <t>gcamel_27@hotmail.com</t>
+  </si>
+  <si>
+    <t>Clay</t>
+  </si>
+  <si>
+    <t>gerges.bocanegra@hotmail.com</t>
+  </si>
+  <si>
+    <t>Gerges</t>
+  </si>
+  <si>
+    <t>miguel.almeyda@rawfood.com.pe</t>
+  </si>
+  <si>
+    <t>smoncada@selcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>ftravi@nematsa.com.pe</t>
+  </si>
+  <si>
+    <t>grupohummer.gerencia@gmail.com</t>
+  </si>
+  <si>
+    <t>Wiliam</t>
+  </si>
+  <si>
+    <t>grupohummer@gmail.com</t>
+  </si>
+  <si>
+    <t>info@perumaderas.com</t>
+  </si>
+  <si>
+    <t>Leovigildo</t>
+  </si>
+  <si>
+    <t>mcalderon@perumaderas.com</t>
+  </si>
+  <si>
+    <t>Matilde</t>
+  </si>
+  <si>
+    <t>stravi@nematsa.com.pe</t>
+  </si>
+  <si>
+    <t>Sandra</t>
   </si>
 </sst>
 </file>
@@ -428,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -443,19 +986,801 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>98</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>129</v>
+      </c>
+      <c r="B69" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>131</v>
+      </c>
+      <c r="B70" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>133</v>
+      </c>
+      <c r="B71" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>139</v>
+      </c>
+      <c r="B74" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B78" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>155</v>
+      </c>
+      <c r="B82" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>157</v>
+      </c>
+      <c r="B83" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>159</v>
+      </c>
+      <c r="B84" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>160</v>
+      </c>
+      <c r="B85" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>162</v>
+      </c>
+      <c r="B86" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>163</v>
+      </c>
+      <c r="B87" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>164</v>
+      </c>
+      <c r="B88" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>168</v>
+      </c>
+      <c r="B90" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>170</v>
+      </c>
+      <c r="B91" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>172</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>173</v>
+      </c>
+      <c r="B93" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>175</v>
+      </c>
+      <c r="B94" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>176</v>
+      </c>
+      <c r="B95" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>178</v>
+      </c>
+      <c r="B96" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>179</v>
+      </c>
+      <c r="B97" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>181</v>
+      </c>
+      <c r="B98" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B100" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D6" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
+    <hyperlink ref="A100" r:id="rId1" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427996A4-6B22-49B0-B046-EA48F9E51016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205AF29E-D684-4F15-8769-FE06DB55D7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>correo</t>
   </si>
@@ -51,6 +51,18 @@
   </si>
   <si>
     <t>Alexandra</t>
+  </si>
+  <si>
+    <t>hmelgarejo@partnertech.pe</t>
+  </si>
+  <si>
+    <t>Helio</t>
+  </si>
+  <si>
+    <t>ncardozo@olssa.com.pe</t>
+  </si>
+  <si>
+    <t>fguerrero@olssa.com.pe</t>
   </si>
 </sst>
 </file>
@@ -434,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -464,13 +476,38 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
       <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{F1971FD1-7C25-438C-B0AA-563448125D87}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{228B21B2-F6D7-46DD-81B4-3C9AD96DA160}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{1A016AB9-0375-4056-B892-A261D4BFC8BF}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{7E44E4A6-0531-4587-83FB-2389671C49B6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205AF29E-D684-4F15-8769-FE06DB55D7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C04C5E-D3D2-4B8F-B7CA-959A516AE513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="335">
   <si>
     <t>correo</t>
   </si>
@@ -44,25 +44,1000 @@
     <t>Franco</t>
   </si>
   <si>
-    <t>negocios@partnertech.pe</t>
-  </si>
-  <si>
-    <t>acardozo@partnertech.pe</t>
-  </si>
-  <si>
-    <t>Alexandra</t>
-  </si>
-  <si>
-    <t>hmelgarejo@partnertech.pe</t>
-  </si>
-  <si>
-    <t>Helio</t>
-  </si>
-  <si>
-    <t>ncardozo@olssa.com.pe</t>
-  </si>
-  <si>
-    <t>fguerrero@olssa.com.pe</t>
+    <t>administraciontepco@engineeringtotalperu.com</t>
+  </si>
+  <si>
+    <t>Darwin</t>
+  </si>
+  <si>
+    <t>afalcontarazona@gmail.com</t>
+  </si>
+  <si>
+    <t>Anabell</t>
+  </si>
+  <si>
+    <t>cmartinez@pipingindustrial.com</t>
+  </si>
+  <si>
+    <t>Veronica</t>
+  </si>
+  <si>
+    <t>cramirez@redesur.com.pe</t>
+  </si>
+  <si>
+    <t>Cynthia</t>
+  </si>
+  <si>
+    <t>mbilibio@redesur.com.pe</t>
+  </si>
+  <si>
+    <t>Mariella</t>
+  </si>
+  <si>
+    <t>mvenero@redesur.com.pe</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>rececpcion@coelvisac.com.pe</t>
+  </si>
+  <si>
+    <t>Percy</t>
+  </si>
+  <si>
+    <t>tesusr@tesur.pe</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>ventas01@engineeringtotalperu.com</t>
+  </si>
+  <si>
+    <t>Sunli</t>
+  </si>
+  <si>
+    <t>info@auracreativa.com</t>
+  </si>
+  <si>
+    <t>Julian</t>
+  </si>
+  <si>
+    <t>info@pameladepaz.com</t>
+  </si>
+  <si>
+    <t>Gianina</t>
+  </si>
+  <si>
+    <t>info@sumelect.pe</t>
+  </si>
+  <si>
+    <t>Angie</t>
+  </si>
+  <si>
+    <t>jcarbajal@dnp.com.pe</t>
+  </si>
+  <si>
+    <t>jriva@assaperu.com</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>jrpiiroja@fuegosdelmilenio.com</t>
+  </si>
+  <si>
+    <t>logistica@diplomaslalo.com.pe</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>sumelect@hotmail.com</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>ventas2@darsen.dev</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>ealdea@sole.com.pe</t>
+  </si>
+  <si>
+    <t>Milagros</t>
+  </si>
+  <si>
+    <t>galberca@corpvsi.com</t>
+  </si>
+  <si>
+    <t>Gissella</t>
+  </si>
+  <si>
+    <t>jhares.ingenieros@gmail.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>jmerzthal@soldexa.com.pe</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>meyimsac@hotmail.com</t>
+  </si>
+  <si>
+    <t>Yime</t>
+  </si>
+  <si>
+    <t>ssattler@sole.com.pe</t>
+  </si>
+  <si>
+    <t>Sandro</t>
+  </si>
+  <si>
+    <t>supervision.meyim@gmail.com</t>
+  </si>
+  <si>
+    <t>vchristodulu@corpvsi.com</t>
+  </si>
+  <si>
+    <t>Vasilios</t>
+  </si>
+  <si>
+    <t>ventas@meyimsac.com</t>
+  </si>
+  <si>
+    <t>Kerly</t>
+  </si>
+  <si>
+    <t>administrador@serlisa.com.pe</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>cbarinotto@copepdelperu.com</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>ccaballero@monteazul.com.pe</t>
+  </si>
+  <si>
+    <t>Claudio</t>
+  </si>
+  <si>
+    <t>clopezc3@copepdelperu.com</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>freyna@copepdelperu.com</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>gerentecorporativo@copetrolperu.com</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>jhernandez@monteazul.com.pe</t>
+  </si>
+  <si>
+    <t>Jennyfer</t>
+  </si>
+  <si>
+    <t>mbrazzoduro@monteazul.com.pe</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>pmartinez@monteazul.com.pe</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>acaceres@fujifilm.com.pe</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>acortez@ptmarket.com.pe</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>cgomez@ptmarket.com.pe</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>jpaul@fujifilm.com.pe</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>jramirez@fujifilm.com.pe</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>logistica@fujifilm.com.pe</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>mmondragon@ptmarket.com.pe</t>
+  </si>
+  <si>
+    <t>salvarez@fujifilm.com.pe</t>
+  </si>
+  <si>
+    <t>Salvador</t>
+  </si>
+  <si>
+    <t>sinfante@fujifilm.com.pe</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>accoyccosi@greenersac.com</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>ccgomez6@hotmail.com</t>
+  </si>
+  <si>
+    <t>Carol</t>
+  </si>
+  <si>
+    <t>cevaristo@greenersac.com</t>
+  </si>
+  <si>
+    <t>Carmina</t>
+  </si>
+  <si>
+    <t>ciro.bedoya@gmail.com</t>
+  </si>
+  <si>
+    <t>Ciro</t>
+  </si>
+  <si>
+    <t>exitoparati77@gmail.com</t>
+  </si>
+  <si>
+    <t>Nilda</t>
+  </si>
+  <si>
+    <t>lisseth_zb@hotmail.com</t>
+  </si>
+  <si>
+    <t>Marisol</t>
+  </si>
+  <si>
+    <t>pablocolfer@gmail.com</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>patty_rochabrun@hotmail.com</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>rocio@rocioames.com</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>acpadmin@apoyoconsultoria.com</t>
+  </si>
+  <si>
+    <t>arodriguez@vitalikgroup.com</t>
+  </si>
+  <si>
+    <t>Alisson</t>
+  </si>
+  <si>
+    <t>cenytec@infonegocio.net.pe</t>
+  </si>
+  <si>
+    <t>Otilia</t>
+  </si>
+  <si>
+    <t>elsamolmos@gmail.com</t>
+  </si>
+  <si>
+    <t>Elsa</t>
+  </si>
+  <si>
+    <t>gerencia@cenytec.com</t>
+  </si>
+  <si>
+    <t>gerenciageneral@djn.com</t>
+  </si>
+  <si>
+    <t>Jessica</t>
+  </si>
+  <si>
+    <t>mellycuarez@gmail.com</t>
+  </si>
+  <si>
+    <t>Melly</t>
+  </si>
+  <si>
+    <t>milthongr@gmail.com</t>
+  </si>
+  <si>
+    <t>tniltons@gmail.com</t>
+  </si>
+  <si>
+    <t>Nilton</t>
+  </si>
+  <si>
+    <t>alvaro.aymar@ehiglobal.pe</t>
+  </si>
+  <si>
+    <t>Alvaro</t>
+  </si>
+  <si>
+    <t>cristobal@ocarrol.com</t>
+  </si>
+  <si>
+    <t>Cristobal</t>
+  </si>
+  <si>
+    <t>cvargas@mitta.pe</t>
+  </si>
+  <si>
+    <t>director@jcbasurto.com</t>
+  </si>
+  <si>
+    <t>eyokoyama@mitta.pe</t>
+  </si>
+  <si>
+    <t>Eddy</t>
+  </si>
+  <si>
+    <t>jordan.1998@gmail.com</t>
+  </si>
+  <si>
+    <t>Aaron</t>
+  </si>
+  <si>
+    <t>katia.manrique@ehiglobal.pe</t>
+  </si>
+  <si>
+    <t>Katia</t>
+  </si>
+  <si>
+    <t>rentacarpatricia@hotmail.com</t>
+  </si>
+  <si>
+    <t>sales@jcbasurto.com</t>
+  </si>
+  <si>
+    <t>Lurdes</t>
+  </si>
+  <si>
+    <t>abarriga@byc.com.pe</t>
+  </si>
+  <si>
+    <t>cdiaz@tarjetasperuanas.com.pe</t>
+  </si>
+  <si>
+    <t>ecastillo@tarjetasperuanas.com.pe</t>
+  </si>
+  <si>
+    <t>Elvira</t>
+  </si>
+  <si>
+    <t>gbarriga@byc.com.pe</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>malva@tarjetasperuanas.com.pe</t>
+  </si>
+  <si>
+    <t>mdiaz@tarjetasperuanas.com.pe</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>melbc07@gmail.com</t>
+  </si>
+  <si>
+    <t>Melva</t>
+  </si>
+  <si>
+    <t>zbazan@tarjetasperuanas.com.pe</t>
+  </si>
+  <si>
+    <t>agerencia@corporacionpro.com</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>gcoloma@psacificlatam.com</t>
+  </si>
+  <si>
+    <t>Hector</t>
+  </si>
+  <si>
+    <t>gkmori@hotmail.com</t>
+  </si>
+  <si>
+    <t>joserojasmendez.rojas@gmail.com</t>
+  </si>
+  <si>
+    <t>kmendoza@pacificlatam.com</t>
+  </si>
+  <si>
+    <t>Kurt</t>
+  </si>
+  <si>
+    <t>percy.lamadrid@milenium.group</t>
+  </si>
+  <si>
+    <t>rosa@rosajustiniano.com</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>tesoreria@pacificlatam.com</t>
+  </si>
+  <si>
+    <t>Melina</t>
+  </si>
+  <si>
+    <t>androwdavid@bluraudiovisual.com</t>
+  </si>
+  <si>
+    <t>Androw</t>
+  </si>
+  <si>
+    <t>colorete@hotmail.com</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>daniel.saldarriaga@esesncialmc.com</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>happyboxperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>irreverentia@gmail.com</t>
+  </si>
+  <si>
+    <t>luis.mendoza@bluraudiovisual.com</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>prakticasac@gmail.com</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>timetodesignperu@gmail.com</t>
+  </si>
+  <si>
+    <t>administracion@abbasolucionesintegrales.com</t>
+  </si>
+  <si>
+    <t>aliosk@gmail.com</t>
+  </si>
+  <si>
+    <t>Alioska</t>
+  </si>
+  <si>
+    <t>bdiaz@bbhgroup.com.pe</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>coronel.richard@gmail.com</t>
+  </si>
+  <si>
+    <t>Raul</t>
+  </si>
+  <si>
+    <t>jacqueline.quiliano@gmail.com</t>
+  </si>
+  <si>
+    <t>Jacqueline</t>
+  </si>
+  <si>
+    <t>mcabezas@abbasolucionesintegrales.com</t>
+  </si>
+  <si>
+    <t>r.ore@abbasolucionesintegrales.com</t>
+  </si>
+  <si>
+    <t>Roy</t>
+  </si>
+  <si>
+    <t>rmendoza@bygsac.com</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>cesar.torres@maccaferri.com.pe</t>
+  </si>
+  <si>
+    <t>gisela.galindo@ferri.com.pe</t>
+  </si>
+  <si>
+    <t>Gisela</t>
+  </si>
+  <si>
+    <t>leonor.gavidia@vmetais.com.pe</t>
+  </si>
+  <si>
+    <t>Warley</t>
+  </si>
+  <si>
+    <t>mario.balbin@maccaferri.com.pe</t>
+  </si>
+  <si>
+    <t>paschual.cataldi@vmetais.com.pe</t>
+  </si>
+  <si>
+    <t>Paschual</t>
+  </si>
+  <si>
+    <t>rodolfo.arias@nexaresources.com</t>
+  </si>
+  <si>
+    <t>Arnaldo</t>
+  </si>
+  <si>
+    <t>vanessa.arauco@maccaferri.com.pe</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>wilber.monteagudo@vmetais.com.pe</t>
+  </si>
+  <si>
+    <t>Wilber</t>
+  </si>
+  <si>
+    <t>aramos@siriegoing.com</t>
+  </si>
+  <si>
+    <t>creditosycobranzas@sistemasderiegoing.com</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>eloayza@sistemasderiego.pe</t>
+  </si>
+  <si>
+    <t>eloayza@sistemasderiegoing.com</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>hidyarte@gmail.com</t>
+  </si>
+  <si>
+    <t>mariakamishikiriyo@sisriegoing.com</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>sisrieg@terra.com.pe</t>
+  </si>
+  <si>
+    <t>zp080905@gmail.com</t>
+  </si>
+  <si>
+    <t>Zoila</t>
+  </si>
+  <si>
+    <t>administracion@cp-infamin.com</t>
+  </si>
+  <si>
+    <t>María</t>
+  </si>
+  <si>
+    <t>info@groupmesias.com</t>
+  </si>
+  <si>
+    <t>Alexia</t>
+  </si>
+  <si>
+    <t>jcaisahuana@cp-infamin.com</t>
+  </si>
+  <si>
+    <t>Zenaida</t>
+  </si>
+  <si>
+    <t>jportuguez@qorikallpa.com.pe</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>lfernandez@cemprotec.com.pe</t>
+  </si>
+  <si>
+    <t>mecoserge@groupmesias.com</t>
+  </si>
+  <si>
+    <t>Freddy.</t>
+  </si>
+  <si>
+    <t>speralta@cemprotec.com.pe</t>
+  </si>
+  <si>
+    <t>Shirley</t>
+  </si>
+  <si>
+    <t>tula.montalvan@cemprotec.com.pe</t>
+  </si>
+  <si>
+    <t>Tula</t>
+  </si>
+  <si>
+    <t>a.zcucciramo02@gmail.com</t>
+  </si>
+  <si>
+    <t>Alessandra</t>
+  </si>
+  <si>
+    <t>bezada@gmail.com</t>
+  </si>
+  <si>
+    <t>Nicolas</t>
+  </si>
+  <si>
+    <t>jmalpartida@bxports.com</t>
+  </si>
+  <si>
+    <t>jvasquez@monrepos-peru.com</t>
+  </si>
+  <si>
+    <t>lrodriguez@monrepos-peru.com</t>
+  </si>
+  <si>
+    <t>Lucila</t>
+  </si>
+  <si>
+    <t>pibanez@textilcolca.com.pe</t>
+  </si>
+  <si>
+    <t>sales@monrepos-peru.com</t>
+  </si>
+  <si>
+    <t>Gilma</t>
+  </si>
+  <si>
+    <t>sales@textilcolca.com.pe</t>
+  </si>
+  <si>
+    <t>Felipe</t>
+  </si>
+  <si>
+    <t>admin@encap.edu.pe</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>coordinacion@encap.edu.pe</t>
+  </si>
+  <si>
+    <t>Pamela</t>
+  </si>
+  <si>
+    <t>edson.aguilar@vocesciudadanas.pe</t>
+  </si>
+  <si>
+    <t>Edson</t>
+  </si>
+  <si>
+    <t>edualitos@gmail.com</t>
+  </si>
+  <si>
+    <t>Edual</t>
+  </si>
+  <si>
+    <t>gerenciadeoperaciones@informatikediciones.net</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>jvelasquez285@yahoo.com</t>
+  </si>
+  <si>
+    <t>Jenny</t>
+  </si>
+  <si>
+    <t>pilar.collantes@vocesciudadanas.pe</t>
+  </si>
+  <si>
+    <t>renatorivasr@peru.com</t>
+  </si>
+  <si>
+    <t>Renato</t>
+  </si>
+  <si>
+    <t>administracion@institutoperuanochino.pe</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>auccallaperu@gmail.com</t>
+  </si>
+  <si>
+    <t>daniel_derteano14@hotmail.com</t>
+  </si>
+  <si>
+    <t>erlindaauccallamuje@gmail.com</t>
+  </si>
+  <si>
+    <t>Herlinda</t>
+  </si>
+  <si>
+    <t>henryjimenezch@gmail.com</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>informes@institutoninadesign.com</t>
+  </si>
+  <si>
+    <t>Nila</t>
+  </si>
+  <si>
+    <t>presidencia@institutoperuanochino.pe</t>
+  </si>
+  <si>
+    <t>sedesurco0@gmail.com</t>
+  </si>
+  <si>
+    <t>giancarlo.villacorta@jmtoutdoors.com.pe</t>
+  </si>
+  <si>
+    <t>Giancarlo</t>
+  </si>
+  <si>
+    <t>humberto.aguinaga@jmtoutdoors.com.pe</t>
+  </si>
+  <si>
+    <t>Humberto</t>
+  </si>
+  <si>
+    <t>leska_17@hotmail.com</t>
+  </si>
+  <si>
+    <t>Leslie</t>
+  </si>
+  <si>
+    <t>marlonbarrantes074@gmail.com</t>
+  </si>
+  <si>
+    <t>Marlo</t>
+  </si>
+  <si>
+    <t>ojocreativompsac@gmail.com</t>
+  </si>
+  <si>
+    <t>Lierka</t>
+  </si>
+  <si>
+    <t>pyp@serccolorsac.com.pe</t>
+  </si>
+  <si>
+    <t>Noemi</t>
+  </si>
+  <si>
+    <t>vcandela@identidad-visual.com</t>
+  </si>
+  <si>
+    <t>ventas@identidad-visual.com</t>
+  </si>
+  <si>
+    <t>carritosdemercado@gmail.com</t>
+  </si>
+  <si>
+    <t>Miriam</t>
+  </si>
+  <si>
+    <t>controlremoto_mayer@hotmail.com</t>
+  </si>
+  <si>
+    <t>Azucena</t>
+  </si>
+  <si>
+    <t>info@royercars.com</t>
+  </si>
+  <si>
+    <t>j.aguirre@segurblock.pe</t>
+  </si>
+  <si>
+    <t>jagarciacassadof@cassado.com.pe</t>
+  </si>
+  <si>
+    <t>jgarciacassado@cassado.com.pe</t>
+  </si>
+  <si>
+    <t>liftrangerperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>marketing@mayer.pe</t>
+  </si>
+  <si>
+    <t>administracion@mobiliaindustrial.com.pe</t>
+  </si>
+  <si>
+    <t>Tania</t>
+  </si>
+  <si>
+    <t>apradoleon@yahoo.es</t>
+  </si>
+  <si>
+    <t>Aron</t>
+  </si>
+  <si>
+    <t>cprado@mobiliaindustrial.com.pe</t>
+  </si>
+  <si>
+    <t>Cristian</t>
+  </si>
+  <si>
+    <t>lucyadominguez0820@gmail.com</t>
+  </si>
+  <si>
+    <t>Lucia</t>
+  </si>
+  <si>
+    <t>p.merles@hotmail.com</t>
+  </si>
+  <si>
+    <t>pprado@mobiliaindustrial.com.pe</t>
+  </si>
+  <si>
+    <t>ventas@ecprefabricados.com</t>
+  </si>
+  <si>
+    <t>wlcing@hotmail.com</t>
+  </si>
+  <si>
+    <t>Judith</t>
+  </si>
+  <si>
+    <t>andrewarcacano@jesuselmaestro.edu.pe</t>
+  </si>
+  <si>
+    <t>angelrdelacruz.08@gmail.com</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>ariaanthony123@gmail.com</t>
+  </si>
+  <si>
+    <t>Aldair</t>
+  </si>
+  <si>
+    <t>centro.contigo.psi@gmail.com</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>cesarbazalar@gmail.com</t>
+  </si>
+  <si>
+    <t>informes@tiempodeamar.pe</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>netcram.consultores@gmail.com</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>asalvador@adeserv.com.pe</t>
+  </si>
+  <si>
+    <t>Adelaida</t>
+  </si>
+  <si>
+    <t>atencionalcliente@adeserv.com.pe</t>
+  </si>
+  <si>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>contabilidad@amaoutfitters.com</t>
+  </si>
+  <si>
+    <t>Tulio</t>
+  </si>
+  <si>
+    <t>ely_del@icloud.com</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>j.diaz@dyagroupsac.com</t>
+  </si>
+  <si>
+    <t>mery@adeserv.com.pe</t>
+  </si>
+  <si>
+    <t>Mery</t>
+  </si>
+  <si>
+    <t>vburga@entex.pe</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>fguerrero@partnertech.pe</t>
   </si>
 </sst>
 </file>
@@ -446,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -462,7 +1437,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>334</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -470,44 +1445,1542 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>120</v>
+      </c>
+      <c r="B65" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>122</v>
+      </c>
+      <c r="B66" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>128</v>
+      </c>
+      <c r="B70" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>130</v>
+      </c>
+      <c r="B71" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>134</v>
+      </c>
+      <c r="B73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>137</v>
+      </c>
+      <c r="B75" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>138</v>
+      </c>
+      <c r="B76" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>139</v>
+      </c>
+      <c r="B77" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>141</v>
+      </c>
+      <c r="B78" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>144</v>
+      </c>
+      <c r="B80" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>146</v>
+      </c>
+      <c r="B81" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>148</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>149</v>
+      </c>
+      <c r="B83" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>151</v>
+      </c>
+      <c r="B84" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>153</v>
+      </c>
+      <c r="B85" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>154</v>
+      </c>
+      <c r="B86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>157</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>158</v>
+      </c>
+      <c r="B89" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>160</v>
+      </c>
+      <c r="B90" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>164</v>
+      </c>
+      <c r="B92" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>166</v>
+      </c>
+      <c r="B93" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>168</v>
+      </c>
+      <c r="B94" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>170</v>
+      </c>
+      <c r="B95" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>171</v>
+      </c>
+      <c r="B96" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>173</v>
+      </c>
+      <c r="B97" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>175</v>
+      </c>
+      <c r="B98" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>177</v>
+      </c>
+      <c r="B100" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>179</v>
+      </c>
+      <c r="B101" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>181</v>
+      </c>
+      <c r="B102" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>185</v>
+      </c>
+      <c r="B104" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>186</v>
+      </c>
+      <c r="B105" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>188</v>
+      </c>
+      <c r="B106" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>190</v>
+      </c>
+      <c r="B107" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>191</v>
+      </c>
+      <c r="B108" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>193</v>
+      </c>
+      <c r="B109" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>195</v>
+      </c>
+      <c r="B110" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>196</v>
+      </c>
+      <c r="B111" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>198</v>
+      </c>
+      <c r="B112" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>200</v>
+      </c>
+      <c r="B113" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>202</v>
+      </c>
+      <c r="B114" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>204</v>
+      </c>
+      <c r="B115" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>205</v>
+      </c>
+      <c r="B116" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>207</v>
+      </c>
+      <c r="B117" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>208</v>
+      </c>
+      <c r="B118" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>210</v>
+      </c>
+      <c r="B119" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>211</v>
+      </c>
+      <c r="B120" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>213</v>
+      </c>
+      <c r="B121" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>214</v>
+      </c>
+      <c r="B122" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>216</v>
+      </c>
+      <c r="B123" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>218</v>
+      </c>
+      <c r="B124" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>220</v>
+      </c>
+      <c r="B125" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>222</v>
+      </c>
+      <c r="B126" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>224</v>
+      </c>
+      <c r="B127" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>225</v>
+      </c>
+      <c r="B128" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>227</v>
+      </c>
+      <c r="B129" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>229</v>
+      </c>
+      <c r="B130" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>231</v>
+      </c>
+      <c r="B131" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>233</v>
+      </c>
+      <c r="B132" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>235</v>
+      </c>
+      <c r="B133" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>236</v>
+      </c>
+      <c r="B134" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>237</v>
+      </c>
+      <c r="B135" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>239</v>
+      </c>
+      <c r="B136" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>240</v>
+      </c>
+      <c r="B137" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>242</v>
+      </c>
+      <c r="B138" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>244</v>
+      </c>
+      <c r="B139" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>246</v>
+      </c>
+      <c r="B140" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>248</v>
+      </c>
+      <c r="B141" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>250</v>
+      </c>
+      <c r="B142" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>252</v>
+      </c>
+      <c r="B143" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>254</v>
+      </c>
+      <c r="B144" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>256</v>
+      </c>
+      <c r="B145" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>257</v>
+      </c>
+      <c r="B146" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>259</v>
+      </c>
+      <c r="B147" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>261</v>
+      </c>
+      <c r="B148" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>262</v>
+      </c>
+      <c r="B149" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>263</v>
+      </c>
+      <c r="B150" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>265</v>
+      </c>
+      <c r="B151" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>267</v>
+      </c>
+      <c r="B152" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>269</v>
+      </c>
+      <c r="B153" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>270</v>
+      </c>
+      <c r="B154" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>271</v>
+      </c>
+      <c r="B155" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>273</v>
+      </c>
+      <c r="B156" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>275</v>
+      </c>
+      <c r="B157" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>277</v>
+      </c>
+      <c r="B158" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>279</v>
+      </c>
+      <c r="B159" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>281</v>
+      </c>
+      <c r="B160" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>283</v>
+      </c>
+      <c r="B161" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>284</v>
+      </c>
+      <c r="B162" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>285</v>
+      </c>
+      <c r="B163" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>287</v>
+      </c>
+      <c r="B164" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>289</v>
+      </c>
+      <c r="B165" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>290</v>
+      </c>
+      <c r="B166" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>291</v>
+      </c>
+      <c r="B167" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>292</v>
+      </c>
+      <c r="B168" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>293</v>
+      </c>
+      <c r="B169" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>295</v>
+      </c>
+      <c r="B170" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>296</v>
+      </c>
+      <c r="B171" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>298</v>
+      </c>
+      <c r="B172" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>300</v>
+      </c>
+      <c r="B173" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>302</v>
+      </c>
+      <c r="B174" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>304</v>
+      </c>
+      <c r="B175" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>305</v>
+      </c>
+      <c r="B176" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>306</v>
+      </c>
+      <c r="B177" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>307</v>
+      </c>
+      <c r="B178" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>309</v>
+      </c>
+      <c r="B179" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>310</v>
+      </c>
+      <c r="B180" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>312</v>
+      </c>
+      <c r="B181" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>314</v>
+      </c>
+      <c r="B182" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>316</v>
+      </c>
+      <c r="B183" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>317</v>
+      </c>
+      <c r="B184" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>319</v>
+      </c>
+      <c r="B185" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>321</v>
+      </c>
+      <c r="B186" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>323</v>
+      </c>
+      <c r="B187" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>325</v>
+      </c>
+      <c r="B188" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>327</v>
+      </c>
+      <c r="B189" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>329</v>
+      </c>
+      <c r="B190" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>330</v>
+      </c>
+      <c r="B191" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>332</v>
+      </c>
+      <c r="B192" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B193" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{F1971FD1-7C25-438C-B0AA-563448125D87}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{228B21B2-F6D7-46DD-81B4-3C9AD96DA160}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{1A016AB9-0375-4056-B892-A261D4BFC8BF}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{7E44E4A6-0531-4587-83FB-2389671C49B6}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
+    <hyperlink ref="A193" r:id="rId2" xr:uid="{2A60B044-2956-4470-9026-8142D3E23CF9}"/>
+    <hyperlink ref="A7" r:id="rId3" display="ncardozo@olssa.com.pe" xr:uid="{7E44E4A6-0531-4587-83FB-2389671C49B6}"/>
+    <hyperlink ref="A6" r:id="rId4" display="hmelgarejo@partnertech.pe" xr:uid="{1A016AB9-0375-4056-B892-A261D4BFC8BF}"/>
+    <hyperlink ref="A5" r:id="rId5" display="fguerrero@olssa.com.pe" xr:uid="{228B21B2-F6D7-46DD-81B4-3C9AD96DA160}"/>
+    <hyperlink ref="A4" r:id="rId6" display="acardozo@partnertech.pe" xr:uid="{F1971FD1-7C25-438C-B0AA-563448125D87}"/>
+    <hyperlink ref="A3" r:id="rId7" display="negocios@partnertech.pe" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C04C5E-D3D2-4B8F-B7CA-959A516AE513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB3F228-5CDB-446C-AE4D-276F7EDAE441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="348">
   <si>
     <t>correo</t>
   </si>
@@ -44,1000 +44,1039 @@
     <t>Franco</t>
   </si>
   <si>
-    <t>administraciontepco@engineeringtotalperu.com</t>
-  </si>
-  <si>
-    <t>Darwin</t>
-  </si>
-  <si>
-    <t>afalcontarazona@gmail.com</t>
-  </si>
-  <si>
-    <t>Anabell</t>
-  </si>
-  <si>
-    <t>cmartinez@pipingindustrial.com</t>
-  </si>
-  <si>
     <t>Veronica</t>
   </si>
   <si>
-    <t>cramirez@redesur.com.pe</t>
-  </si>
-  <si>
-    <t>Cynthia</t>
-  </si>
-  <si>
-    <t>mbilibio@redesur.com.pe</t>
-  </si>
-  <si>
-    <t>Mariella</t>
-  </si>
-  <si>
-    <t>mvenero@redesur.com.pe</t>
-  </si>
-  <si>
     <t>Mario</t>
   </si>
   <si>
-    <t>rececpcion@coelvisac.com.pe</t>
-  </si>
-  <si>
-    <t>Percy</t>
-  </si>
-  <si>
-    <t>tesusr@tesur.pe</t>
-  </si>
-  <si>
     <t>Juan</t>
   </si>
   <si>
-    <t>ventas01@engineeringtotalperu.com</t>
-  </si>
-  <si>
-    <t>Sunli</t>
-  </si>
-  <si>
-    <t>info@auracreativa.com</t>
-  </si>
-  <si>
-    <t>Julian</t>
-  </si>
-  <si>
-    <t>info@pameladepaz.com</t>
-  </si>
-  <si>
-    <t>Gianina</t>
-  </si>
-  <si>
-    <t>info@sumelect.pe</t>
-  </si>
-  <si>
-    <t>Angie</t>
-  </si>
-  <si>
-    <t>jcarbajal@dnp.com.pe</t>
-  </si>
-  <si>
-    <t>jriva@assaperu.com</t>
-  </si>
-  <si>
     <t>Julio</t>
   </si>
   <si>
-    <t>jrpiiroja@fuegosdelmilenio.com</t>
-  </si>
-  <si>
-    <t>logistica@diplomaslalo.com.pe</t>
-  </si>
-  <si>
-    <t>Camila</t>
-  </si>
-  <si>
-    <t>sumelect@hotmail.com</t>
-  </si>
-  <si>
     <t>Silvia</t>
   </si>
   <si>
-    <t>ventas2@darsen.dev</t>
-  </si>
-  <si>
-    <t>Gabriel</t>
-  </si>
-  <si>
-    <t>ealdea@sole.com.pe</t>
-  </si>
-  <si>
-    <t>Milagros</t>
-  </si>
-  <si>
-    <t>galberca@corpvsi.com</t>
-  </si>
-  <si>
-    <t>Gissella</t>
-  </si>
-  <si>
-    <t>jhares.ingenieros@gmail.com</t>
-  </si>
-  <si>
     <t>Jose</t>
   </si>
   <si>
-    <t>jmerzthal@soldexa.com.pe</t>
-  </si>
-  <si>
     <t>Jorge</t>
   </si>
   <si>
-    <t>meyimsac@hotmail.com</t>
-  </si>
-  <si>
-    <t>Yime</t>
-  </si>
-  <si>
-    <t>ssattler@sole.com.pe</t>
-  </si>
-  <si>
-    <t>Sandro</t>
-  </si>
-  <si>
-    <t>supervision.meyim@gmail.com</t>
-  </si>
-  <si>
-    <t>vchristodulu@corpvsi.com</t>
-  </si>
-  <si>
-    <t>Vasilios</t>
-  </si>
-  <si>
-    <t>ventas@meyimsac.com</t>
-  </si>
-  <si>
-    <t>Kerly</t>
-  </si>
-  <si>
-    <t>administrador@serlisa.com.pe</t>
-  </si>
-  <si>
     <t>Diana</t>
   </si>
   <si>
-    <t>cbarinotto@copepdelperu.com</t>
-  </si>
-  <si>
     <t>Carlos</t>
   </si>
   <si>
-    <t>ccaballero@monteazul.com.pe</t>
-  </si>
-  <si>
-    <t>Claudio</t>
-  </si>
-  <si>
-    <t>clopezc3@copepdelperu.com</t>
-  </si>
-  <si>
     <t>Cesar</t>
   </si>
   <si>
-    <t>freyna@copepdelperu.com</t>
-  </si>
-  <si>
     <t>Francisco</t>
   </si>
   <si>
-    <t>gerentecorporativo@copetrolperu.com</t>
-  </si>
-  <si>
     <t>Jaime</t>
   </si>
   <si>
-    <t>jhernandez@monteazul.com.pe</t>
-  </si>
-  <si>
-    <t>Jennyfer</t>
-  </si>
-  <si>
-    <t>mbrazzoduro@monteazul.com.pe</t>
-  </si>
-  <si>
-    <t>Marco</t>
-  </si>
-  <si>
-    <t>pmartinez@monteazul.com.pe</t>
-  </si>
-  <si>
-    <t>Pedro</t>
-  </si>
-  <si>
-    <t>acaceres@fujifilm.com.pe</t>
-  </si>
-  <si>
-    <t>Alberto</t>
-  </si>
-  <si>
-    <t>acortez@ptmarket.com.pe</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>cgomez@ptmarket.com.pe</t>
-  </si>
-  <si>
-    <t>Cristina</t>
-  </si>
-  <si>
-    <t>jpaul@fujifilm.com.pe</t>
-  </si>
-  <si>
     <t>Jean</t>
   </si>
   <si>
-    <t>jramirez@fujifilm.com.pe</t>
-  </si>
-  <si>
     <t>José</t>
   </si>
   <si>
-    <t>logistica@fujifilm.com.pe</t>
-  </si>
-  <si>
     <t>Roberto</t>
   </si>
   <si>
-    <t>mmondragon@ptmarket.com.pe</t>
-  </si>
-  <si>
-    <t>salvarez@fujifilm.com.pe</t>
-  </si>
-  <si>
-    <t>Salvador</t>
-  </si>
-  <si>
-    <t>sinfante@fujifilm.com.pe</t>
-  </si>
-  <si>
-    <t>Sara</t>
-  </si>
-  <si>
-    <t>accoyccosi@greenersac.com</t>
-  </si>
-  <si>
-    <t>Abel</t>
-  </si>
-  <si>
-    <t>ccgomez6@hotmail.com</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>cevaristo@greenersac.com</t>
-  </si>
-  <si>
-    <t>Carmina</t>
-  </si>
-  <si>
-    <t>ciro.bedoya@gmail.com</t>
-  </si>
-  <si>
-    <t>Ciro</t>
-  </si>
-  <si>
-    <t>exitoparati77@gmail.com</t>
-  </si>
-  <si>
-    <t>Nilda</t>
-  </si>
-  <si>
-    <t>lisseth_zb@hotmail.com</t>
-  </si>
-  <si>
-    <t>Marisol</t>
-  </si>
-  <si>
-    <t>pablocolfer@gmail.com</t>
-  </si>
-  <si>
-    <t>Pablo</t>
-  </si>
-  <si>
-    <t>patty_rochabrun@hotmail.com</t>
-  </si>
-  <si>
     <t>Patricia</t>
   </si>
   <si>
-    <t>rocio@rocioames.com</t>
-  </si>
-  <si>
     <t>Ana</t>
   </si>
   <si>
-    <t>acpadmin@apoyoconsultoria.com</t>
-  </si>
-  <si>
-    <t>arodriguez@vitalikgroup.com</t>
-  </si>
-  <si>
-    <t>Alisson</t>
-  </si>
-  <si>
-    <t>cenytec@infonegocio.net.pe</t>
-  </si>
-  <si>
-    <t>Otilia</t>
-  </si>
-  <si>
-    <t>elsamolmos@gmail.com</t>
-  </si>
-  <si>
-    <t>Elsa</t>
-  </si>
-  <si>
-    <t>gerencia@cenytec.com</t>
-  </si>
-  <si>
-    <t>gerenciageneral@djn.com</t>
-  </si>
-  <si>
     <t>Jessica</t>
   </si>
   <si>
-    <t>mellycuarez@gmail.com</t>
-  </si>
-  <si>
-    <t>Melly</t>
-  </si>
-  <si>
-    <t>milthongr@gmail.com</t>
-  </si>
-  <si>
-    <t>tniltons@gmail.com</t>
-  </si>
-  <si>
-    <t>Nilton</t>
-  </si>
-  <si>
-    <t>alvaro.aymar@ehiglobal.pe</t>
-  </si>
-  <si>
     <t>Alvaro</t>
   </si>
   <si>
-    <t>cristobal@ocarrol.com</t>
-  </si>
-  <si>
-    <t>Cristobal</t>
-  </si>
-  <si>
-    <t>cvargas@mitta.pe</t>
-  </si>
-  <si>
-    <t>director@jcbasurto.com</t>
-  </si>
-  <si>
-    <t>eyokoyama@mitta.pe</t>
-  </si>
-  <si>
-    <t>Eddy</t>
-  </si>
-  <si>
-    <t>jordan.1998@gmail.com</t>
-  </si>
-  <si>
-    <t>Aaron</t>
-  </si>
-  <si>
-    <t>katia.manrique@ehiglobal.pe</t>
-  </si>
-  <si>
-    <t>Katia</t>
-  </si>
-  <si>
-    <t>rentacarpatricia@hotmail.com</t>
-  </si>
-  <si>
-    <t>sales@jcbasurto.com</t>
-  </si>
-  <si>
-    <t>Lurdes</t>
-  </si>
-  <si>
-    <t>abarriga@byc.com.pe</t>
-  </si>
-  <si>
-    <t>cdiaz@tarjetasperuanas.com.pe</t>
-  </si>
-  <si>
-    <t>ecastillo@tarjetasperuanas.com.pe</t>
-  </si>
-  <si>
-    <t>Elvira</t>
-  </si>
-  <si>
-    <t>gbarriga@byc.com.pe</t>
-  </si>
-  <si>
-    <t>Gloria</t>
-  </si>
-  <si>
-    <t>malva@tarjetasperuanas.com.pe</t>
-  </si>
-  <si>
-    <t>mdiaz@tarjetasperuanas.com.pe</t>
-  </si>
-  <si>
     <t>Miguel</t>
   </si>
   <si>
-    <t>melbc07@gmail.com</t>
-  </si>
-  <si>
-    <t>Melva</t>
-  </si>
-  <si>
-    <t>zbazan@tarjetasperuanas.com.pe</t>
-  </si>
-  <si>
-    <t>agerencia@corporacionpro.com</t>
-  </si>
-  <si>
     <t>Christian</t>
   </si>
   <si>
-    <t>gcoloma@psacificlatam.com</t>
-  </si>
-  <si>
     <t>Hector</t>
   </si>
   <si>
-    <t>gkmori@hotmail.com</t>
-  </si>
-  <si>
-    <t>joserojasmendez.rojas@gmail.com</t>
-  </si>
-  <si>
-    <t>kmendoza@pacificlatam.com</t>
-  </si>
-  <si>
-    <t>Kurt</t>
-  </si>
-  <si>
-    <t>percy.lamadrid@milenium.group</t>
-  </si>
-  <si>
-    <t>rosa@rosajustiniano.com</t>
-  </si>
-  <si>
-    <t>Rosa</t>
-  </si>
-  <si>
-    <t>tesoreria@pacificlatam.com</t>
-  </si>
-  <si>
-    <t>Melina</t>
-  </si>
-  <si>
-    <t>androwdavid@bluraudiovisual.com</t>
-  </si>
-  <si>
-    <t>Androw</t>
-  </si>
-  <si>
-    <t>colorete@hotmail.com</t>
-  </si>
-  <si>
-    <t>William</t>
-  </si>
-  <si>
-    <t>daniel.saldarriaga@esesncialmc.com</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>happyboxperu@gmail.com</t>
-  </si>
-  <si>
     <t>Edgar</t>
   </si>
   <si>
-    <t>irreverentia@gmail.com</t>
-  </si>
-  <si>
-    <t>luis.mendoza@bluraudiovisual.com</t>
-  </si>
-  <si>
     <t>Luis</t>
   </si>
   <si>
-    <t>prakticasac@gmail.com</t>
-  </si>
-  <si>
-    <t>Claudia</t>
-  </si>
-  <si>
-    <t>timetodesignperu@gmail.com</t>
-  </si>
-  <si>
-    <t>administracion@abbasolucionesintegrales.com</t>
-  </si>
-  <si>
-    <t>aliosk@gmail.com</t>
-  </si>
-  <si>
-    <t>Alioska</t>
-  </si>
-  <si>
-    <t>bdiaz@bbhgroup.com.pe</t>
-  </si>
-  <si>
-    <t>Bruno</t>
-  </si>
-  <si>
-    <t>coronel.richard@gmail.com</t>
-  </si>
-  <si>
-    <t>Raul</t>
-  </si>
-  <si>
-    <t>jacqueline.quiliano@gmail.com</t>
-  </si>
-  <si>
-    <t>Jacqueline</t>
-  </si>
-  <si>
-    <t>mcabezas@abbasolucionesintegrales.com</t>
-  </si>
-  <si>
-    <t>r.ore@abbasolucionesintegrales.com</t>
-  </si>
-  <si>
-    <t>Roy</t>
-  </si>
-  <si>
-    <t>rmendoza@bygsac.com</t>
-  </si>
-  <si>
     <t>Gonzalo</t>
   </si>
   <si>
-    <t>cesar.torres@maccaferri.com.pe</t>
-  </si>
-  <si>
-    <t>gisela.galindo@ferri.com.pe</t>
-  </si>
-  <si>
-    <t>Gisela</t>
-  </si>
-  <si>
-    <t>leonor.gavidia@vmetais.com.pe</t>
-  </si>
-  <si>
-    <t>Warley</t>
-  </si>
-  <si>
-    <t>mario.balbin@maccaferri.com.pe</t>
-  </si>
-  <si>
-    <t>paschual.cataldi@vmetais.com.pe</t>
-  </si>
-  <si>
-    <t>Paschual</t>
-  </si>
-  <si>
-    <t>rodolfo.arias@nexaresources.com</t>
-  </si>
-  <si>
-    <t>Arnaldo</t>
-  </si>
-  <si>
-    <t>vanessa.arauco@maccaferri.com.pe</t>
-  </si>
-  <si>
     <t>Vanessa</t>
   </si>
   <si>
-    <t>wilber.monteagudo@vmetais.com.pe</t>
-  </si>
-  <si>
-    <t>Wilber</t>
-  </si>
-  <si>
-    <t>aramos@siriegoing.com</t>
-  </si>
-  <si>
-    <t>creditosycobranzas@sistemasderiegoing.com</t>
-  </si>
-  <si>
     <t>Eduardo</t>
   </si>
   <si>
-    <t>eloayza@sistemasderiego.pe</t>
-  </si>
-  <si>
-    <t>eloayza@sistemasderiegoing.com</t>
-  </si>
-  <si>
     <t>Andrea</t>
   </si>
   <si>
-    <t>hidyarte@gmail.com</t>
-  </si>
-  <si>
-    <t>mariakamishikiriyo@sisriegoing.com</t>
-  </si>
-  <si>
     <t>Maria</t>
   </si>
   <si>
-    <t>sisrieg@terra.com.pe</t>
-  </si>
-  <si>
-    <t>zp080905@gmail.com</t>
-  </si>
-  <si>
-    <t>Zoila</t>
-  </si>
-  <si>
-    <t>administracion@cp-infamin.com</t>
-  </si>
-  <si>
     <t>María</t>
   </si>
   <si>
-    <t>info@groupmesias.com</t>
-  </si>
-  <si>
-    <t>Alexia</t>
-  </si>
-  <si>
-    <t>jcaisahuana@cp-infamin.com</t>
-  </si>
-  <si>
-    <t>Zenaida</t>
-  </si>
-  <si>
-    <t>jportuguez@qorikallpa.com.pe</t>
-  </si>
-  <si>
     <t>Javier</t>
   </si>
   <si>
-    <t>lfernandez@cemprotec.com.pe</t>
-  </si>
-  <si>
-    <t>mecoserge@groupmesias.com</t>
-  </si>
-  <si>
-    <t>Freddy.</t>
-  </si>
-  <si>
-    <t>speralta@cemprotec.com.pe</t>
-  </si>
-  <si>
-    <t>Shirley</t>
-  </si>
-  <si>
-    <t>tula.montalvan@cemprotec.com.pe</t>
-  </si>
-  <si>
-    <t>Tula</t>
-  </si>
-  <si>
-    <t>a.zcucciramo02@gmail.com</t>
-  </si>
-  <si>
-    <t>Alessandra</t>
-  </si>
-  <si>
-    <t>bezada@gmail.com</t>
-  </si>
-  <si>
     <t>Nicolas</t>
   </si>
   <si>
-    <t>jmalpartida@bxports.com</t>
-  </si>
-  <si>
-    <t>jvasquez@monrepos-peru.com</t>
-  </si>
-  <si>
-    <t>lrodriguez@monrepos-peru.com</t>
-  </si>
-  <si>
-    <t>Lucila</t>
-  </si>
-  <si>
-    <t>pibanez@textilcolca.com.pe</t>
-  </si>
-  <si>
-    <t>sales@monrepos-peru.com</t>
-  </si>
-  <si>
-    <t>Gilma</t>
-  </si>
-  <si>
-    <t>sales@textilcolca.com.pe</t>
-  </si>
-  <si>
-    <t>Felipe</t>
-  </si>
-  <si>
-    <t>admin@encap.edu.pe</t>
-  </si>
-  <si>
     <t>Elizabeth</t>
   </si>
   <si>
-    <t>coordinacion@encap.edu.pe</t>
-  </si>
-  <si>
-    <t>Pamela</t>
-  </si>
-  <si>
-    <t>edson.aguilar@vocesciudadanas.pe</t>
-  </si>
-  <si>
-    <t>Edson</t>
-  </si>
-  <si>
-    <t>edualitos@gmail.com</t>
-  </si>
-  <si>
-    <t>Edual</t>
-  </si>
-  <si>
-    <t>gerenciadeoperaciones@informatikediciones.net</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
-    <t>jvelasquez285@yahoo.com</t>
-  </si>
-  <si>
-    <t>Jenny</t>
-  </si>
-  <si>
-    <t>pilar.collantes@vocesciudadanas.pe</t>
-  </si>
-  <si>
-    <t>renatorivasr@peru.com</t>
-  </si>
-  <si>
-    <t>Renato</t>
-  </si>
-  <si>
-    <t>administracion@institutoperuanochino.pe</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>auccallaperu@gmail.com</t>
-  </si>
-  <si>
-    <t>daniel_derteano14@hotmail.com</t>
-  </si>
-  <si>
-    <t>erlindaauccallamuje@gmail.com</t>
-  </si>
-  <si>
-    <t>Herlinda</t>
-  </si>
-  <si>
-    <t>henryjimenezch@gmail.com</t>
-  </si>
-  <si>
     <t>Henry</t>
   </si>
   <si>
-    <t>informes@institutoninadesign.com</t>
-  </si>
-  <si>
-    <t>Nila</t>
-  </si>
-  <si>
-    <t>presidencia@institutoperuanochino.pe</t>
-  </si>
-  <si>
-    <t>sedesurco0@gmail.com</t>
-  </si>
-  <si>
-    <t>giancarlo.villacorta@jmtoutdoors.com.pe</t>
-  </si>
-  <si>
-    <t>Giancarlo</t>
-  </si>
-  <si>
-    <t>humberto.aguinaga@jmtoutdoors.com.pe</t>
-  </si>
-  <si>
-    <t>Humberto</t>
-  </si>
-  <si>
-    <t>leska_17@hotmail.com</t>
-  </si>
-  <si>
-    <t>Leslie</t>
-  </si>
-  <si>
-    <t>marlonbarrantes074@gmail.com</t>
-  </si>
-  <si>
-    <t>Marlo</t>
-  </si>
-  <si>
-    <t>ojocreativompsac@gmail.com</t>
-  </si>
-  <si>
-    <t>Lierka</t>
-  </si>
-  <si>
-    <t>pyp@serccolorsac.com.pe</t>
-  </si>
-  <si>
-    <t>Noemi</t>
-  </si>
-  <si>
-    <t>vcandela@identidad-visual.com</t>
-  </si>
-  <si>
-    <t>ventas@identidad-visual.com</t>
-  </si>
-  <si>
-    <t>carritosdemercado@gmail.com</t>
-  </si>
-  <si>
-    <t>Miriam</t>
-  </si>
-  <si>
-    <t>controlremoto_mayer@hotmail.com</t>
-  </si>
-  <si>
-    <t>Azucena</t>
-  </si>
-  <si>
-    <t>info@royercars.com</t>
-  </si>
-  <si>
-    <t>j.aguirre@segurblock.pe</t>
-  </si>
-  <si>
-    <t>jagarciacassadof@cassado.com.pe</t>
-  </si>
-  <si>
-    <t>jgarciacassado@cassado.com.pe</t>
-  </si>
-  <si>
-    <t>liftrangerperu@gmail.com</t>
-  </si>
-  <si>
-    <t>Diego</t>
-  </si>
-  <si>
-    <t>marketing@mayer.pe</t>
-  </si>
-  <si>
-    <t>administracion@mobiliaindustrial.com.pe</t>
-  </si>
-  <si>
-    <t>Tania</t>
-  </si>
-  <si>
-    <t>apradoleon@yahoo.es</t>
-  </si>
-  <si>
-    <t>Aron</t>
-  </si>
-  <si>
-    <t>cprado@mobiliaindustrial.com.pe</t>
-  </si>
-  <si>
-    <t>Cristian</t>
-  </si>
-  <si>
-    <t>lucyadominguez0820@gmail.com</t>
-  </si>
-  <si>
-    <t>Lucia</t>
-  </si>
-  <si>
-    <t>p.merles@hotmail.com</t>
-  </si>
-  <si>
-    <t>pprado@mobiliaindustrial.com.pe</t>
-  </si>
-  <si>
-    <t>ventas@ecprefabricados.com</t>
-  </si>
-  <si>
-    <t>wlcing@hotmail.com</t>
-  </si>
-  <si>
     <t>Judith</t>
   </si>
   <si>
-    <t>andrewarcacano@jesuselmaestro.edu.pe</t>
-  </si>
-  <si>
-    <t>angelrdelacruz.08@gmail.com</t>
-  </si>
-  <si>
-    <t>Angel</t>
-  </si>
-  <si>
-    <t>ariaanthony123@gmail.com</t>
-  </si>
-  <si>
-    <t>Aldair</t>
-  </si>
-  <si>
-    <t>centro.contigo.psi@gmail.com</t>
-  </si>
-  <si>
-    <t>Paola</t>
-  </si>
-  <si>
-    <t>cesarbazalar@gmail.com</t>
-  </si>
-  <si>
-    <t>informes@tiempodeamar.pe</t>
-  </si>
-  <si>
     <t>Liliana</t>
   </si>
   <si>
-    <t>netcram.consultores@gmail.com</t>
-  </si>
-  <si>
-    <t>Leonardo</t>
-  </si>
-  <si>
-    <t>asalvador@adeserv.com.pe</t>
-  </si>
-  <si>
-    <t>Adelaida</t>
-  </si>
-  <si>
-    <t>atencionalcliente@adeserv.com.pe</t>
-  </si>
-  <si>
-    <t>Angelica</t>
-  </si>
-  <si>
-    <t>contabilidad@amaoutfitters.com</t>
-  </si>
-  <si>
-    <t>Tulio</t>
-  </si>
-  <si>
-    <t>ely_del@icloud.com</t>
-  </si>
-  <si>
     <t>Eliana</t>
   </si>
   <si>
-    <t>j.diaz@dyagroupsac.com</t>
-  </si>
-  <si>
-    <t>mery@adeserv.com.pe</t>
-  </si>
-  <si>
-    <t>Mery</t>
-  </si>
-  <si>
-    <t>vburga@entex.pe</t>
-  </si>
-  <si>
     <t>Victor</t>
   </si>
   <si>
-    <t>fguerrero@partnertech.pe</t>
+    <t>negocios@partnertech.pe</t>
+  </si>
+  <si>
+    <t>Alexandra</t>
+  </si>
+  <si>
+    <t>augusta.aljovin@esmeraldacorp.pe</t>
+  </si>
+  <si>
+    <t>Augusta</t>
+  </si>
+  <si>
+    <t>comex@costaseafood.com</t>
+  </si>
+  <si>
+    <t>Andres</t>
+  </si>
+  <si>
+    <t>empresa@costaseafood.com</t>
+  </si>
+  <si>
+    <t>Franz</t>
+  </si>
+  <si>
+    <t>fily.marquez@esmeraldacorp.pe</t>
+  </si>
+  <si>
+    <t>Fily</t>
+  </si>
+  <si>
+    <t>gerencia@ichibandelperu.pe</t>
+  </si>
+  <si>
+    <t>gisellamp@soalvida.com</t>
+  </si>
+  <si>
+    <t>Gisella</t>
+  </si>
+  <si>
+    <t>lorelita.arce@esmeraldacorp.pe</t>
+  </si>
+  <si>
+    <t>Eliot</t>
+  </si>
+  <si>
+    <t>miguel.aljovin@esmeraldacorp.pe</t>
+  </si>
+  <si>
+    <t>ponceemilio@soalvida.com</t>
+  </si>
+  <si>
+    <t>sales1@costaseafood.com</t>
+  </si>
+  <si>
+    <t>Herwin</t>
+  </si>
+  <si>
+    <t>bladmin@blasociados.com.pe</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>contabilidad@blasociados.com.pe</t>
+  </si>
+  <si>
+    <t>Rolando</t>
+  </si>
+  <si>
+    <t>excalib@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Óscar</t>
+  </si>
+  <si>
+    <t>ftello@grupovega.com</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>j.tuesta@prosedain.com</t>
+  </si>
+  <si>
+    <t>Jheferson</t>
+  </si>
+  <si>
+    <t>juliopedrocuzcano@gmail.com</t>
+  </si>
+  <si>
+    <t>lsdefreitas@blasociados.com.pe</t>
+  </si>
+  <si>
+    <t>maguardia@blasociados.com.pe</t>
+  </si>
+  <si>
+    <t>msilva@grupovega.com</t>
+  </si>
+  <si>
+    <t>ventas@prosedain.com</t>
+  </si>
+  <si>
+    <t>Brandon</t>
+  </si>
+  <si>
+    <t>canampa@triplexinv.com</t>
+  </si>
+  <si>
+    <t>dhernandez@hpdglass.com</t>
+  </si>
+  <si>
+    <t>Danessa</t>
+  </si>
+  <si>
+    <t>ehuaccharaqui@hpdglass.com</t>
+  </si>
+  <si>
+    <t>Emerita</t>
+  </si>
+  <si>
+    <t>emiranda@rabbitglass.com</t>
+  </si>
+  <si>
+    <t>Estefany</t>
+  </si>
+  <si>
+    <t>gen@triplexinv.com</t>
+  </si>
+  <si>
+    <t>Emperatriz</t>
+  </si>
+  <si>
+    <t>hsanchez@hpdglass.com</t>
+  </si>
+  <si>
+    <t>ismailyontas@gmail.com</t>
+  </si>
+  <si>
+    <t>Ismail</t>
+  </si>
+  <si>
+    <t>pquinones@hpdglass.com</t>
+  </si>
+  <si>
+    <t>Piera</t>
+  </si>
+  <si>
+    <t>rabbitglass@hotmail.com</t>
+  </si>
+  <si>
+    <t>yanila.098@gmail.com</t>
+  </si>
+  <si>
+    <t>Yasmin</t>
+  </si>
+  <si>
+    <t>7jarmell@gmail.com</t>
+  </si>
+  <si>
+    <t>bflores@nibray.pe</t>
+  </si>
+  <si>
+    <t>Briyan</t>
+  </si>
+  <si>
+    <t>francia181995@gmail.com</t>
+  </si>
+  <si>
+    <t>Nicoll</t>
+  </si>
+  <si>
+    <t>havellcar@hotmail.com</t>
+  </si>
+  <si>
+    <t>jarmell7@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jimmy</t>
+  </si>
+  <si>
+    <t>jfhuanco@gmail.com</t>
+  </si>
+  <si>
+    <t>mario.astengo@isdin.com</t>
+  </si>
+  <si>
+    <t>miguel2510@hotmail.com</t>
+  </si>
+  <si>
+    <t>miriam.vecco@isdin.com</t>
+  </si>
+  <si>
+    <t>Ramiro</t>
+  </si>
+  <si>
+    <t>rberrios@americanasolutions.com</t>
+  </si>
+  <si>
+    <t>Benita</t>
+  </si>
+  <si>
+    <t>agutierrez@thomasgreg.com.pe</t>
+  </si>
+  <si>
+    <t>beberli_anabel@hotmail.com</t>
+  </si>
+  <si>
+    <t>Beberli</t>
+  </si>
+  <si>
+    <t>cecilia@printystore.com.pe</t>
+  </si>
+  <si>
+    <t>Cecilia</t>
+  </si>
+  <si>
+    <t>jjimenez@editorialsalesiana.pe</t>
+  </si>
+  <si>
+    <t>jmachado@thomasgreg.com.pe</t>
+  </si>
+  <si>
+    <t>Joel</t>
+  </si>
+  <si>
+    <t>jsebas0417@gmail.com</t>
+  </si>
+  <si>
+    <t>k.moebius@protonmail.com</t>
+  </si>
+  <si>
+    <t>Klara</t>
+  </si>
+  <si>
+    <t>michael.carrillo.contable@gmail.com</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>oscar.ceballos.acosta@gmail.com</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>pjesusj@gmail.com</t>
+  </si>
+  <si>
+    <t>Jesús</t>
+  </si>
+  <si>
+    <t>adhirohid@gmail.com</t>
+  </si>
+  <si>
+    <t>Adolfo</t>
+  </si>
+  <si>
+    <t>alimentosbalanceadoshidalgo@gmail.com</t>
+  </si>
+  <si>
+    <t>Desiree</t>
+  </si>
+  <si>
+    <t>contabilidad@corina.com.pe</t>
+  </si>
+  <si>
+    <t>Leonidas</t>
+  </si>
+  <si>
+    <t>fallonagurto@gmail.com</t>
+  </si>
+  <si>
+    <t>Fallon</t>
+  </si>
+  <si>
+    <t>jessicaobesoc@gmail.com</t>
+  </si>
+  <si>
+    <t>jorgecavero1@hotmail.com</t>
+  </si>
+  <si>
+    <t>luiscanalle@cosaval.com</t>
+  </si>
+  <si>
+    <t>nzarepastor@gmail.com</t>
+  </si>
+  <si>
+    <t>rosmeryyulia@gmail.com</t>
+  </si>
+  <si>
+    <t>Yuliana</t>
+  </si>
+  <si>
+    <t>yasser.c.94@hotmail.com</t>
+  </si>
+  <si>
+    <t>Yasser</t>
+  </si>
+  <si>
+    <t>agarcia@airperu.com.pe</t>
+  </si>
+  <si>
+    <t>Alejandro</t>
+  </si>
+  <si>
+    <t>alvarocr.mqp@gmail.com</t>
+  </si>
+  <si>
+    <t>apchoque@willybusch.com.pe</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>asistente_iwb@willybush.com.pe</t>
+  </si>
+  <si>
+    <t>Susana</t>
+  </si>
+  <si>
+    <t>derechb@willybusch.com.pe</t>
+  </si>
+  <si>
+    <t>Derech</t>
+  </si>
+  <si>
+    <t>dmechan@willybusch.com.pe</t>
+  </si>
+  <si>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>gerencia@perumaquinarias-co.pe</t>
+  </si>
+  <si>
+    <t>icaceres@trackengineslab.com</t>
+  </si>
+  <si>
+    <t>Isrrael</t>
+  </si>
+  <si>
+    <t>john1478@hotmail.com</t>
+  </si>
+  <si>
+    <t>Zoraida</t>
+  </si>
+  <si>
+    <t>johncito.revagas@gmail.com</t>
+  </si>
+  <si>
+    <t>caylas@scrconsultores.com.pe</t>
+  </si>
+  <si>
+    <t>corporativo@enlacetraducciones.com</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>finanzas@enlacetraducciones.com</t>
+  </si>
+  <si>
+    <t>francisco.roman@ascex.com.pe</t>
+  </si>
+  <si>
+    <t>franco@linkolanguages.com</t>
+  </si>
+  <si>
+    <t>informes@scrconsultores.com.pe</t>
+  </si>
+  <si>
+    <t>mvera73@yahoo.es</t>
+  </si>
+  <si>
+    <t>patricia@linkolanguages.com</t>
+  </si>
+  <si>
+    <t>sonia@effetha.com</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>ssequeiros@hotmail.com</t>
+  </si>
+  <si>
+    <t>enora@laparmesana.com</t>
+  </si>
+  <si>
+    <t>Rosanna</t>
+  </si>
+  <si>
+    <t>enriconora@hotmail.com</t>
+  </si>
+  <si>
+    <t>Enrico</t>
+  </si>
+  <si>
+    <t>exportaciones@envafronperu.com</t>
+  </si>
+  <si>
+    <t>gerencia@biofrutos.pe</t>
+  </si>
+  <si>
+    <t>Eufemia</t>
+  </si>
+  <si>
+    <t>gerencia@sansen.com.pe</t>
+  </si>
+  <si>
+    <t>informes@fabricadefideoseltriunfo.com</t>
+  </si>
+  <si>
+    <t>Evelyn</t>
+  </si>
+  <si>
+    <t>informes@fideoseltriunfo.com.pe</t>
+  </si>
+  <si>
+    <t>lnavarro@biofrutos.pe</t>
+  </si>
+  <si>
+    <t>sansenperu@hotmail.com</t>
+  </si>
+  <si>
+    <t>Mara</t>
+  </si>
+  <si>
+    <t>ventas@laparmesana.com</t>
+  </si>
+  <si>
+    <t>administracion.ti@gkmtechnology.com.pe</t>
+  </si>
+  <si>
+    <t>Damaris</t>
+  </si>
+  <si>
+    <t>administracion@datamundo.pe</t>
+  </si>
+  <si>
+    <t>Janina</t>
+  </si>
+  <si>
+    <t>asistente.contable1@netcorporate.net</t>
+  </si>
+  <si>
+    <t>Oriana</t>
+  </si>
+  <si>
+    <t>asistente.marketing1@netcorporate.net</t>
+  </si>
+  <si>
+    <t>Deyna</t>
+  </si>
+  <si>
+    <t>bianca.trejo@netcorporate.net</t>
+  </si>
+  <si>
+    <t>Bianca</t>
+  </si>
+  <si>
+    <t>gian.majuan@gkmtechnology.com.pe</t>
+  </si>
+  <si>
+    <t>Gian</t>
+  </si>
+  <si>
+    <t>kmott@netcorporate.net</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>nelly.anaya@netcorporate.net</t>
+  </si>
+  <si>
+    <t>Nelly</t>
+  </si>
+  <si>
+    <t>rosariosalazar86@hotmail.com</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>ventas1@gkmtechnology.com.pe</t>
+  </si>
+  <si>
+    <t>Efrain</t>
+  </si>
+  <si>
+    <t>andrea@ecuapack.com</t>
+  </si>
+  <si>
+    <t>bramirez@mvelarde.com</t>
+  </si>
+  <si>
+    <t>Bertha</t>
+  </si>
+  <si>
+    <t>david.arias@palagroperu.com</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>edgardo.perez@grupoafaperu.com</t>
+  </si>
+  <si>
+    <t>Edgardo</t>
+  </si>
+  <si>
+    <t>emilmdd@gmail.com</t>
+  </si>
+  <si>
+    <t>Emil</t>
+  </si>
+  <si>
+    <t>emilmdd@hotmail.com</t>
+  </si>
+  <si>
+    <t>Einstein</t>
+  </si>
+  <si>
+    <t>johan.araujo1985@gmail.com</t>
+  </si>
+  <si>
+    <t>Johan</t>
+  </si>
+  <si>
+    <t>jose.fernandez@grupoafaperu.com</t>
+  </si>
+  <si>
+    <t>maxvela@mvelarde.com</t>
+  </si>
+  <si>
+    <t>melissa.mendieta@palagroperu.com</t>
+  </si>
+  <si>
+    <t>Melissa</t>
+  </si>
+  <si>
+    <t>carbonela@iata.org</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>cdiaz@grupoargenia.com</t>
+  </si>
+  <si>
+    <t>gcanchaya@grupoargenia.com</t>
+  </si>
+  <si>
+    <t>Genesis</t>
+  </si>
+  <si>
+    <t>gconejo@smmpp.org.pe</t>
+  </si>
+  <si>
+    <t>Guissela</t>
+  </si>
+  <si>
+    <t>gestiondelasociado@smmmpp.org.pe</t>
+  </si>
+  <si>
+    <t>luis.solis@smmpp.org.pe</t>
+  </si>
+  <si>
+    <t>rossim@iata.org</t>
+  </si>
+  <si>
+    <t>Frankz</t>
+  </si>
+  <si>
+    <t>rramos@grupoargenia.com</t>
+  </si>
+  <si>
+    <t>Ronald</t>
+  </si>
+  <si>
+    <t>snoasc@speedy.com.pe</t>
+  </si>
+  <si>
+    <t>valonso@grupoargenia.com</t>
+  </si>
+  <si>
+    <t>cotizaciones@omegaestructuras.com</t>
+  </si>
+  <si>
+    <t>Terry</t>
+  </si>
+  <si>
+    <t>giannina.dangelo@crowe.pe</t>
+  </si>
+  <si>
+    <t>Giannina</t>
+  </si>
+  <si>
+    <t>hugo@somoshta.com</t>
+  </si>
+  <si>
+    <t>jose.gandolfo50@gmail.com</t>
+  </si>
+  <si>
+    <t>karincadenaseventos@gmail.com</t>
+  </si>
+  <si>
+    <t>Karin</t>
+  </si>
+  <si>
+    <t>mon_jenriquez@hotmail.com</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>omega.estructuras@gmail.com</t>
+  </si>
+  <si>
+    <t>Elias</t>
+  </si>
+  <si>
+    <t>ricardo@rblproducciones.com</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>rodrigo@summitvisuals.pe</t>
+  </si>
+  <si>
+    <t>Rodrigo</t>
+  </si>
+  <si>
+    <t>susanam@rblproducciones.com</t>
+  </si>
+  <si>
+    <t>Naldy</t>
+  </si>
+  <si>
+    <t>alancanon10@gmail.com</t>
+  </si>
+  <si>
+    <t>amalia.huaman@panoramahogar.com</t>
+  </si>
+  <si>
+    <t>Amalia</t>
+  </si>
+  <si>
+    <t>betsy.tapia@panoramahogar.com</t>
+  </si>
+  <si>
+    <t>Betsy</t>
+  </si>
+  <si>
+    <t>eduoc18@gmail.com</t>
+  </si>
+  <si>
+    <t>Rivelino</t>
+  </si>
+  <si>
+    <t>eleazar.tapia@panoramahogar.com</t>
+  </si>
+  <si>
+    <t>Eleazar</t>
+  </si>
+  <si>
+    <t>jortizchinchay@gmail.com</t>
+  </si>
+  <si>
+    <t>ltapia@panoramadistribuidores.com</t>
+  </si>
+  <si>
+    <t>oscarortega@centrosuizorelojero.com.pe</t>
+  </si>
+  <si>
+    <t>rrtapia1@hotmail.com</t>
+  </si>
+  <si>
+    <t>Roxana</t>
+  </si>
+  <si>
+    <t>vvigoibarra@gmail.com</t>
+  </si>
+  <si>
+    <t>ahuarcaya@corpsps.com</t>
+  </si>
+  <si>
+    <t>carla.pacchioni@caoyco.com</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>eliana.davila@caoyco.com</t>
+  </si>
+  <si>
+    <t>gerencia@caoyco.com</t>
+  </si>
+  <si>
+    <t>norma.uribe@caoyco.com</t>
+  </si>
+  <si>
+    <t>Norma</t>
+  </si>
+  <si>
+    <t>ohuarcaya@sps.com.pe</t>
+  </si>
+  <si>
+    <t>presidencia@camaradecomerciomipyme.com</t>
+  </si>
+  <si>
+    <t>Graciela</t>
+  </si>
+  <si>
+    <t>recoji@gmail.com</t>
+  </si>
+  <si>
+    <t>victorhmadridpaz@gmail.com</t>
+  </si>
+  <si>
+    <t>yrodriguez@cuantica.com.pe</t>
+  </si>
+  <si>
+    <t>aku@sbtrading.net</t>
+  </si>
+  <si>
+    <t>Josefina</t>
+  </si>
+  <si>
+    <t>carlos.ramosl@miniso.pe</t>
+  </si>
+  <si>
+    <t>cintia.huaman@miniso.pe</t>
+  </si>
+  <si>
+    <t>Cintia</t>
+  </si>
+  <si>
+    <t>dis_com_juanita@hotmail.com</t>
+  </si>
+  <si>
+    <t>Juana</t>
+  </si>
+  <si>
+    <t>emaritzahreynoso@gmail.com</t>
+  </si>
+  <si>
+    <t>informes@sbtrading.com.pe</t>
+  </si>
+  <si>
+    <t>informes@sbtrading.net</t>
+  </si>
+  <si>
+    <t>javiermonrroy50391@gmail.com</t>
+  </si>
+  <si>
+    <t>roberto.prado@miniso.com.mx</t>
+  </si>
+  <si>
+    <t>siulihugo@yahoo.com</t>
+  </si>
+  <si>
+    <t>Jau</t>
+  </si>
+  <si>
+    <t>aroman@aytcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Albertini</t>
+  </si>
+  <si>
+    <t>coop.emunicipal408@hotmail.com</t>
+  </si>
+  <si>
+    <t>gsanchez@elbosque.org.pe</t>
+  </si>
+  <si>
+    <t>guillermo.garciaurrutia@aytcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Guillermo</t>
+  </si>
+  <si>
+    <t>ines.garcia1872@gmail.com</t>
+  </si>
+  <si>
+    <t>Ines</t>
+  </si>
+  <si>
+    <t>naomi.arakaki@aytcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Naomi</t>
+  </si>
+  <si>
+    <t>sergio@elbosque.org.pe</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>vanexxa.e.u82@hotmail.com</t>
+  </si>
+  <si>
+    <t>ventascorporativas@elpinodecardal.com</t>
+  </si>
+  <si>
+    <t>vtorrejon@aytcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Helen</t>
+  </si>
+  <si>
+    <t>anpaico@gmail.com</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>atilio@speedy.com.pe</t>
+  </si>
+  <si>
+    <t>Atilio</t>
+  </si>
+  <si>
+    <t>cuzcano.10.98@gmail.com</t>
+  </si>
+  <si>
+    <t>Maricarmen</t>
+  </si>
+  <si>
+    <t>emi.mendoza.rodriguez@gmail.com</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>evidal@vidalfoods.com</t>
+  </si>
+  <si>
+    <t>Elio</t>
+  </si>
+  <si>
+    <t>j.castilla@allfoodselected.com</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>kennymendozarodriguez@gmail.com</t>
+  </si>
+  <si>
+    <t>Kenny</t>
+  </si>
+  <si>
+    <t>mvilcarino@gmail.com</t>
+  </si>
+  <si>
+    <t>Maribel</t>
+  </si>
+  <si>
+    <t>rochyvi@speedy.com.pe</t>
+  </si>
+  <si>
+    <t>ventas@allfoodselected.com</t>
+  </si>
+  <si>
+    <t>Cinthya</t>
+  </si>
+  <si>
+    <t>a.caballero@mpinstitucional.com</t>
+  </si>
+  <si>
+    <t>carbaiza@edipesa.com.pe</t>
+  </si>
+  <si>
+    <t>d.caballero@mpinstitucional.com</t>
+  </si>
+  <si>
+    <t>Daniela</t>
+  </si>
+  <si>
+    <t>inversionesnikkomiranda@inmisac.com</t>
+  </si>
+  <si>
+    <t>jdiaz@edipesa.com.pe</t>
+  </si>
+  <si>
+    <t>k.delaguila@mpinstitucional.com</t>
+  </si>
+  <si>
+    <t>Karina</t>
+  </si>
+  <si>
+    <t>l.abad@mpinstitucional.com</t>
+  </si>
+  <si>
+    <t>Lisseth</t>
+  </si>
+  <si>
+    <t>mrios@coroimport.com</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>raurrunaga@coroimport.com</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>rurrunaga@coroimport.com</t>
   </si>
 </sst>
 </file>
@@ -1437,1550 +1476,1545 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>334</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="B63" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="B71" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="B72" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="B73" t="s">
-        <v>104</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="B74" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B80" t="s">
-        <v>145</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B81" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B82" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="B83" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B85" t="s">
-        <v>142</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="B87" t="s">
-        <v>156</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="B89" t="s">
-        <v>159</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B90" t="s">
-        <v>161</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B91" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="B92" t="s">
-        <v>165</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B93" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B94" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B95" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="B96" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B97" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="B99" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="B100" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="B101" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="B102" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="B103" t="s">
-        <v>184</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="B104" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="B106" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
-        <v>61</v>
+        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="B109" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="B111" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="B112" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B113" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="B114" t="s">
-        <v>203</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="B115" t="s">
-        <v>102</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="B116" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="B117" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="B118" t="s">
-        <v>209</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B119" t="s">
-        <v>57</v>
+        <v>233</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B120" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="B121" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B122" t="s">
-        <v>215</v>
+        <v>41</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B123" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B124" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="B125" t="s">
-        <v>221</v>
+        <v>68</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="B126" t="s">
-        <v>223</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="B127" t="s">
-        <v>172</v>
+        <v>245</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B128" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B129" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="B130" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B131" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="B132" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B133" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="B134" t="s">
-        <v>44</v>
+        <v>258</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="B135" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="B136" t="s">
-        <v>102</v>
+        <v>262</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="B137" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="B138" t="s">
-        <v>243</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="B139" t="s">
-        <v>245</v>
+        <v>39</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="B140" t="s">
-        <v>247</v>
+        <v>123</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B141" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="B142" t="s">
-        <v>251</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="B143" t="s">
-        <v>253</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B144" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B145" t="s">
-        <v>212</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B146" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="B147" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B148" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="B149" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B150" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B151" t="s">
-        <v>266</v>
+        <v>41</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B152" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B153" t="s">
-        <v>61</v>
+        <v>285</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B155" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B156" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B157" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B158" t="s">
-        <v>278</v>
+        <v>68</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B159" t="s">
-        <v>280</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B160" t="s">
-        <v>282</v>
+        <v>33</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B161" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B162" t="s">
-        <v>104</v>
+        <v>297</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B163" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B164" t="s">
-        <v>288</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B166" t="s">
-        <v>44</v>
+        <v>303</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B167" t="s">
-        <v>18</v>
+        <v>305</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B168" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B169" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B170" t="s">
-        <v>152</v>
+        <v>28</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B171" t="s">
-        <v>297</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B172" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B173" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B174" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B175" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B176" t="s">
-        <v>247</v>
+        <v>321</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B177" t="s">
-        <v>245</v>
+        <v>323</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B178" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="B179" t="s">
-        <v>172</v>
+        <v>327</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B180" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="B181" t="s">
-        <v>313</v>
+        <v>269</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B182" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B183" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="B184" t="s">
-        <v>318</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="B185" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B186" t="s">
-        <v>322</v>
+        <v>34</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B187" t="s">
-        <v>324</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B188" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B189" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B190" t="s">
-        <v>18</v>
+        <v>344</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B191" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B192" t="s">
-        <v>333</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>334</v>
+        <v>42</v>
       </c>
       <c r="B193" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
-    <hyperlink ref="A193" r:id="rId2" xr:uid="{2A60B044-2956-4470-9026-8142D3E23CF9}"/>
-    <hyperlink ref="A7" r:id="rId3" display="ncardozo@olssa.com.pe" xr:uid="{7E44E4A6-0531-4587-83FB-2389671C49B6}"/>
-    <hyperlink ref="A6" r:id="rId4" display="hmelgarejo@partnertech.pe" xr:uid="{1A016AB9-0375-4056-B892-A261D4BFC8BF}"/>
-    <hyperlink ref="A5" r:id="rId5" display="fguerrero@olssa.com.pe" xr:uid="{228B21B2-F6D7-46DD-81B4-3C9AD96DA160}"/>
-    <hyperlink ref="A4" r:id="rId6" display="acardozo@partnertech.pe" xr:uid="{F1971FD1-7C25-438C-B0AA-563448125D87}"/>
-    <hyperlink ref="A3" r:id="rId7" display="negocios@partnertech.pe" xr:uid="{3D2C3250-E20D-4CD9-B8FC-9906793DA48E}"/>
+    <hyperlink ref="A193" r:id="rId2" xr:uid="{993285C6-CD98-47C2-8220-969A27FD1A05}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raulu\OneDrive\Documentos\Repositorios\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DE1EEF-CEFF-48B5-859F-03F326E1AF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C5BBA7-B69D-42E8-B163-0997C9C3B7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>correo</t>
   </si>
@@ -45,6 +45,12 @@
   </si>
   <si>
     <t>Alexandra</t>
+  </si>
+  <si>
+    <t>fguerrero@partnertech.pe</t>
+  </si>
+  <si>
+    <t>Franco</t>
   </si>
 </sst>
 </file>
@@ -451,7 +457,12 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -472,6 +483,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{E5116652-71CB-49E1-AA48-3CFD6BF94903}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raulu\OneDrive\Documentos\Repositorios\Correos-Masivos-Partner-Tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C5BBA7-B69D-42E8-B163-0997C9C3B7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB181D4E-167B-4BBF-B951-7A0298817497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>correo</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Franco</t>
+  </si>
+  <si>
+    <t>acardozo@partnertech.pe</t>
   </si>
 </sst>
 </file>
@@ -465,7 +468,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -484,6 +492,7 @@
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{E5116652-71CB-49E1-AA48-3CFD6BF94903}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{E932B598-6476-41B7-B673-B791A9B630CB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB181D4E-167B-4BBF-B951-7A0298817497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272BCF29-F21B-4108-9C39-7D44B963D0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="352">
   <si>
     <t>correo</t>
   </si>
@@ -47,13 +47,1048 @@
     <t>Alexandra</t>
   </si>
   <si>
-    <t>fguerrero@partnertech.pe</t>
-  </si>
-  <si>
-    <t>Franco</t>
-  </si>
-  <si>
-    <t>acardozo@partnertech.pe</t>
+    <t>abdul.carrillo@gescel.com</t>
+  </si>
+  <si>
+    <t>Abdul</t>
+  </si>
+  <si>
+    <t>an_ie07@hotmail.com</t>
+  </si>
+  <si>
+    <t>Rocio</t>
+  </si>
+  <si>
+    <t>arturo.quiroz@globalelectric.pe</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>ernesto.velit@ferreyros.com.pe</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>gerente.operaciones@romaxfm.com</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>gestor.operaciones@romaxfm.com</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>miguel.quispe@gescel.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>nelly.velez@ferreyros.com.pe</t>
+  </si>
+  <si>
+    <t>Nelly</t>
+  </si>
+  <si>
+    <t>peru@cie.com.py</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>rafael.bernal@globalelectric.pe</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>sandra.talledo@gescel.com</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>victor.cardenas@cie.compy</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>alfonso.chavez@gea-westfalia.com.pe</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>contabilidad@izacorp-kransysteme.com.pe</t>
+  </si>
+  <si>
+    <t>Sheyla</t>
+  </si>
+  <si>
+    <t>dleocadio@izacorp-kransysteme.com.pe</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>jpcavero@lcturbo.com.pe</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>lcturbo@qnet.com.pe</t>
+  </si>
+  <si>
+    <t>mchavarria@detecin.com</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>mponce@mym.com.pe</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>ppacheco@mym.com.pe</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>rosario.galvez@gea-westfalia.com.pe</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>sponce@mym.com.pe</t>
+  </si>
+  <si>
+    <t>Stephanie</t>
+  </si>
+  <si>
+    <t>vquispe@izacorp-kransysteme.com.pe</t>
+  </si>
+  <si>
+    <t>Veronica</t>
+  </si>
+  <si>
+    <t>contabilidad@dargui.com</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>contabilidad@lacandelariaperu.com</t>
+  </si>
+  <si>
+    <t>Yissela</t>
+  </si>
+  <si>
+    <t>contabilidad@overseasperu.com</t>
+  </si>
+  <si>
+    <t>Roxana</t>
+  </si>
+  <si>
+    <t>darenas@lacandelariaperu.com</t>
+  </si>
+  <si>
+    <t>Dino</t>
+  </si>
+  <si>
+    <t>dargui.alfredo@dargui.com</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>dargui.eden@dargui.com</t>
+  </si>
+  <si>
+    <t>Eden</t>
+  </si>
+  <si>
+    <t>dargui.elizabeth@dargui.com</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>eventos@lacandelariaperu.com</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>jarenas@lacandelariaperu.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>jordan.chaviguri@gmail.com</t>
+  </si>
+  <si>
+    <t>Luiggi</t>
+  </si>
+  <si>
+    <t>yeni.morales@overseasperu.com</t>
+  </si>
+  <si>
+    <t>Yeni</t>
+  </si>
+  <si>
+    <t>administracion@amazingcyg.pe</t>
+  </si>
+  <si>
+    <t>Giovanna</t>
+  </si>
+  <si>
+    <t>amazingcyg@gmail.com</t>
+  </si>
+  <si>
+    <t>central@jpsolucionesperu.com</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>cobranzas@amazingcyg.pe</t>
+  </si>
+  <si>
+    <t>Jesús</t>
+  </si>
+  <si>
+    <t>contabilidad@amazingcyg.pe</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>efrain.huaman@progascon.com</t>
+  </si>
+  <si>
+    <t>Efrain</t>
+  </si>
+  <si>
+    <t>importacion@amazingcyg.pe</t>
+  </si>
+  <si>
+    <t>Katherin</t>
+  </si>
+  <si>
+    <t>jguillermo@jpsolucionesperu.com</t>
+  </si>
+  <si>
+    <t>mpanduro@tisgasequipments.com.pe</t>
+  </si>
+  <si>
+    <t>Mariela</t>
+  </si>
+  <si>
+    <t>nancy.bernardo@progascon.com</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>rvalencia@tisgas.pe</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>administracion@sistema-automotriz.pe</t>
+  </si>
+  <si>
+    <t>Sabine</t>
+  </si>
+  <si>
+    <t>asistencia_proyectos@qfleetperu.com</t>
+  </si>
+  <si>
+    <t>Kristell</t>
+  </si>
+  <si>
+    <t>contabilidad@sistema-automotriz.pe</t>
+  </si>
+  <si>
+    <t>Pierre</t>
+  </si>
+  <si>
+    <t>gcomercializacion@seman.com.pe</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>jacky-689@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jackelin</t>
+  </si>
+  <si>
+    <t>jaquelineme@qellpu.com</t>
+  </si>
+  <si>
+    <t>Jaqueline</t>
+  </si>
+  <si>
+    <t>mferro@sistema-automotriz.pe</t>
+  </si>
+  <si>
+    <t>Karsten</t>
+  </si>
+  <si>
+    <t>oscarrq@qellpu.com</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>oscarsoto112@hotmail.com</t>
+  </si>
+  <si>
+    <t>proyectos@qfleetperu.com</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>williamrr@qellpu.com</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>administracion@oftalmologoscontreras.com</t>
+  </si>
+  <si>
+    <t>Cecilia</t>
+  </si>
+  <si>
+    <t>cleidymendoza1988@gmail.com</t>
+  </si>
+  <si>
+    <t>Cleidy</t>
+  </si>
+  <si>
+    <t>fdelacruz@opticasunjhana.com</t>
+  </si>
+  <si>
+    <t>figueroanunezelmer@gmail.com</t>
+  </si>
+  <si>
+    <t>Elmer</t>
+  </si>
+  <si>
+    <t>hassiel.solucionescreativas@gmail.com</t>
+  </si>
+  <si>
+    <t>Ruth</t>
+  </si>
+  <si>
+    <t>holafutureeyes@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>ivanadonde21@gmail.com</t>
+  </si>
+  <si>
+    <t>Hiban</t>
+  </si>
+  <si>
+    <t>ivonleonarro@hotmail.com</t>
+  </si>
+  <si>
+    <t>Yvon</t>
+  </si>
+  <si>
+    <t>jbaraybarv.quality@gmail.com</t>
+  </si>
+  <si>
+    <t>Janell</t>
+  </si>
+  <si>
+    <t>lsalazar@opticasunjhana.com</t>
+  </si>
+  <si>
+    <t>Leniz</t>
+  </si>
+  <si>
+    <t>rrhh@oftalmologoscontreras.com</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>analizvarui@gmail.com</t>
+  </si>
+  <si>
+    <t>Flor</t>
+  </si>
+  <si>
+    <t>compras@newonemq.com</t>
+  </si>
+  <si>
+    <t>Yuri</t>
+  </si>
+  <si>
+    <t>dramirez@panamericantrading.com.pe</t>
+  </si>
+  <si>
+    <t>Dora</t>
+  </si>
+  <si>
+    <t>egaceperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Edilberto</t>
+  </si>
+  <si>
+    <t>juan.vasquez@maxlimsrl.com.pe</t>
+  </si>
+  <si>
+    <t>mherrada@panamericantrading.com.pe</t>
+  </si>
+  <si>
+    <t>panamtra@panamericantrading.com.pe</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>panamtra@panamericantradingsa.net</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>tocrospoma@panamericantradingsa.net</t>
+  </si>
+  <si>
+    <t>Toledo</t>
+  </si>
+  <si>
+    <t>ventas@newonemq.com</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>vperez@artidororodriguez.com</t>
+  </si>
+  <si>
+    <t>alfredo.salgado@marcfieldsll.com</t>
+  </si>
+  <si>
+    <t>edgarcz@motosracing.pe</t>
+  </si>
+  <si>
+    <t>Digna</t>
+  </si>
+  <si>
+    <t>elvacc@motosracing.pe</t>
+  </si>
+  <si>
+    <t>Elva</t>
+  </si>
+  <si>
+    <t>javier.erausquin@latamtradecapital.com</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>jponcedeleon@supraperu.com</t>
+  </si>
+  <si>
+    <t>jserna@supraperu.com</t>
+  </si>
+  <si>
+    <t>Janeth</t>
+  </si>
+  <si>
+    <t>mbohorquezdelportal@gmail.com</t>
+  </si>
+  <si>
+    <t>rarroyo@supraperu.com</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>rmazzini@marcfieldsllc.com</t>
+  </si>
+  <si>
+    <t>Renzo</t>
+  </si>
+  <si>
+    <t>rosariosc@motosracing.pe</t>
+  </si>
+  <si>
+    <t>smf2183@columbia.edu</t>
+  </si>
+  <si>
+    <t>Sebastian</t>
+  </si>
+  <si>
+    <t>a.morales@ficeminsac.com</t>
+  </si>
+  <si>
+    <t>Enith</t>
+  </si>
+  <si>
+    <t>araujorepresentaciones@hotmail.es</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>fszenes@siersac.com</t>
+  </si>
+  <si>
+    <t>geomembranaseirl@hotmail.com</t>
+  </si>
+  <si>
+    <t>Doris</t>
+  </si>
+  <si>
+    <t>gerencia@vaneco.com.pe</t>
+  </si>
+  <si>
+    <t>h.aguirre@ficeminsac.com</t>
+  </si>
+  <si>
+    <t>john.araujo@ucsp.edu.pe</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>mmacetas@vaneco.com.pe</t>
+  </si>
+  <si>
+    <t>Matilde</t>
+  </si>
+  <si>
+    <t>pedrod@vaneco.com.pe</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>rrhh@hotmail.com</t>
+  </si>
+  <si>
+    <t>sistemas.integrados.calidad@siersac.com</t>
+  </si>
+  <si>
+    <t>a.kohatsu@moblesoluciones.com</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>abel.tairo@hotmail.com</t>
+  </si>
+  <si>
+    <t>bent_modulacion_integral@hotmail.com</t>
+  </si>
+  <si>
+    <t>Benito</t>
+  </si>
+  <si>
+    <t>carlos.irupailla@mueblesandina.com</t>
+  </si>
+  <si>
+    <t>d.reyes@moblesoluciones.com</t>
+  </si>
+  <si>
+    <t>Adita</t>
+  </si>
+  <si>
+    <t>eisenhower.tairo@gmail.com</t>
+  </si>
+  <si>
+    <t>Arquimedes</t>
+  </si>
+  <si>
+    <t>fernanda.almeyda@mueblesandina.com</t>
+  </si>
+  <si>
+    <t>miguelirupailla@tablemas.com</t>
+  </si>
+  <si>
+    <t>muebles-formesac@hotmail.com</t>
+  </si>
+  <si>
+    <t>Maxima</t>
+  </si>
+  <si>
+    <t>scardenas@kvmperu.com</t>
+  </si>
+  <si>
+    <t>Silva</t>
+  </si>
+  <si>
+    <t>vidrieria_quezada@hotmail.com</t>
+  </si>
+  <si>
+    <t>Josefina</t>
+  </si>
+  <si>
+    <t>administracion@gmgsac.com</t>
+  </si>
+  <si>
+    <t>administracion@melyac.com</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>contempo@terra.com.pe</t>
+  </si>
+  <si>
+    <t>detarqui_proyectos@gmail.com</t>
+  </si>
+  <si>
+    <t>Susana</t>
+  </si>
+  <si>
+    <t>julio.mena@melyac.com</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>mespinoza@imsa.com.pe</t>
+  </si>
+  <si>
+    <t>mvalderrama@imsa.com.pe</t>
+  </si>
+  <si>
+    <t>Maribel</t>
+  </si>
+  <si>
+    <t>proyectos@gmgsac.com</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>recursoshumanos@imsa.com.pe</t>
+  </si>
+  <si>
+    <t>Leslie</t>
+  </si>
+  <si>
+    <t>susa.floresojeda@gmail.es</t>
+  </si>
+  <si>
+    <t>Hipólita</t>
+  </si>
+  <si>
+    <t>vcarranza@vicarsoluciones.com.pe</t>
+  </si>
+  <si>
+    <t>Sintia</t>
+  </si>
+  <si>
+    <t>apenarroya@nalandaglobal.com</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>asistentemkt@taxigreen.com.pe</t>
+  </si>
+  <si>
+    <t>Melanie</t>
+  </si>
+  <si>
+    <t>corporativo@bvientos.com.pe</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
+    <t>darylrobalino99@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>gerencia@easycard.com.ec</t>
+  </si>
+  <si>
+    <t>gerencia@taxigreen.com.pe</t>
+  </si>
+  <si>
+    <t>Augusto</t>
+  </si>
+  <si>
+    <t>lmuzio@villamuzio.com</t>
+  </si>
+  <si>
+    <t>Luigi</t>
+  </si>
+  <si>
+    <t>lucho.7468@hotmail.com</t>
+  </si>
+  <si>
+    <t>mperalta@taxigreen.com.pe</t>
+  </si>
+  <si>
+    <t>novoataxi@novoataxi.com.pe</t>
+  </si>
+  <si>
+    <t>peru@easycard.com.ec</t>
+  </si>
+  <si>
+    <t>angelica.sandoval@brindon-bekaert.com</t>
+  </si>
+  <si>
+    <t>Mirko</t>
+  </si>
+  <si>
+    <t>apalacios@procables.com</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>asandoval@procables.com</t>
+  </si>
+  <si>
+    <t>cealvarez@celsa.com.pe</t>
+  </si>
+  <si>
+    <t>cmalvarez@celsa.com.pe</t>
+  </si>
+  <si>
+    <t>esuarez@procables.com</t>
+  </si>
+  <si>
+    <t>Edgard</t>
+  </si>
+  <si>
+    <t>jmartinez@procables.com</t>
+  </si>
+  <si>
+    <t>mbarahona@celsa.com.pe</t>
+  </si>
+  <si>
+    <t>mbeltran@procables.com</t>
+  </si>
+  <si>
+    <t>patricia.bravo@bridon-bekaert.com</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>rguevara@procables.com</t>
+  </si>
+  <si>
+    <t>Regina</t>
+  </si>
+  <si>
+    <t>administradores@zamerperu.com</t>
+  </si>
+  <si>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>christopher.hurtado@adnselection.com</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>cvignolo@conserh.com</t>
+  </si>
+  <si>
+    <t>dmorales@zamerperu.com</t>
+  </si>
+  <si>
+    <t>Deisy</t>
+  </si>
+  <si>
+    <t>grover@inngresa.com</t>
+  </si>
+  <si>
+    <t>Grover</t>
+  </si>
+  <si>
+    <t>ingry113@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ingrid</t>
+  </si>
+  <si>
+    <t>msoto@conserh.com</t>
+  </si>
+  <si>
+    <t>Marisa</t>
+  </si>
+  <si>
+    <t>nlopez@inngresa.com</t>
+  </si>
+  <si>
+    <t>Nioyesli</t>
+  </si>
+  <si>
+    <t>notiene@hotmail.com</t>
+  </si>
+  <si>
+    <t>nvalverde@talentohumanoperu.pe</t>
+  </si>
+  <si>
+    <t>Noris</t>
+  </si>
+  <si>
+    <t>walner79@hotmail.com</t>
+  </si>
+  <si>
+    <t>Walner</t>
+  </si>
+  <si>
+    <t>administracion@aglambayeque.com</t>
+  </si>
+  <si>
+    <t>asistente_gerencia@carydersac.com</t>
+  </si>
+  <si>
+    <t>Janella</t>
+  </si>
+  <si>
+    <t>diana.mrnn@gmail.com</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>diegofebrero@gmail.com</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>elias.x@carydersac.com</t>
+  </si>
+  <si>
+    <t>Elias</t>
+  </si>
+  <si>
+    <t>felixngh@outlook.com</t>
+  </si>
+  <si>
+    <t>jpardo@carydersac.com</t>
+  </si>
+  <si>
+    <t>rcotrina@carydersac.com</t>
+  </si>
+  <si>
+    <t>Rider</t>
+  </si>
+  <si>
+    <t>rportillo@mafrox.com</t>
+  </si>
+  <si>
+    <t>Renato</t>
+  </si>
+  <si>
+    <t>rruiz@ideacreativa.pe</t>
+  </si>
+  <si>
+    <t>Reimer</t>
+  </si>
+  <si>
+    <t>yabregu@carydersac.com</t>
+  </si>
+  <si>
+    <t>Denissi</t>
+  </si>
+  <si>
+    <t>a.torres@beatwaveperu.com</t>
+  </si>
+  <si>
+    <t>Aldo</t>
+  </si>
+  <si>
+    <t>anahi@maca-nudo.com</t>
+  </si>
+  <si>
+    <t>Anahi</t>
+  </si>
+  <si>
+    <t>b.galarza@beatwaveperu.com</t>
+  </si>
+  <si>
+    <t>Bertha</t>
+  </si>
+  <si>
+    <t>carmenantoniacamacgallardo@gmail.com</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>eventos@estradosperu.com</t>
+  </si>
+  <si>
+    <t>Wualter</t>
+  </si>
+  <si>
+    <t>luis.angel.bravo.adriano@gmail.com</t>
+  </si>
+  <si>
+    <t>rebecameza.2022@hotmail.com</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>rodolfoheredia0@gmail.com</t>
+  </si>
+  <si>
+    <t>Rodolfo</t>
+  </si>
+  <si>
+    <t>vanesa.lazaro4@gmail.com</t>
+  </si>
+  <si>
+    <t>Vanesa</t>
+  </si>
+  <si>
+    <t>ventasnovumpublicidad@gmail.com</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>ventasnovumpublicidada@gmail.com</t>
+  </si>
+  <si>
+    <t>Leticia</t>
+  </si>
+  <si>
+    <t>adomatt@hotmail.com</t>
+  </si>
+  <si>
+    <t>Adolfo</t>
+  </si>
+  <si>
+    <t>ajeri@derrama.org.pe</t>
+  </si>
+  <si>
+    <t>Amador</t>
+  </si>
+  <si>
+    <t>asantander@derrama.org.pe</t>
+  </si>
+  <si>
+    <t>Armando</t>
+  </si>
+  <si>
+    <t>creyes@derrama.org.pe</t>
+  </si>
+  <si>
+    <t>César</t>
+  </si>
+  <si>
+    <t>cristhiantorresbarboza@gmail.com</t>
+  </si>
+  <si>
+    <t>Cristhian</t>
+  </si>
+  <si>
+    <t>fzavaleta@laportuaria.com.pe</t>
+  </si>
+  <si>
+    <t>Felipe</t>
+  </si>
+  <si>
+    <t>informes@laportuaria.com.pe</t>
+  </si>
+  <si>
+    <t>Elio</t>
+  </si>
+  <si>
+    <t>larauco@laportuaria.com.pe</t>
+  </si>
+  <si>
+    <t>Soraya</t>
+  </si>
+  <si>
+    <t>lventocilla@credicoop.com.pe</t>
+  </si>
+  <si>
+    <t>petra.balladares@czechtrade.cz</t>
+  </si>
+  <si>
+    <t>Petra</t>
+  </si>
+  <si>
+    <t>rubenlaravillavicencio@gmail.com</t>
+  </si>
+  <si>
+    <t>Ruben</t>
+  </si>
+  <si>
+    <t>administracion@pdl.edu.pe</t>
+  </si>
+  <si>
+    <t>danielpax1@gmail.com</t>
+  </si>
+  <si>
+    <t>Dany</t>
+  </si>
+  <si>
+    <t>diego-jaime15@hotmail.com</t>
+  </si>
+  <si>
+    <t>gustavoruiz99@gmail.com</t>
+  </si>
+  <si>
+    <t>jackelinmoralesruiz@gmail.com</t>
+  </si>
+  <si>
+    <t>Jackeline</t>
+  </si>
+  <si>
+    <t>jose.samanez@deltron.com.pe</t>
+  </si>
+  <si>
+    <t>leyla.perez@huawei.com</t>
+  </si>
+  <si>
+    <t>Leyla</t>
+  </si>
+  <si>
+    <t>mr.omar2214@gmail.com</t>
+  </si>
+  <si>
+    <t>Erick</t>
+  </si>
+  <si>
+    <t>perufinance2@huawei.com</t>
+  </si>
+  <si>
+    <t>virgo.gaby7@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -437,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -472,27 +1507,1592 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>119</v>
+      </c>
+      <c r="B63" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>127</v>
+      </c>
+      <c r="B67" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>133</v>
+      </c>
+      <c r="B70" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>135</v>
+      </c>
+      <c r="B71" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>142</v>
+      </c>
+      <c r="B75" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B78" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>153</v>
+      </c>
+      <c r="B82" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>157</v>
+      </c>
+      <c r="B84" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>159</v>
+      </c>
+      <c r="B85" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>160</v>
+      </c>
+      <c r="B86" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>162</v>
+      </c>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>163</v>
+      </c>
+      <c r="B88" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>165</v>
+      </c>
+      <c r="B89" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>167</v>
+      </c>
+      <c r="B90" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>168</v>
+      </c>
+      <c r="B91" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>172</v>
+      </c>
+      <c r="B93" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>174</v>
+      </c>
+      <c r="B94" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>175</v>
+      </c>
+      <c r="B95" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>177</v>
+      </c>
+      <c r="B96" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>178</v>
+      </c>
+      <c r="B97" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>179</v>
+      </c>
+      <c r="B98" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>181</v>
+      </c>
+      <c r="B99" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>183</v>
+      </c>
+      <c r="B100" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>185</v>
+      </c>
+      <c r="B101" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>186</v>
+      </c>
+      <c r="B102" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>189</v>
+      </c>
+      <c r="B104" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>190</v>
+      </c>
+      <c r="B105" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>192</v>
+      </c>
+      <c r="B106" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>193</v>
+      </c>
+      <c r="B107" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>195</v>
+      </c>
+      <c r="B108" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>197</v>
+      </c>
+      <c r="B109" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>198</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>199</v>
+      </c>
+      <c r="B111" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>201</v>
+      </c>
+      <c r="B112" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>203</v>
+      </c>
+      <c r="B113" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>205</v>
+      </c>
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>206</v>
+      </c>
+      <c r="B115" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>208</v>
+      </c>
+      <c r="B116" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>209</v>
+      </c>
+      <c r="B117" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>211</v>
+      </c>
+      <c r="B118" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>213</v>
+      </c>
+      <c r="B119" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>214</v>
+      </c>
+      <c r="B120" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>216</v>
+      </c>
+      <c r="B121" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>218</v>
+      </c>
+      <c r="B122" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>220</v>
+      </c>
+      <c r="B123" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>222</v>
+      </c>
+      <c r="B124" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>224</v>
+      </c>
+      <c r="B125" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>226</v>
+      </c>
+      <c r="B126" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>228</v>
+      </c>
+      <c r="B127" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>230</v>
+      </c>
+      <c r="B128" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>232</v>
+      </c>
+      <c r="B129" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>233</v>
+      </c>
+      <c r="B130" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>235</v>
+      </c>
+      <c r="B131" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>237</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>238</v>
+      </c>
+      <c r="B133" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>239</v>
+      </c>
+      <c r="B134" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>240</v>
+      </c>
+      <c r="B135" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" s="2"/>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>241</v>
+      </c>
+      <c r="B136" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>243</v>
+      </c>
+      <c r="B137" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>245</v>
+      </c>
+      <c r="B138" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>246</v>
+      </c>
+      <c r="B139" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>247</v>
+      </c>
+      <c r="B140" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>248</v>
+      </c>
+      <c r="B141" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>250</v>
+      </c>
+      <c r="B142" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>251</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>252</v>
+      </c>
+      <c r="B144" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>253</v>
+      </c>
+      <c r="B145" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>255</v>
+      </c>
+      <c r="B146" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>257</v>
+      </c>
+      <c r="B147" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>259</v>
+      </c>
+      <c r="B148" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>261</v>
+      </c>
+      <c r="B149" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>262</v>
+      </c>
+      <c r="B150" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>264</v>
+      </c>
+      <c r="B151" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>266</v>
+      </c>
+      <c r="B152" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>268</v>
+      </c>
+      <c r="B153" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>270</v>
+      </c>
+      <c r="B154" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>272</v>
+      </c>
+      <c r="B155" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>273</v>
+      </c>
+      <c r="B156" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>275</v>
+      </c>
+      <c r="B157" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>277</v>
+      </c>
+      <c r="B158" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>278</v>
+      </c>
+      <c r="B159" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>280</v>
+      </c>
+      <c r="B160" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>282</v>
+      </c>
+      <c r="B161" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>284</v>
+      </c>
+      <c r="B162" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>286</v>
+      </c>
+      <c r="B163" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>287</v>
+      </c>
+      <c r="B164" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>288</v>
+      </c>
+      <c r="B165" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>290</v>
+      </c>
+      <c r="B166" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>292</v>
+      </c>
+      <c r="B167" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>294</v>
+      </c>
+      <c r="B168" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>296</v>
+      </c>
+      <c r="B169" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>298</v>
+      </c>
+      <c r="B170" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>300</v>
+      </c>
+      <c r="B171" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>302</v>
+      </c>
+      <c r="B172" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>304</v>
+      </c>
+      <c r="B173" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>306</v>
+      </c>
+      <c r="B174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>307</v>
+      </c>
+      <c r="B175" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>309</v>
+      </c>
+      <c r="B176" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>311</v>
+      </c>
+      <c r="B177" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>313</v>
+      </c>
+      <c r="B178" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>315</v>
+      </c>
+      <c r="B179" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>317</v>
+      </c>
+      <c r="B180" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>319</v>
+      </c>
+      <c r="B181" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>321</v>
+      </c>
+      <c r="B182" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>323</v>
+      </c>
+      <c r="B183" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>325</v>
+      </c>
+      <c r="B184" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>327</v>
+      </c>
+      <c r="B185" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>329</v>
+      </c>
+      <c r="B186" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>331</v>
+      </c>
+      <c r="B187" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>333</v>
+      </c>
+      <c r="B188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>334</v>
+      </c>
+      <c r="B189" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>336</v>
+      </c>
+      <c r="B190" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>338</v>
+      </c>
+      <c r="B191" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>339</v>
+      </c>
+      <c r="B192" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B193" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>342</v>
+      </c>
+      <c r="B194" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>343</v>
+      </c>
+      <c r="B195" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>345</v>
+      </c>
+      <c r="B196" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>346</v>
+      </c>
+      <c r="B197" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>348</v>
+      </c>
+      <c r="B198" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>350</v>
+      </c>
+      <c r="B199" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>351</v>
+      </c>
+      <c r="B200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B201" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{E5116652-71CB-49E1-AA48-3CFD6BF94903}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{E932B598-6476-41B7-B673-B791A9B630CB}"/>
+    <hyperlink ref="A3" r:id="rId2" display="fguerrero@partnertech.pe" xr:uid="{E5116652-71CB-49E1-AA48-3CFD6BF94903}"/>
+    <hyperlink ref="A4" r:id="rId3" display="acardozo@partnertech.pe" xr:uid="{E932B598-6476-41B7-B673-B791A9B630CB}"/>
+    <hyperlink ref="A201" r:id="rId4" xr:uid="{93E78217-C68F-4636-9A49-768AB813067B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Repositorios\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446C4176-8749-4697-883A-A77F95B24BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1EB6C8-0C4F-45BF-97AA-C2CF1A2A3C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="441">
   <si>
     <t>correo</t>
   </si>
@@ -45,13 +45,1324 @@
   </si>
   <si>
     <t>Alexandra</t>
+  </si>
+  <si>
+    <t>barrieta@corefo.com</t>
+  </si>
+  <si>
+    <t>Bryam</t>
+  </si>
+  <si>
+    <t>cecilia.rodriguez@pearson.com</t>
+  </si>
+  <si>
+    <t>Cecilia</t>
+  </si>
+  <si>
+    <t>cmejia@santillana.com</t>
+  </si>
+  <si>
+    <t>corefo@corefo.com</t>
+  </si>
+  <si>
+    <t>Margarita</t>
+  </si>
+  <si>
+    <t>corp_nehemias@hotmail.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>elicq82@gmail.com</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>fernando.chavez@pearson.com</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>fernandoojeda@corefo.com</t>
+  </si>
+  <si>
+    <t>jderojas@santillana.com</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>lourdesrodel2016@gmail.com</t>
+  </si>
+  <si>
+    <t>Louerdes</t>
+  </si>
+  <si>
+    <t>luis.davila@pearson.com</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>rarauco@santillana.com</t>
+  </si>
+  <si>
+    <t>Rune</t>
+  </si>
+  <si>
+    <t>rjulca@santillana.com</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>vmartinez@santillana.com</t>
+  </si>
+  <si>
+    <t>administracion@cabosrestaurante.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>administracion@healthyperu.com</t>
+  </si>
+  <si>
+    <t>Katiusca</t>
+  </si>
+  <si>
+    <t>cflores@foodpack.com.pe</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>claudia.valdivia@ngr.com.pe</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>comercial@andessuperfood.com</t>
+  </si>
+  <si>
+    <t>Jhordan</t>
+  </si>
+  <si>
+    <t>dsorni@cabosrestaurante.com</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>gloria.lopez@ngr.com.pe</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>laestacionhuaral@gmail.com</t>
+  </si>
+  <si>
+    <t>Jacinto</t>
+  </si>
+  <si>
+    <t>mariamatt89@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>nroca@andesperusuperfood.com</t>
+  </si>
+  <si>
+    <t>Nadia</t>
+  </si>
+  <si>
+    <t>restauranteelcharrua@speedy.com.pe</t>
+  </si>
+  <si>
+    <t>roberto.chinen@gmail.com</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>svelarde@foodpack.com.pe</t>
+  </si>
+  <si>
+    <t>Solange</t>
+  </si>
+  <si>
+    <t>ventas@healthyperu.com</t>
+  </si>
+  <si>
+    <t>Sandro</t>
+  </si>
+  <si>
+    <t>15101194@ue.edu.pe</t>
+  </si>
+  <si>
+    <t>Grecia</t>
+  </si>
+  <si>
+    <t>cnavarro@estacionessanjose.pe</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>derober23@hotmail.com</t>
+  </si>
+  <si>
+    <t>fiorellacallupe@isurdgas.com</t>
+  </si>
+  <si>
+    <t>Fiorella</t>
+  </si>
+  <si>
+    <t>gcastillo@estacionessanjose.pe</t>
+  </si>
+  <si>
+    <t>Gunter</t>
+  </si>
+  <si>
+    <t>girasolchile@gmail.com</t>
+  </si>
+  <si>
+    <t>Nelly</t>
+  </si>
+  <si>
+    <t>glanoire@laney.com.pe</t>
+  </si>
+  <si>
+    <t>Gilbert</t>
+  </si>
+  <si>
+    <t>jorgeburneo@yahoo.com</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>lucduquette@yahoo.com</t>
+  </si>
+  <si>
+    <t>Luc</t>
+  </si>
+  <si>
+    <t>pedrito2809@hotmail.com</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>rzorrilla@corsersac.com</t>
+  </si>
+  <si>
+    <t>Rocio</t>
+  </si>
+  <si>
+    <t>secretariabpz@infonegocio.net.pe</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>secretary.peru@sayboltlatam.com</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>shirahoka@corsersac.com</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>asistente.adm@hcsuministros.com</t>
+  </si>
+  <si>
+    <t>Esthefani</t>
+  </si>
+  <si>
+    <t>calvarez@glocalsac.com</t>
+  </si>
+  <si>
+    <t>cobranza@hcsuministros.com</t>
+  </si>
+  <si>
+    <t>Roxana</t>
+  </si>
+  <si>
+    <t>eaguirre@solucionesel21.com</t>
+  </si>
+  <si>
+    <t>Erika</t>
+  </si>
+  <si>
+    <t>fdavila@glocalsac.com</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>giulissaliliana@gmail.com</t>
+  </si>
+  <si>
+    <t>Giulissa</t>
+  </si>
+  <si>
+    <t>hcueva@hcsuministros.com</t>
+  </si>
+  <si>
+    <t>Hellens</t>
+  </si>
+  <si>
+    <t>inverferresur@gmail.com</t>
+  </si>
+  <si>
+    <t>Rene</t>
+  </si>
+  <si>
+    <t>mdiaz@bosstpackingperu.com</t>
+  </si>
+  <si>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>oficina.tecnica@hcsuministros.com</t>
+  </si>
+  <si>
+    <t>Jhon</t>
+  </si>
+  <si>
+    <t>sayubc.95@gmail.com</t>
+  </si>
+  <si>
+    <t>Shayumi</t>
+  </si>
+  <si>
+    <t>ventas@hcsuministros.com</t>
+  </si>
+  <si>
+    <t>Yolanda</t>
+  </si>
+  <si>
+    <t>ventas@solucionesel21.com</t>
+  </si>
+  <si>
+    <t>Gino</t>
+  </si>
+  <si>
+    <t>ventascoronel.peru@gmail.com</t>
+  </si>
+  <si>
+    <t>cquinones@paraiso-peru.com</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>dani.17.depc@hotmail.com</t>
+  </si>
+  <si>
+    <t>Danitza</t>
+  </si>
+  <si>
+    <t>eboyco@paraiso-peru.com</t>
+  </si>
+  <si>
+    <t>Baruch</t>
+  </si>
+  <si>
+    <t>hmurayama@paraiso-peru.com</t>
+  </si>
+  <si>
+    <t>Héctor</t>
+  </si>
+  <si>
+    <t>humbertop@paraiso-peru.com</t>
+  </si>
+  <si>
+    <t>Humberto</t>
+  </si>
+  <si>
+    <t>javier.zuniga@rosen-corp.com</t>
+  </si>
+  <si>
+    <t>jorge.sandoval@rosen-corp.com</t>
+  </si>
+  <si>
+    <t>juan.rojas@rosen-corp.com</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>marizelatc26@gmail.com</t>
+  </si>
+  <si>
+    <t>Marizela</t>
+  </si>
+  <si>
+    <t>matias.fredes@rosen-corp.com</t>
+  </si>
+  <si>
+    <t>Matias</t>
+  </si>
+  <si>
+    <t>oscar.paredes@rosen-corp.com</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>pcabrera@paraiso-peru.com</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>postmaster@paraiso-peru.com</t>
+  </si>
+  <si>
+    <t>María</t>
+  </si>
+  <si>
+    <t>ybravo@paraiso-peru.com</t>
+  </si>
+  <si>
+    <t>Jenny</t>
+  </si>
+  <si>
+    <t>aldovalle@qmpharma.com</t>
+  </si>
+  <si>
+    <t>Aldo</t>
+  </si>
+  <si>
+    <t>aporras@boticasperu.com.pe</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>contabilidad@farmachif.com</t>
+  </si>
+  <si>
+    <t>cpereda@farmachif.com</t>
+  </si>
+  <si>
+    <t>ebelmont@belcorp.biz</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>emartorana@belcorp.biz</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>farmacomedperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>farmacumedperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Jhovanna</t>
+  </si>
+  <si>
+    <t>jsoriano78@hotmail.com</t>
+  </si>
+  <si>
+    <t>lmontagne@belcorp.biz</t>
+  </si>
+  <si>
+    <t>Lourdes</t>
+  </si>
+  <si>
+    <t>nsalcedo@boticasperu.com.pe</t>
+  </si>
+  <si>
+    <t>pamelaarce@qmpharma.com</t>
+  </si>
+  <si>
+    <t>Pamela</t>
+  </si>
+  <si>
+    <t>qfliliana23@gmail.com</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>scogorno@farmachif.com</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>admin@climaxingenieros.com</t>
+  </si>
+  <si>
+    <t>Estefany</t>
+  </si>
+  <si>
+    <t>admin_latam@aceroestudio.com</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>carlos.urteaga@hurteco.com</t>
+  </si>
+  <si>
+    <t>diego.centurion@climaxingenieros.com</t>
+  </si>
+  <si>
+    <t>dvalenzuela@aceroestudio.com</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>ecambra@aceroestudio.com</t>
+  </si>
+  <si>
+    <t>edamborenea@aceroestudio.com</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>horacio.urteaga@hurteco.com</t>
+  </si>
+  <si>
+    <t>Horacio</t>
+  </si>
+  <si>
+    <t>jorge.silva@seicansac.com</t>
+  </si>
+  <si>
+    <t>jose.urteaga@hurteco.com</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>luis.urteaga@hurteco.com</t>
+  </si>
+  <si>
+    <t>mymcons@qnet.com.pe</t>
+  </si>
+  <si>
+    <t>rore@mymconsultores.com.pe</t>
+  </si>
+  <si>
+    <t>Rebeca</t>
+  </si>
+  <si>
+    <t>ventasyservicios@seicansac.com</t>
+  </si>
+  <si>
+    <t>Yovana</t>
+  </si>
+  <si>
+    <t>aamand@plasticosdiamand.com</t>
+  </si>
+  <si>
+    <t>Alvaro</t>
+  </si>
+  <si>
+    <t>cesaramand@plasticosdiamand.com</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>contabilidad@pimentel.com.pe</t>
+  </si>
+  <si>
+    <t>Matilde</t>
+  </si>
+  <si>
+    <t>jannet.torres@pimentel.com.pe</t>
+  </si>
+  <si>
+    <t>Jeanette</t>
+  </si>
+  <si>
+    <t>jose.chinga@pimentel.com.pe</t>
+  </si>
+  <si>
+    <t>jphiguchi@elsol.com.pe</t>
+  </si>
+  <si>
+    <t>marketing@pimentel.com.pe</t>
+  </si>
+  <si>
+    <t>mcarrasco@elsol.com.pe</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>neoplast@outlook.com</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>paozambrano@goodridedelperu.com</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>pzambrano@goodridedelperu.com</t>
+  </si>
+  <si>
+    <t>tiresol@tiresol.com.pe</t>
+  </si>
+  <si>
+    <t>vilma.pb85@gmail.com</t>
+  </si>
+  <si>
+    <t>Vilma.</t>
+  </si>
+  <si>
+    <t>administracion@panning.pe</t>
+  </si>
+  <si>
+    <t>Claudio</t>
+  </si>
+  <si>
+    <t>arguedasmarteles@gmail.com</t>
+  </si>
+  <si>
+    <t>Dani</t>
+  </si>
+  <si>
+    <t>asist.gerencia@rauletti.com</t>
+  </si>
+  <si>
+    <t>edgardrisco@gmail.com</t>
+  </si>
+  <si>
+    <t>Edgard</t>
+  </si>
+  <si>
+    <t>gerencia@labaguette.com.pe</t>
+  </si>
+  <si>
+    <t>juan.zambrano@katarisac.com</t>
+  </si>
+  <si>
+    <t>paoloriscoechevarria@gmail.com</t>
+  </si>
+  <si>
+    <t>Lidia</t>
+  </si>
+  <si>
+    <t>rauletti1@hotmail.com</t>
+  </si>
+  <si>
+    <t>Nasario</t>
+  </si>
+  <si>
+    <t>robertoccc.9@gmail.com</t>
+  </si>
+  <si>
+    <t>rvgarciaj@gmail.com</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>sandra.obregon@outlook.com.pe</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>tesoreria@katarisac.com</t>
+  </si>
+  <si>
+    <t>Armando</t>
+  </si>
+  <si>
+    <t>uchita.up@gmail.com</t>
+  </si>
+  <si>
+    <t>Ursula</t>
+  </si>
+  <si>
+    <t>abarreda@dispercol.pe</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>benitoplas@hotmail.com</t>
+  </si>
+  <si>
+    <t>Elsa</t>
+  </si>
+  <si>
+    <t>calejos@carvajal.com</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>claudia.estupinanv@jalexsa.com</t>
+  </si>
+  <si>
+    <t>compras@vym.pe</t>
+  </si>
+  <si>
+    <t>Angélica</t>
+  </si>
+  <si>
+    <t>icvernazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t>jtorres@ximesa.com</t>
+  </si>
+  <si>
+    <t>juancarlos.polimeros@gmail.com</t>
+  </si>
+  <si>
+    <t>maria.vela@carvajal.com</t>
+  </si>
+  <si>
+    <t>msosaya@dispercol.pe</t>
+  </si>
+  <si>
+    <t>rosy199226@gmail.com</t>
+  </si>
+  <si>
+    <t>roxana.gutierrez@carvajal.com</t>
+  </si>
+  <si>
+    <t>ventas_clasver@hotmail.com</t>
+  </si>
+  <si>
+    <t>bautistaingcix@gmail.com</t>
+  </si>
+  <si>
+    <t>ccusinga@cagperu.com</t>
+  </si>
+  <si>
+    <t>cmoreno@cagperu.com</t>
+  </si>
+  <si>
+    <t>Cirila</t>
+  </si>
+  <si>
+    <t>gerencia@promasejm.com.pe</t>
+  </si>
+  <si>
+    <t>Mili</t>
+  </si>
+  <si>
+    <t>giovana1994@hotmail.com</t>
+  </si>
+  <si>
+    <t>Giovana</t>
+  </si>
+  <si>
+    <t>j.ramos@puntoespacio-estudio.com</t>
+  </si>
+  <si>
+    <t>Jimena</t>
+  </si>
+  <si>
+    <t>luismiguelbautista1997@gmail.com</t>
+  </si>
+  <si>
+    <t>m.ventura@puntoespacio-estudio.com</t>
+  </si>
+  <si>
+    <t>Moises</t>
+  </si>
+  <si>
+    <t>mocayara29@gmail.com</t>
+  </si>
+  <si>
+    <t>Yarais</t>
+  </si>
+  <si>
+    <t>monicagms.97@gmail.com</t>
+  </si>
+  <si>
+    <t>ovizcarra@cagperu.com</t>
+  </si>
+  <si>
+    <t>proyectos@promasejm.com.pe</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>unimaxsac@gmail.com</t>
+  </si>
+  <si>
+    <t>Joaquin</t>
+  </si>
+  <si>
+    <t>aqatec@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Doris</t>
+  </si>
+  <si>
+    <t>denmed.inversiones@gmail.com</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>emdepriego@energotecsac.com</t>
+  </si>
+  <si>
+    <t>emontalvo@energotecsac.com</t>
+  </si>
+  <si>
+    <t>heroescivilesperu@gmail.com</t>
+  </si>
+  <si>
+    <t>jlira@energotecsac.com</t>
+  </si>
+  <si>
+    <t>luzrc1821@gmail.com</t>
+  </si>
+  <si>
+    <t>Luz</t>
+  </si>
+  <si>
+    <t>mramirez@energotecsac.com</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>nurhedin.sotelo@kqtech-solutions.com</t>
+  </si>
+  <si>
+    <t>Nurhedin</t>
+  </si>
+  <si>
+    <t>sales@kqtech-solutions.com</t>
+  </si>
+  <si>
+    <t>segama883@gmail.com</t>
+  </si>
+  <si>
+    <t>Efrain</t>
+  </si>
+  <si>
+    <t>smacassi@gmail.com</t>
+  </si>
+  <si>
+    <t>Delia</t>
+  </si>
+  <si>
+    <t>ventas@energotecsac.com</t>
+  </si>
+  <si>
+    <t>Jeanet</t>
+  </si>
+  <si>
+    <t>amassa@southernperu.com.pe</t>
+  </si>
+  <si>
+    <t>amina@mineradeisi.com</t>
+  </si>
+  <si>
+    <t>fmejia@southernperu.com.pe</t>
+  </si>
+  <si>
+    <t>info@quimicosasociados.com</t>
+  </si>
+  <si>
+    <t>Rosalina</t>
+  </si>
+  <si>
+    <t>jorge.perez-wilson@mineradeisi.com</t>
+  </si>
+  <si>
+    <t>Gianfranco</t>
+  </si>
+  <si>
+    <t>leslielucero28@gmail.com</t>
+  </si>
+  <si>
+    <t>Ivonne</t>
+  </si>
+  <si>
+    <t>mcnevares@southermperu.com.pe</t>
+  </si>
+  <si>
+    <t>milacondemarin@yahoo.es</t>
+  </si>
+  <si>
+    <t>Luzmila</t>
+  </si>
+  <si>
+    <t>mmunguia@southernperu.com.pe</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>ricardo.espinoza@quimicosasociados.com</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>rsanchez@southernperu.com.pe</t>
+  </si>
+  <si>
+    <t>Raul</t>
+  </si>
+  <si>
+    <t>rsegurag@southernperu.com.pe</t>
+  </si>
+  <si>
+    <t>Renzo</t>
+  </si>
+  <si>
+    <t>rtorres@southernperu.com.pe</t>
+  </si>
+  <si>
+    <t>Germán</t>
+  </si>
+  <si>
+    <t>b.gastañaga@indubrassac.com.pe</t>
+  </si>
+  <si>
+    <t>Buenaventura</t>
+  </si>
+  <si>
+    <t>carlos@pronex.com.pe</t>
+  </si>
+  <si>
+    <t>diana@pronex.com.pe</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>durrutia@unibell.com.pe</t>
+  </si>
+  <si>
+    <t>Duilio</t>
+  </si>
+  <si>
+    <t>gagena@unibell.com.pe</t>
+  </si>
+  <si>
+    <t>gaguena@unibell.com.pe</t>
+  </si>
+  <si>
+    <t>marcial.cuadros@indubrassac.com.pe</t>
+  </si>
+  <si>
+    <t>Marcial</t>
+  </si>
+  <si>
+    <t>palomino.liliana@dystar.com</t>
+  </si>
+  <si>
+    <t>Bryan</t>
+  </si>
+  <si>
+    <t>paraindustrias@paraindustrias.com.pe</t>
+  </si>
+  <si>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>pronex@pronex.com.pe</t>
+  </si>
+  <si>
+    <t>recepcion@unibell.com.pe</t>
+  </si>
+  <si>
+    <t>Ramón</t>
+  </si>
+  <si>
+    <t>rosio.cuadros@indubrassac.com.pe</t>
+  </si>
+  <si>
+    <t>Rosio</t>
+  </si>
+  <si>
+    <t>ventas@paraindustrias.com.pe</t>
+  </si>
+  <si>
+    <t>aniceto@maruplast.com</t>
+  </si>
+  <si>
+    <t>Aniceto</t>
+  </si>
+  <si>
+    <t>crisbeldetallespersonalizados@gmail.com</t>
+  </si>
+  <si>
+    <t>Brenda</t>
+  </si>
+  <si>
+    <t>dpardo@grupogrameco.com</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>floryvera_sac@hotmail.com</t>
+  </si>
+  <si>
+    <t>gerencia@floryverasac.com</t>
+  </si>
+  <si>
+    <t>jpardo@grupogrameco.com</t>
+  </si>
+  <si>
+    <t>katherine7a.kae@gmail.com</t>
+  </si>
+  <si>
+    <t>Katherine</t>
+  </si>
+  <si>
+    <t>keatherine7a.kae@gmail.com</t>
+  </si>
+  <si>
+    <t>Nora</t>
+  </si>
+  <si>
+    <t>lpardo@grupogrameco.com</t>
+  </si>
+  <si>
+    <t>nlujan@grupogrameco.com</t>
+  </si>
+  <si>
+    <t>tatianallontop1601@gmail.com</t>
+  </si>
+  <si>
+    <t>vanessa@maruplast.com</t>
+  </si>
+  <si>
+    <t>abantorj1803@gmail.com</t>
+  </si>
+  <si>
+    <t>contacto@crimsonstudio.pe</t>
+  </si>
+  <si>
+    <t>contacto@tutuma.pe</t>
+  </si>
+  <si>
+    <t>Guillermo</t>
+  </si>
+  <si>
+    <t>fabanto@pixxel.pe</t>
+  </si>
+  <si>
+    <t>gmartinez@kreandocontigo.com</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>joel.flores@fbcisac.com</t>
+  </si>
+  <si>
+    <t>Joel</t>
+  </si>
+  <si>
+    <t>josymar.briceno@fbcisac.com</t>
+  </si>
+  <si>
+    <t>Josymar</t>
+  </si>
+  <si>
+    <t>jptasayco@grupovisualmedia.com</t>
+  </si>
+  <si>
+    <t>miguel@tondero.com.pe</t>
+  </si>
+  <si>
+    <t>milagros@tondero.com.pe</t>
+  </si>
+  <si>
+    <t>Milagros</t>
+  </si>
+  <si>
+    <t>produccion.peru@visualmedia.com</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>roy.flores@fbcisac.com</t>
+  </si>
+  <si>
+    <t>Royci</t>
+  </si>
+  <si>
+    <t>artec.publi@gmail.com</t>
+  </si>
+  <si>
+    <t>Andres</t>
+  </si>
+  <si>
+    <t>ciapervidrio@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>corporacionmadrid@gmail.com</t>
+  </si>
+  <si>
+    <t>cristinaperezvilchez@gmail.com</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>deysicastanong@gmail.com</t>
+  </si>
+  <si>
+    <t>Deysi</t>
+  </si>
+  <si>
+    <t>gandradej@grafargosinv.com</t>
+  </si>
+  <si>
+    <t>jose_madrid_r@hotmail.com</t>
+  </si>
+  <si>
+    <t>lgandrader@grafargosinv.com</t>
+  </si>
+  <si>
+    <t>oficina@ciapervidrio.com</t>
+  </si>
+  <si>
+    <t>peserosmarcos@gmail.com</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>ventas@grafargosinv.com</t>
+  </si>
+  <si>
+    <t>ventas@madridperu.com</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>btubino@danper.com</t>
+  </si>
+  <si>
+    <t>Beatriz</t>
+  </si>
+  <si>
+    <t>carlosjnalta@gmail.com</t>
+  </si>
+  <si>
+    <t>cnunez@cajenual.com</t>
+  </si>
+  <si>
+    <t>Beronica</t>
+  </si>
+  <si>
+    <t>consultoriaperu2024@gmail.com</t>
+  </si>
+  <si>
+    <t>Wilder</t>
+  </si>
+  <si>
+    <t>contabilidadft@fructusterrum.com</t>
+  </si>
+  <si>
+    <t>dbustillos@agroindustriasosho.com</t>
+  </si>
+  <si>
+    <t>Elisabet</t>
+  </si>
+  <si>
+    <t>elizabeth.ponce@estacionverde.pe</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>glinares@agroindustriasosho.com</t>
+  </si>
+  <si>
+    <t>Giulianna</t>
+  </si>
+  <si>
+    <t>jpsantillana@agroindustriasosho.com</t>
+  </si>
+  <si>
+    <t>rbazan@danper.com</t>
+  </si>
+  <si>
+    <t>Aurora</t>
+  </si>
+  <si>
+    <t>ventas@agroindustriasosho.com</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>ventas@merfreshorganics.com.pe</t>
+  </si>
+  <si>
+    <t>angeltubillas@indextusac.com</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>asoria@ccoinsa.com.pe</t>
+  </si>
+  <si>
+    <t>Alcides</t>
+  </si>
+  <si>
+    <t>finanzas@inet.com.pe</t>
+  </si>
+  <si>
+    <t>Gladys</t>
+  </si>
+  <si>
+    <t>fterry@inet.com.pe</t>
+  </si>
+  <si>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>gestiondecalidad@hpytelectric.com</t>
+  </si>
+  <si>
+    <t>Odalis</t>
+  </si>
+  <si>
+    <t>industriasdelcalor@gmail.com</t>
+  </si>
+  <si>
+    <t>jzutta@3pingenieria.com</t>
+  </si>
+  <si>
+    <t>Jheyner</t>
+  </si>
+  <si>
+    <t>mtubillas@indextusac.com</t>
+  </si>
+  <si>
+    <t>nalvarado@allpa-tech.com</t>
+  </si>
+  <si>
+    <t>Nelzon</t>
+  </si>
+  <si>
+    <t>rrhh@inet.com.pe</t>
+  </si>
+  <si>
+    <t>Pilar</t>
+  </si>
+  <si>
+    <t>soe.industrial2020@gmial.com</t>
+  </si>
+  <si>
+    <t>vasthi@hpytelectric.com</t>
+  </si>
+  <si>
+    <t>Vasthi</t>
+  </si>
+  <si>
+    <t>administracion@biosoporteperu.com</t>
+  </si>
+  <si>
+    <t>alexander062923f@hotmail.com</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>dtantaleanvalverde@gmail.com</t>
+  </si>
+  <si>
+    <t>Darwin</t>
+  </si>
+  <si>
+    <t>gdavila@hotmail.com.pe</t>
+  </si>
+  <si>
+    <t>gerencia@biosoporteperu.com</t>
+  </si>
+  <si>
+    <t>gerencia@limamed.com</t>
+  </si>
+  <si>
+    <t>importaciones@limamed.pe</t>
+  </si>
+  <si>
+    <t>Jhonatan</t>
+  </si>
+  <si>
+    <t>industriasromacall@hotmail.com</t>
+  </si>
+  <si>
+    <t>Juliet</t>
+  </si>
+  <si>
+    <t>industriasromancall@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ronald</t>
+  </si>
+  <si>
+    <t>sales@diecomcorporation.com</t>
+  </si>
+  <si>
+    <t>tumimed_srl@infonegocio.net.pe</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>ventas@limamed.com</t>
+  </si>
+  <si>
+    <t>Nellida</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +1386,14 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -118,13 +1437,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -428,7 +1748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:D264"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -451,30 +1771,2106 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" s="2"/>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A201" s="2"/>
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B65" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B66" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B67" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B68" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B70" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B74" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B75" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B76" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B77" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B78" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B79" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B80" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B81" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B83" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B84" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B86" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B87" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B88" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B89" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B91" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B92" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B93" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B94" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B95" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B96" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B99" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B100" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B101" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B102" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B103" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B104" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B105" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B106" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B107" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B108" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B109" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B110" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B111" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B112" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B113" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B114" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B115" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B116" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B117" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B118" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B119" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B120" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B121" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B122" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B123" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B124" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B125" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B126" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B127" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B128" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B129" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B130" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B131" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B132" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B133" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B134" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B135" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B137" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B138" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B139" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B140" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B141" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B142" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B143" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B144" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B145" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B146" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B147" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B148" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B149" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B150" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B151" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B152" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B153" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B154" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B155" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B156" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B157" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B158" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B159" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B160" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B161" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B162" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B163" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B164" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B165" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B166" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B167" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B170" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B171" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B172" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B173" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B174" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B175" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B176" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B177" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B178" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B179" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B180" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B181" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B182" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B183" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B184" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B185" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B186" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B187" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B188" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B189" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B190" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B191" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B192" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B193" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B194" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B195" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B196" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B197" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B198" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B199" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B200" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B201" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B202" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B203" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B204" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B205" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B206" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B207" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B208" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B209" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B210" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B211" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B212" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B213" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B214" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B215" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B216" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B217" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B218" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B219" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B220" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B221" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B222" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B223" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B224" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B225" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B226" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B227" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B228" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B229" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B230" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B231" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B232" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B233" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B234" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B235" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B236" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B237" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B238" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B239" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B240" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B241" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B242" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B243" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B244" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B245" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B246" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B247" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B248" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B249" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B250" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B251" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B252" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B253" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B254" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B255" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B256" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B257" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B258" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B259" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B260" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B261" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B262" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B263" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B264" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
+    <hyperlink ref="A264" r:id="rId2" xr:uid="{5A39FD24-E5C3-4318-9E18-BB688DFED8AB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980B7CC6-CACA-48EE-A0E0-5522EE1F25A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41518977-2AB1-4B3A-9AEE-C2586D7D0C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,10 +41,10 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>Alexandra</t>
+    <t>ricardo.noriega@pmoperu.com</t>
   </si>
   <si>
-    <t>ricardo.noriega@pmoperu.com</t>
+    <t>Ricardo</t>
   </si>
 </sst>
 </file>
@@ -453,10 +453,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Repositorios\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980B7CC6-CACA-48EE-A0E0-5522EE1F25A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FE21CF-ED97-445E-968F-7270A56A1A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,24 +16,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="187">
   <si>
     <t>correo</t>
   </si>
@@ -45,6 +32,555 @@
   </si>
   <si>
     <t>ricardo.noriega@pmoperu.com</t>
+  </si>
+  <si>
+    <t>administracion.peru@movilmax.com</t>
+  </si>
+  <si>
+    <t>Erika</t>
+  </si>
+  <si>
+    <t>andres.escudero@movilmax.com</t>
+  </si>
+  <si>
+    <t>Andres</t>
+  </si>
+  <si>
+    <t>aternero@fiberlux.pe</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>contacto@winempresas.pe</t>
+  </si>
+  <si>
+    <t>Nilton</t>
+  </si>
+  <si>
+    <t>daniel.ayala@getcom.pe</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>diana.patricio@movilmax.com</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>ernesto.arana@aitsecurity.com.pe</t>
+  </si>
+  <si>
+    <t>Ernesto</t>
+  </si>
+  <si>
+    <t>franco.roldan@aitsecurity.com.pe</t>
+  </si>
+  <si>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>kenji@movilmax.com</t>
+  </si>
+  <si>
+    <t>Kenji</t>
+  </si>
+  <si>
+    <t>moisesalarcon@jlbusiness.com</t>
+  </si>
+  <si>
+    <t>Grover</t>
+  </si>
+  <si>
+    <t>rosalia.rosel@fecorp.com.pe</t>
+  </si>
+  <si>
+    <t>Rosalia</t>
+  </si>
+  <si>
+    <t>socrates.angeles@getcom.pe</t>
+  </si>
+  <si>
+    <t>Sòcrates</t>
+  </si>
+  <si>
+    <t>stalin.rivera@ipt.pe</t>
+  </si>
+  <si>
+    <t>Stalin</t>
+  </si>
+  <si>
+    <t>teresa.gomes@ipt.pe</t>
+  </si>
+  <si>
+    <t>Teresa</t>
+  </si>
+  <si>
+    <t>acostaflorezi@gmail.com</t>
+  </si>
+  <si>
+    <t>Karina</t>
+  </si>
+  <si>
+    <t>cludowieg@edificios.com.pe</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>ejoya@edificios.com.pe</t>
+  </si>
+  <si>
+    <t>eltriangulomus@hotmail.com</t>
+  </si>
+  <si>
+    <t>Danna</t>
+  </si>
+  <si>
+    <t>esvicenor@gmail.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>iselagracia@hotmail.com</t>
+  </si>
+  <si>
+    <t>Isela</t>
+  </si>
+  <si>
+    <t>jarthur2808@hotmail.com</t>
+  </si>
+  <si>
+    <t>marketing@fiesac.com.pe</t>
+  </si>
+  <si>
+    <t>Marcia</t>
+  </si>
+  <si>
+    <t>mcanchari@edificios.com.pe</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>pascualyupa@hotmail.com</t>
+  </si>
+  <si>
+    <t>Gianella</t>
+  </si>
+  <si>
+    <t>rmelendez@creaplast.pe</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>rosa.egusquiza@fiesac.com.pe</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>ventas2@fiesac.com.pe</t>
+  </si>
+  <si>
+    <t>Ammy</t>
+  </si>
+  <si>
+    <t>william_cuadros@yahoo.es</t>
+  </si>
+  <si>
+    <t>Joel</t>
+  </si>
+  <si>
+    <t>administracion@bcaperu.com</t>
+  </si>
+  <si>
+    <t>Yeison</t>
+  </si>
+  <si>
+    <t>comercial@ecodefperu.com</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>contabilidad@goldenanka.com</t>
+  </si>
+  <si>
+    <t>daniel.asto@goldenanka.com</t>
+  </si>
+  <si>
+    <t>E.</t>
+  </si>
+  <si>
+    <t>dionicio.tauma@jksoltec.com</t>
+  </si>
+  <si>
+    <t>Dionicio</t>
+  </si>
+  <si>
+    <t>gerencia@esmirwal.com</t>
+  </si>
+  <si>
+    <t>Raul</t>
+  </si>
+  <si>
+    <t>gerencia@geocorperu.com</t>
+  </si>
+  <si>
+    <t>Brindis</t>
+  </si>
+  <si>
+    <t>info@umtys.pe</t>
+  </si>
+  <si>
+    <t>jarlanrioscoloma@gmail.com</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>jhonatan.juno@jksoltec.com</t>
+  </si>
+  <si>
+    <t>Jhonatan</t>
+  </si>
+  <si>
+    <t>jmoreto@bcaperu.com</t>
+  </si>
+  <si>
+    <t>Lincol</t>
+  </si>
+  <si>
+    <t>jrios@mekipa.com</t>
+  </si>
+  <si>
+    <t>mayra.miranda@esmirwal.com</t>
+  </si>
+  <si>
+    <t>Mayra</t>
+  </si>
+  <si>
+    <t>vkhazz@hotmail.com</t>
+  </si>
+  <si>
+    <t>Veronikha</t>
+  </si>
+  <si>
+    <t>administracion@acerosanmartin.com.pe</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>antonio.garma@sinoxsac.com</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>contabilidad@acerosanmartin.com.pe</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <t>frediangelesoyola@gmail.com</t>
+  </si>
+  <si>
+    <t>Fredi</t>
+  </si>
+  <si>
+    <t>graciela.caceres@sinoxsac.com</t>
+  </si>
+  <si>
+    <t>Angie</t>
+  </si>
+  <si>
+    <t>gusconfe@gmail.com</t>
+  </si>
+  <si>
+    <t>Gustavo</t>
+  </si>
+  <si>
+    <t>henry.alvarez@hacautomatizacionycontrol.com</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>jaime@galyhasac.com.pe</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>jzaragoza@discoverinox.com.pe</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>kzaragoza@discoverinox.com.pe</t>
+  </si>
+  <si>
+    <t>Kathy</t>
+  </si>
+  <si>
+    <t>nancy.valverde@hacautomatizacionycontrol.com</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>tesoreria@acerosanmartin.com.pe</t>
+  </si>
+  <si>
+    <t>Gerardo</t>
+  </si>
+  <si>
+    <t>vifemserg.lpr@gmail.com</t>
+  </si>
+  <si>
+    <t>Looy</t>
+  </si>
+  <si>
+    <t>ymerinorocha49@gmail.com</t>
+  </si>
+  <si>
+    <t>Yuri</t>
+  </si>
+  <si>
+    <t>administracion@lagranjavilla.com</t>
+  </si>
+  <si>
+    <t>Cecilia</t>
+  </si>
+  <si>
+    <t>anaharamartinez17@gmail.com</t>
+  </si>
+  <si>
+    <t>Adys</t>
+  </si>
+  <si>
+    <t>asistenciadedireccion@lagranjavilla.com</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>cecilia.chavez@lagranjavilla.com</t>
+  </si>
+  <si>
+    <t>contabilidad@clubpetroperu.com.pe</t>
+  </si>
+  <si>
+    <t>dsilva@coneyparkperu.com</t>
+  </si>
+  <si>
+    <t>Dora</t>
+  </si>
+  <si>
+    <t>dvillavicencio@clubrinconada.org.pe</t>
+  </si>
+  <si>
+    <t>gadm@clubpetroperu.com.pe</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>iturrymilton@hotmail.com</t>
+  </si>
+  <si>
+    <t>Milton</t>
+  </si>
+  <si>
+    <t>judeli28@hotmail.com</t>
+  </si>
+  <si>
+    <t>Judith</t>
+  </si>
+  <si>
+    <t>logistica01@clubrinconada.org.pe</t>
+  </si>
+  <si>
+    <t>Jenny</t>
+  </si>
+  <si>
+    <t>tesoreria1@clubrinconada.org.pe</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>tury.munozr@gmail.com</t>
+  </si>
+  <si>
+    <t>Arturo</t>
+  </si>
+  <si>
+    <t>victor.chamorro@lagranjavilla.com</t>
+  </si>
+  <si>
+    <t>Víctor</t>
+  </si>
+  <si>
+    <t>agustin.boulangger@gmail.com</t>
+  </si>
+  <si>
+    <t>Luz</t>
+  </si>
+  <si>
+    <t>alcar_2003@hotmail.com</t>
+  </si>
+  <si>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>ambardiazc24@gmail.com</t>
+  </si>
+  <si>
+    <t>Ambar</t>
+  </si>
+  <si>
+    <t>conaesdelperu7@gmail.com</t>
+  </si>
+  <si>
+    <t>Edwin</t>
+  </si>
+  <si>
+    <t>conaesdelsur7@gmail.com</t>
+  </si>
+  <si>
+    <t>Evelin</t>
+  </si>
+  <si>
+    <t>doidc.7@gmail.com</t>
+  </si>
+  <si>
+    <t>Merlina</t>
+  </si>
+  <si>
+    <t>jl.titolopez@gmail.com</t>
+  </si>
+  <si>
+    <t>jose.montalva@gmail.com</t>
+  </si>
+  <si>
+    <t>karitogale0528@gmail.com</t>
+  </si>
+  <si>
+    <t>logistica@kayshosac.com</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>medicalhck@gmail.com</t>
+  </si>
+  <si>
+    <t>Mitchael</t>
+  </si>
+  <si>
+    <t>mvidal@olviglobal.com.pe</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>vzabc@hotmail.com</t>
+  </si>
+  <si>
+    <t>Veronica</t>
+  </si>
+  <si>
+    <t>winsorperu@hotmail.com</t>
+  </si>
+  <si>
+    <t>aaronpg_866@hotmail.com</t>
+  </si>
+  <si>
+    <t>Moises</t>
+  </si>
+  <si>
+    <t>alexander.zurita@tapiahermanos.pe</t>
+  </si>
+  <si>
+    <t>Amador</t>
+  </si>
+  <si>
+    <t>csegundo@confiperu.com.pe</t>
+  </si>
+  <si>
+    <t>Corina</t>
+  </si>
+  <si>
+    <t>edith_sanabria@hotmail.com</t>
+  </si>
+  <si>
+    <t>Enith</t>
+  </si>
+  <si>
+    <t>edrojas@arcor.com</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>enithbdes@hotmail.com</t>
+  </si>
+  <si>
+    <t>garizola@confiperu.com.pe</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>jteodoro@arcor.com</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>ltejada@confiperu.com.pe</t>
+  </si>
+  <si>
+    <t>Lorena</t>
+  </si>
+  <si>
+    <t>lu9va8@gmail.com</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>mcondemarin1@gmail.com</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>mmasias@confiperu.com.pe</t>
+  </si>
+  <si>
+    <t>tgarcia@confiperu.com.pe</t>
+  </si>
+  <si>
+    <t>Tomas</t>
+  </si>
+  <si>
+    <t>vilca.karim@gmail.com</t>
+  </si>
+  <si>
+    <t>Karim</t>
+  </si>
+  <si>
+    <t>negocios@partnertech.pe</t>
   </si>
 </sst>
 </file>
@@ -460,334 +996,829 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="4"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="4"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="4"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="4"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="4"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="4"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="4"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="4"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="4"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="4"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="4"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="4"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="4"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="4"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="4"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="4"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="4"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="4"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="4"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B66" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B74" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B80" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B82" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B83" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B84" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B85" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B87" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B88" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B90" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B91" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B93" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B94" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B95" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B96" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B97" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B98" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B99" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B100" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B101" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="4"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
@@ -1249,6 +2280,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
+    <hyperlink ref="A101" r:id="rId2" xr:uid="{07085133-5B2A-4BFD-A3E7-D378EFE11351}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Repositorios\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D39320C-AA52-4C54-A50B-36AD402F7DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCA98B1-1F51-465B-824A-F3C3366DBBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="181">
   <si>
     <t>correo</t>
   </si>
@@ -31,184 +31,538 @@
     <t>Alexandra</t>
   </si>
   <si>
-    <t>Andres</t>
-  </si>
-  <si>
     <t>Jose</t>
   </si>
   <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>negocios@partnertech.pe</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Erika</t>
+  </si>
+  <si>
+    <t>Susana</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>fguerrero@partnertech.pe</t>
+  </si>
+  <si>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>Karin</t>
+  </si>
+  <si>
+    <t>Beatriz</t>
+  </si>
+  <si>
+    <t>Nicolas</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>abarranzuela@dualempresas.com</t>
+  </si>
+  <si>
+    <t>Duber</t>
+  </si>
+  <si>
+    <t>abarranzuela2@gmail.com</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>corporationdisarksac@gmail.com</t>
+  </si>
+  <si>
+    <t>daniel.caballero@edgewell.com</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>gerencia@morcagroup.com.pe</t>
+  </si>
+  <si>
+    <t>Armando</t>
+  </si>
+  <si>
+    <t>hector.zegarra@edgewell.com</t>
+  </si>
+  <si>
+    <t>Héctor</t>
+  </si>
+  <si>
+    <t>jguerrero@morcagroup.com.pe</t>
+  </si>
+  <si>
+    <t>laura.delgado@edgewell.com</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>licett.monzon@edgewell.com</t>
+  </si>
+  <si>
+    <t>Licett</t>
+  </si>
+  <si>
+    <t>lmontalvan@brandisco.pe</t>
+  </si>
+  <si>
+    <t>Lizbeth</t>
+  </si>
+  <si>
+    <t>luis.ramirez@edgewell.com</t>
+  </si>
+  <si>
+    <t>miriansr1008@gmail.com</t>
+  </si>
+  <si>
+    <t>Minny</t>
+  </si>
+  <si>
+    <t>naturareperu@gmail.com</t>
+  </si>
+  <si>
+    <t>nicolas.cuberos@edgewell.com</t>
+  </si>
+  <si>
+    <t>nicolledayannatoledocharaja6@gmail.com</t>
+  </si>
+  <si>
+    <t>Nicolle</t>
+  </si>
+  <si>
+    <t>plozada@amenitik.com</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>ventas@amenitik.com</t>
+  </si>
+  <si>
+    <t>Anghela</t>
+  </si>
+  <si>
+    <t>administracion@jlaproyectos.com</t>
+  </si>
+  <si>
+    <t>Mariella</t>
+  </si>
+  <si>
+    <t>alexanderlupu@outlook.com</t>
+  </si>
+  <si>
+    <t>asistente.gerencia@aircoolsystemsmsac.com</t>
+  </si>
+  <si>
+    <t>Giannina</t>
+  </si>
+  <si>
+    <t>comercial@jlaproyectos.com</t>
+  </si>
+  <si>
+    <t>Jenner</t>
+  </si>
+  <si>
+    <t>erickson.brayner96@gmail.com</t>
+  </si>
+  <si>
+    <t>Erickson</t>
+  </si>
+  <si>
+    <t>jared.echia@aircoolsystemsmsac.com</t>
+  </si>
+  <si>
+    <t>Jared</t>
+  </si>
+  <si>
+    <t>jkise@climasolutionsperu.com</t>
+  </si>
+  <si>
+    <t>juanpenafiel@ventiplus.pe</t>
+  </si>
+  <si>
+    <t>leonelvicente.alcala@gmail.com</t>
+  </si>
+  <si>
+    <t>Richie</t>
+  </si>
+  <si>
+    <t>lesteban@ecotermoautomatic.com</t>
+  </si>
+  <si>
+    <t>Lidiana</t>
+  </si>
+  <si>
+    <t>nenablancas@ventiplus.pe</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>omatazoglio@climasolutionsperu.com</t>
+  </si>
+  <si>
+    <t>operaciones@latinorefrigeracion.com</t>
+  </si>
+  <si>
     <t>Frank</t>
   </si>
   <si>
+    <t>rcaceres@dhequipos.com</t>
+  </si>
+  <si>
+    <t>tflores@ecotermoautomatic.com</t>
+  </si>
+  <si>
+    <t>Thonny</t>
+  </si>
+  <si>
+    <t>thamideh@dhequipos.com</t>
+  </si>
+  <si>
+    <t>Tania</t>
+  </si>
+  <si>
+    <t>agustin.guevaraballon@adm.com</t>
+  </si>
+  <si>
+    <t>Agustin</t>
+  </si>
+  <si>
+    <t>cvega@marvesaperu.com</t>
+  </si>
+  <si>
+    <t>dcepeda@setopsac.com</t>
+  </si>
+  <si>
+    <t>ealbala@kosterperu.com</t>
+  </si>
+  <si>
+    <t>Eleazar</t>
+  </si>
+  <si>
+    <t>enapacerdan@gmail.com</t>
+  </si>
+  <si>
+    <t>Evan</t>
+  </si>
+  <si>
+    <t>gerencia@aitsac.com</t>
+  </si>
+  <si>
+    <t>hdewit@amauta.rcp.net.pe</t>
+  </si>
+  <si>
+    <t>Hans</t>
+  </si>
+  <si>
+    <t>jackiecornejo_68@hotmail.com</t>
+  </si>
+  <si>
+    <t>Emilia</t>
+  </si>
+  <si>
+    <t>jfernandezco95@gmail.com</t>
+  </si>
+  <si>
+    <t>kdavila@kosterperu.com</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>miguel.burga@adm.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>mobeso@setopsac.com</t>
+  </si>
+  <si>
+    <t>Mirian</t>
+  </si>
+  <si>
+    <t>mvilca@kosterperu.com</t>
+  </si>
+  <si>
+    <t>Margarita</t>
+  </si>
+  <si>
+    <t>rdoza@marvesaperu.com</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>susana.bances@adm.com</t>
+  </si>
+  <si>
+    <t>vilzeth@outlook.com</t>
+  </si>
+  <si>
+    <t>Vilzeth</t>
+  </si>
+  <si>
+    <t>cfebres@teka.com.pe</t>
+  </si>
+  <si>
+    <t>Claudio</t>
+  </si>
+  <si>
+    <t>chfloresdennis@gmail.com</t>
+  </si>
+  <si>
+    <t>Dennis</t>
+  </si>
+  <si>
+    <t>dayr_inversiones@hotmail.com</t>
+  </si>
+  <si>
     <t>Ana</t>
   </si>
   <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>negocios@partnertech.pe</t>
-  </si>
-  <si>
-    <t>aarias@caa.com.pe</t>
-  </si>
-  <si>
-    <t>administracion@icoasperu.com</t>
-  </si>
-  <si>
-    <t>Steny</t>
-  </si>
-  <si>
-    <t>alberto1410274@hotmail.com</t>
-  </si>
-  <si>
-    <t>Alberto</t>
-  </si>
-  <si>
-    <t>amontero@caa.com.pe</t>
-  </si>
-  <si>
-    <t>Alicia</t>
-  </si>
-  <si>
-    <t>cinthiatimana_y@hotmail.com</t>
-  </si>
-  <si>
-    <t>Cinthia</t>
-  </si>
-  <si>
-    <t>gbustamante@bbidelperu.com</t>
+    <t>elizabethchp1215@gmail.com</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>gerencia@corpgemabe.com</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>gerencia@dayrinversiones.com</t>
+  </si>
+  <si>
+    <t>gerencia@doubleclick.pe</t>
+  </si>
+  <si>
+    <t>Nataly</t>
+  </si>
+  <si>
+    <t>gmontoya@thomas.com.pe</t>
   </si>
   <si>
     <t>Guillermo</t>
   </si>
   <si>
-    <t>info@abecosistemas.com</t>
-  </si>
-  <si>
-    <t>lbastante@caa.com.pe</t>
-  </si>
-  <si>
-    <t>Jorge</t>
-  </si>
-  <si>
-    <t>mcingenieros1706@hotmail.com</t>
-  </si>
-  <si>
-    <t>mcingenieros1708@hotmail.com</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
-    <t>proyectos@icoasperu.com</t>
-  </si>
-  <si>
-    <t>rbustamante@bbidelperu.com</t>
-  </si>
-  <si>
-    <t>Rita</t>
-  </si>
-  <si>
-    <t>rochoaojeda@icoasperu.com</t>
-  </si>
-  <si>
-    <t>Ronald</t>
-  </si>
-  <si>
-    <t>sylviarocioa@gmail.com</t>
-  </si>
-  <si>
-    <t>Sylvia</t>
-  </si>
-  <si>
-    <t>ventas@abecosistemas.com</t>
-  </si>
-  <si>
-    <t>Pamela</t>
-  </si>
-  <si>
-    <t>angelobelfiore10@gmail.com</t>
-  </si>
-  <si>
-    <t>Angelo</t>
-  </si>
-  <si>
-    <t>c.t.recepcion@xcmg-underground.com</t>
-  </si>
-  <si>
-    <t>Candy</t>
-  </si>
-  <si>
-    <t>ca.judita@gmail.com</t>
-  </si>
-  <si>
-    <t>Yudita</t>
-  </si>
-  <si>
-    <t>contabilidad@dimarzachile.cl</t>
-  </si>
-  <si>
-    <t>Lizeth</t>
-  </si>
-  <si>
-    <t>eac.company.inc@gmail.com</t>
-  </si>
-  <si>
-    <t>Francisco</t>
-  </si>
-  <si>
-    <t>francisco.paz@cgcompass.com</t>
-  </si>
-  <si>
-    <t>gerencia@dimarza.com</t>
-  </si>
-  <si>
-    <t>Ricardo</t>
-  </si>
-  <si>
-    <t>jese.contabilidad@wardia.com.pe</t>
-  </si>
-  <si>
-    <t>Leslie</t>
-  </si>
-  <si>
-    <t>jose.chinchay@drillingcorpmj.com</t>
-  </si>
-  <si>
-    <t>k.r.gerencia@xcmg-underground.com</t>
-  </si>
-  <si>
-    <t>Katy</t>
-  </si>
-  <si>
-    <t>martinvallenas@hotmail.com</t>
-  </si>
-  <si>
-    <t>Augusto</t>
-  </si>
-  <si>
-    <t>moises.rudas@drillingcorpmj.com</t>
-  </si>
-  <si>
-    <t>Geny</t>
-  </si>
-  <si>
-    <t>mruiz@equifax.com.pe</t>
-  </si>
-  <si>
-    <t>Mara</t>
-  </si>
-  <si>
-    <t>royer@wardia.com.pe</t>
-  </si>
-  <si>
-    <t>Royer</t>
-  </si>
-  <si>
-    <t>sergio.soto@equifax.com</t>
-  </si>
-  <si>
-    <t>Sergio</t>
+    <t>gygingenierias@gmail.com</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>jcsoto@teka.com.pe</t>
+  </si>
+  <si>
+    <t>joseluisvj@gservacom.com</t>
+  </si>
+  <si>
+    <t>karen.mejia@teka.com.pe</t>
+  </si>
+  <si>
+    <t>mrivasq@corpgemabe.com</t>
+  </si>
+  <si>
+    <t>Manuela</t>
+  </si>
+  <si>
+    <t>santillanamilagros22@gmail.com</t>
+  </si>
+  <si>
+    <t>Milagros</t>
+  </si>
+  <si>
+    <t>sumaq.artesaniasdebarro@gmail.com</t>
+  </si>
+  <si>
+    <t>ventas@gservacom.com</t>
+  </si>
+  <si>
+    <t>allhannagouveia@gmail.com</t>
+  </si>
+  <si>
+    <t>Allhanna</t>
+  </si>
+  <si>
+    <t>bcbueno@hotmail.com</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>blanquita_29_@hotmail.com</t>
+  </si>
+  <si>
+    <t>Blanca</t>
+  </si>
+  <si>
+    <t>canchiswalter1980@gmail.com</t>
+  </si>
+  <si>
+    <t>Brenda</t>
+  </si>
+  <si>
+    <t>cesarzaragozab@gmail.com</t>
+  </si>
+  <si>
+    <t>corporativo@calidoalivio.com</t>
+  </si>
+  <si>
+    <t>edher.muoca@gmail.com</t>
+  </si>
+  <si>
+    <t>Edher</t>
+  </si>
+  <si>
+    <t>institutodeterapiamanualperu@gmail.com</t>
+  </si>
+  <si>
+    <t>inversioneszarria@speedy.com.pe</t>
+  </si>
+  <si>
+    <t>Elio</t>
+  </si>
+  <si>
+    <t>inversioneszarriag@hotmail.com</t>
+  </si>
+  <si>
+    <t>javiermatos@clinicasanjudastadeo.com.pe</t>
+  </si>
+  <si>
+    <t>kenyecamd@gmail.com</t>
+  </si>
+  <si>
+    <t>Kenye</t>
+  </si>
+  <si>
+    <t>kmiljanovich@clinicasanjudastadeo.com.pe</t>
+  </si>
+  <si>
+    <t>marisita.dlce@gmail.com</t>
+  </si>
+  <si>
+    <t>Marisol</t>
+  </si>
+  <si>
+    <t>rociogomezosoz@hotmail.com</t>
+  </si>
+  <si>
+    <t>Rocio</t>
+  </si>
+  <si>
+    <t>salazar-luisa@hotmail.com</t>
+  </si>
+  <si>
+    <t>atalledo@kobsa.com.pe</t>
+  </si>
+  <si>
+    <t>avera@kobsa.com.pe</t>
+  </si>
+  <si>
+    <t>ballesterosabog@hotmail.com</t>
+  </si>
+  <si>
+    <t>carla.gongora@sci.com.pe</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>ebarboza@normaliza.com</t>
+  </si>
+  <si>
+    <t>facundo@moonflow.ai</t>
+  </si>
+  <si>
+    <t>Facundo</t>
+  </si>
+  <si>
+    <t>jalburquerque@sci.com.pe</t>
+  </si>
+  <si>
+    <t>jmorales@sci.com.pe</t>
+  </si>
+  <si>
+    <t>Jesús</t>
+  </si>
+  <si>
+    <t>jorge.pereyra@recsa.com</t>
+  </si>
+  <si>
+    <t>jorge.perez@sci.com.pe</t>
+  </si>
+  <si>
+    <t>katherine.corcuera@recsa.com</t>
+  </si>
+  <si>
+    <t>Katherine</t>
+  </si>
+  <si>
+    <t>liseth.segura@recsa.com</t>
+  </si>
+  <si>
+    <t>Liseth</t>
+  </si>
+  <si>
+    <t>milena.henandez@recsa.com</t>
+  </si>
+  <si>
+    <t>milena.hernandez@recsa.com</t>
+  </si>
+  <si>
+    <t>Milena</t>
+  </si>
+  <si>
+    <t>psantoss@sci.com.pe</t>
+  </si>
+  <si>
+    <t>Pepe</t>
+  </si>
+  <si>
+    <t>srodriguez@sci.com.pe</t>
+  </si>
+  <si>
+    <t>Sandra</t>
   </si>
 </sst>
 </file>
@@ -617,7 +971,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -625,192 +979,192 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
@@ -818,295 +1172,630 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>8</v>
+      <c r="A33" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
+      <c r="A34" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
+      <c r="A35" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
+      <c r="A36" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
+      <c r="A37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
+      <c r="A38" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
+      <c r="A39" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
+      <c r="A40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
+      <c r="A41" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
+      <c r="A42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
+      <c r="A43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
+      <c r="A44" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
+      <c r="A45" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
+      <c r="A46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
+      <c r="A47" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="4"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="4"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="4"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="4"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="4"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="4"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="4"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="4"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="4"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="4"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="4"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="4"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="4"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="4"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="4"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="4"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="4"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="4"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B55" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B74" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B84" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B85" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B86" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B87" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B88" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B89" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B91" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B94" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B95" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B96" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B98" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B99" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="4"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="4"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
@@ -1164,7 +1853,7 @@
       <c r="A130" s="4"/>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="4"/>
+      <c r="A131" s="2"/>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="4"/>
@@ -1568,7 +2257,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
-    <hyperlink ref="A33" r:id="rId2" xr:uid="{956A31B4-EE33-48C8-B5D3-3E9D59FB15AA}"/>
+    <hyperlink ref="A100" r:id="rId2" xr:uid="{84A98273-6D18-43FD-BA21-B5995BF8E17F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E32F22-8350-49C7-810E-4FE47542A947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85002E20-07E1-468F-9DC4-988999D8F515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>correo</t>
   </si>
@@ -32,6 +32,138 @@
   </si>
   <si>
     <t>Franco</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>ra.galane@alum.up.edu.pe</t>
+  </si>
+  <si>
+    <t>Rodrigo</t>
+  </si>
+  <si>
+    <t>Giovanna</t>
+  </si>
+  <si>
+    <t>administracion@remugraf.com</t>
+  </si>
+  <si>
+    <t>Clever</t>
+  </si>
+  <si>
+    <t>administracion@ychiformas.com</t>
+  </si>
+  <si>
+    <t>alvespinozaalm@gmail.com</t>
+  </si>
+  <si>
+    <t>Alvaro</t>
+  </si>
+  <si>
+    <t>carias@cartolan.com</t>
+  </si>
+  <si>
+    <t>Cirilo</t>
+  </si>
+  <si>
+    <t>cmoranted@esttilodigitalsa.com</t>
+  </si>
+  <si>
+    <t>comercial@alquiler-fotocopiadora.com</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>comercializacion@ychiformas.com</t>
+  </si>
+  <si>
+    <t>contabilidad@ychiformas.com</t>
+  </si>
+  <si>
+    <t>Patrcia</t>
+  </si>
+  <si>
+    <t>contacto@alquiler-fotocopiadora.com</t>
+  </si>
+  <si>
+    <t>Telmo</t>
+  </si>
+  <si>
+    <t>creditosycobranzas@termilperu.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>fidel.reyes@pacificimpresores.com</t>
+  </si>
+  <si>
+    <t>Fidel</t>
+  </si>
+  <si>
+    <t>gerencia@ychiformas.com</t>
+  </si>
+  <si>
+    <t>grafsanisidro@gmail.com</t>
+  </si>
+  <si>
+    <t>laycolor@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jaqueline</t>
+  </si>
+  <si>
+    <t>marielena.reyes@pacificimpresores.com</t>
+  </si>
+  <si>
+    <t>mshibuya@termilperu.com</t>
+  </si>
+  <si>
+    <t>Mauricio</t>
+  </si>
+  <si>
+    <t>patrick.rojas@peruoffset.com.pe</t>
+  </si>
+  <si>
+    <t>Patrick</t>
+  </si>
+  <si>
+    <t>percy.rojas@peruoffset.pe</t>
+  </si>
+  <si>
+    <t>Percy</t>
+  </si>
+  <si>
+    <t>pilar.flores@peruoffset.com.pe</t>
+  </si>
+  <si>
+    <t>Pilar</t>
+  </si>
+  <si>
+    <t>pmatute@termilperu.com</t>
+  </si>
+  <si>
+    <t>segundomanuelmacalupu@gmail.com</t>
+  </si>
+  <si>
+    <t>Segundo</t>
+  </si>
+  <si>
+    <t>ventas@ychiformas.com</t>
+  </si>
+  <si>
+    <t>Guillermo</t>
   </si>
 </sst>
 </file>
@@ -447,94 +579,209 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
@@ -915,6 +1162,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{2644568F-B0CD-481A-B62A-09E075749541}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85002E20-07E1-468F-9DC4-988999D8F515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3480D3-A2B2-49C7-B1D7-B9CF2D90C8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>correo</t>
   </si>
@@ -34,136 +34,10 @@
     <t>Franco</t>
   </si>
   <si>
-    <t>Carlos</t>
-  </si>
-  <si>
-    <t>Maria</t>
-  </si>
-  <si>
-    <t>Monica</t>
-  </si>
-  <si>
-    <t>Patricia</t>
-  </si>
-  <si>
     <t>ra.galane@alum.up.edu.pe</t>
   </si>
   <si>
     <t>Rodrigo</t>
-  </si>
-  <si>
-    <t>Giovanna</t>
-  </si>
-  <si>
-    <t>administracion@remugraf.com</t>
-  </si>
-  <si>
-    <t>Clever</t>
-  </si>
-  <si>
-    <t>administracion@ychiformas.com</t>
-  </si>
-  <si>
-    <t>alvespinozaalm@gmail.com</t>
-  </si>
-  <si>
-    <t>Alvaro</t>
-  </si>
-  <si>
-    <t>carias@cartolan.com</t>
-  </si>
-  <si>
-    <t>Cirilo</t>
-  </si>
-  <si>
-    <t>cmoranted@esttilodigitalsa.com</t>
-  </si>
-  <si>
-    <t>comercial@alquiler-fotocopiadora.com</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>comercializacion@ychiformas.com</t>
-  </si>
-  <si>
-    <t>contabilidad@ychiformas.com</t>
-  </si>
-  <si>
-    <t>Patrcia</t>
-  </si>
-  <si>
-    <t>contacto@alquiler-fotocopiadora.com</t>
-  </si>
-  <si>
-    <t>Telmo</t>
-  </si>
-  <si>
-    <t>creditosycobranzas@termilperu.com</t>
-  </si>
-  <si>
-    <t>Jose</t>
-  </si>
-  <si>
-    <t>fidel.reyes@pacificimpresores.com</t>
-  </si>
-  <si>
-    <t>Fidel</t>
-  </si>
-  <si>
-    <t>gerencia@ychiformas.com</t>
-  </si>
-  <si>
-    <t>grafsanisidro@gmail.com</t>
-  </si>
-  <si>
-    <t>laycolor@hotmail.com</t>
-  </si>
-  <si>
-    <t>Jaqueline</t>
-  </si>
-  <si>
-    <t>marielena.reyes@pacificimpresores.com</t>
-  </si>
-  <si>
-    <t>mshibuya@termilperu.com</t>
-  </si>
-  <si>
-    <t>Mauricio</t>
-  </si>
-  <si>
-    <t>patrick.rojas@peruoffset.com.pe</t>
-  </si>
-  <si>
-    <t>Patrick</t>
-  </si>
-  <si>
-    <t>percy.rojas@peruoffset.pe</t>
-  </si>
-  <si>
-    <t>Percy</t>
-  </si>
-  <si>
-    <t>pilar.flores@peruoffset.com.pe</t>
-  </si>
-  <si>
-    <t>Pilar</t>
-  </si>
-  <si>
-    <t>pmatute@termilperu.com</t>
-  </si>
-  <si>
-    <t>segundomanuelmacalupu@gmail.com</t>
-  </si>
-  <si>
-    <t>Segundo</t>
-  </si>
-  <si>
-    <t>ventas@ychiformas.com</t>
-  </si>
-  <si>
-    <t>Guillermo</t>
   </si>
 </sst>
 </file>
@@ -580,208 +454,98 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3480D3-A2B2-49C7-B1D7-B9CF2D90C8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C95523-FAE0-43D5-9D71-72431DCFA0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="210">
   <si>
     <t>correo</t>
   </si>
@@ -38,6 +38,618 @@
   </si>
   <si>
     <t>Rodrigo</t>
+  </si>
+  <si>
+    <t>administracion@creacioneszomac.com</t>
+  </si>
+  <si>
+    <t>Zully</t>
+  </si>
+  <si>
+    <t>blopez@blsperu.com</t>
+  </si>
+  <si>
+    <t>Borman</t>
+  </si>
+  <si>
+    <t>blsperu@hotmail.com</t>
+  </si>
+  <si>
+    <t>carmen.rozas@vicunha.com</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>cecilia.vidal20@gmail.com</t>
+  </si>
+  <si>
+    <t>Cecilia</t>
+  </si>
+  <si>
+    <t>cesar.grados@vicunha.com</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>comercial@peruvianfood.com.pe</t>
+  </si>
+  <si>
+    <t>Greysi</t>
+  </si>
+  <si>
+    <t>demauleondb@gmail.com</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <t>edemauleon@gmail.com</t>
+  </si>
+  <si>
+    <t>Emmanuel</t>
+  </si>
+  <si>
+    <t>export@tricotfinesa.com.pe</t>
+  </si>
+  <si>
+    <t>Stephanie</t>
+  </si>
+  <si>
+    <t>gadmin@camelltex.com.pe</t>
+  </si>
+  <si>
+    <t>Mirian</t>
+  </si>
+  <si>
+    <t>gerencia01@tricotfine.com.pe</t>
+  </si>
+  <si>
+    <t>Liseth</t>
+  </si>
+  <si>
+    <t>jcvidalr.2000@gmail.com</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>logistica@creacioneszomac.com</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>luciogutierrez0503@gmail.com</t>
+  </si>
+  <si>
+    <t>Lucio</t>
+  </si>
+  <si>
+    <t>maldonadocastre.enrique@gmail.com</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>migue_rrr@hotmail.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>nemeciorojas@hotmail.com</t>
+  </si>
+  <si>
+    <t>Nemecio</t>
+  </si>
+  <si>
+    <t>robert30.will@gmail.com</t>
+  </si>
+  <si>
+    <t>Gerson</t>
+  </si>
+  <si>
+    <t>silvia.seminario@vicunha.com</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>victorlevanoa@gmail.com</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>vulcano.pe@gmail.com</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>bocanegrac877@gmail.com</t>
+  </si>
+  <si>
+    <t>camila@multivende.com</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>ccicone@flow.cl</t>
+  </si>
+  <si>
+    <t>Constanza</t>
+  </si>
+  <si>
+    <t>daniel.vargas@mercadolibre.com</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>diorama4@hornail.com</t>
+  </si>
+  <si>
+    <t>Renzo</t>
+  </si>
+  <si>
+    <t>globalwisa2025@gmail.com</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>karen.huaman@mifact.net</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>karina.morenorofriguez@gmail.com</t>
+  </si>
+  <si>
+    <t>Karina</t>
+  </si>
+  <si>
+    <t>la@fenicio.io</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>lottech.ventas@gmail.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>msaldarriaga@flowpagos.com</t>
+  </si>
+  <si>
+    <t>Marilea</t>
+  </si>
+  <si>
+    <t>natalia.bobadilla@pasalaposta.pe</t>
+  </si>
+  <si>
+    <t>Natalia.</t>
+  </si>
+  <si>
+    <t>omar.cajusol@eximio.com.pe</t>
+  </si>
+  <si>
+    <t>Edinson</t>
+  </si>
+  <si>
+    <t>oneqliq2023@gmail.com</t>
+  </si>
+  <si>
+    <t>Alexcey</t>
+  </si>
+  <si>
+    <t>oralmedclinicadental@gmail.com</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>oscar.rosa@mifact.net</t>
+  </si>
+  <si>
+    <t>pablo.yanez@feniocio.io</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>pedro.white@mercadolibre.com</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>ricardorojas@blacksip.com</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>sherellyn.barreto@eximio.com.pe</t>
+  </si>
+  <si>
+    <t>Sherellyn</t>
+  </si>
+  <si>
+    <t>tledperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Franger</t>
+  </si>
+  <si>
+    <t>wthiagmr@gmail.com</t>
+  </si>
+  <si>
+    <t>Wilber</t>
+  </si>
+  <si>
+    <t>adrian@jaamsa.com</t>
+  </si>
+  <si>
+    <t>Adrián</t>
+  </si>
+  <si>
+    <t>aurora@jaamsa.com</t>
+  </si>
+  <si>
+    <t>cpaisig@tierragel.com</t>
+  </si>
+  <si>
+    <t>Christopher</t>
+  </si>
+  <si>
+    <t>dianaduran72@hotmail.com</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>eduardo@majermetal.com</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>eliseo@tierragel.com</t>
+  </si>
+  <si>
+    <t>Eliseo</t>
+  </si>
+  <si>
+    <t>estabilizador-sergios@hotmail.com</t>
+  </si>
+  <si>
+    <t>Fuo</t>
+  </si>
+  <si>
+    <t>fmontjoy@tierragel.com</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>gcespedes@asterlinsac.com</t>
+  </si>
+  <si>
+    <t>Gustavo</t>
+  </si>
+  <si>
+    <t>gilcespedes@asterlinsac.com</t>
+  </si>
+  <si>
+    <t>Gil</t>
+  </si>
+  <si>
+    <t>jdaza@jaamsa.com</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>jw.cia@infonegocio.net.pe</t>
+  </si>
+  <si>
+    <t>Juana</t>
+  </si>
+  <si>
+    <t>lespinoza@jwcia.com</t>
+  </si>
+  <si>
+    <t>Lizbeth</t>
+  </si>
+  <si>
+    <t>lucila0401@hotmail.com</t>
+  </si>
+  <si>
+    <t>Lucila</t>
+  </si>
+  <si>
+    <t>marcia@jaamsa.com</t>
+  </si>
+  <si>
+    <t>Marcia</t>
+  </si>
+  <si>
+    <t>martin.oviedo@robinsonme.com</t>
+  </si>
+  <si>
+    <t>mguer112@flu.edu</t>
+  </si>
+  <si>
+    <t>Milagritos</t>
+  </si>
+  <si>
+    <t>mvasquezp@hotmail.com</t>
+  </si>
+  <si>
+    <t>raul@majermetal.com</t>
+  </si>
+  <si>
+    <t>Raul</t>
+  </si>
+  <si>
+    <t>robinsonperu@robinsonme.com</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>vocana@jwcia.com</t>
+  </si>
+  <si>
+    <t>Agustin</t>
+  </si>
+  <si>
+    <t>ycespedes@asterlinsac.com.pe</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>aberckemeyer@contacto.com.pe</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>analuisaalva@cesce.pe</t>
+  </si>
+  <si>
+    <t>apeirano@addvalora-wmoller.com</t>
+  </si>
+  <si>
+    <t>Alfieri</t>
+  </si>
+  <si>
+    <t>cfdefil@mapfre.com.pe</t>
+  </si>
+  <si>
+    <t>contactoenlinea@contacto.com.pe</t>
+  </si>
+  <si>
+    <t>Irene</t>
+  </si>
+  <si>
+    <t>creyna@kcs.pe</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>dreyna@kallpacorredoresdeseguros.pe</t>
+  </si>
+  <si>
+    <t>Guisella</t>
+  </si>
+  <si>
+    <t>dreyna@kcs.pe</t>
+  </si>
+  <si>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>giulio.rivera@howdengroup.com</t>
+  </si>
+  <si>
+    <t>Giulio</t>
+  </si>
+  <si>
+    <t>gleon@contacto.com.pe</t>
+  </si>
+  <si>
+    <t>Guillermo</t>
+  </si>
+  <si>
+    <t>hchong@contacto.com.pe</t>
+  </si>
+  <si>
+    <t>Hernan</t>
+  </si>
+  <si>
+    <t>javierguzman@cesce.pe</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>mcotlear@mapfre.com.pe</t>
+  </si>
+  <si>
+    <t>Maritza</t>
+  </si>
+  <si>
+    <t>mcotlear@mapfreperu.com</t>
+  </si>
+  <si>
+    <t>mpaya@mapfreperu.com</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>oswaldocohaila@secrex.com.pe</t>
+  </si>
+  <si>
+    <t>Oswaldo</t>
+  </si>
+  <si>
+    <t>pmoreano@contacto.com.pe</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>pqm_91@hotmail.com</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>robertoangulo@cesce.pe</t>
+  </si>
+  <si>
+    <t>rreyna@kcs.pe</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>vsalas@mapfreperu.com</t>
+  </si>
+  <si>
+    <t>ytorriani@addvalora-wmoller.com</t>
+  </si>
+  <si>
+    <t>Yolanda</t>
+  </si>
+  <si>
+    <t>administracion@gmrc.pe</t>
+  </si>
+  <si>
+    <t>Fabiola</t>
+  </si>
+  <si>
+    <t>administracion@gsoluciones.pe</t>
+  </si>
+  <si>
+    <t>administracion@solucioneshdp.com</t>
+  </si>
+  <si>
+    <t>Ghersi</t>
+  </si>
+  <si>
+    <t>alisonreynafarjedavila@gmail.com</t>
+  </si>
+  <si>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>carlosguevara@mgdigitalcopier.com</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>carmen.diaz@mcesac.com</t>
+  </si>
+  <si>
+    <t>darwin.eventos23@gmail.com</t>
+  </si>
+  <si>
+    <t>Darwin</t>
+  </si>
+  <si>
+    <t>edwinolave@gmail.com</t>
+  </si>
+  <si>
+    <t>Edwin</t>
+  </si>
+  <si>
+    <t>esthefanycalderon.o@gmail.com</t>
+  </si>
+  <si>
+    <t>Esthefany</t>
+  </si>
+  <si>
+    <t>fernando.martinez@femago.pe</t>
+  </si>
+  <si>
+    <t>fiorella.martinez@femago.pe</t>
+  </si>
+  <si>
+    <t>Fiorella</t>
+  </si>
+  <si>
+    <t>gerencia@gmrc.pe</t>
+  </si>
+  <si>
+    <t>Donny</t>
+  </si>
+  <si>
+    <t>jaimecalderont@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>lcabanillas@apoyologistico.com.pe</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>lmcabanillas@apoyologistico.com.pe</t>
+  </si>
+  <si>
+    <t>Lisset</t>
+  </si>
+  <si>
+    <t>m.sanchez@solucioneshdp.com</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>mkong@apoyologistico.com.pe</t>
+  </si>
+  <si>
+    <t>Maya</t>
+  </si>
+  <si>
+    <t>msanchez@solucioneshdp.com</t>
+  </si>
+  <si>
+    <t>netxiomyalexandra@gmail.com</t>
+  </si>
+  <si>
+    <t>Xiomy</t>
+  </si>
+  <si>
+    <t>solucioneshdp@gmail.com</t>
+  </si>
+  <si>
+    <t>ventas@antimateriaplus.com</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>veragenice@gmail.com</t>
+  </si>
+  <si>
+    <t>Genice</t>
   </si>
 </sst>
 </file>
@@ -461,373 +1073,923 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="4"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="4"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="4"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="4"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="4"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="4"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="4"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="4"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="4"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="4"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="4"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="4"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="4"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="4"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="4"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="4"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="4"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="4"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="4"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="4"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="4"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="4"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="4"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="4"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="4"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="2"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="4"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="4"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B68" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B69" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B71" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B74" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B83" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B84" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B85" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B86" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B87" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B88" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B90" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B91" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B92" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B93" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B94" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B95" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B96" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B98" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B100" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B101" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B102" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B103" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B104" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B105" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B106" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B107" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B108" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B109" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B110" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B111" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B112" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B113" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="4"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="4"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="4"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="4"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="4"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="4"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="4"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Repositorios\Correos-Masivos-Partner-Tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318A5C5B-8163-48A1-B2F5-F84BCD0DB679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B639CE2-6065-4098-B709-5EBCA0F9ABFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +78,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -119,7 +132,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -127,6 +140,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -431,12 +446,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,7 +459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -452,7 +467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -460,467 +475,520 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="4"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="4"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="4"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="4"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="4"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="4"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="4"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="4"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="4"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="4"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="4"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="4"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="4"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="4"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="4"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="4"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="4"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="4"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="4"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="4"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="4"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="4"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="4"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="4"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="4"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="4"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="4"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="2"/>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="2"/>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="4"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="4"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="4"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="4"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="4"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="4"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="4"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="4"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="4"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="4"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="4"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="4"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="4"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="4"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="4"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="4"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="4"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="4"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="4"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="4"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="4"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="4"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="4"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="4"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="4"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="4"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="4"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="4"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="4"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="4"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="4"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="4"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="4"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="4"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="4"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="4"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="4"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="4"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
     </row>
   </sheetData>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B639CE2-6065-4098-B709-5EBCA0F9ABFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C17DD1-FB3D-4AFE-B6DA-E16A9B6D172C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="229">
   <si>
     <t>correo</t>
   </si>
@@ -38,13 +38,682 @@
   </si>
   <si>
     <t>Rodrigo</t>
+  </si>
+  <si>
+    <t>a.rivasmd@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>cchipoco@wongoftalmologos.com.pe</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>convenios@opeluce.com.pe</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>cwong@institutowong.com</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>dwong@institutowong.com</t>
+  </si>
+  <si>
+    <t>Melisa</t>
+  </si>
+  <si>
+    <t>emontenegro@opeluce.com.pe</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>gestion.adm.vm@gmail.com</t>
+  </si>
+  <si>
+    <t>Analy</t>
+  </si>
+  <si>
+    <t>globalpharma@speedy.com.pe</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>j.vega@topsaretail.com.pe</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>jechevarria@opeluce.com.pe</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>jroncal@opeluce.com.pe</t>
+  </si>
+  <si>
+    <t>Lid</t>
+  </si>
+  <si>
+    <t>lidiafigueroagiraldo938@gmail.com</t>
+  </si>
+  <si>
+    <t>Lidia</t>
+  </si>
+  <si>
+    <t>maculadt@hotmail.com</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>mejorvision2024@gmail.com</t>
+  </si>
+  <si>
+    <t>Ruth</t>
+  </si>
+  <si>
+    <t>mwong@institutowong.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>nilsaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>Nilsa</t>
+  </si>
+  <si>
+    <t>ntinageros@gmail.com</t>
+  </si>
+  <si>
+    <t>Nicanor</t>
+  </si>
+  <si>
+    <t>opticalosheroespremium@gmail.com</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>rrhh@opeluce.com.pe</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>rtambra@oftalmovissum.pe</t>
+  </si>
+  <si>
+    <t>Romina</t>
+  </si>
+  <si>
+    <t>spmontenegro@opeluce.com.pe</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>tomas3@gmail.com</t>
+  </si>
+  <si>
+    <t>Tomas</t>
+  </si>
+  <si>
+    <t>topsa@topsaretail.com.pe</t>
+  </si>
+  <si>
+    <t>Mónica</t>
+  </si>
+  <si>
+    <t>webmaster@maculadt.com</t>
+  </si>
+  <si>
+    <t>Silvio</t>
+  </si>
+  <si>
+    <t>ymuñoz@oftalmovissum.pe</t>
+  </si>
+  <si>
+    <t>Yvan</t>
+  </si>
+  <si>
+    <t>yparedesb@maculadt.com</t>
+  </si>
+  <si>
+    <t>Yovanna</t>
+  </si>
+  <si>
+    <t>acordova@andeanvet.com</t>
+  </si>
+  <si>
+    <t>Antonella</t>
+  </si>
+  <si>
+    <t>administracion@mardecolas.pe</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>angelo3rd@hotmail.com</t>
+  </si>
+  <si>
+    <t>Angelo</t>
+  </si>
+  <si>
+    <t>carul9@hotmail.com</t>
+  </si>
+  <si>
+    <t>chuari@jcmedicalsuplies.com</t>
+  </si>
+  <si>
+    <t>cjmaju22@gmail.com</t>
+  </si>
+  <si>
+    <t>Mela</t>
+  </si>
+  <si>
+    <t>cruzivett.martinez@outlook.com</t>
+  </si>
+  <si>
+    <t>Cruz</t>
+  </si>
+  <si>
+    <t>danielarondon@veterinariarondon.com</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>discoverypets@hotmail.com</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>fhinostroza@midaf.com.pe</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>gerencia@laboratoriosgyt.com</t>
+  </si>
+  <si>
+    <t>Johanes</t>
+  </si>
+  <si>
+    <t>gerenciacva24horas@gmail.com</t>
+  </si>
+  <si>
+    <t>Juana</t>
+  </si>
+  <si>
+    <t>info@santuariocochahuasi.com</t>
+  </si>
+  <si>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>jcarmona@jcmedicalsupplies.com</t>
+  </si>
+  <si>
+    <t>Johny</t>
+  </si>
+  <si>
+    <t>jefatura.comercial@jcmedicalsupplies.com</t>
+  </si>
+  <si>
+    <t>Myros</t>
+  </si>
+  <si>
+    <t>jf_penarandah@hotmail.com</t>
+  </si>
+  <si>
+    <t>joshua.gavelan@gmail.com</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>mjibaja@andeanvet.com</t>
+  </si>
+  <si>
+    <t>Mariela</t>
+  </si>
+  <si>
+    <t>pamela.suloaga@gmail.com</t>
+  </si>
+  <si>
+    <t>Pamela</t>
+  </si>
+  <si>
+    <t>psjosemartinez@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>rhinostroza@midaf.com.pe</t>
+  </si>
+  <si>
+    <t>supervisionclinicaaristocat@gmail.com</t>
+  </si>
+  <si>
+    <t>ventas@jcmedicalsupplies.com</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>veterinariapetpoint@gmail.com</t>
+  </si>
+  <si>
+    <t>Jimmy</t>
+  </si>
+  <si>
+    <t>zulmaguillen@veterinariarondon.com</t>
+  </si>
+  <si>
+    <t>Maximiliana</t>
+  </si>
+  <si>
+    <t>administracion@endomedica.com.pe</t>
+  </si>
+  <si>
+    <t>Carol</t>
+  </si>
+  <si>
+    <t>ariega@catalonia.com</t>
+  </si>
+  <si>
+    <t>bettyagapito@orprotec.com.pe</t>
+  </si>
+  <si>
+    <t>Betty</t>
+  </si>
+  <si>
+    <t>camarena.sinfronteras@gmail.com</t>
+  </si>
+  <si>
+    <t>centrosoliana@gmail.com</t>
+  </si>
+  <si>
+    <t>Karla</t>
+  </si>
+  <si>
+    <t>contabilidad@bransonsport.com</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>endoventas@gmail.com</t>
+  </si>
+  <si>
+    <t>Edson</t>
+  </si>
+  <si>
+    <t>farias@bransonsport.com</t>
+  </si>
+  <si>
+    <t>Leonidas</t>
+  </si>
+  <si>
+    <t>gialmedica@hotmail.com</t>
+  </si>
+  <si>
+    <t>Hilda</t>
+  </si>
+  <si>
+    <t>info@abl-alpstein.com</t>
+  </si>
+  <si>
+    <t>Andreas</t>
+  </si>
+  <si>
+    <t>info@orprotec.com.pe</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>l.arias@abl-alpstein.com</t>
+  </si>
+  <si>
+    <t>Lela</t>
+  </si>
+  <si>
+    <t>leocamapa@gmail.com</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>m.suyon@traumasolutions.pe</t>
+  </si>
+  <si>
+    <t>Mercedes</t>
+  </si>
+  <si>
+    <t>marcobiomecortopedia@gmail.com</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>merylintaipe@gmail.com</t>
+  </si>
+  <si>
+    <t>Merylin</t>
+  </si>
+  <si>
+    <t>mirellaleon@orprotec.com.pe</t>
+  </si>
+  <si>
+    <t>Mirella</t>
+  </si>
+  <si>
+    <t>pedro.pereda@traumasolutions.com</t>
+  </si>
+  <si>
+    <t>pedropabloarasaki@hotmail.com</t>
+  </si>
+  <si>
+    <t>rpodesta@andinamedica.com</t>
+  </si>
+  <si>
+    <t>Rosanna</t>
+  </si>
+  <si>
+    <t>rpodesta@andinamedica.com.pe</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>saesteve@catalonia.com</t>
+  </si>
+  <si>
+    <t>Salvador</t>
+  </si>
+  <si>
+    <t>servicioalcliente@endomedica.com.pe</t>
+  </si>
+  <si>
+    <t>Peggy</t>
+  </si>
+  <si>
+    <t>sonialeon@orprotec.com.pe</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>chavieri_e@hotmail.com</t>
+  </si>
+  <si>
+    <t>Erika</t>
+  </si>
+  <si>
+    <t>eespinosa@kahanlicores.pe</t>
+  </si>
+  <si>
+    <t>Emilio</t>
+  </si>
+  <si>
+    <t>ftorres@cartaviorumco.pe</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>gcabrejos@cartaviorumco.pe</t>
+  </si>
+  <si>
+    <t>Guillermo</t>
+  </si>
+  <si>
+    <t>gkahan@drokasa.com.pe</t>
+  </si>
+  <si>
+    <t>Gustavo</t>
+  </si>
+  <si>
+    <t>gschenone@dklicores.com.pe</t>
+  </si>
+  <si>
+    <t>Giulissa</t>
+  </si>
+  <si>
+    <t>jcarrascogonzales@yahoo.es</t>
+  </si>
+  <si>
+    <t>jceracio@sibaritaperu.com</t>
+  </si>
+  <si>
+    <t>Rolando</t>
+  </si>
+  <si>
+    <t>jpineda@realservice.com.pe</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>jpizarro_@hotmail.com</t>
+  </si>
+  <si>
+    <t>Hellen</t>
+  </si>
+  <si>
+    <t>juan.c.pizarro@diageo.com</t>
+  </si>
+  <si>
+    <t>lsilva@licoresmimar.net</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>monica.m.lanata@diageo.com</t>
+  </si>
+  <si>
+    <t>msilva@licoresmimar.net</t>
+  </si>
+  <si>
+    <t>olgapicon.piccoli@outlook.es</t>
+  </si>
+  <si>
+    <t>Wilmer</t>
+  </si>
+  <si>
+    <t>oscar.sastre@bp-peru.com</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>pagos@coctelpiccoli.com</t>
+  </si>
+  <si>
+    <t>Vivian</t>
+  </si>
+  <si>
+    <t>rcisneros@cartaviorumco.pe</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>realserviceperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>rkastner@cartaviorumco.pe</t>
+  </si>
+  <si>
+    <t>Johana</t>
+  </si>
+  <si>
+    <t>rodrigo.allemant@bebidaspremium.com</t>
+  </si>
+  <si>
+    <t>rodrigo.diaz@campari.com</t>
+  </si>
+  <si>
+    <t>sandraquevedo@disadm.com</t>
+  </si>
+  <si>
+    <t>vishalsabnani@hotmail.com</t>
+  </si>
+  <si>
+    <t>Miahong</t>
+  </si>
+  <si>
+    <t>apupucheg@corporacionlely.com.pe</t>
+  </si>
+  <si>
+    <t>Anny</t>
+  </si>
+  <si>
+    <t>cgomezl@corporacionlely.com.pe</t>
+  </si>
+  <si>
+    <t>cguimack@tvventas.com</t>
+  </si>
+  <si>
+    <t>Catherine</t>
+  </si>
+  <si>
+    <t>chirinos.valex@gmail.com</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>crecuenco@grupogss.com</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>d.pereyra@invitro.pe</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>diego.alvarez@conceptomovil.com</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>dirpol@dirpol.pe</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>dlevano@grupogss.com</t>
+  </si>
+  <si>
+    <t>elivillegasr@gmail.com</t>
+  </si>
+  <si>
+    <t>Elisa</t>
+  </si>
+  <si>
+    <t>fbeltran@mdybpo.com</t>
+  </si>
+  <si>
+    <t>Fausto</t>
+  </si>
+  <si>
+    <t>gescate@covisian.com</t>
+  </si>
+  <si>
+    <t>Guilermo</t>
+  </si>
+  <si>
+    <t>jcollantes@crea360.com.pe</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>jgl@tvventas.com</t>
+  </si>
+  <si>
+    <t>jp@tvventas.com</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>ksolano@grupogss.com</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>lsarmiento@avalperu.com</t>
+  </si>
+  <si>
+    <t>m.angeles@invitro.pe</t>
+  </si>
+  <si>
+    <t>Marlon</t>
+  </si>
+  <si>
+    <t>m21217412@gmail.com</t>
+  </si>
+  <si>
+    <t>mauricio@conceptomovil.com</t>
+  </si>
+  <si>
+    <t>miracel.morales@avalperu.com</t>
+  </si>
+  <si>
+    <t>Miracel</t>
+  </si>
+  <si>
+    <t>msaenz@grupogss.com</t>
+  </si>
+  <si>
+    <t>sergio@conceptomovil.com</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>yhuaman@avalperu.com</t>
+  </si>
+  <si>
+    <t>Yoshelin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,19 +747,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -132,7 +788,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -140,8 +796,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -476,402 +1130,994 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
+      <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
+      <c r="A18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
+      <c r="A19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
+      <c r="A20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
+      <c r="A21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
+      <c r="A22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
+      <c r="A23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
+      <c r="A24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
+      <c r="A25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
+      <c r="A26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
+      <c r="A27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
+      <c r="A29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
+      <c r="A31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
+      <c r="A32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
+      <c r="A33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6"/>
+      <c r="A34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
+      <c r="A35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6"/>
+      <c r="A36" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6"/>
+      <c r="A37" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
+      <c r="A38" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6"/>
+      <c r="A39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6"/>
+      <c r="A40" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
+      <c r="A41" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
+      <c r="A42" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6"/>
+      <c r="A44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
+      <c r="A45" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6"/>
+      <c r="A46" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6"/>
+      <c r="A47" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6"/>
+      <c r="A48" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6"/>
+      <c r="A49" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
+      <c r="A50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
+      <c r="A51" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
+      <c r="A52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
+      <c r="A53" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
+      <c r="A54" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="4"/>
+      <c r="A55" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
+      <c r="A56" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
+      <c r="A57" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
+      <c r="A58" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
+      <c r="A59" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
+      <c r="A60" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="4"/>
+      <c r="A61" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
+      <c r="A62" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="4"/>
+      <c r="A63" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="4"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="4"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="4"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="4"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="4"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="4"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="4"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="4"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="4"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="4"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="4"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="4"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="4"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="4"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="4"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="4"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="4"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="4"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="4"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="4"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="4"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="4"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="4"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="4"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="4"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="4"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="4"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="4"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="4"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="4"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="4"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="4"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="4"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="4"/>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="4"/>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="4"/>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="4"/>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B69" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B70" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B71" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B74" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B75" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B76" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B77" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B78" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B79" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B80" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B82" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B84" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B85" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B86" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B87" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B88" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B90" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B91" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B93" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B94" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B95" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B96" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B97" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B98" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B101" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B102" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B103" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B104" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B105" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B106" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B107" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B108" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B109" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B110" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B111" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B112" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B113" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B114" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B115" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B116" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B117" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B118" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B119" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B120" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B121" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B122" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B123" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B124" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B125" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B126" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="4"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="4"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D609FD14-DB91-46B3-A241-A9E766833B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE7806E-26A6-4F8E-9C96-6E0D52C98C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>correo</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Alexandra</t>
-  </si>
-  <si>
-    <t>Franco</t>
   </si>
 </sst>
 </file>
@@ -448,9 +445,6 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386B3ED4-3F0E-49DC-806B-EF99AF4CD591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09874AE9-8262-479F-94EE-C49C2DF8D09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="207">
   <si>
     <t>correo</t>
   </si>
@@ -46,595 +46,601 @@
     <t>Juan</t>
   </si>
   <si>
-    <t>Alberto</t>
-  </si>
-  <si>
     <t>Jorge</t>
   </si>
   <si>
     <t>Pedro</t>
   </si>
   <si>
-    <t>Wilmer</t>
-  </si>
-  <si>
     <t>Luis</t>
   </si>
   <si>
-    <t>Alfonso</t>
-  </si>
-  <si>
     <t>Carmen</t>
   </si>
   <si>
-    <t>Giovanna</t>
-  </si>
-  <si>
     <t>Rosa</t>
   </si>
   <si>
-    <t>Alfredo</t>
-  </si>
-  <si>
-    <t>Cesar</t>
-  </si>
-  <si>
-    <t>Roy</t>
-  </si>
-  <si>
     <t>Victor</t>
   </si>
   <si>
     <t>Walter</t>
   </si>
   <si>
-    <t>Denis</t>
-  </si>
-  <si>
-    <t>Eduardo</t>
-  </si>
-  <si>
-    <t>Diana</t>
-  </si>
-  <si>
-    <t>Angel</t>
-  </si>
-  <si>
-    <t>acardoso@maquinando.pe</t>
-  </si>
-  <si>
-    <t>administracion@maquinando.pe</t>
-  </si>
-  <si>
-    <t>Liszetti</t>
-  </si>
-  <si>
-    <t>aechaiz@coopacsanmiguel.pe</t>
-  </si>
-  <si>
     <t>Ana</t>
   </si>
   <si>
-    <t>anieri@visanet.com.pe</t>
-  </si>
-  <si>
-    <t>Annarita</t>
-  </si>
-  <si>
-    <t>arecelly.avalos@fogapi.com.pe</t>
-  </si>
-  <si>
-    <t>Aracelly.</t>
-  </si>
-  <si>
-    <t>asistente@tasatop.com</t>
-  </si>
-  <si>
-    <t>cecilia.obando@bpo-advisors.net</t>
-  </si>
-  <si>
-    <t>Cecilia</t>
-  </si>
-  <si>
-    <t>cferreyros@cce.com.pe</t>
-  </si>
-  <si>
-    <t>contabilidad1@jccontables.com</t>
-  </si>
-  <si>
     <t>Patricia</t>
   </si>
   <si>
-    <t>dabad@bisande.com.pe</t>
-  </si>
-  <si>
-    <t>dleon@tasatop.com</t>
-  </si>
-  <si>
     <t>Dante</t>
   </si>
   <si>
-    <t>fernanda@inversionesbloom.com</t>
-  </si>
-  <si>
-    <t>Fernanda</t>
-  </si>
-  <si>
-    <t>gleano@niubiz.com.pe</t>
-  </si>
-  <si>
-    <t>Gustavo</t>
-  </si>
-  <si>
-    <t>hcheca@niubiz.com.pe</t>
-  </si>
-  <si>
-    <t>Haydeé</t>
-  </si>
-  <si>
-    <t>josefina@joamrep.com.pe</t>
-  </si>
-  <si>
-    <t>Josefina</t>
-  </si>
-  <si>
-    <t>marcelo.mora@bpo-advisors.net</t>
-  </si>
-  <si>
-    <t>Marcelo</t>
-  </si>
-  <si>
-    <t>mariano@macgasesores.com</t>
-  </si>
-  <si>
-    <t>Mariano</t>
-  </si>
-  <si>
-    <t>marketing@coopacsanmiguel.pe</t>
-  </si>
-  <si>
-    <t>mmontenegro@niubiz.com.pe</t>
-  </si>
-  <si>
-    <t>Marisol</t>
-  </si>
-  <si>
-    <t>mvonlindenberg@prmg.net</t>
-  </si>
-  <si>
-    <t>Mili</t>
-  </si>
-  <si>
-    <t>njimenez@jccontables.com</t>
-  </si>
-  <si>
-    <t>Natividad</t>
-  </si>
-  <si>
-    <t>oscar.portocarrero@fogapi.com.pe</t>
-  </si>
-  <si>
-    <t>Oscar.</t>
-  </si>
-  <si>
-    <t>prios@cce.com.pe</t>
-  </si>
-  <si>
-    <t>rcalderon@cce.com.pe</t>
-  </si>
-  <si>
     <t>Rocio</t>
   </si>
   <si>
-    <t>rochoa@joamrep.com.pe</t>
-  </si>
-  <si>
-    <t>scondori@jccontables.com</t>
-  </si>
-  <si>
-    <t>Sonia</t>
-  </si>
-  <si>
-    <t>vflores@prmg.net</t>
-  </si>
-  <si>
-    <t>Veronica</t>
-  </si>
-  <si>
-    <t>acervantes@emanor.pe</t>
-  </si>
-  <si>
-    <t>admin@inttecin.com</t>
-  </si>
-  <si>
-    <t>administracion@reverdeceperu.com</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>andrea.victoria.castro.ayala@gmail.com</t>
-  </si>
-  <si>
     <t>Andrea</t>
   </si>
   <si>
-    <t>antonytelch@hotmail.com</t>
-  </si>
-  <si>
-    <t>Antony</t>
-  </si>
-  <si>
-    <t>berlypacheco@hotmail.com</t>
-  </si>
-  <si>
-    <t>Berli</t>
-  </si>
-  <si>
-    <t>carmen-casla@hotmail.com</t>
-  </si>
-  <si>
-    <t>ccontreras@rmconsulting.com.pe</t>
-  </si>
-  <si>
-    <t>Carolina</t>
-  </si>
-  <si>
-    <t>desarrolloyproyectos@celebrabypaolas.com</t>
-  </si>
-  <si>
-    <t>Lidia</t>
-  </si>
-  <si>
-    <t>irvinolave@gmail.com</t>
-  </si>
-  <si>
-    <t>Irvin</t>
-  </si>
-  <si>
-    <t>jcontreras@rmconsulting.com.pe</t>
-  </si>
-  <si>
-    <t>Julio</t>
-  </si>
-  <si>
-    <t>jrumayn@inttecinc.com</t>
-  </si>
-  <si>
-    <t>Jonathan</t>
-  </si>
-  <si>
-    <t>luish_28@hotmail.com</t>
-  </si>
-  <si>
-    <t>luismiguelnichojurado87@gmail.com</t>
-  </si>
-  <si>
-    <t>m-acosta2012@hotmail.com</t>
-  </si>
-  <si>
-    <t>Jessica</t>
-  </si>
-  <si>
-    <t>maggisister@gmail.com</t>
-  </si>
-  <si>
-    <t>Magaly</t>
-  </si>
-  <si>
-    <t>paolaalvarado@celebrabypaolas.com</t>
-  </si>
-  <si>
-    <t>Paola</t>
-  </si>
-  <si>
-    <t>pcontreras@rmconsulting.com.pe</t>
-  </si>
-  <si>
-    <t>Paula</t>
-  </si>
-  <si>
-    <t>produccionesquelisura@gmail.com</t>
-  </si>
-  <si>
-    <t>renee.rojas@reverdeceperu.com</t>
-  </si>
-  <si>
-    <t>Nilda</t>
-  </si>
-  <si>
-    <t>rgalvezp@inttecin.com</t>
-  </si>
-  <si>
-    <t>Susana</t>
-  </si>
-  <si>
-    <t>rminaya@gvalentinus.com</t>
-  </si>
-  <si>
-    <t>Richard</t>
-  </si>
-  <si>
-    <t>sherilyn.carpio22@gmail.com</t>
-  </si>
-  <si>
-    <t>Sherilyn</t>
-  </si>
-  <si>
-    <t>ventas@donregalo.pe</t>
-  </si>
-  <si>
-    <t>ventas@reverdeceperu.com</t>
-  </si>
-  <si>
-    <t>vrlaserna2011@gmail.com</t>
-  </si>
-  <si>
-    <t>zhernandez@propuse.com.pe</t>
-  </si>
-  <si>
-    <t>Zaadit</t>
-  </si>
-  <si>
-    <t>administracion@fyrcom.com.pe</t>
-  </si>
-  <si>
-    <t>Evelyn</t>
-  </si>
-  <si>
-    <t>admrosynol@gmail.com</t>
-  </si>
-  <si>
-    <t>americawlr@hotmail.com</t>
-  </si>
-  <si>
-    <t>Raquel</t>
-  </si>
-  <si>
-    <t>aunnotiene@gmail.com</t>
-  </si>
-  <si>
-    <t>Marlene</t>
-  </si>
-  <si>
-    <t>bbarrantes1398@gmail.com</t>
-  </si>
-  <si>
-    <t>Brad</t>
-  </si>
-  <si>
-    <t>carlosrubiobond@yahoo.com.mx</t>
-  </si>
-  <si>
-    <t>crommets_pst@hotmail.com</t>
-  </si>
-  <si>
-    <t>Pelagio</t>
-  </si>
-  <si>
-    <t>dalinfernandez@gmail.com</t>
-  </si>
-  <si>
-    <t>Dallin</t>
-  </si>
-  <si>
-    <t>gargumedo@ihuasa.com.pe</t>
-  </si>
-  <si>
-    <t>Gabriela</t>
-  </si>
-  <si>
-    <t>gerencia@byvgroupimport.com</t>
-  </si>
-  <si>
-    <t>Rogelio</t>
-  </si>
-  <si>
-    <t>giova_sl@hotmail.com</t>
-  </si>
-  <si>
-    <t>globalcromperu@gmail.com</t>
-  </si>
-  <si>
-    <t>ihuasa@hotmail.com</t>
-  </si>
-  <si>
-    <t>Rosber</t>
-  </si>
-  <si>
-    <t>importaciones@ditersa.com</t>
-  </si>
-  <si>
-    <t>jalarcon@fyrcom.com.pe</t>
-  </si>
-  <si>
-    <t>jmseas@ditersa.com</t>
-  </si>
-  <si>
-    <t>katherine201822@gmail.com</t>
-  </si>
-  <si>
-    <t>Katherine</t>
-  </si>
-  <si>
-    <t>magdae@alarinsa.com</t>
-  </si>
-  <si>
-    <t>Bernardete</t>
-  </si>
-  <si>
-    <t>magdoniaconsultoria1@gmail.com</t>
-  </si>
-  <si>
-    <t>Magdonia</t>
-  </si>
-  <si>
-    <t>marcostorrey@gmail.com</t>
-  </si>
-  <si>
-    <t>Marcos</t>
-  </si>
-  <si>
-    <t>mario@swift.pe</t>
-  </si>
-  <si>
-    <t>Mario</t>
-  </si>
-  <si>
-    <t>mdelacruz@ddperu.com.pe</t>
-  </si>
-  <si>
-    <t>Margarita</t>
-  </si>
-  <si>
-    <t>nolberto2811@hotmail.com</t>
-  </si>
-  <si>
-    <t>Gregorio</t>
-  </si>
-  <si>
-    <t>rkalice.136@gmail.com</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>sandraval@ditersa.com</t>
-  </si>
-  <si>
-    <t>Sara</t>
-  </si>
-  <si>
-    <t>ventas@fyrcomsrl.com</t>
-  </si>
-  <si>
-    <t>Shirley</t>
-  </si>
-  <si>
-    <t>wlarar@yahoo.es</t>
-  </si>
-  <si>
-    <t>administracion@serviciosempresarialesperu.com</t>
-  </si>
-  <si>
-    <t>Cinthya</t>
-  </si>
-  <si>
-    <t>administracion@tfm.pe</t>
-  </si>
-  <si>
-    <t>alfonso.ibaceta@tea.com.pe</t>
-  </si>
-  <si>
-    <t>cmendiola@serviciosempresariales.com</t>
-  </si>
-  <si>
-    <t>cnrengifo@vhrperu.com</t>
-  </si>
-  <si>
-    <t>comercial@areyaku.com.pe</t>
-  </si>
-  <si>
-    <t>czavala@domusperu.com</t>
-  </si>
-  <si>
-    <t>fschwarz@ecocentury.pe</t>
-  </si>
-  <si>
-    <t>Franz</t>
-  </si>
-  <si>
-    <t>giuseppe.jacinto@ecoseam.com.pe</t>
-  </si>
-  <si>
-    <t>Giuseppe</t>
-  </si>
-  <si>
-    <t>icee@ecocentury.pe</t>
-  </si>
-  <si>
-    <t>ingenieros@corehidro.com.pe</t>
-  </si>
-  <si>
-    <t>jfalckenheiner@ecocentury.pe</t>
-  </si>
-  <si>
-    <t>jflores@awsperu.com</t>
-  </si>
-  <si>
-    <t>jimena.jacinto@ecoseam.com.pe</t>
-  </si>
-  <si>
-    <t>Jimena</t>
-  </si>
-  <si>
-    <t>kreyes@domusperu.com</t>
-  </si>
-  <si>
-    <t>Kelvin</t>
-  </si>
-  <si>
-    <t>moises.flores@awsperu.com</t>
-  </si>
-  <si>
-    <t>Moises</t>
-  </si>
-  <si>
-    <t>mrosales@enviroclean.pe</t>
-  </si>
-  <si>
-    <t>Madeleine</t>
-  </si>
-  <si>
-    <t>nisk@ecocentury.pe</t>
-  </si>
-  <si>
-    <t>Niscar</t>
-  </si>
-  <si>
-    <t>operaciones@tfm.pe</t>
-  </si>
-  <si>
-    <t>postmast@domusperu.com</t>
-  </si>
-  <si>
-    <t>Mariela</t>
-  </si>
-  <si>
-    <t>rcastillo@awsperu.com</t>
-  </si>
-  <si>
-    <t>Rebeca</t>
-  </si>
-  <si>
-    <t>rtarazona@domusperu.com</t>
-  </si>
-  <si>
-    <t>Ruben</t>
-  </si>
-  <si>
-    <t>ventas@lugoraservice.com.pe</t>
-  </si>
-  <si>
-    <t>Hector</t>
-  </si>
-  <si>
-    <t>vhrengifo@vhrperu.com</t>
-  </si>
-  <si>
-    <t>wilmer.muñoz@ecoseam.com.pe</t>
-  </si>
-  <si>
-    <t>zeyla.huaman@ecoseam.com.pe</t>
-  </si>
-  <si>
-    <t>Zeyla</t>
-  </si>
-  <si>
-    <t>zrosales@enviroclean.pe</t>
-  </si>
-  <si>
-    <t>Zulma</t>
+    <t>abinaggia@suminoxaceros.com</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>aponte@frionox.com</t>
+  </si>
+  <si>
+    <t>bbautista@moservin.pe</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>contabilidad@frionox.com</t>
+  </si>
+  <si>
+    <t>contabilidad2@frionox.com</t>
+  </si>
+  <si>
+    <t>Gisella</t>
+  </si>
+  <si>
+    <t>corpbomhys@outllok.com</t>
+  </si>
+  <si>
+    <t>Bonifacio</t>
+  </si>
+  <si>
+    <t>enrique.harster@prodac.pe</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>fmoreno@fumosac.com.pe</t>
+  </si>
+  <si>
+    <t>herca@speedy.com.pe</t>
+  </si>
+  <si>
+    <t>Hernan</t>
+  </si>
+  <si>
+    <t>hugo.palomino@cipesa.net</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>jheremy.laurrano@gmail.com</t>
+  </si>
+  <si>
+    <t>Jheremy</t>
+  </si>
+  <si>
+    <t>kadefsac@gmail.com</t>
+  </si>
+  <si>
+    <t>Dennis</t>
+  </si>
+  <si>
+    <t>karla.valdez@prodac.pe</t>
+  </si>
+  <si>
+    <t>Karla</t>
+  </si>
+  <si>
+    <t>lilian.zapata@cipesa.net</t>
+  </si>
+  <si>
+    <t>Lilian</t>
+  </si>
+  <si>
+    <t>lizet.valencia@prodac.pe</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>logistica@acerosmoservin.pe</t>
+  </si>
+  <si>
+    <t>monica.forsberg@cipesa.net</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>moservin@hotmail.com</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>mvaldez@frionox.com</t>
+  </si>
+  <si>
+    <t>nrq_ingenieros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Hilda</t>
+  </si>
+  <si>
+    <t>ogarcia@benertec.com</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>recepcion@frionox.com</t>
+  </si>
+  <si>
+    <t>rosana.almestar@cipesa.pe</t>
+  </si>
+  <si>
+    <t>Rosana</t>
+  </si>
+  <si>
+    <t>ssedano@suminoxaceros.net</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>tesoreria@cipesa.pe</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <t>ventas.elevacomascensores@gmail.com</t>
+  </si>
+  <si>
+    <t>Alison</t>
+  </si>
+  <si>
+    <t>vmarquina@prodac.com.pe</t>
+  </si>
+  <si>
+    <t>Víctor</t>
+  </si>
+  <si>
+    <t>yalvarado@fumosac.com.pe</t>
+  </si>
+  <si>
+    <t>Yisela</t>
+  </si>
+  <si>
+    <t>administracion@velkoncargo.com</t>
+  </si>
+  <si>
+    <t>Isacc</t>
+  </si>
+  <si>
+    <t>andreay@itcperu.com</t>
+  </si>
+  <si>
+    <t>apena@cargobusiness.com.pe</t>
+  </si>
+  <si>
+    <t>arojas@southexpress.cl</t>
+  </si>
+  <si>
+    <t>Alejandra</t>
+  </si>
+  <si>
+    <t>contabilidad@velkoncargo.com</t>
+  </si>
+  <si>
+    <t>Marian</t>
+  </si>
+  <si>
+    <t>ddiaz@tclisac.com</t>
+  </si>
+  <si>
+    <t>Dany</t>
+  </si>
+  <si>
+    <t>duezo@tclisac.com</t>
+  </si>
+  <si>
+    <t>evinatea@cargobusiness.com.pe</t>
+  </si>
+  <si>
+    <t>finanzas@caplogistic.com.pe</t>
+  </si>
+  <si>
+    <t>frank.monroy@impexwk.com</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>fromero@cargobusiness.com.pe</t>
+  </si>
+  <si>
+    <t>gaf@trans-solution.pe</t>
+  </si>
+  <si>
+    <t>Sindhey</t>
+  </si>
+  <si>
+    <t>gerencia@trans-solution.pe</t>
+  </si>
+  <si>
+    <t>Juana</t>
+  </si>
+  <si>
+    <t>info@cargoconnect.com.pe</t>
+  </si>
+  <si>
+    <t>jhon.anticona@star-ol.com</t>
+  </si>
+  <si>
+    <t>Jhon</t>
+  </si>
+  <si>
+    <t>jnalvarte@adlogisticsperu.com</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>logistica@adlogisticsperu.com</t>
+  </si>
+  <si>
+    <t>Deybi</t>
+  </si>
+  <si>
+    <t>lsilva@adlogisticsperu.com</t>
+  </si>
+  <si>
+    <t>mbautista@itcperu.com</t>
+  </si>
+  <si>
+    <t>Miriam</t>
+  </si>
+  <si>
+    <t>mzavala@curtis.com.pe</t>
+  </si>
+  <si>
+    <t>Milagros</t>
+  </si>
+  <si>
+    <t>operaciones1@southexpress.pe</t>
+  </si>
+  <si>
+    <t>pfernandez@southexpress.pe</t>
+  </si>
+  <si>
+    <t>Pamela</t>
+  </si>
+  <si>
+    <t>romina.bracamonte@star-ol.com</t>
+  </si>
+  <si>
+    <t>Lisset</t>
+  </si>
+  <si>
+    <t>rosmery.luque@impexwk.com</t>
+  </si>
+  <si>
+    <t>Rosmery</t>
+  </si>
+  <si>
+    <t>smazure@cargobusiness.com.pe</t>
+  </si>
+  <si>
+    <t>ventas@caplogistic.com.pe</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>waldocarrasco@southexpress.cl</t>
+  </si>
+  <si>
+    <t>Waldo</t>
+  </si>
+  <si>
+    <t>watzer.monroy@impexwk.com</t>
+  </si>
+  <si>
+    <t>Watzer</t>
+  </si>
+  <si>
+    <t>administracion@creativeg.net</t>
+  </si>
+  <si>
+    <t>angela.sifuentes058@gmail.com</t>
+  </si>
+  <si>
+    <t>aym-srl@lapicerosypublicidad.pe</t>
+  </si>
+  <si>
+    <t>Andres</t>
+  </si>
+  <si>
+    <t>cchiang@3nch.biz</t>
+  </si>
+  <si>
+    <t>Aida</t>
+  </si>
+  <si>
+    <t>cimmesersrl@hotmail.com</t>
+  </si>
+  <si>
+    <t>creativegiftsperu@yahoo.com</t>
+  </si>
+  <si>
+    <t>Mauricio</t>
+  </si>
+  <si>
+    <t>ctcruzr24@gmail.com</t>
+  </si>
+  <si>
+    <t>Coraly</t>
+  </si>
+  <si>
+    <t>ecabrera_2805@hotmail.com</t>
+  </si>
+  <si>
+    <t>Eunice</t>
+  </si>
+  <si>
+    <t>esarpublicidad@gmail.com</t>
+  </si>
+  <si>
+    <t>Elida</t>
+  </si>
+  <si>
+    <t>eurbano@eyfimport.com</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>gamboa_camasca@gmail.com</t>
+  </si>
+  <si>
+    <t>Teodomiro</t>
+  </si>
+  <si>
+    <t>hmiranda@3nch.biz</t>
+  </si>
+  <si>
+    <t>importaciones@creativeg.net</t>
+  </si>
+  <si>
+    <t>info@acrilicosperu.com</t>
+  </si>
+  <si>
+    <t>Renzo</t>
+  </si>
+  <si>
+    <t>jhidalgo@3nch.biz</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>jogarciape@gmail.com</t>
+  </si>
+  <si>
+    <t>jzuazo@promos.com.pe</t>
+  </si>
+  <si>
+    <t>lbmservicios@hotmail.com</t>
+  </si>
+  <si>
+    <t>Lorenzo</t>
+  </si>
+  <si>
+    <t>lchavezesteban@gmail.com</t>
+  </si>
+  <si>
+    <t>luisfelipegarcia@hotmail.com</t>
+  </si>
+  <si>
+    <t>marycabrera18@hotmail.com</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>melinaodar@gmail.com</t>
+  </si>
+  <si>
+    <t>Melina</t>
+  </si>
+  <si>
+    <t>nicoleparedesstudio@gmail.com</t>
+  </si>
+  <si>
+    <t>Nicole</t>
+  </si>
+  <si>
+    <t>recepcion@a1premium.com.pe</t>
+  </si>
+  <si>
+    <t>riza@promos.com.pe</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>tesoreria_publi@outlook.com</t>
+  </si>
+  <si>
+    <t>Cenaida</t>
+  </si>
+  <si>
+    <t>ventasbrasil@grupojosegarcia.com</t>
+  </si>
+  <si>
+    <t>victorraul@grupodragma.com</t>
+  </si>
+  <si>
+    <t>alexander@naybetravel.com</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>amiranda@naybetravel.com</t>
+  </si>
+  <si>
+    <t>Marithza</t>
+  </si>
+  <si>
+    <t>carmen@viajesterranova.com.pe</t>
+  </si>
+  <si>
+    <t>carmenolmos@hotelmajoro.com</t>
+  </si>
+  <si>
+    <t>christopherterry@hostal110.com</t>
+  </si>
+  <si>
+    <t>Christopher</t>
+  </si>
+  <si>
+    <t>cindixwang@kingdomhotelperu.com</t>
+  </si>
+  <si>
+    <t>Yingy</t>
+  </si>
+  <si>
+    <t>comercial@kingdomhotelperu.com</t>
+  </si>
+  <si>
+    <t>Erika</t>
+  </si>
+  <si>
+    <t>ebulmes@hoteleltumi.com</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>elva.cordova@hotelcarrera.com.pe</t>
+  </si>
+  <si>
+    <t>Elva</t>
+  </si>
+  <si>
+    <t>emanuel@escapemundial.com</t>
+  </si>
+  <si>
+    <t>Emanuel</t>
+  </si>
+  <si>
+    <t>enrique@vicac.pe</t>
+  </si>
+  <si>
+    <t>enriquepasrdo@hotelmajoro.com</t>
+  </si>
+  <si>
+    <t>hola@aventurismo-travel.com</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>hotelesbelen@hotmail.com</t>
+  </si>
+  <si>
+    <t>Raymundo</t>
+  </si>
+  <si>
+    <t>hotellosapus@gmail.com</t>
+  </si>
+  <si>
+    <t>isabel@vipac.pe</t>
+  </si>
+  <si>
+    <t>javier@vipac.pe</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>jmfelices@invertur.com.pe</t>
+  </si>
+  <si>
+    <t>lps@invertur.com.pe</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>maritebazo@hotelmajoro.com</t>
+  </si>
+  <si>
+    <t>marketing@kingdomhotelperu.com</t>
+  </si>
+  <si>
+    <t>Makarena</t>
+  </si>
+  <si>
+    <t>maureen.n@hotelcarrera.com.pe</t>
+  </si>
+  <si>
+    <t>Maureen</t>
+  </si>
+  <si>
+    <t>patricia@vipac.pe</t>
+  </si>
+  <si>
+    <t>reservas@hotelcarrera.com.pe</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>sadr@kingdomhotelperu.com</t>
+  </si>
+  <si>
+    <t>Zhijian</t>
+  </si>
+  <si>
+    <t>viajesydestinos26@gmail.co</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>viajesydestinossac@gmail.com</t>
+  </si>
+  <si>
+    <t>Luisa</t>
+  </si>
+  <si>
+    <t>wilmantour@hotmail.com</t>
+  </si>
+  <si>
+    <t>Wilman</t>
   </si>
 </sst>
 </file>
@@ -1059,672 +1065,672 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B63" t="s">
-        <v>7</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B66" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B76" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B77" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B80" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B81" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B82" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B83" t="s">
-        <v>162</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B85" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B86" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -1732,245 +1738,265 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B88" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
+        <v>163</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B90" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B92" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B93" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B94" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B95" t="s">
-        <v>22</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>181</v>
+        <v>31</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>183</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B101" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B102" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B103" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B104" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B105" t="s">
-        <v>194</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B106" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B107" t="s">
-        <v>198</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B108" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B110" t="s">
-        <v>202</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B111" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B112" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B113" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B114" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="4"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B115" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="4"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="4"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="4"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="4"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="4"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="4"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="4"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="4"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="4"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09874AE9-8262-479F-94EE-C49C2DF8D09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A3C6B6-1153-4C8C-AB26-BF86891B5CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,598 +49,598 @@
     <t>Jorge</t>
   </si>
   <si>
-    <t>Pedro</t>
-  </si>
-  <si>
     <t>Luis</t>
   </si>
   <si>
-    <t>Carmen</t>
-  </si>
-  <si>
     <t>Rosa</t>
   </si>
   <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>Walter</t>
-  </si>
-  <si>
     <t>Ana</t>
   </si>
   <si>
     <t>Patricia</t>
   </si>
   <si>
-    <t>Dante</t>
-  </si>
-  <si>
-    <t>Rocio</t>
-  </si>
-  <si>
-    <t>Andrea</t>
-  </si>
-  <si>
-    <t>abinaggia@suminoxaceros.com</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>aponte@frionox.com</t>
-  </si>
-  <si>
-    <t>bbautista@moservin.pe</t>
-  </si>
-  <si>
-    <t>Brian</t>
-  </si>
-  <si>
-    <t>contabilidad@frionox.com</t>
-  </si>
-  <si>
-    <t>contabilidad2@frionox.com</t>
-  </si>
-  <si>
-    <t>Gisella</t>
-  </si>
-  <si>
-    <t>corpbomhys@outllok.com</t>
-  </si>
-  <si>
-    <t>Bonifacio</t>
-  </si>
-  <si>
-    <t>enrique.harster@prodac.pe</t>
-  </si>
-  <si>
-    <t>Enrique</t>
-  </si>
-  <si>
-    <t>fmoreno@fumosac.com.pe</t>
-  </si>
-  <si>
-    <t>herca@speedy.com.pe</t>
-  </si>
-  <si>
-    <t>Hernan</t>
-  </si>
-  <si>
-    <t>hugo.palomino@cipesa.net</t>
-  </si>
-  <si>
-    <t>Hugo</t>
-  </si>
-  <si>
-    <t>jheremy.laurrano@gmail.com</t>
-  </si>
-  <si>
-    <t>Jheremy</t>
-  </si>
-  <si>
-    <t>kadefsac@gmail.com</t>
-  </si>
-  <si>
-    <t>Dennis</t>
-  </si>
-  <si>
-    <t>karla.valdez@prodac.pe</t>
-  </si>
-  <si>
-    <t>Karla</t>
-  </si>
-  <si>
-    <t>lilian.zapata@cipesa.net</t>
-  </si>
-  <si>
-    <t>Lilian</t>
-  </si>
-  <si>
-    <t>lizet.valencia@prodac.pe</t>
-  </si>
-  <si>
     <t>Manuel</t>
   </si>
   <si>
-    <t>logistica@acerosmoservin.pe</t>
-  </si>
-  <si>
-    <t>monica.forsberg@cipesa.net</t>
-  </si>
-  <si>
-    <t>Monica</t>
-  </si>
-  <si>
-    <t>moservin@hotmail.com</t>
-  </si>
-  <si>
     <t>Carlos</t>
   </si>
   <si>
-    <t>mvaldez@frionox.com</t>
-  </si>
-  <si>
-    <t>nrq_ingenieros@hotmail.com</t>
-  </si>
-  <si>
     <t>Hilda</t>
   </si>
   <si>
-    <t>ogarcia@benertec.com</t>
-  </si>
-  <si>
-    <t>Orlando</t>
-  </si>
-  <si>
-    <t>recepcion@frionox.com</t>
-  </si>
-  <si>
-    <t>rosana.almestar@cipesa.pe</t>
-  </si>
-  <si>
-    <t>Rosana</t>
-  </si>
-  <si>
-    <t>ssedano@suminoxaceros.net</t>
-  </si>
-  <si>
-    <t>Silvia</t>
-  </si>
-  <si>
-    <t>tesoreria@cipesa.pe</t>
-  </si>
-  <si>
-    <t>Isabel</t>
-  </si>
-  <si>
-    <t>ventas.elevacomascensores@gmail.com</t>
-  </si>
-  <si>
-    <t>Alison</t>
-  </si>
-  <si>
-    <t>vmarquina@prodac.com.pe</t>
-  </si>
-  <si>
     <t>Víctor</t>
   </si>
   <si>
-    <t>yalvarado@fumosac.com.pe</t>
-  </si>
-  <si>
-    <t>Yisela</t>
-  </si>
-  <si>
-    <t>administracion@velkoncargo.com</t>
-  </si>
-  <si>
-    <t>Isacc</t>
-  </si>
-  <si>
-    <t>andreay@itcperu.com</t>
-  </si>
-  <si>
-    <t>apena@cargobusiness.com.pe</t>
-  </si>
-  <si>
-    <t>arojas@southexpress.cl</t>
-  </si>
-  <si>
-    <t>Alejandra</t>
-  </si>
-  <si>
-    <t>contabilidad@velkoncargo.com</t>
-  </si>
-  <si>
-    <t>Marian</t>
-  </si>
-  <si>
-    <t>ddiaz@tclisac.com</t>
-  </si>
-  <si>
-    <t>Dany</t>
-  </si>
-  <si>
-    <t>duezo@tclisac.com</t>
-  </si>
-  <si>
-    <t>evinatea@cargobusiness.com.pe</t>
-  </si>
-  <si>
-    <t>finanzas@caplogistic.com.pe</t>
-  </si>
-  <si>
-    <t>frank.monroy@impexwk.com</t>
-  </si>
-  <si>
-    <t>Frank</t>
-  </si>
-  <si>
-    <t>fromero@cargobusiness.com.pe</t>
-  </si>
-  <si>
-    <t>gaf@trans-solution.pe</t>
-  </si>
-  <si>
-    <t>Sindhey</t>
-  </si>
-  <si>
-    <t>gerencia@trans-solution.pe</t>
-  </si>
-  <si>
     <t>Juana</t>
   </si>
   <si>
-    <t>info@cargoconnect.com.pe</t>
-  </si>
-  <si>
-    <t>jhon.anticona@star-ol.com</t>
-  </si>
-  <si>
-    <t>Jhon</t>
-  </si>
-  <si>
-    <t>jnalvarte@adlogisticsperu.com</t>
-  </si>
-  <si>
-    <t>Jose</t>
-  </si>
-  <si>
-    <t>logistica@adlogisticsperu.com</t>
-  </si>
-  <si>
-    <t>Deybi</t>
-  </si>
-  <si>
-    <t>lsilva@adlogisticsperu.com</t>
-  </si>
-  <si>
-    <t>mbautista@itcperu.com</t>
-  </si>
-  <si>
-    <t>Miriam</t>
-  </si>
-  <si>
-    <t>mzavala@curtis.com.pe</t>
-  </si>
-  <si>
-    <t>Milagros</t>
-  </si>
-  <si>
-    <t>operaciones1@southexpress.pe</t>
-  </si>
-  <si>
-    <t>pfernandez@southexpress.pe</t>
-  </si>
-  <si>
-    <t>Pamela</t>
-  </si>
-  <si>
-    <t>romina.bracamonte@star-ol.com</t>
-  </si>
-  <si>
-    <t>Lisset</t>
-  </si>
-  <si>
-    <t>rosmery.luque@impexwk.com</t>
-  </si>
-  <si>
-    <t>Rosmery</t>
-  </si>
-  <si>
-    <t>smazure@cargobusiness.com.pe</t>
-  </si>
-  <si>
-    <t>ventas@caplogistic.com.pe</t>
-  </si>
-  <si>
-    <t>Christian</t>
-  </si>
-  <si>
-    <t>waldocarrasco@southexpress.cl</t>
-  </si>
-  <si>
-    <t>Waldo</t>
-  </si>
-  <si>
-    <t>watzer.monroy@impexwk.com</t>
-  </si>
-  <si>
-    <t>Watzer</t>
-  </si>
-  <si>
-    <t>administracion@creativeg.net</t>
-  </si>
-  <si>
-    <t>angela.sifuentes058@gmail.com</t>
-  </si>
-  <si>
-    <t>aym-srl@lapicerosypublicidad.pe</t>
-  </si>
-  <si>
-    <t>Andres</t>
-  </si>
-  <si>
-    <t>cchiang@3nch.biz</t>
-  </si>
-  <si>
-    <t>Aida</t>
-  </si>
-  <si>
-    <t>cimmesersrl@hotmail.com</t>
-  </si>
-  <si>
-    <t>creativegiftsperu@yahoo.com</t>
-  </si>
-  <si>
-    <t>Mauricio</t>
-  </si>
-  <si>
-    <t>ctcruzr24@gmail.com</t>
-  </si>
-  <si>
-    <t>Coraly</t>
-  </si>
-  <si>
-    <t>ecabrera_2805@hotmail.com</t>
-  </si>
-  <si>
-    <t>Eunice</t>
-  </si>
-  <si>
-    <t>esarpublicidad@gmail.com</t>
-  </si>
-  <si>
-    <t>Elida</t>
-  </si>
-  <si>
-    <t>eurbano@eyfimport.com</t>
-  </si>
-  <si>
-    <t>Edgar</t>
-  </si>
-  <si>
-    <t>gamboa_camasca@gmail.com</t>
-  </si>
-  <si>
-    <t>Teodomiro</t>
-  </si>
-  <si>
-    <t>hmiranda@3nch.biz</t>
-  </si>
-  <si>
-    <t>importaciones@creativeg.net</t>
-  </si>
-  <si>
-    <t>info@acrilicosperu.com</t>
-  </si>
-  <si>
-    <t>Renzo</t>
-  </si>
-  <si>
-    <t>jhidalgo@3nch.biz</t>
-  </si>
-  <si>
-    <t>Franklin</t>
-  </si>
-  <si>
-    <t>jogarciape@gmail.com</t>
-  </si>
-  <si>
-    <t>jzuazo@promos.com.pe</t>
-  </si>
-  <si>
-    <t>lbmservicios@hotmail.com</t>
-  </si>
-  <si>
-    <t>Lorenzo</t>
-  </si>
-  <si>
-    <t>lchavezesteban@gmail.com</t>
-  </si>
-  <si>
-    <t>luisfelipegarcia@hotmail.com</t>
-  </si>
-  <si>
-    <t>marycabrera18@hotmail.com</t>
-  </si>
-  <si>
-    <t>Mary</t>
-  </si>
-  <si>
-    <t>melinaodar@gmail.com</t>
-  </si>
-  <si>
-    <t>Melina</t>
-  </si>
-  <si>
-    <t>nicoleparedesstudio@gmail.com</t>
-  </si>
-  <si>
-    <t>Nicole</t>
-  </si>
-  <si>
-    <t>recepcion@a1premium.com.pe</t>
-  </si>
-  <si>
-    <t>riza@promos.com.pe</t>
-  </si>
-  <si>
-    <t>Rafael</t>
-  </si>
-  <si>
-    <t>tesoreria_publi@outlook.com</t>
-  </si>
-  <si>
-    <t>Cenaida</t>
-  </si>
-  <si>
-    <t>ventasbrasil@grupojosegarcia.com</t>
-  </si>
-  <si>
-    <t>victorraul@grupodragma.com</t>
-  </si>
-  <si>
-    <t>alexander@naybetravel.com</t>
-  </si>
-  <si>
-    <t>Alexander</t>
-  </si>
-  <si>
-    <t>amiranda@naybetravel.com</t>
-  </si>
-  <si>
-    <t>Marithza</t>
-  </si>
-  <si>
-    <t>carmen@viajesterranova.com.pe</t>
-  </si>
-  <si>
-    <t>carmenolmos@hotelmajoro.com</t>
-  </si>
-  <si>
-    <t>christopherterry@hostal110.com</t>
-  </si>
-  <si>
-    <t>Christopher</t>
-  </si>
-  <si>
-    <t>cindixwang@kingdomhotelperu.com</t>
-  </si>
-  <si>
-    <t>Yingy</t>
-  </si>
-  <si>
-    <t>comercial@kingdomhotelperu.com</t>
-  </si>
-  <si>
-    <t>Erika</t>
-  </si>
-  <si>
-    <t>ebulmes@hoteleltumi.com</t>
-  </si>
-  <si>
     <t>Elizabeth</t>
   </si>
   <si>
-    <t>elva.cordova@hotelcarrera.com.pe</t>
-  </si>
-  <si>
     <t>Elva</t>
   </si>
   <si>
-    <t>emanuel@escapemundial.com</t>
-  </si>
-  <si>
-    <t>Emanuel</t>
-  </si>
-  <si>
-    <t>enrique@vicac.pe</t>
-  </si>
-  <si>
-    <t>enriquepasrdo@hotelmajoro.com</t>
-  </si>
-  <si>
-    <t>hola@aventurismo-travel.com</t>
-  </si>
-  <si>
     <t>Daniel</t>
   </si>
   <si>
-    <t>hotelesbelen@hotmail.com</t>
-  </si>
-  <si>
-    <t>Raymundo</t>
-  </si>
-  <si>
-    <t>hotellosapus@gmail.com</t>
-  </si>
-  <si>
-    <t>isabel@vipac.pe</t>
-  </si>
-  <si>
-    <t>javier@vipac.pe</t>
-  </si>
-  <si>
     <t>Javier</t>
   </si>
   <si>
-    <t>jmfelices@invertur.com.pe</t>
-  </si>
-  <si>
-    <t>lps@invertur.com.pe</t>
-  </si>
-  <si>
-    <t>Liliana</t>
-  </si>
-  <si>
-    <t>maritebazo@hotelmajoro.com</t>
-  </si>
-  <si>
-    <t>marketing@kingdomhotelperu.com</t>
-  </si>
-  <si>
-    <t>Makarena</t>
-  </si>
-  <si>
-    <t>maureen.n@hotelcarrera.com.pe</t>
-  </si>
-  <si>
-    <t>Maureen</t>
-  </si>
-  <si>
-    <t>patricia@vipac.pe</t>
-  </si>
-  <si>
-    <t>reservas@hotelcarrera.com.pe</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>sadr@kingdomhotelperu.com</t>
-  </si>
-  <si>
-    <t>Zhijian</t>
-  </si>
-  <si>
-    <t>viajesydestinos26@gmail.co</t>
-  </si>
-  <si>
-    <t>Camila</t>
-  </si>
-  <si>
-    <t>viajesydestinossac@gmail.com</t>
-  </si>
-  <si>
-    <t>Luisa</t>
-  </si>
-  <si>
-    <t>wilmantour@hotmail.com</t>
-  </si>
-  <si>
-    <t>Wilman</t>
+    <t>adm.general@casalindaperu.com</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>adminhc@signomed.com</t>
+  </si>
+  <si>
+    <t>administracion@copemo.com.pe</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>amarquez@casalindaperu.com</t>
+  </si>
+  <si>
+    <t>Alejandro</t>
+  </si>
+  <si>
+    <t>antoalsac.ventas@gmail.com</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>antonieta.aliaga@lumicenter.com.pe</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>areacontable@casalindaperu.com</t>
+  </si>
+  <si>
+    <t>Zenina</t>
+  </si>
+  <si>
+    <t>atesoreria@casalindaperu.com</t>
+  </si>
+  <si>
+    <t>Romario</t>
+  </si>
+  <si>
+    <t>comercial@interandinomuebles.com</t>
+  </si>
+  <si>
+    <t>ertesa.homecenter@gmail.com</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>etorres@magensa.com</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>gallardojesus907@gmail.com</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>gerencia@multimuebles.pe</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>hgonzalez@casalindaperu.com</t>
+  </si>
+  <si>
+    <t>Hector</t>
+  </si>
+  <si>
+    <t>humberto.moreno@signomed.com</t>
+  </si>
+  <si>
+    <t>Humberto</t>
+  </si>
+  <si>
+    <t>jcrodasf26@gmail.com</t>
+  </si>
+  <si>
+    <t>jesusmarquez@casalindaperu.com</t>
+  </si>
+  <si>
+    <t>jimisco@grupoimcesa.com.pe</t>
+  </si>
+  <si>
+    <t>Jimis</t>
+  </si>
+  <si>
+    <t>magensa@magensa.com</t>
+  </si>
+  <si>
+    <t>Zoila</t>
+  </si>
+  <si>
+    <t>mmarquez@casalindaperu.com</t>
+  </si>
+  <si>
+    <t>operaciones@antoal.pe</t>
+  </si>
+  <si>
+    <t>Rogger</t>
+  </si>
+  <si>
+    <t>pagos.antoalsac@gmail.com</t>
+  </si>
+  <si>
+    <t>Tania</t>
+  </si>
+  <si>
+    <t>signomedventas@signomed.com</t>
+  </si>
+  <si>
+    <t>vanessa.farfan@lumicenter.com.pe</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>ventas@dgalldisac.com</t>
+  </si>
+  <si>
+    <t>Angie</t>
+  </si>
+  <si>
+    <t>ventas@fursysperu.com.pe</t>
+  </si>
+  <si>
+    <t>ventas@grupoimcesa.com.pe</t>
+  </si>
+  <si>
+    <t>Enma</t>
+  </si>
+  <si>
+    <t>ventas@signomed.com</t>
+  </si>
+  <si>
+    <t>Carlomagno</t>
+  </si>
+  <si>
+    <t>administradorgeneral@ittsabus.com</t>
+  </si>
+  <si>
+    <t>Harold</t>
+  </si>
+  <si>
+    <t>atencionalcliente@empresalamerced.com</t>
+  </si>
+  <si>
+    <t>Noemi</t>
+  </si>
+  <si>
+    <t>b_michel@hotmail.com</t>
+  </si>
+  <si>
+    <t>Michel</t>
+  </si>
+  <si>
+    <t>cele@sertur-riosanta.com</t>
+  </si>
+  <si>
+    <t>Celestina</t>
+  </si>
+  <si>
+    <t>coseunsac@hotmail.com</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>dlopez@elogtec.com</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
+    <t>gamarraventas@outlook.com</t>
+  </si>
+  <si>
+    <t>gbenavides@ittsabus.com</t>
+  </si>
+  <si>
+    <t>Guillermo</t>
+  </si>
+  <si>
+    <t>gerencia@empresalamerced.com</t>
+  </si>
+  <si>
+    <t>gerencia@gamarrasecurity.com</t>
+  </si>
+  <si>
+    <t>gerencia@unimotor.com.pe</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>gerenteadministrativo@ittsabus.com</t>
+  </si>
+  <si>
+    <t>Sandro</t>
+  </si>
+  <si>
+    <t>jadams@perutaxi.com.pe</t>
+  </si>
+  <si>
+    <t>Jimmy</t>
+  </si>
+  <si>
+    <t>javier.flores.ardiles@gmail.com</t>
+  </si>
+  <si>
+    <t>jimmyadamsterry@hotmail.com</t>
+  </si>
+  <si>
+    <t>logistica@apoyototal24horas.com</t>
+  </si>
+  <si>
+    <t>madams@perutaxi.com.pe</t>
+  </si>
+  <si>
+    <t>Milenko</t>
+  </si>
+  <si>
+    <t>marketing@aeroprop.pe</t>
+  </si>
+  <si>
+    <t>Raul</t>
+  </si>
+  <si>
+    <t>mosorio@ittsabus.com</t>
+  </si>
+  <si>
+    <t>noindica.@gmail.com</t>
+  </si>
+  <si>
+    <t>Mery</t>
+  </si>
+  <si>
+    <t>operacionesyseguridad@gamarrasecurity.com</t>
+  </si>
+  <si>
+    <t>Raquel</t>
+  </si>
+  <si>
+    <t>rbejarano@aeroprop.pe</t>
+  </si>
+  <si>
+    <t>reservas@atravelperu.com</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>supertours@supertoursperu.com</t>
+  </si>
+  <si>
+    <t>Marienela</t>
+  </si>
+  <si>
+    <t>taisia.tupayachi@gmail.com</t>
+  </si>
+  <si>
+    <t>Taisia</t>
+  </si>
+  <si>
+    <t>ventas@sertur-riosanta.com</t>
+  </si>
+  <si>
+    <t>viczavala157@gmail.com</t>
+  </si>
+  <si>
+    <t>wjbrios@gmail.com</t>
+  </si>
+  <si>
+    <t>Wilbe</t>
+  </si>
+  <si>
+    <t>a.america_sac@hotmail.com</t>
+  </si>
+  <si>
+    <t>Dionisio</t>
+  </si>
+  <si>
+    <t>administracion@artesanosdonbosco.org</t>
+  </si>
+  <si>
+    <t>Giuditta</t>
+  </si>
+  <si>
+    <t>administracion@mlosrobles.pe</t>
+  </si>
+  <si>
+    <t>Milagro</t>
+  </si>
+  <si>
+    <t>angelmanuelsuybate@gmail.com</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>aoropeza@bozovichc.om</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>aroca@bozovich.com</t>
+  </si>
+  <si>
+    <t>Francesca</t>
+  </si>
+  <si>
+    <t>asistentecomercial@fadet.pe</t>
+  </si>
+  <si>
+    <t>Mirtha</t>
+  </si>
+  <si>
+    <t>comercialeo@yahoo.es</t>
+  </si>
+  <si>
+    <t>compras.electronicas@martin.com.pe</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>compras@fadet.pe</t>
+  </si>
+  <si>
+    <t>Vaneza</t>
+  </si>
+  <si>
+    <t>contacto.melamatrix@gmail.com</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>echang@bozovich.com</t>
+  </si>
+  <si>
+    <t>Evelin</t>
+  </si>
+  <si>
+    <t>elizabeth@gruposimon.com.pe</t>
+  </si>
+  <si>
+    <t>Mariluz</t>
+  </si>
+  <si>
+    <t>fernando.lamas@spectralatam.com</t>
+  </si>
+  <si>
+    <t>gustavo.chaucca@martin.com.pe</t>
+  </si>
+  <si>
+    <t>Gustavo</t>
+  </si>
+  <si>
+    <t>italamejiazarate@hotmail.es</t>
+  </si>
+  <si>
+    <t>jesus.alberca@martin.com.pe</t>
+  </si>
+  <si>
+    <t>mapie@telefonica.net.pe</t>
+  </si>
+  <si>
+    <t>Maritza</t>
+  </si>
+  <si>
+    <t>mena_tre14@hotmail.com</t>
+  </si>
+  <si>
+    <t>mmujica@bozovich.com</t>
+  </si>
+  <si>
+    <t>mobel@mobel.com.pe</t>
+  </si>
+  <si>
+    <t>mobelsa@gmail.com</t>
+  </si>
+  <si>
+    <t>Jessica</t>
+  </si>
+  <si>
+    <t>ohernandez@hcembalajes.com</t>
+  </si>
+  <si>
+    <t>omglima@omgperu.com</t>
+  </si>
+  <si>
+    <t>Giorgio</t>
+  </si>
+  <si>
+    <t>oswaluismayer120@gmail.com</t>
+  </si>
+  <si>
+    <t>Oswaldo</t>
+  </si>
+  <si>
+    <t>peruartesanias@hotmail.com</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>ventas.americasac@gmail.com</t>
+  </si>
+  <si>
+    <t>Percy</t>
+  </si>
+  <si>
+    <t>ventas@comercialleoperu.com</t>
+  </si>
+  <si>
+    <t>Ashley</t>
+  </si>
+  <si>
+    <t>administracion@angeplast.com</t>
+  </si>
+  <si>
+    <t>Naysha</t>
+  </si>
+  <si>
+    <t>ahr278601@gmail.com</t>
+  </si>
+  <si>
+    <t>Abrahan</t>
+  </si>
+  <si>
+    <t>cbragagnini@amforapackaging.com</t>
+  </si>
+  <si>
+    <t>comercial@angeplast.com</t>
+  </si>
+  <si>
+    <t>Janet</t>
+  </si>
+  <si>
+    <t>creditoscob@uysa.com.pe</t>
+  </si>
+  <si>
+    <t>cychicawa@uysa.com.pe</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>dnecochea@specialpaints.pe</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>garrojhosep58@gmail.com</t>
+  </si>
+  <si>
+    <t>Ernesto</t>
+  </si>
+  <si>
+    <t>info@alle.pe</t>
+  </si>
+  <si>
+    <t>Marjorie</t>
+  </si>
+  <si>
+    <t>inversionesgarro50@gmail.com</t>
+  </si>
+  <si>
+    <t>Gladys</t>
+  </si>
+  <si>
+    <t>jnecochea@specialbags.pe</t>
+  </si>
+  <si>
+    <t>jnecochea@specialpaints.pe</t>
+  </si>
+  <si>
+    <t>jpadilla@angeplast.com</t>
+  </si>
+  <si>
+    <t>Juvenal</t>
+  </si>
+  <si>
+    <t>jrivadeneira@industriasjr.com</t>
+  </si>
+  <si>
+    <t>jtapia@specialpaints.pe</t>
+  </si>
+  <si>
+    <t>jvenegas@cordilleraproducts.com.pe</t>
+  </si>
+  <si>
+    <t>kcanova@pieriplast.com</t>
+  </si>
+  <si>
+    <t>kvelaochaga@cordilleraproducts.com</t>
+  </si>
+  <si>
+    <t>lamk@uysa.com.pe</t>
+  </si>
+  <si>
+    <t>lcenteno@pieriplast.com</t>
+  </si>
+  <si>
+    <t>Leticia</t>
+  </si>
+  <si>
+    <t>luisnenegarro@gmail.com</t>
+  </si>
+  <si>
+    <t>mcollazos@pieriplast.com</t>
+  </si>
+  <si>
+    <t>Marlon</t>
+  </si>
+  <si>
+    <t>mychicawa@uysa.com.pe</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>plasticosfenixe.i.r.l@gmail.com</t>
+  </si>
+  <si>
+    <t>Isaias</t>
+  </si>
+  <si>
+    <t>pmarquez@uysa.com.pe</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>presidencia@jcp.org.pe</t>
+  </si>
+  <si>
+    <t>renzocarrera@gdcindustrial.com</t>
+  </si>
+  <si>
+    <t>rrhh@uysa.com.pe</t>
   </si>
 </sst>
 </file>
@@ -1065,899 +1065,899 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>3</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B74" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B76" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B77" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B80" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B85" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B88" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B89" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>171</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B95" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B96" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B97" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B98" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B99" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B100" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B101" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B102" t="s">
-        <v>155</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B103" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B104" t="s">
-        <v>187</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B105" t="s">
-        <v>7</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B108" t="s">
-        <v>193</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>199</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B111" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B112" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B113" t="s">
-        <v>202</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B114" t="s">
-        <v>204</v>
+        <v>47</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B115" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A3C6B6-1153-4C8C-AB26-BF86891B5CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED14F7A-331D-40B3-A59A-362EC463BEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="214">
   <si>
     <t>correo</t>
   </si>
@@ -67,580 +67,601 @@
     <t>Carlos</t>
   </si>
   <si>
-    <t>Hilda</t>
-  </si>
-  <si>
-    <t>Víctor</t>
-  </si>
-  <si>
-    <t>Juana</t>
-  </si>
-  <si>
     <t>Elizabeth</t>
   </si>
   <si>
-    <t>Elva</t>
-  </si>
-  <si>
     <t>Daniel</t>
   </si>
   <si>
-    <t>Javier</t>
-  </si>
-  <si>
-    <t>adm.general@casalindaperu.com</t>
-  </si>
-  <si>
-    <t>Carla</t>
-  </si>
-  <si>
-    <t>adminhc@signomed.com</t>
-  </si>
-  <si>
-    <t>administracion@copemo.com.pe</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>amarquez@casalindaperu.com</t>
-  </si>
-  <si>
     <t>Alejandro</t>
   </si>
   <si>
-    <t>antoalsac.ventas@gmail.com</t>
-  </si>
-  <si>
-    <t>Claudia</t>
-  </si>
-  <si>
-    <t>antonieta.aliaga@lumicenter.com.pe</t>
-  </si>
-  <si>
-    <t>Jaime</t>
-  </si>
-  <si>
-    <t>areacontable@casalindaperu.com</t>
-  </si>
-  <si>
-    <t>Zenina</t>
-  </si>
-  <si>
-    <t>atesoreria@casalindaperu.com</t>
-  </si>
-  <si>
-    <t>Romario</t>
-  </si>
-  <si>
-    <t>comercial@interandinomuebles.com</t>
-  </si>
-  <si>
-    <t>ertesa.homecenter@gmail.com</t>
-  </si>
-  <si>
-    <t>Joseph</t>
-  </si>
-  <si>
-    <t>etorres@magensa.com</t>
-  </si>
-  <si>
-    <t>Eduardo</t>
-  </si>
-  <si>
-    <t>gallardojesus907@gmail.com</t>
-  </si>
-  <si>
-    <t>Jesus</t>
-  </si>
-  <si>
-    <t>gerencia@multimuebles.pe</t>
-  </si>
-  <si>
-    <t>Gabriela</t>
-  </si>
-  <si>
-    <t>hgonzalez@casalindaperu.com</t>
-  </si>
-  <si>
-    <t>Hector</t>
-  </si>
-  <si>
-    <t>humberto.moreno@signomed.com</t>
-  </si>
-  <si>
-    <t>Humberto</t>
-  </si>
-  <si>
-    <t>jcrodasf26@gmail.com</t>
-  </si>
-  <si>
-    <t>jesusmarquez@casalindaperu.com</t>
-  </si>
-  <si>
-    <t>jimisco@grupoimcesa.com.pe</t>
-  </si>
-  <si>
-    <t>Jimis</t>
-  </si>
-  <si>
-    <t>magensa@magensa.com</t>
-  </si>
-  <si>
-    <t>Zoila</t>
-  </si>
-  <si>
-    <t>mmarquez@casalindaperu.com</t>
-  </si>
-  <si>
-    <t>operaciones@antoal.pe</t>
-  </si>
-  <si>
-    <t>Rogger</t>
-  </si>
-  <si>
-    <t>pagos.antoalsac@gmail.com</t>
-  </si>
-  <si>
-    <t>Tania</t>
-  </si>
-  <si>
-    <t>signomedventas@signomed.com</t>
-  </si>
-  <si>
-    <t>vanessa.farfan@lumicenter.com.pe</t>
-  </si>
-  <si>
-    <t>Vanessa</t>
-  </si>
-  <si>
-    <t>ventas@dgalldisac.com</t>
-  </si>
-  <si>
-    <t>Angie</t>
-  </si>
-  <si>
-    <t>ventas@fursysperu.com.pe</t>
-  </si>
-  <si>
-    <t>ventas@grupoimcesa.com.pe</t>
-  </si>
-  <si>
-    <t>Enma</t>
-  </si>
-  <si>
-    <t>ventas@signomed.com</t>
-  </si>
-  <si>
-    <t>Carlomagno</t>
-  </si>
-  <si>
-    <t>administradorgeneral@ittsabus.com</t>
-  </si>
-  <si>
-    <t>Harold</t>
-  </si>
-  <si>
-    <t>atencionalcliente@empresalamerced.com</t>
-  </si>
-  <si>
-    <t>Noemi</t>
-  </si>
-  <si>
-    <t>b_michel@hotmail.com</t>
-  </si>
-  <si>
-    <t>Michel</t>
-  </si>
-  <si>
-    <t>cele@sertur-riosanta.com</t>
-  </si>
-  <si>
-    <t>Celestina</t>
-  </si>
-  <si>
-    <t>coseunsac@hotmail.com</t>
-  </si>
-  <si>
     <t>Miguel</t>
   </si>
   <si>
-    <t>dlopez@elogtec.com</t>
-  </si>
-  <si>
-    <t>Felix</t>
-  </si>
-  <si>
-    <t>gamarraventas@outlook.com</t>
-  </si>
-  <si>
-    <t>gbenavides@ittsabus.com</t>
-  </si>
-  <si>
     <t>Guillermo</t>
   </si>
   <si>
-    <t>gerencia@empresalamerced.com</t>
-  </si>
-  <si>
-    <t>gerencia@gamarrasecurity.com</t>
-  </si>
-  <si>
-    <t>gerencia@unimotor.com.pe</t>
-  </si>
-  <si>
     <t>Cesar</t>
   </si>
   <si>
-    <t>gerenteadministrativo@ittsabus.com</t>
-  </si>
-  <si>
-    <t>Sandro</t>
-  </si>
-  <si>
-    <t>jadams@perutaxi.com.pe</t>
-  </si>
-  <si>
-    <t>Jimmy</t>
-  </si>
-  <si>
-    <t>javier.flores.ardiles@gmail.com</t>
-  </si>
-  <si>
-    <t>jimmyadamsterry@hotmail.com</t>
-  </si>
-  <si>
-    <t>logistica@apoyototal24horas.com</t>
-  </si>
-  <si>
-    <t>madams@perutaxi.com.pe</t>
-  </si>
-  <si>
-    <t>Milenko</t>
-  </si>
-  <si>
-    <t>marketing@aeroprop.pe</t>
-  </si>
-  <si>
-    <t>Raul</t>
-  </si>
-  <si>
-    <t>mosorio@ittsabus.com</t>
-  </si>
-  <si>
-    <t>noindica.@gmail.com</t>
-  </si>
-  <si>
-    <t>Mery</t>
-  </si>
-  <si>
-    <t>operacionesyseguridad@gamarrasecurity.com</t>
-  </si>
-  <si>
-    <t>Raquel</t>
-  </si>
-  <si>
-    <t>rbejarano@aeroprop.pe</t>
-  </si>
-  <si>
-    <t>reservas@atravelperu.com</t>
-  </si>
-  <si>
-    <t>Alfonso</t>
-  </si>
-  <si>
-    <t>supertours@supertoursperu.com</t>
-  </si>
-  <si>
-    <t>Marienela</t>
-  </si>
-  <si>
-    <t>taisia.tupayachi@gmail.com</t>
-  </si>
-  <si>
-    <t>Taisia</t>
-  </si>
-  <si>
-    <t>ventas@sertur-riosanta.com</t>
-  </si>
-  <si>
-    <t>viczavala157@gmail.com</t>
-  </si>
-  <si>
-    <t>wjbrios@gmail.com</t>
-  </si>
-  <si>
-    <t>Wilbe</t>
-  </si>
-  <si>
-    <t>a.america_sac@hotmail.com</t>
-  </si>
-  <si>
-    <t>Dionisio</t>
-  </si>
-  <si>
-    <t>administracion@artesanosdonbosco.org</t>
-  </si>
-  <si>
-    <t>Giuditta</t>
-  </si>
-  <si>
-    <t>administracion@mlosrobles.pe</t>
-  </si>
-  <si>
-    <t>Milagro</t>
-  </si>
-  <si>
-    <t>angelmanuelsuybate@gmail.com</t>
-  </si>
-  <si>
-    <t>Angel</t>
-  </si>
-  <si>
-    <t>aoropeza@bozovichc.om</t>
-  </si>
-  <si>
-    <t>Angela</t>
-  </si>
-  <si>
-    <t>aroca@bozovich.com</t>
-  </si>
-  <si>
-    <t>Francesca</t>
-  </si>
-  <si>
-    <t>asistentecomercial@fadet.pe</t>
-  </si>
-  <si>
-    <t>Mirtha</t>
-  </si>
-  <si>
-    <t>comercialeo@yahoo.es</t>
-  </si>
-  <si>
-    <t>compras.electronicas@martin.com.pe</t>
-  </si>
-  <si>
-    <t>Rosario</t>
-  </si>
-  <si>
-    <t>compras@fadet.pe</t>
-  </si>
-  <si>
-    <t>Vaneza</t>
-  </si>
-  <si>
-    <t>contacto.melamatrix@gmail.com</t>
-  </si>
-  <si>
-    <t>Karen</t>
-  </si>
-  <si>
-    <t>echang@bozovich.com</t>
-  </si>
-  <si>
-    <t>Evelin</t>
-  </si>
-  <si>
-    <t>elizabeth@gruposimon.com.pe</t>
-  </si>
-  <si>
-    <t>Mariluz</t>
-  </si>
-  <si>
-    <t>fernando.lamas@spectralatam.com</t>
-  </si>
-  <si>
-    <t>gustavo.chaucca@martin.com.pe</t>
-  </si>
-  <si>
     <t>Gustavo</t>
   </si>
   <si>
-    <t>italamejiazarate@hotmail.es</t>
-  </si>
-  <si>
-    <t>jesus.alberca@martin.com.pe</t>
-  </si>
-  <si>
-    <t>mapie@telefonica.net.pe</t>
-  </si>
-  <si>
-    <t>Maritza</t>
-  </si>
-  <si>
-    <t>mena_tre14@hotmail.com</t>
-  </si>
-  <si>
-    <t>mmujica@bozovich.com</t>
-  </si>
-  <si>
-    <t>mobel@mobel.com.pe</t>
-  </si>
-  <si>
-    <t>mobelsa@gmail.com</t>
-  </si>
-  <si>
     <t>Jessica</t>
   </si>
   <si>
-    <t>ohernandez@hcembalajes.com</t>
-  </si>
-  <si>
-    <t>omglima@omgperu.com</t>
-  </si>
-  <si>
-    <t>Giorgio</t>
-  </si>
-  <si>
-    <t>oswaluismayer120@gmail.com</t>
-  </si>
-  <si>
-    <t>Oswaldo</t>
-  </si>
-  <si>
-    <t>peruartesanias@hotmail.com</t>
-  </si>
-  <si>
     <t>Sandra</t>
   </si>
   <si>
-    <t>ventas.americasac@gmail.com</t>
-  </si>
-  <si>
-    <t>Percy</t>
-  </si>
-  <si>
-    <t>ventas@comercialleoperu.com</t>
-  </si>
-  <si>
-    <t>Ashley</t>
-  </si>
-  <si>
-    <t>administracion@angeplast.com</t>
-  </si>
-  <si>
-    <t>Naysha</t>
-  </si>
-  <si>
-    <t>ahr278601@gmail.com</t>
-  </si>
-  <si>
-    <t>Abrahan</t>
-  </si>
-  <si>
-    <t>cbragagnini@amforapackaging.com</t>
-  </si>
-  <si>
-    <t>comercial@angeplast.com</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
-    <t>creditoscob@uysa.com.pe</t>
-  </si>
-  <si>
-    <t>cychicawa@uysa.com.pe</t>
-  </si>
-  <si>
-    <t>Julio</t>
-  </si>
-  <si>
-    <t>dnecochea@specialpaints.pe</t>
-  </si>
-  <si>
     <t>Diana</t>
   </si>
   <si>
-    <t>garrojhosep58@gmail.com</t>
-  </si>
-  <si>
-    <t>Ernesto</t>
-  </si>
-  <si>
-    <t>info@alle.pe</t>
-  </si>
-  <si>
-    <t>Marjorie</t>
-  </si>
-  <si>
-    <t>inversionesgarro50@gmail.com</t>
-  </si>
-  <si>
-    <t>Gladys</t>
-  </si>
-  <si>
-    <t>jnecochea@specialbags.pe</t>
-  </si>
-  <si>
-    <t>jnecochea@specialpaints.pe</t>
-  </si>
-  <si>
-    <t>jpadilla@angeplast.com</t>
-  </si>
-  <si>
-    <t>Juvenal</t>
-  </si>
-  <si>
-    <t>jrivadeneira@industriasjr.com</t>
-  </si>
-  <si>
-    <t>jtapia@specialpaints.pe</t>
-  </si>
-  <si>
-    <t>jvenegas@cordilleraproducts.com.pe</t>
-  </si>
-  <si>
-    <t>kcanova@pieriplast.com</t>
-  </si>
-  <si>
-    <t>kvelaochaga@cordilleraproducts.com</t>
-  </si>
-  <si>
-    <t>lamk@uysa.com.pe</t>
-  </si>
-  <si>
-    <t>lcenteno@pieriplast.com</t>
-  </si>
-  <si>
-    <t>Leticia</t>
-  </si>
-  <si>
-    <t>luisnenegarro@gmail.com</t>
-  </si>
-  <si>
-    <t>mcollazos@pieriplast.com</t>
-  </si>
-  <si>
-    <t>Marlon</t>
-  </si>
-  <si>
-    <t>mychicawa@uysa.com.pe</t>
-  </si>
-  <si>
-    <t>Mariana</t>
-  </si>
-  <si>
-    <t>plasticosfenixe.i.r.l@gmail.com</t>
-  </si>
-  <si>
     <t>Isaias</t>
   </si>
   <si>
-    <t>pmarquez@uysa.com.pe</t>
-  </si>
-  <si>
-    <t>Pablo</t>
-  </si>
-  <si>
-    <t>presidencia@jcp.org.pe</t>
-  </si>
-  <si>
-    <t>renzocarrera@gdcindustrial.com</t>
-  </si>
-  <si>
-    <t>rrhh@uysa.com.pe</t>
+    <t>aabuhadba@pharmaxsolucionesintegrales.pe</t>
+  </si>
+  <si>
+    <t>Arturo</t>
+  </si>
+  <si>
+    <t>administracion@certyhomo.com</t>
+  </si>
+  <si>
+    <t>Greyssi</t>
+  </si>
+  <si>
+    <t>administracion@drgconsultoria.com.pe</t>
+  </si>
+  <si>
+    <t>Marilyn</t>
+  </si>
+  <si>
+    <t>administracion@effio.com.pe</t>
+  </si>
+  <si>
+    <t>adoig2016@gmail.com</t>
+  </si>
+  <si>
+    <t>analuzflorianventuro@gmail.com</t>
+  </si>
+  <si>
+    <t>ap.espinozadoig@gmail.com</t>
+  </si>
+  <si>
+    <t>cinthia.rivera.c@gmail.com</t>
+  </si>
+  <si>
+    <t>Cinthia</t>
+  </si>
+  <si>
+    <t>cmorim@alemanmori-consultores.com</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>drojas@drgconsultoria.com.pe</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>eatarama@unimpro.org</t>
+  </si>
+  <si>
+    <t>Yvett</t>
+  </si>
+  <si>
+    <t>fernando.correa@bacconsultores.pe</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>gbracamonte@unimpro.org</t>
+  </si>
+  <si>
+    <t>gerencia@certyhomo.com</t>
+  </si>
+  <si>
+    <t>Evelyn</t>
+  </si>
+  <si>
+    <t>gisellabianca@gmail.com</t>
+  </si>
+  <si>
+    <t>Gisella</t>
+  </si>
+  <si>
+    <t>gmadrid@aycestudio.com</t>
+  </si>
+  <si>
+    <t>Geovanni</t>
+  </si>
+  <si>
+    <t>heylp2095@gmail.com</t>
+  </si>
+  <si>
+    <t>Heydi</t>
+  </si>
+  <si>
+    <t>ivalverde@mtvingenieros.com</t>
+  </si>
+  <si>
+    <t>juanmori76113@gmail.com</t>
+  </si>
+  <si>
+    <t>kpizarro@pharmaxsolucionesintegrales.pe</t>
+  </si>
+  <si>
+    <t>lleon@summatalento.com.pe</t>
+  </si>
+  <si>
+    <t>Lilia</t>
+  </si>
+  <si>
+    <t>mcardenasn.21@gmail.com</t>
+  </si>
+  <si>
+    <t>moisesmartinez_3@hotmail.com</t>
+  </si>
+  <si>
+    <t>Moises</t>
+  </si>
+  <si>
+    <t>nilamendozah@gmail.com</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>oborja0072@gmail.com</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>orojas@hupestudio.com</t>
+  </si>
+  <si>
+    <t>patty36_2001@hotmail.com</t>
+  </si>
+  <si>
+    <t>pchacaltana@pharmaxsolucionesintegrales.pe</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>yanethalisheh@gmail.com</t>
+  </si>
+  <si>
+    <t>Yaneth</t>
+  </si>
+  <si>
+    <t>a_abusada@inkacrops.com</t>
+  </si>
+  <si>
+    <t>Andres</t>
+  </si>
+  <si>
+    <t>angelica@choice-peru.com</t>
+  </si>
+  <si>
+    <t>aybpasac@hotmail.com</t>
+  </si>
+  <si>
+    <t>carmelina@olivae</t>
+  </si>
+  <si>
+    <t>Carmelina</t>
+  </si>
+  <si>
+    <t>contabilidad@rasil.com.pe</t>
+  </si>
+  <si>
+    <t>Rosmery</t>
+  </si>
+  <si>
+    <t>corporacionnestor.sac@gmail.com</t>
+  </si>
+  <si>
+    <t>Nelly</t>
+  </si>
+  <si>
+    <t>cpanta@califrut.pe</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>ctorres@disebas.com.pe</t>
+  </si>
+  <si>
+    <t>ctorres@rasil.com.pe</t>
+  </si>
+  <si>
+    <t>Cristian</t>
+  </si>
+  <si>
+    <t>dbustamante@califrut.pe</t>
+  </si>
+  <si>
+    <t>Denis</t>
+  </si>
+  <si>
+    <t>flavio.x.f@hotmail.com</t>
+  </si>
+  <si>
+    <t>Flavio</t>
+  </si>
+  <si>
+    <t>fsoto@califrut.pe</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>gmoron@nesdecsac.com</t>
+  </si>
+  <si>
+    <t>import@hsmfoods.com</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>jramos@hotmail.com</t>
+  </si>
+  <si>
+    <t>Franciso</t>
+  </si>
+  <si>
+    <t>kramos@oregonfoodscorp.com</t>
+  </si>
+  <si>
+    <t>Kathia</t>
+  </si>
+  <si>
+    <t>lorena.ochoa@florafg.com</t>
+  </si>
+  <si>
+    <t>Lorena</t>
+  </si>
+  <si>
+    <t>lrojo@serviam.com.pe</t>
+  </si>
+  <si>
+    <t>Lidia</t>
+  </si>
+  <si>
+    <t>manuel.hanson@upfield.com</t>
+  </si>
+  <si>
+    <t>marslay14@gmail.com</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>mchavez@inkacrops.com</t>
+  </si>
+  <si>
+    <t>Mercedes</t>
+  </si>
+  <si>
+    <t>n.abusada@polysol.com.pe</t>
+  </si>
+  <si>
+    <t>Nicolas</t>
+  </si>
+  <si>
+    <t>sebastian.echegaray@upfield.com</t>
+  </si>
+  <si>
+    <t>Sebastian</t>
+  </si>
+  <si>
+    <t>smedina@rasil.com.pe</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>starlayza.quispe@gmail.com</t>
+  </si>
+  <si>
+    <t>Estrellita</t>
+  </si>
+  <si>
+    <t>storres@disebas.com.pe</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>tupaqsumaq@gmail.com</t>
+  </si>
+  <si>
+    <t>verodelucio@gmail.com</t>
+  </si>
+  <si>
+    <t>Consuelo</t>
+  </si>
+  <si>
+    <t>anthony_00810@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jhon</t>
+  </si>
+  <si>
+    <t>bethsy.maceda@praxiscomercial.com</t>
+  </si>
+  <si>
+    <t>Bethsy</t>
+  </si>
+  <si>
+    <t>cfvergaray@leograf.pe</t>
+  </si>
+  <si>
+    <t>classic@qnet.com</t>
+  </si>
+  <si>
+    <t>Hermelinda</t>
+  </si>
+  <si>
+    <t>classic@qnet.com.pe</t>
+  </si>
+  <si>
+    <t>Jesús</t>
+  </si>
+  <si>
+    <t>contabilidad@classic.com.pe</t>
+  </si>
+  <si>
+    <t>Máximo</t>
+  </si>
+  <si>
+    <t>corpincorvil2023@outlook.es</t>
+  </si>
+  <si>
+    <t>Uriel</t>
+  </si>
+  <si>
+    <t>cvergaray@leograf.pe</t>
+  </si>
+  <si>
+    <t>Bartolome</t>
+  </si>
+  <si>
+    <t>cwong@scpcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Carola</t>
+  </si>
+  <si>
+    <t>daniel.niquen@globalpaper.net</t>
+  </si>
+  <si>
+    <t>ectg2000@hotmail.com</t>
+  </si>
+  <si>
+    <t>gbardales@leograf.pe</t>
+  </si>
+  <si>
+    <t>Geraldine</t>
+  </si>
+  <si>
+    <t>gerencia@gastegraf.com</t>
+  </si>
+  <si>
+    <t>jdiaz@scpcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>jose.larrea@praxiscomercial.com</t>
+  </si>
+  <si>
+    <t>lgastelumendi@gastegraf.com</t>
+  </si>
+  <si>
+    <t>mary.aguilar@praxiscomercial.com</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>mgastelumendi@gastegraf.com</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>mmurdoch@scpcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Martha</t>
+  </si>
+  <si>
+    <t>neuropublicidad8@gmail.com</t>
+  </si>
+  <si>
+    <t>Algreen</t>
+  </si>
+  <si>
+    <t>nmarin@leograf.pe</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>peruseiton@gmail.com</t>
+  </si>
+  <si>
+    <t>pjesicar71@gmail.com</t>
+  </si>
+  <si>
+    <t>pjgonzales@scpcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Walter</t>
+  </si>
+  <si>
+    <t>pperez@scpcorp.com.pe</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>prodriguez@rollosdepapel.pe</t>
+  </si>
+  <si>
+    <t>tesoreria@praxiscomercial.com</t>
+  </si>
+  <si>
+    <t>Miriam</t>
+  </si>
+  <si>
+    <t>yrenem@gastegraf.com</t>
+  </si>
+  <si>
+    <t>Yrene</t>
+  </si>
+  <si>
+    <t>administracion@iatechnology.com.pe</t>
+  </si>
+  <si>
+    <t>Karina</t>
+  </si>
+  <si>
+    <t>administracion@peruvianvending.com</t>
+  </si>
+  <si>
+    <t>Leonela</t>
+  </si>
+  <si>
+    <t>amiranda@peruvianvending.com</t>
+  </si>
+  <si>
+    <t>Luz</t>
+  </si>
+  <si>
+    <t>angelica.berrocal@pe.multivac.com</t>
+  </si>
+  <si>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>arodriguez@arrefrigeracion.com</t>
+  </si>
+  <si>
+    <t>bruno.sarmiento@pe.multivac.com</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>carolina.sanroman@nova.pe</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>castanitasdelperuochv1@gmail.com</t>
+  </si>
+  <si>
+    <t>ccarhuancho@iatechnology.com.pe</t>
+  </si>
+  <si>
+    <t>comercial@peruvianvending.com</t>
+  </si>
+  <si>
+    <t>contabilidad@cold96.com</t>
+  </si>
+  <si>
+    <t>contabilidad1@cold96.com</t>
+  </si>
+  <si>
+    <t>Anadeli</t>
+  </si>
+  <si>
+    <t>cynthia.laysiu@pe.multivac.com</t>
+  </si>
+  <si>
+    <t>Cynthia</t>
+  </si>
+  <si>
+    <t>fabricacionesmyj@yahoo.es</t>
+  </si>
+  <si>
+    <t>Edith</t>
+  </si>
+  <si>
+    <t>gerencia@corporaciongiapack.com</t>
+  </si>
+  <si>
+    <t>haydee.gutierrez@nova.pe</t>
+  </si>
+  <si>
+    <t>Haydee</t>
+  </si>
+  <si>
+    <t>jrojas@refamij.com</t>
+  </si>
+  <si>
+    <t>logistica@refamij.com</t>
+  </si>
+  <si>
+    <t>Joao</t>
+  </si>
+  <si>
+    <t>mfernandez@peruvianvending.com</t>
+  </si>
+  <si>
+    <t>Marcelino</t>
+  </si>
+  <si>
+    <t>mhuarcaya@manpan.com</t>
+  </si>
+  <si>
+    <t>miguel.torrejonmaguina@mitor.com.pe</t>
+  </si>
+  <si>
+    <t>mtorrejon@mitor.com.pe</t>
+  </si>
+  <si>
+    <t>mupe@pe.multivac.com</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>tamaras@refamij.com</t>
+  </si>
+  <si>
+    <t>Tamara</t>
+  </si>
+  <si>
+    <t>tecmaquind1@gmail.com</t>
+  </si>
+  <si>
+    <t>ventas@corporaciongiapack.com</t>
+  </si>
+  <si>
+    <t>ventas@ecotiendaelixir.com</t>
+  </si>
+  <si>
+    <t>Ines</t>
+  </si>
+  <si>
+    <t>ventas@tecmaquind.com</t>
+  </si>
+  <si>
+    <t>Giuliana</t>
   </si>
 </sst>
 </file>
@@ -1065,179 +1086,179 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1245,39 +1266,39 @@
         <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1309,63 +1330,63 @@
         <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" t="s">
         <v>84</v>
-      </c>
-      <c r="B39" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" t="s">
         <v>87</v>
-      </c>
-      <c r="B41" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1405,563 +1426,568 @@
         <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B65" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B66" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B67" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B68" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
-        <v>139</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B72" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B82" t="s">
-        <v>137</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B84" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B86" t="s">
-        <v>162</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B90" t="s">
-        <v>14</v>
+        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B93" t="s">
-        <v>174</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B94" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B95" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B96" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B97" t="s">
-        <v>182</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B98" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B99" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B100" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B101" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B102" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B103" t="s">
-        <v>7</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B104" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B105" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B107" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B108" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B109" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B110" t="s">
-        <v>199</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B111" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B112" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B113" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B114" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B115" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="4"/>
+      <c r="A116" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B116" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="4"/>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED14F7A-331D-40B3-A59A-362EC463BEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62BC381-B061-4DFB-B43C-E5CC91D4B3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="226">
   <si>
     <t>correo</t>
   </si>
@@ -52,616 +52,652 @@
     <t>Luis</t>
   </si>
   <si>
-    <t>Rosa</t>
-  </si>
-  <si>
     <t>Ana</t>
   </si>
   <si>
     <t>Patricia</t>
   </si>
   <si>
-    <t>Manuel</t>
-  </si>
-  <si>
     <t>Carlos</t>
   </si>
   <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
     <t>Daniel</t>
   </si>
   <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t>Miguel</t>
-  </si>
-  <si>
-    <t>Guillermo</t>
-  </si>
-  <si>
     <t>Cesar</t>
   </si>
   <si>
-    <t>Gustavo</t>
-  </si>
-  <si>
-    <t>Jessica</t>
-  </si>
-  <si>
-    <t>Sandra</t>
-  </si>
-  <si>
-    <t>Diana</t>
-  </si>
-  <si>
-    <t>Isaias</t>
-  </si>
-  <si>
-    <t>aabuhadba@pharmaxsolucionesintegrales.pe</t>
-  </si>
-  <si>
-    <t>Arturo</t>
-  </si>
-  <si>
-    <t>administracion@certyhomo.com</t>
-  </si>
-  <si>
-    <t>Greyssi</t>
-  </si>
-  <si>
-    <t>administracion@drgconsultoria.com.pe</t>
-  </si>
-  <si>
-    <t>Marilyn</t>
-  </si>
-  <si>
-    <t>administracion@effio.com.pe</t>
-  </si>
-  <si>
-    <t>adoig2016@gmail.com</t>
-  </si>
-  <si>
-    <t>analuzflorianventuro@gmail.com</t>
-  </si>
-  <si>
-    <t>ap.espinozadoig@gmail.com</t>
-  </si>
-  <si>
-    <t>cinthia.rivera.c@gmail.com</t>
-  </si>
-  <si>
-    <t>Cinthia</t>
-  </si>
-  <si>
-    <t>cmorim@alemanmori-consultores.com</t>
-  </si>
-  <si>
-    <t>Cristina</t>
-  </si>
-  <si>
-    <t>drojas@drgconsultoria.com.pe</t>
-  </si>
-  <si>
     <t>Diego</t>
   </si>
   <si>
-    <t>eatarama@unimpro.org</t>
-  </si>
-  <si>
-    <t>Yvett</t>
-  </si>
-  <si>
-    <t>fernando.correa@bacconsultores.pe</t>
-  </si>
-  <si>
     <t>Fernando</t>
   </si>
   <si>
-    <t>gbracamonte@unimpro.org</t>
-  </si>
-  <si>
-    <t>gerencia@certyhomo.com</t>
-  </si>
-  <si>
     <t>Evelyn</t>
   </si>
   <si>
-    <t>gisellabianca@gmail.com</t>
-  </si>
-  <si>
-    <t>Gisella</t>
-  </si>
-  <si>
-    <t>gmadrid@aycestudio.com</t>
-  </si>
-  <si>
-    <t>Geovanni</t>
-  </si>
-  <si>
-    <t>heylp2095@gmail.com</t>
-  </si>
-  <si>
-    <t>Heydi</t>
-  </si>
-  <si>
-    <t>ivalverde@mtvingenieros.com</t>
-  </si>
-  <si>
-    <t>juanmori76113@gmail.com</t>
-  </si>
-  <si>
-    <t>kpizarro@pharmaxsolucionesintegrales.pe</t>
-  </si>
-  <si>
-    <t>lleon@summatalento.com.pe</t>
-  </si>
-  <si>
-    <t>Lilia</t>
-  </si>
-  <si>
-    <t>mcardenasn.21@gmail.com</t>
-  </si>
-  <si>
-    <t>moisesmartinez_3@hotmail.com</t>
-  </si>
-  <si>
-    <t>Moises</t>
-  </si>
-  <si>
-    <t>nilamendozah@gmail.com</t>
-  </si>
-  <si>
-    <t>Ivan</t>
-  </si>
-  <si>
-    <t>oborja0072@gmail.com</t>
-  </si>
-  <si>
-    <t>Orlando</t>
-  </si>
-  <si>
-    <t>orojas@hupestudio.com</t>
-  </si>
-  <si>
-    <t>patty36_2001@hotmail.com</t>
-  </si>
-  <si>
-    <t>pchacaltana@pharmaxsolucionesintegrales.pe</t>
-  </si>
-  <si>
-    <t>Paola</t>
-  </si>
-  <si>
-    <t>yanethalisheh@gmail.com</t>
-  </si>
-  <si>
-    <t>Yaneth</t>
-  </si>
-  <si>
-    <t>a_abusada@inkacrops.com</t>
-  </si>
-  <si>
-    <t>Andres</t>
-  </si>
-  <si>
-    <t>angelica@choice-peru.com</t>
-  </si>
-  <si>
-    <t>aybpasac@hotmail.com</t>
-  </si>
-  <si>
-    <t>carmelina@olivae</t>
-  </si>
-  <si>
-    <t>Carmelina</t>
-  </si>
-  <si>
-    <t>contabilidad@rasil.com.pe</t>
-  </si>
-  <si>
-    <t>Rosmery</t>
-  </si>
-  <si>
-    <t>corporacionnestor.sac@gmail.com</t>
-  </si>
-  <si>
-    <t>Nelly</t>
-  </si>
-  <si>
-    <t>cpanta@califrut.pe</t>
-  </si>
-  <si>
-    <t>Christian</t>
-  </si>
-  <si>
-    <t>ctorres@disebas.com.pe</t>
-  </si>
-  <si>
-    <t>ctorres@rasil.com.pe</t>
-  </si>
-  <si>
     <t>Cristian</t>
   </si>
   <si>
-    <t>dbustamante@califrut.pe</t>
-  </si>
-  <si>
-    <t>Denis</t>
-  </si>
-  <si>
-    <t>flavio.x.f@hotmail.com</t>
-  </si>
-  <si>
-    <t>Flavio</t>
-  </si>
-  <si>
-    <t>fsoto@califrut.pe</t>
-  </si>
-  <si>
-    <t>Franklin</t>
-  </si>
-  <si>
-    <t>gmoron@nesdecsac.com</t>
-  </si>
-  <si>
-    <t>import@hsmfoods.com</t>
-  </si>
-  <si>
     <t>Hugo</t>
   </si>
   <si>
-    <t>jramos@hotmail.com</t>
-  </si>
-  <si>
-    <t>Franciso</t>
-  </si>
-  <si>
-    <t>kramos@oregonfoodscorp.com</t>
-  </si>
-  <si>
-    <t>Kathia</t>
-  </si>
-  <si>
-    <t>lorena.ochoa@florafg.com</t>
-  </si>
-  <si>
-    <t>Lorena</t>
-  </si>
-  <si>
-    <t>lrojo@serviam.com.pe</t>
-  </si>
-  <si>
     <t>Lidia</t>
   </si>
   <si>
-    <t>manuel.hanson@upfield.com</t>
-  </si>
-  <si>
-    <t>marslay14@gmail.com</t>
-  </si>
-  <si>
-    <t>Sara</t>
-  </si>
-  <si>
-    <t>mchavez@inkacrops.com</t>
-  </si>
-  <si>
-    <t>Mercedes</t>
-  </si>
-  <si>
-    <t>n.abusada@polysol.com.pe</t>
-  </si>
-  <si>
-    <t>Nicolas</t>
-  </si>
-  <si>
-    <t>sebastian.echegaray@upfield.com</t>
-  </si>
-  <si>
-    <t>Sebastian</t>
-  </si>
-  <si>
-    <t>smedina@rasil.com.pe</t>
-  </si>
-  <si>
-    <t>Silvia</t>
-  </si>
-  <si>
-    <t>starlayza.quispe@gmail.com</t>
-  </si>
-  <si>
-    <t>Estrellita</t>
-  </si>
-  <si>
-    <t>storres@disebas.com.pe</t>
-  </si>
-  <si>
-    <t>Samuel</t>
-  </si>
-  <si>
-    <t>tupaqsumaq@gmail.com</t>
-  </si>
-  <si>
-    <t>verodelucio@gmail.com</t>
-  </si>
-  <si>
-    <t>Consuelo</t>
-  </si>
-  <si>
-    <t>anthony_00810@hotmail.com</t>
-  </si>
-  <si>
-    <t>Jhon</t>
-  </si>
-  <si>
-    <t>bethsy.maceda@praxiscomercial.com</t>
-  </si>
-  <si>
-    <t>Bethsy</t>
-  </si>
-  <si>
-    <t>cfvergaray@leograf.pe</t>
-  </si>
-  <si>
-    <t>classic@qnet.com</t>
-  </si>
-  <si>
-    <t>Hermelinda</t>
-  </si>
-  <si>
-    <t>classic@qnet.com.pe</t>
-  </si>
-  <si>
-    <t>Jesús</t>
-  </si>
-  <si>
-    <t>contabilidad@classic.com.pe</t>
-  </si>
-  <si>
-    <t>Máximo</t>
-  </si>
-  <si>
-    <t>corpincorvil2023@outlook.es</t>
-  </si>
-  <si>
-    <t>Uriel</t>
-  </si>
-  <si>
-    <t>cvergaray@leograf.pe</t>
-  </si>
-  <si>
-    <t>Bartolome</t>
-  </si>
-  <si>
-    <t>cwong@scpcorp.com.pe</t>
-  </si>
-  <si>
-    <t>Carola</t>
-  </si>
-  <si>
-    <t>daniel.niquen@globalpaper.net</t>
-  </si>
-  <si>
-    <t>ectg2000@hotmail.com</t>
-  </si>
-  <si>
-    <t>gbardales@leograf.pe</t>
-  </si>
-  <si>
-    <t>Geraldine</t>
-  </si>
-  <si>
-    <t>gerencia@gastegraf.com</t>
-  </si>
-  <si>
-    <t>jdiaz@scpcorp.com.pe</t>
-  </si>
-  <si>
     <t>Jose</t>
   </si>
   <si>
-    <t>jose.larrea@praxiscomercial.com</t>
-  </si>
-  <si>
-    <t>lgastelumendi@gastegraf.com</t>
-  </si>
-  <si>
-    <t>mary.aguilar@praxiscomercial.com</t>
-  </si>
-  <si>
-    <t>Mary</t>
-  </si>
-  <si>
-    <t>mgastelumendi@gastegraf.com</t>
-  </si>
-  <si>
-    <t>Marco</t>
-  </si>
-  <si>
-    <t>mmurdoch@scpcorp.com.pe</t>
-  </si>
-  <si>
-    <t>Martha</t>
-  </si>
-  <si>
-    <t>neuropublicidad8@gmail.com</t>
-  </si>
-  <si>
-    <t>Algreen</t>
-  </si>
-  <si>
-    <t>nmarin@leograf.pe</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>peruseiton@gmail.com</t>
-  </si>
-  <si>
-    <t>pjesicar71@gmail.com</t>
-  </si>
-  <si>
-    <t>pjgonzales@scpcorp.com.pe</t>
-  </si>
-  <si>
-    <t>Walter</t>
-  </si>
-  <si>
-    <t>pperez@scpcorp.com.pe</t>
-  </si>
-  <si>
     <t>Pedro</t>
   </si>
   <si>
-    <t>prodriguez@rollosdepapel.pe</t>
-  </si>
-  <si>
-    <t>tesoreria@praxiscomercial.com</t>
-  </si>
-  <si>
-    <t>Miriam</t>
-  </si>
-  <si>
-    <t>yrenem@gastegraf.com</t>
-  </si>
-  <si>
-    <t>Yrene</t>
-  </si>
-  <si>
-    <t>administracion@iatechnology.com.pe</t>
-  </si>
-  <si>
-    <t>Karina</t>
-  </si>
-  <si>
-    <t>administracion@peruvianvending.com</t>
-  </si>
-  <si>
-    <t>Leonela</t>
-  </si>
-  <si>
-    <t>amiranda@peruvianvending.com</t>
-  </si>
-  <si>
     <t>Luz</t>
   </si>
   <si>
-    <t>angelica.berrocal@pe.multivac.com</t>
-  </si>
-  <si>
     <t>Angelica</t>
   </si>
   <si>
-    <t>arodriguez@arrefrigeracion.com</t>
-  </si>
-  <si>
-    <t>bruno.sarmiento@pe.multivac.com</t>
-  </si>
-  <si>
-    <t>Bruno</t>
-  </si>
-  <si>
-    <t>carolina.sanroman@nova.pe</t>
-  </si>
-  <si>
-    <t>Carolina</t>
-  </si>
-  <si>
-    <t>castanitasdelperuochv1@gmail.com</t>
-  </si>
-  <si>
-    <t>ccarhuancho@iatechnology.com.pe</t>
-  </si>
-  <si>
-    <t>comercial@peruvianvending.com</t>
-  </si>
-  <si>
-    <t>contabilidad@cold96.com</t>
-  </si>
-  <si>
-    <t>contabilidad1@cold96.com</t>
-  </si>
-  <si>
-    <t>Anadeli</t>
-  </si>
-  <si>
-    <t>cynthia.laysiu@pe.multivac.com</t>
-  </si>
-  <si>
-    <t>Cynthia</t>
-  </si>
-  <si>
-    <t>fabricacionesmyj@yahoo.es</t>
-  </si>
-  <si>
-    <t>Edith</t>
-  </si>
-  <si>
-    <t>gerencia@corporaciongiapack.com</t>
-  </si>
-  <si>
-    <t>haydee.gutierrez@nova.pe</t>
-  </si>
-  <si>
     <t>Haydee</t>
   </si>
   <si>
-    <t>jrojas@refamij.com</t>
-  </si>
-  <si>
-    <t>logistica@refamij.com</t>
-  </si>
-  <si>
-    <t>Joao</t>
-  </si>
-  <si>
-    <t>mfernandez@peruvianvending.com</t>
-  </si>
-  <si>
-    <t>Marcelino</t>
-  </si>
-  <si>
-    <t>mhuarcaya@manpan.com</t>
-  </si>
-  <si>
-    <t>miguel.torrejonmaguina@mitor.com.pe</t>
-  </si>
-  <si>
-    <t>mtorrejon@mitor.com.pe</t>
-  </si>
-  <si>
-    <t>mupe@pe.multivac.com</t>
-  </si>
-  <si>
-    <t>Carmen</t>
-  </si>
-  <si>
-    <t>tamaras@refamij.com</t>
-  </si>
-  <si>
-    <t>Tamara</t>
-  </si>
-  <si>
-    <t>tecmaquind1@gmail.com</t>
-  </si>
-  <si>
-    <t>ventas@corporaciongiapack.com</t>
-  </si>
-  <si>
-    <t>ventas@ecotiendaelixir.com</t>
-  </si>
-  <si>
-    <t>Ines</t>
-  </si>
-  <si>
-    <t>ventas@tecmaquind.com</t>
-  </si>
-  <si>
     <t>Giuliana</t>
+  </si>
+  <si>
+    <t>alonsorm84@hotmail.com</t>
+  </si>
+  <si>
+    <t>Alonso</t>
+  </si>
+  <si>
+    <t>andrea@jhadetextile.com</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>bbnanitas@hotmail.com</t>
+  </si>
+  <si>
+    <t>Hubert</t>
+  </si>
+  <si>
+    <t>blancadls@madmen.pe</t>
+  </si>
+  <si>
+    <t>Blanca</t>
+  </si>
+  <si>
+    <t>chcubas@verach.pe</t>
+  </si>
+  <si>
+    <t>Charles</t>
+  </si>
+  <si>
+    <t>comercial@textilairin.pe</t>
+  </si>
+  <si>
+    <t>Zczar</t>
+  </si>
+  <si>
+    <t>conta04@metaljeans.com.pe</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>finanzas@mpdsac.com</t>
+  </si>
+  <si>
+    <t>Fernanda</t>
+  </si>
+  <si>
+    <t>haydee@jhadetextile.com</t>
+  </si>
+  <si>
+    <t>janina.coronel@metaljeans.com.pe</t>
+  </si>
+  <si>
+    <t>Sandrita</t>
+  </si>
+  <si>
+    <t>jfconfeccione09@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jeronimo</t>
+  </si>
+  <si>
+    <t>jlatorre@mpdsac.com</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>juanjo04689@gmail.com</t>
+  </si>
+  <si>
+    <t>l.torres@stratagarments.pe</t>
+  </si>
+  <si>
+    <t>luisangel@mpdsac.com</t>
+  </si>
+  <si>
+    <t>luz.h@mpdsac.com</t>
+  </si>
+  <si>
+    <t>marcial74@hotmail.com</t>
+  </si>
+  <si>
+    <t>Edwin</t>
+  </si>
+  <si>
+    <t>metaljeans@metaljeans.com.pe</t>
+  </si>
+  <si>
+    <t>mmontanez@disenoacmm.com</t>
+  </si>
+  <si>
+    <t>Mirko</t>
+  </si>
+  <si>
+    <t>rajumahtani2@gmail.com</t>
+  </si>
+  <si>
+    <t>Raju</t>
+  </si>
+  <si>
+    <t>rayumactani@gmail.com</t>
+  </si>
+  <si>
+    <t>Hari</t>
+  </si>
+  <si>
+    <t>reneepena@raffaproexco.com</t>
+  </si>
+  <si>
+    <t>Allan</t>
+  </si>
+  <si>
+    <t>rmarure@textilairin.pe</t>
+  </si>
+  <si>
+    <t>Roberth</t>
+  </si>
+  <si>
+    <t>strata.garments.sac@gmail.com</t>
+  </si>
+  <si>
+    <t>swag69clothing@gmail.com</t>
+  </si>
+  <si>
+    <t>Lizett</t>
+  </si>
+  <si>
+    <t>textilgrubba@outlook.com</t>
+  </si>
+  <si>
+    <t>Alejandrina</t>
+  </si>
+  <si>
+    <t>tsotelo27@hotmail.com</t>
+  </si>
+  <si>
+    <t>Tania</t>
+  </si>
+  <si>
+    <t>ventas@textilgrubba.com</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>ymarcelo@mpdsac.com</t>
+  </si>
+  <si>
+    <t>Yuly</t>
+  </si>
+  <si>
+    <t>yoanna24@hotmail.com</t>
+  </si>
+  <si>
+    <t>Yoanna</t>
+  </si>
+  <si>
+    <t>aburgos@itsanet.com</t>
+  </si>
+  <si>
+    <t>Augusto</t>
+  </si>
+  <si>
+    <t>acarrion@wulee.pe</t>
+  </si>
+  <si>
+    <t>achiclla@almacenesmyrsa.com</t>
+  </si>
+  <si>
+    <t>acruz@amtcontadoresyasesores.com</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>administracion.peru@rems.pe</t>
+  </si>
+  <si>
+    <t>Jennifer</t>
+  </si>
+  <si>
+    <t>administracionlima@almacenes-sos.com</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>araceli.moreno@rems.pe</t>
+  </si>
+  <si>
+    <t>Araceli</t>
+  </si>
+  <si>
+    <t>asistente@almaceneratrujillo.com.pe</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>bquijano@itsanet.com</t>
+  </si>
+  <si>
+    <t>Beatriz</t>
+  </si>
+  <si>
+    <t>cesar.soriano@fargoline.com.pe</t>
+  </si>
+  <si>
+    <t>cmontoya@alsud.com.pe</t>
+  </si>
+  <si>
+    <t>Mariano</t>
+  </si>
+  <si>
+    <t>crojas@intsol.com.pe</t>
+  </si>
+  <si>
+    <t>Christhyam</t>
+  </si>
+  <si>
+    <t>davis.gomez@grupoe2e.com</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>direccion.tecnica@intsol.com.pe</t>
+  </si>
+  <si>
+    <t>Janett</t>
+  </si>
+  <si>
+    <t>finanzas@shohin.com.pe</t>
+  </si>
+  <si>
+    <t>fpeirano@itsanet.com</t>
+  </si>
+  <si>
+    <t>gabriel.garcia@rems.pe</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>gerencia@almacenes-sos.com</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>guillermo.marroquin@intsol.com.pe</t>
+  </si>
+  <si>
+    <t>hbohme@shohin.com.pe</t>
+  </si>
+  <si>
+    <t>Heinz</t>
+  </si>
+  <si>
+    <t>informes@davayasociados.com</t>
+  </si>
+  <si>
+    <t>Delfin</t>
+  </si>
+  <si>
+    <t>jaime.ferrero@fargoline.com.pe</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>marcos.garciami@rems.pe</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>mcajo@shohin.com.pe</t>
+  </si>
+  <si>
+    <t>paul.sairitupac@rems.pe</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>practicanterrhh@fargoline.com.pe</t>
+  </si>
+  <si>
+    <t>raventos@infonegocio.net.pe</t>
+  </si>
+  <si>
+    <t>recepcion@fargoline.com.pe</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>rsotero@almacenesmyrsa.com</t>
+  </si>
+  <si>
+    <t>ventas@alsud.com.pe</t>
+  </si>
+  <si>
+    <t>Cecilia</t>
+  </si>
+  <si>
+    <t>analista.marketing@gogroup.com.pe</t>
+  </si>
+  <si>
+    <t>Karol</t>
+  </si>
+  <si>
+    <t>arnaldo.marrubbio@carpitech.com</t>
+  </si>
+  <si>
+    <t>Arnaldo</t>
+  </si>
+  <si>
+    <t>casacoroeru@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Veronica</t>
+  </si>
+  <si>
+    <t>casacorperu@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>contacto@ximenatuesta.com</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>dvelasquez@flujolibre.com</t>
+  </si>
+  <si>
+    <t>ecasahuaman@jmengineering.com.pe</t>
+  </si>
+  <si>
+    <t>Elmer</t>
+  </si>
+  <si>
+    <t>fanny@casacorperu.com</t>
+  </si>
+  <si>
+    <t>Fanny</t>
+  </si>
+  <si>
+    <t>felipe.sanjuan@rlc.pe</t>
+  </si>
+  <si>
+    <t>Felipe</t>
+  </si>
+  <si>
+    <t>fgarcia@gogroup.com.pe</t>
+  </si>
+  <si>
+    <t>Freddy</t>
+  </si>
+  <si>
+    <t>fmilla-leon@gmlarquitectos.com.pe</t>
+  </si>
+  <si>
+    <t>Fiorella</t>
+  </si>
+  <si>
+    <t>franki1603@gmail.com</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>gcristian@gempresarialgelsa.com</t>
+  </si>
+  <si>
+    <t>gianfranco.olortegui@carpitech.com</t>
+  </si>
+  <si>
+    <t>Gianfranco</t>
+  </si>
+  <si>
+    <t>hanitalv@gmail.com</t>
+  </si>
+  <si>
+    <t>Johana</t>
+  </si>
+  <si>
+    <t>jose.garcia@andritz.com</t>
+  </si>
+  <si>
+    <t>jyarlaque@jmengineering.com.pe</t>
+  </si>
+  <si>
+    <t>kassiavjrsac@hotmail.com</t>
+  </si>
+  <si>
+    <t>larce@3g-office.com</t>
+  </si>
+  <si>
+    <t>luis.utreras@rlc.pe</t>
+  </si>
+  <si>
+    <t>marcela.marcos@andritz.com</t>
+  </si>
+  <si>
+    <t>Marcela</t>
+  </si>
+  <si>
+    <t>pedro_venegas_@outlook.com</t>
+  </si>
+  <si>
+    <t>remcojm@gmail.com</t>
+  </si>
+  <si>
+    <t>Gladys</t>
+  </si>
+  <si>
+    <t>remysta95@gmail.com</t>
+  </si>
+  <si>
+    <t>Micheline</t>
+  </si>
+  <si>
+    <t>renzo.malca@carpitech.com</t>
+  </si>
+  <si>
+    <t>Renzo</t>
+  </si>
+  <si>
+    <t>roy_1251@hotmail.com</t>
+  </si>
+  <si>
+    <t>Roy</t>
+  </si>
+  <si>
+    <t>rusal_toledo@hotmail.com</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>ruth_zavala70@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ruth</t>
+  </si>
+  <si>
+    <t>sortiz@gogroup.com.pe</t>
+  </si>
+  <si>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>vahrens@flujolibre.com</t>
+  </si>
+  <si>
+    <t>Valerie</t>
+  </si>
+  <si>
+    <t>administracion@cavalindustrial.pe</t>
+  </si>
+  <si>
+    <t>Wilber</t>
+  </si>
+  <si>
+    <t>administracion@corcasac.com.pe</t>
+  </si>
+  <si>
+    <t>anneth.diaz.veliz@gmail.com</t>
+  </si>
+  <si>
+    <t>Anneth</t>
+  </si>
+  <si>
+    <t>contabilidad@corcasac.com.pe</t>
+  </si>
+  <si>
+    <t>controlinterno@cavalindustrial.com</t>
+  </si>
+  <si>
+    <t>Monica</t>
+  </si>
+  <si>
+    <t>daker.navarro@espiasa.com.pe</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>eamarquina@manicsac.com</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>erick.espinoza@espiasa.com.pe</t>
+  </si>
+  <si>
+    <t>Armando</t>
+  </si>
+  <si>
+    <t>espiasa@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Víctor</t>
+  </si>
+  <si>
+    <t>gcauchosyanexos@gmail.com</t>
+  </si>
+  <si>
+    <t>gcauchosyanexos@hotmail.com</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>gerencia@cavalindustrial.pe</t>
+  </si>
+  <si>
+    <t>Percy</t>
+  </si>
+  <si>
+    <t>gerenciacomercial@imersoportes.com.pe</t>
+  </si>
+  <si>
+    <t>gomperflex@gmail.com</t>
+  </si>
+  <si>
+    <t>hsalas@siom-mineria.com</t>
+  </si>
+  <si>
+    <t>Hector</t>
+  </si>
+  <si>
+    <t>jorge.capunay@espiasa.com.pe</t>
+  </si>
+  <si>
+    <t>lerk_93@hotmail.com</t>
+  </si>
+  <si>
+    <t>lfranco@indelband.com.pe</t>
+  </si>
+  <si>
+    <t>lgavidia@indelband.com.pe</t>
+  </si>
+  <si>
+    <t>lisbeth.espinoza@espiasa.com.pe</t>
+  </si>
+  <si>
+    <t>Liliam</t>
+  </si>
+  <si>
+    <t>logistica@indelband.com.pe</t>
+  </si>
+  <si>
+    <t>manicsac@manicsac.com</t>
+  </si>
+  <si>
+    <t>Dina</t>
+  </si>
+  <si>
+    <t>ovilca@corcasac.com</t>
+  </si>
+  <si>
+    <t>pcherres@makersperu.com</t>
+  </si>
+  <si>
+    <t>percy.espinoza@espiasa.com.pe</t>
+  </si>
+  <si>
+    <t>secretaria@espiasa.com.pe</t>
+  </si>
+  <si>
+    <t>Emer</t>
+  </si>
+  <si>
+    <t>ventas@corcasac.com.pe</t>
+  </si>
+  <si>
+    <t>ventas@espiasa.com.pe</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>ventas@waikegroupsac.com</t>
+  </si>
+  <si>
+    <t>Edison</t>
   </si>
 </sst>
 </file>
@@ -1086,926 +1122,956 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B55" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B66" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B69" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B72" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B73" t="s">
-        <v>10</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B84" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B85" t="s">
-        <v>164</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B88" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B90" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B91" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B92" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>181</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B98" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B100" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B101" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B103" t="s">
-        <v>146</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B104" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B105" t="s">
-        <v>8</v>
+        <v>202</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B106" t="s">
-        <v>198</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B107" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B109" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>205</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B112" t="s">
-        <v>207</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B114" t="s">
-        <v>146</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B115" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B116" t="s">
-        <v>213</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="4"/>
+      <c r="A117" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B117" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="4"/>
+      <c r="A118" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B118" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="4"/>
+      <c r="A119" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B119" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="4"/>
+      <c r="A120" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B120" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="4"/>
+      <c r="A121" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B121" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
+      <c r="A122" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B122" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="4"/>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62BC381-B061-4DFB-B43C-E5CC91D4B3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2ACE3E-040A-4EAB-A337-551430954084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="221">
   <si>
     <t>correo</t>
   </si>
@@ -52,39 +52,15 @@
     <t>Luis</t>
   </si>
   <si>
-    <t>Ana</t>
-  </si>
-  <si>
-    <t>Patricia</t>
-  </si>
-  <si>
     <t>Carlos</t>
   </si>
   <si>
     <t>Daniel</t>
   </si>
   <si>
-    <t>Cesar</t>
-  </si>
-  <si>
-    <t>Diego</t>
-  </si>
-  <si>
     <t>Fernando</t>
   </si>
   <si>
-    <t>Evelyn</t>
-  </si>
-  <si>
-    <t>Cristian</t>
-  </si>
-  <si>
-    <t>Hugo</t>
-  </si>
-  <si>
-    <t>Lidia</t>
-  </si>
-  <si>
     <t>Jose</t>
   </si>
   <si>
@@ -97,607 +73,616 @@
     <t>Angelica</t>
   </si>
   <si>
-    <t>Haydee</t>
-  </si>
-  <si>
-    <t>Giuliana</t>
-  </si>
-  <si>
-    <t>alonsorm84@hotmail.com</t>
-  </si>
-  <si>
-    <t>Alonso</t>
-  </si>
-  <si>
-    <t>andrea@jhadetextile.com</t>
-  </si>
-  <si>
-    <t>Andrea</t>
-  </si>
-  <si>
-    <t>bbnanitas@hotmail.com</t>
-  </si>
-  <si>
-    <t>Hubert</t>
-  </si>
-  <si>
-    <t>blancadls@madmen.pe</t>
-  </si>
-  <si>
-    <t>Blanca</t>
-  </si>
-  <si>
-    <t>chcubas@verach.pe</t>
-  </si>
-  <si>
-    <t>Charles</t>
-  </si>
-  <si>
-    <t>comercial@textilairin.pe</t>
-  </si>
-  <si>
-    <t>Zczar</t>
-  </si>
-  <si>
-    <t>conta04@metaljeans.com.pe</t>
-  </si>
-  <si>
     <t>Liliana</t>
   </si>
   <si>
-    <t>finanzas@mpdsac.com</t>
-  </si>
-  <si>
-    <t>Fernanda</t>
-  </si>
-  <si>
-    <t>haydee@jhadetextile.com</t>
-  </si>
-  <si>
-    <t>janina.coronel@metaljeans.com.pe</t>
-  </si>
-  <si>
-    <t>Sandrita</t>
-  </si>
-  <si>
-    <t>jfconfeccione09@hotmail.com</t>
-  </si>
-  <si>
-    <t>Jeronimo</t>
-  </si>
-  <si>
-    <t>jlatorre@mpdsac.com</t>
-  </si>
-  <si>
-    <t>Javier</t>
-  </si>
-  <si>
-    <t>juanjo04689@gmail.com</t>
-  </si>
-  <si>
-    <t>l.torres@stratagarments.pe</t>
-  </si>
-  <si>
-    <t>luisangel@mpdsac.com</t>
-  </si>
-  <si>
-    <t>luz.h@mpdsac.com</t>
-  </si>
-  <si>
-    <t>marcial74@hotmail.com</t>
-  </si>
-  <si>
-    <t>Edwin</t>
-  </si>
-  <si>
-    <t>metaljeans@metaljeans.com.pe</t>
-  </si>
-  <si>
-    <t>mmontanez@disenoacmm.com</t>
-  </si>
-  <si>
-    <t>Mirko</t>
-  </si>
-  <si>
-    <t>rajumahtani2@gmail.com</t>
-  </si>
-  <si>
-    <t>Raju</t>
-  </si>
-  <si>
-    <t>rayumactani@gmail.com</t>
-  </si>
-  <si>
-    <t>Hari</t>
-  </si>
-  <si>
-    <t>reneepena@raffaproexco.com</t>
-  </si>
-  <si>
-    <t>Allan</t>
-  </si>
-  <si>
-    <t>rmarure@textilairin.pe</t>
-  </si>
-  <si>
-    <t>Roberth</t>
-  </si>
-  <si>
-    <t>strata.garments.sac@gmail.com</t>
-  </si>
-  <si>
-    <t>swag69clothing@gmail.com</t>
-  </si>
-  <si>
-    <t>Lizett</t>
-  </si>
-  <si>
-    <t>textilgrubba@outlook.com</t>
-  </si>
-  <si>
-    <t>Alejandrina</t>
-  </si>
-  <si>
-    <t>tsotelo27@hotmail.com</t>
-  </si>
-  <si>
-    <t>Tania</t>
-  </si>
-  <si>
-    <t>ventas@textilgrubba.com</t>
-  </si>
-  <si>
     <t>Jesus</t>
   </si>
   <si>
-    <t>ymarcelo@mpdsac.com</t>
-  </si>
-  <si>
-    <t>Yuly</t>
-  </si>
-  <si>
-    <t>yoanna24@hotmail.com</t>
-  </si>
-  <si>
-    <t>Yoanna</t>
-  </si>
-  <si>
-    <t>aburgos@itsanet.com</t>
-  </si>
-  <si>
-    <t>Augusto</t>
-  </si>
-  <si>
-    <t>acarrion@wulee.pe</t>
-  </si>
-  <si>
-    <t>achiclla@almacenesmyrsa.com</t>
-  </si>
-  <si>
-    <t>acruz@amtcontadoresyasesores.com</t>
-  </si>
-  <si>
-    <t>Anthony</t>
-  </si>
-  <si>
-    <t>administracion.peru@rems.pe</t>
-  </si>
-  <si>
-    <t>Jennifer</t>
-  </si>
-  <si>
-    <t>administracionlima@almacenes-sos.com</t>
-  </si>
-  <si>
-    <t>Lewis</t>
-  </si>
-  <si>
-    <t>araceli.moreno@rems.pe</t>
-  </si>
-  <si>
-    <t>Araceli</t>
-  </si>
-  <si>
-    <t>asistente@almaceneratrujillo.com.pe</t>
-  </si>
-  <si>
-    <t>Angel</t>
-  </si>
-  <si>
-    <t>bquijano@itsanet.com</t>
-  </si>
-  <si>
-    <t>Beatriz</t>
-  </si>
-  <si>
-    <t>cesar.soriano@fargoline.com.pe</t>
-  </si>
-  <si>
-    <t>cmontoya@alsud.com.pe</t>
-  </si>
-  <si>
-    <t>Mariano</t>
-  </si>
-  <si>
-    <t>crojas@intsol.com.pe</t>
-  </si>
-  <si>
-    <t>Christhyam</t>
-  </si>
-  <si>
-    <t>davis.gomez@grupoe2e.com</t>
-  </si>
-  <si>
     <t>Oscar</t>
   </si>
   <si>
-    <t>direccion.tecnica@intsol.com.pe</t>
-  </si>
-  <si>
-    <t>Janett</t>
-  </si>
-  <si>
-    <t>finanzas@shohin.com.pe</t>
-  </si>
-  <si>
-    <t>fpeirano@itsanet.com</t>
-  </si>
-  <si>
-    <t>gabriel.garcia@rems.pe</t>
-  </si>
-  <si>
-    <t>Gabriel</t>
-  </si>
-  <si>
-    <t>gerencia@almacenes-sos.com</t>
-  </si>
-  <si>
-    <t>Ricardo</t>
-  </si>
-  <si>
-    <t>guillermo.marroquin@intsol.com.pe</t>
-  </si>
-  <si>
-    <t>hbohme@shohin.com.pe</t>
-  </si>
-  <si>
-    <t>Heinz</t>
-  </si>
-  <si>
-    <t>informes@davayasociados.com</t>
-  </si>
-  <si>
-    <t>Delfin</t>
-  </si>
-  <si>
-    <t>jaime.ferrero@fargoline.com.pe</t>
-  </si>
-  <si>
-    <t>Jaime</t>
-  </si>
-  <si>
-    <t>marcos.garciami@rems.pe</t>
-  </si>
-  <si>
-    <t>Marcos</t>
-  </si>
-  <si>
-    <t>mcajo@shohin.com.pe</t>
-  </si>
-  <si>
-    <t>paul.sairitupac@rems.pe</t>
-  </si>
-  <si>
     <t>Paul</t>
   </si>
   <si>
-    <t>practicanterrhh@fargoline.com.pe</t>
-  </si>
-  <si>
-    <t>raventos@infonegocio.net.pe</t>
-  </si>
-  <si>
-    <t>recepcion@fargoline.com.pe</t>
-  </si>
-  <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>rsotero@almacenesmyrsa.com</t>
-  </si>
-  <si>
-    <t>ventas@alsud.com.pe</t>
-  </si>
-  <si>
-    <t>Cecilia</t>
-  </si>
-  <si>
-    <t>analista.marketing@gogroup.com.pe</t>
-  </si>
-  <si>
-    <t>Karol</t>
-  </si>
-  <si>
-    <t>arnaldo.marrubbio@carpitech.com</t>
-  </si>
-  <si>
-    <t>Arnaldo</t>
-  </si>
-  <si>
-    <t>casacoroeru@terra.com.pe</t>
-  </si>
-  <si>
-    <t>Veronica</t>
-  </si>
-  <si>
-    <t>casacorperu@terra.com.pe</t>
-  </si>
-  <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t>contacto@ximenatuesta.com</t>
-  </si>
-  <si>
-    <t>Claudia</t>
-  </si>
-  <si>
-    <t>dvelasquez@flujolibre.com</t>
-  </si>
-  <si>
-    <t>ecasahuaman@jmengineering.com.pe</t>
-  </si>
-  <si>
-    <t>Elmer</t>
-  </si>
-  <si>
-    <t>fanny@casacorperu.com</t>
-  </si>
-  <si>
-    <t>Fanny</t>
-  </si>
-  <si>
-    <t>felipe.sanjuan@rlc.pe</t>
-  </si>
-  <si>
-    <t>Felipe</t>
-  </si>
-  <si>
-    <t>fgarcia@gogroup.com.pe</t>
-  </si>
-  <si>
-    <t>Freddy</t>
-  </si>
-  <si>
-    <t>fmilla-leon@gmlarquitectos.com.pe</t>
-  </si>
-  <si>
-    <t>Fiorella</t>
-  </si>
-  <si>
-    <t>franki1603@gmail.com</t>
-  </si>
-  <si>
-    <t>Frank</t>
-  </si>
-  <si>
-    <t>gcristian@gempresarialgelsa.com</t>
-  </si>
-  <si>
-    <t>gianfranco.olortegui@carpitech.com</t>
-  </si>
-  <si>
-    <t>Gianfranco</t>
-  </si>
-  <si>
-    <t>hanitalv@gmail.com</t>
-  </si>
-  <si>
     <t>Johana</t>
   </si>
   <si>
-    <t>jose.garcia@andritz.com</t>
-  </si>
-  <si>
-    <t>jyarlaque@jmengineering.com.pe</t>
-  </si>
-  <si>
-    <t>kassiavjrsac@hotmail.com</t>
-  </si>
-  <si>
-    <t>larce@3g-office.com</t>
-  </si>
-  <si>
-    <t>luis.utreras@rlc.pe</t>
-  </si>
-  <si>
-    <t>marcela.marcos@andritz.com</t>
-  </si>
-  <si>
-    <t>Marcela</t>
-  </si>
-  <si>
-    <t>pedro_venegas_@outlook.com</t>
-  </si>
-  <si>
-    <t>remcojm@gmail.com</t>
-  </si>
-  <si>
-    <t>Gladys</t>
-  </si>
-  <si>
-    <t>remysta95@gmail.com</t>
-  </si>
-  <si>
-    <t>Micheline</t>
-  </si>
-  <si>
-    <t>renzo.malca@carpitech.com</t>
-  </si>
-  <si>
-    <t>Renzo</t>
-  </si>
-  <si>
-    <t>roy_1251@hotmail.com</t>
-  </si>
-  <si>
-    <t>Roy</t>
-  </si>
-  <si>
-    <t>rusal_toledo@hotmail.com</t>
-  </si>
-  <si>
-    <t>Alfonso</t>
-  </si>
-  <si>
-    <t>ruth_zavala70@hotmail.com</t>
-  </si>
-  <si>
-    <t>Ruth</t>
-  </si>
-  <si>
-    <t>sortiz@gogroup.com.pe</t>
-  </si>
-  <si>
-    <t>Susan</t>
-  </si>
-  <si>
-    <t>vahrens@flujolibre.com</t>
-  </si>
-  <si>
-    <t>Valerie</t>
-  </si>
-  <si>
-    <t>administracion@cavalindustrial.pe</t>
-  </si>
-  <si>
-    <t>Wilber</t>
-  </si>
-  <si>
-    <t>administracion@corcasac.com.pe</t>
-  </si>
-  <si>
-    <t>anneth.diaz.veliz@gmail.com</t>
-  </si>
-  <si>
-    <t>Anneth</t>
-  </si>
-  <si>
-    <t>contabilidad@corcasac.com.pe</t>
-  </si>
-  <si>
-    <t>controlinterno@cavalindustrial.com</t>
-  </si>
-  <si>
-    <t>Monica</t>
-  </si>
-  <si>
-    <t>daker.navarro@espiasa.com.pe</t>
-  </si>
-  <si>
     <t>Alberto</t>
   </si>
   <si>
-    <t>eamarquina@manicsac.com</t>
-  </si>
-  <si>
     <t>Edgar</t>
   </si>
   <si>
-    <t>erick.espinoza@espiasa.com.pe</t>
-  </si>
-  <si>
     <t>Armando</t>
   </si>
   <si>
-    <t>espiasa@terra.com.pe</t>
-  </si>
-  <si>
     <t>Víctor</t>
   </si>
   <si>
-    <t>gcauchosyanexos@gmail.com</t>
-  </si>
-  <si>
-    <t>gcauchosyanexos@hotmail.com</t>
-  </si>
-  <si>
     <t>William</t>
   </si>
   <si>
-    <t>gerencia@cavalindustrial.pe</t>
-  </si>
-  <si>
-    <t>Percy</t>
-  </si>
-  <si>
-    <t>gerenciacomercial@imersoportes.com.pe</t>
-  </si>
-  <si>
-    <t>gomperflex@gmail.com</t>
-  </si>
-  <si>
-    <t>hsalas@siom-mineria.com</t>
-  </si>
-  <si>
     <t>Hector</t>
   </si>
   <si>
-    <t>jorge.capunay@espiasa.com.pe</t>
-  </si>
-  <si>
-    <t>lerk_93@hotmail.com</t>
-  </si>
-  <si>
-    <t>lfranco@indelband.com.pe</t>
-  </si>
-  <si>
-    <t>lgavidia@indelband.com.pe</t>
-  </si>
-  <si>
-    <t>lisbeth.espinoza@espiasa.com.pe</t>
-  </si>
-  <si>
-    <t>Liliam</t>
-  </si>
-  <si>
-    <t>logistica@indelband.com.pe</t>
-  </si>
-  <si>
-    <t>manicsac@manicsac.com</t>
-  </si>
-  <si>
-    <t>Dina</t>
-  </si>
-  <si>
-    <t>ovilca@corcasac.com</t>
-  </si>
-  <si>
-    <t>pcherres@makersperu.com</t>
-  </si>
-  <si>
-    <t>percy.espinoza@espiasa.com.pe</t>
-  </si>
-  <si>
-    <t>secretaria@espiasa.com.pe</t>
-  </si>
-  <si>
-    <t>Emer</t>
-  </si>
-  <si>
-    <t>ventas@corcasac.com.pe</t>
-  </si>
-  <si>
-    <t>ventas@espiasa.com.pe</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>ventas@waikegroupsac.com</t>
-  </si>
-  <si>
-    <t>Edison</t>
+    <t>admin@inap.pe</t>
+  </si>
+  <si>
+    <t>Alejandra</t>
+  </si>
+  <si>
+    <t>amaltese@ipesahydro.com.pe</t>
+  </si>
+  <si>
+    <t>apukatinti@yahoo.es</t>
+  </si>
+  <si>
+    <t>arquimedestorres@maizpicota.com</t>
+  </si>
+  <si>
+    <t>Arquimedes</t>
+  </si>
+  <si>
+    <t>brenharu@gmail.com</t>
+  </si>
+  <si>
+    <t>Brenda</t>
+  </si>
+  <si>
+    <t>cherrera@lignoquim.com.ec</t>
+  </si>
+  <si>
+    <t>cmosoni@ipesahydro.com.pe</t>
+  </si>
+  <si>
+    <t>Carlo</t>
+  </si>
+  <si>
+    <t>cocopolanco@hotmail.com</t>
+  </si>
+  <si>
+    <t>contabilidad@colorcenter.pe</t>
+  </si>
+  <si>
+    <t>crojas@avgust.com.pe</t>
+  </si>
+  <si>
+    <t>emora@inap.pe</t>
+  </si>
+  <si>
+    <t>Edith</t>
+  </si>
+  <si>
+    <t>evalle@koppert.pe</t>
+  </si>
+  <si>
+    <t>Emilio</t>
+  </si>
+  <si>
+    <t>francisco.chavez@gruposilvestre.com.pe</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>g.lira@avgust.com.pe</t>
+  </si>
+  <si>
+    <t>Genaro</t>
+  </si>
+  <si>
+    <t>info@paititiperucompany.com</t>
+  </si>
+  <si>
+    <t>isabel.aliaga@netafim.orbia.com</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <t>isalazardc@romex.com.pe</t>
+  </si>
+  <si>
+    <t>Ines</t>
+  </si>
+  <si>
+    <t>jdelcastillo@alcosa-peru.com</t>
+  </si>
+  <si>
+    <t>jorgeviscondech@gmail.com</t>
+  </si>
+  <si>
+    <t>liz.lara@gruposilvestre.com.pe</t>
+  </si>
+  <si>
+    <t>mercolsac@hotmail.com</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>mlopez@colorcenter.pe</t>
+  </si>
+  <si>
+    <t>Melina</t>
+  </si>
+  <si>
+    <t>mreyes@ipesahydro.com.pe</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>palomino.alain@gmail.com</t>
+  </si>
+  <si>
+    <t>Alahin</t>
+  </si>
+  <si>
+    <t>rafael.vidal@netafim.orbia.com</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>raguilera@ipesahydro.com.pe</t>
+  </si>
+  <si>
+    <t>Rocio</t>
+  </si>
+  <si>
+    <t>sistemas@colorcenter.pe</t>
+  </si>
+  <si>
+    <t>skalafatovich@inap.pe</t>
+  </si>
+  <si>
+    <t>Stefhan</t>
+  </si>
+  <si>
+    <t>tesoreria@colorcenter.pe</t>
+  </si>
+  <si>
+    <t>yeshua_486@hotmail.com</t>
+  </si>
+  <si>
+    <t>amorales@continentalperu.com</t>
+  </si>
+  <si>
+    <t>Alejandro</t>
+  </si>
+  <si>
+    <t>crlsrmzpnc@gmail.com</t>
+  </si>
+  <si>
+    <t>daruimportaciones-e.i.r.l@hotmail.com</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
+    <t>dchavez@taiheng.com.pe</t>
+  </si>
+  <si>
+    <t>e.llerena@distribuidoranavarrete.com.pe</t>
+  </si>
+  <si>
+    <t>Estefania</t>
+  </si>
+  <si>
+    <t>elau@brickel.com.pe</t>
+  </si>
+  <si>
+    <t>Eileen</t>
+  </si>
+  <si>
+    <t>fcabrera@faber-castell.com.pe</t>
+  </si>
+  <si>
+    <t>fchinag@taiheng.com.pe</t>
+  </si>
+  <si>
+    <t>gabrielarcarlospoma@gmail.com</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>gerencia@remutools.com</t>
+  </si>
+  <si>
+    <t>haiteperusac@gmail.com</t>
+  </si>
+  <si>
+    <t>info@daruimportaciones.com</t>
+  </si>
+  <si>
+    <t>jc.carrillo@faber-castell.com.pe</t>
+  </si>
+  <si>
+    <t>jefe.corporativo@distribuidoranavarrete.com.pe</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>jenny.12af@gmail.com</t>
+  </si>
+  <si>
+    <t>Jenny</t>
+  </si>
+  <si>
+    <t>jkoc@tailoy.com.pe</t>
+  </si>
+  <si>
+    <t>katherine.navarrete@distribuidoranavarrete.com.pe</t>
+  </si>
+  <si>
+    <t>Hilda</t>
+  </si>
+  <si>
+    <t>lromero@tailoy.com.pe</t>
+  </si>
+  <si>
+    <t>masencios@taiheng.com.pe</t>
+  </si>
+  <si>
+    <t>Mabel</t>
+  </si>
+  <si>
+    <t>mhuarcaya@tailoy.com.pe</t>
+  </si>
+  <si>
+    <t>orojas@taiheng.com.pe</t>
+  </si>
+  <si>
+    <t>Ofelia</t>
+  </si>
+  <si>
+    <t>psilva@tailoy.com.pe</t>
+  </si>
+  <si>
+    <t>pwong@continentalperu.com</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>schung@taiheng.com.pe</t>
+  </si>
+  <si>
+    <t>Shiu</t>
+  </si>
+  <si>
+    <t>vchian@taiheng.com.pe</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>ventas@daruimportaciones.com</t>
+  </si>
+  <si>
+    <t>Daniela</t>
+  </si>
+  <si>
+    <t>victorlauk@brickel.com.pe</t>
+  </si>
+  <si>
+    <t>wlopez@tailoy.com.pe</t>
+  </si>
+  <si>
+    <t>wuilmerhuichohuico@gmail.com</t>
+  </si>
+  <si>
+    <t>Wuilmer</t>
+  </si>
+  <si>
+    <t>ycapcha@brickel.com.pe</t>
+  </si>
+  <si>
+    <t>Yane</t>
+  </si>
+  <si>
+    <t>admin.conta@panguautoperu.com</t>
+  </si>
+  <si>
+    <t>Lia</t>
+  </si>
+  <si>
+    <t>aukipaliza@toyotaperu.com.pe</t>
+  </si>
+  <si>
+    <t>Auki</t>
+  </si>
+  <si>
+    <t>cbalta@grupopana.com.pe</t>
+  </si>
+  <si>
+    <t>directorgerente@grupogesa.com</t>
+  </si>
+  <si>
+    <t>dpto_personal@grupogesa.com</t>
+  </si>
+  <si>
+    <t>Aldo</t>
+  </si>
+  <si>
+    <t>dptocredito@grupogesa.com</t>
+  </si>
+  <si>
+    <t>Norma</t>
+  </si>
+  <si>
+    <t>drubio@modasa.com.pe</t>
+  </si>
+  <si>
+    <t>enrique.pagola@inchcape.com</t>
+  </si>
+  <si>
+    <t>Enrique</t>
+  </si>
+  <si>
+    <t>ext.erika.delgado.r@astara.com</t>
+  </si>
+  <si>
+    <t>facosta@modasa.com.pe</t>
+  </si>
+  <si>
+    <t>fquiroz@autoesparcomas.com</t>
+  </si>
+  <si>
+    <t>ggarcia@modasa.com.pe</t>
+  </si>
+  <si>
+    <t>hgarcia@modasa.com.pe</t>
+  </si>
+  <si>
+    <t>hwatanabe@toyotaperu.com.pe</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>imartinez@toyotaperu.com.pe</t>
+  </si>
+  <si>
+    <t>Daisuke</t>
+  </si>
+  <si>
+    <t>j.ronceros@kamazlatinoamerica.com</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>julia.ardiles@grupogesa.com</t>
+  </si>
+  <si>
+    <t>Josefina</t>
+  </si>
+  <si>
+    <t>karambulo@grupopana.com.pe</t>
+  </si>
+  <si>
+    <t>lnunez@dercoperu.net</t>
+  </si>
+  <si>
+    <t>Lizbeth</t>
+  </si>
+  <si>
+    <t>lorellana@autoesparfiori.com</t>
+  </si>
+  <si>
+    <t>Lina</t>
+  </si>
+  <si>
+    <t>mandy@grupopana.com.pe</t>
+  </si>
+  <si>
+    <t>mcuya@toyotaperu.com.pe</t>
+  </si>
+  <si>
+    <t>mjimenez@autoesparfiori.com</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>mschmiel@modasa.com.pe</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>ochero@toyotaperu.com.pe</t>
+  </si>
+  <si>
+    <t>ohuaman@grupogesa.com</t>
+  </si>
+  <si>
+    <t>Orestes</t>
+  </si>
+  <si>
+    <t>quanweihuang168@gmail.com</t>
+  </si>
+  <si>
+    <t>Huang</t>
+  </si>
+  <si>
+    <t>rbettocchi@modasa.com.pe</t>
+  </si>
+  <si>
+    <t>Rossana</t>
+  </si>
+  <si>
+    <t>river070717@gmail.com</t>
+  </si>
+  <si>
+    <t>Linhao</t>
+  </si>
+  <si>
+    <t>stephanie.guerra@oxyion.com</t>
+  </si>
+  <si>
+    <t>Stephanie</t>
+  </si>
+  <si>
+    <t>aepo1@yahoo.com</t>
+  </si>
+  <si>
+    <t>Alcides</t>
+  </si>
+  <si>
+    <t>alitecnoperu@alitecnoperu.com</t>
+  </si>
+  <si>
+    <t>Renato</t>
+  </si>
+  <si>
+    <t>asistentecontable@efysisa.com.pe</t>
+  </si>
+  <si>
+    <t>Marisol</t>
+  </si>
+  <si>
+    <t>bcarabelli@donitalo.com</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>cbrescia@2cerritos.com.pe</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>cerritos@2cerritos.com.pe</t>
+  </si>
+  <si>
+    <t>Tulio</t>
+  </si>
+  <si>
+    <t>colnatexsac@gmail.com</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>croman@rich.com</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>drodriguez@greenfarm.com.pe</t>
+  </si>
+  <si>
+    <t>Denisse</t>
+  </si>
+  <si>
+    <t>edgarcubas11@gmail.com</t>
+  </si>
+  <si>
+    <t>gcarabelli@donitalo.com</t>
+  </si>
+  <si>
+    <t>Giancarlo</t>
+  </si>
+  <si>
+    <t>hurlich@alejosperu.com.pe</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>isoto@rich.com</t>
+  </si>
+  <si>
+    <t>Ingrid</t>
+  </si>
+  <si>
+    <t>jcormercial@greenfarm.com.pe</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>jmacedo@2cerritos.com.pe</t>
+  </si>
+  <si>
+    <t>joelvt@globalinkat.com</t>
+  </si>
+  <si>
+    <t>Joel</t>
+  </si>
+  <si>
+    <t>josuevillanueva@globalinkat.com</t>
+  </si>
+  <si>
+    <t>Josue</t>
+  </si>
+  <si>
+    <t>jpalejos@alejosperu.com.pe</t>
+  </si>
+  <si>
+    <t>lulapo8@gmail.com</t>
+  </si>
+  <si>
+    <t>Lourdes</t>
+  </si>
+  <si>
+    <t>magrena.espinoza123@gmail.com</t>
+  </si>
+  <si>
+    <t>Magrena</t>
+  </si>
+  <si>
+    <t>manzovini@efysisa.com.pe</t>
+  </si>
+  <si>
+    <t>mindrisita123@gmail.com</t>
+  </si>
+  <si>
+    <t>Lisset</t>
+  </si>
+  <si>
+    <t>norma.delacruz@alitecnoperu.com</t>
+  </si>
+  <si>
+    <t>noyafuso@2cerritos.com.pe</t>
+  </si>
+  <si>
+    <t>palejo@alejosperu.com.pe</t>
+  </si>
+  <si>
+    <t>rgomez@2cerritos.com.pe</t>
+  </si>
+  <si>
+    <t>Raul</t>
+  </si>
+  <si>
+    <t>rosario.griffin@cramer.com.pe</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>sumaqagrotrade@gmail.com</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>vania.yaya@alitecnoperu.com</t>
+  </si>
+  <si>
+    <t>Vania</t>
+  </si>
+  <si>
+    <t>victor.gomez@cramer.com.pe</t>
   </si>
 </sst>
 </file>
@@ -1122,18 +1107,18 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1141,237 +1126,237 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
         <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
         <v>54</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -1379,702 +1364,707 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B55" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s">
-        <v>6</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B62" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B65" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B70" t="s">
-        <v>142</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B71" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="B74" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B77" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="B78" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B79" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B84" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B86" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B87" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B89" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="B93" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B94" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B97" t="s">
-        <v>7</v>
+        <v>176</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B100" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B101" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B102" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B103" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B104" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B105" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B106" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B107" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B108" t="s">
-        <v>206</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>198</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>200</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B111" t="s">
-        <v>9</v>
+        <v>144</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B112" t="s">
-        <v>20</v>
+        <v>203</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B113" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B115" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B117" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B118" t="s">
-        <v>202</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B119" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B120" t="s">
-        <v>139</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B121" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B122" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="4"/>
+      <c r="A123" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B123" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>

--- a/Correos.xlsx
+++ b/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\correos_masivos\Correos-Masivos-Partner-Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2ACE3E-040A-4EAB-A337-551430954084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE3625D-141A-4C56-B75E-31553FE3F3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="225">
   <si>
     <t>correo</t>
   </si>
@@ -55,634 +55,646 @@
     <t>Carlos</t>
   </si>
   <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Fernando</t>
-  </si>
-  <si>
     <t>Jose</t>
   </si>
   <si>
-    <t>Pedro</t>
-  </si>
-  <si>
-    <t>Luz</t>
-  </si>
-  <si>
-    <t>Angelica</t>
-  </si>
-  <si>
     <t>Liliana</t>
   </si>
   <si>
-    <t>Jesus</t>
-  </si>
-  <si>
-    <t>Oscar</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>Johana</t>
-  </si>
-  <si>
     <t>Alberto</t>
   </si>
   <si>
-    <t>Edgar</t>
-  </si>
-  <si>
-    <t>Armando</t>
-  </si>
-  <si>
-    <t>Víctor</t>
-  </si>
-  <si>
-    <t>William</t>
-  </si>
-  <si>
-    <t>Hector</t>
-  </si>
-  <si>
-    <t>admin@inap.pe</t>
-  </si>
-  <si>
-    <t>Alejandra</t>
-  </si>
-  <si>
-    <t>amaltese@ipesahydro.com.pe</t>
-  </si>
-  <si>
-    <t>apukatinti@yahoo.es</t>
-  </si>
-  <si>
-    <t>arquimedestorres@maizpicota.com</t>
-  </si>
-  <si>
-    <t>Arquimedes</t>
-  </si>
-  <si>
-    <t>brenharu@gmail.com</t>
-  </si>
-  <si>
-    <t>Brenda</t>
-  </si>
-  <si>
-    <t>cherrera@lignoquim.com.ec</t>
-  </si>
-  <si>
-    <t>cmosoni@ipesahydro.com.pe</t>
-  </si>
-  <si>
-    <t>Carlo</t>
-  </si>
-  <si>
-    <t>cocopolanco@hotmail.com</t>
-  </si>
-  <si>
-    <t>contabilidad@colorcenter.pe</t>
-  </si>
-  <si>
-    <t>crojas@avgust.com.pe</t>
-  </si>
-  <si>
-    <t>emora@inap.pe</t>
-  </si>
-  <si>
-    <t>Edith</t>
-  </si>
-  <si>
-    <t>evalle@koppert.pe</t>
-  </si>
-  <si>
-    <t>Emilio</t>
-  </si>
-  <si>
-    <t>francisco.chavez@gruposilvestre.com.pe</t>
-  </si>
-  <si>
     <t>Francisco</t>
   </si>
   <si>
-    <t>g.lira@avgust.com.pe</t>
-  </si>
-  <si>
-    <t>Genaro</t>
-  </si>
-  <si>
-    <t>info@paititiperucompany.com</t>
-  </si>
-  <si>
-    <t>isabel.aliaga@netafim.orbia.com</t>
-  </si>
-  <si>
-    <t>Isabel</t>
-  </si>
-  <si>
-    <t>isalazardc@romex.com.pe</t>
-  </si>
-  <si>
-    <t>Ines</t>
-  </si>
-  <si>
-    <t>jdelcastillo@alcosa-peru.com</t>
-  </si>
-  <si>
-    <t>jorgeviscondech@gmail.com</t>
-  </si>
-  <si>
-    <t>liz.lara@gruposilvestre.com.pe</t>
-  </si>
-  <si>
-    <t>mercolsac@hotmail.com</t>
-  </si>
-  <si>
-    <t>Marco</t>
-  </si>
-  <si>
-    <t>mlopez@colorcenter.pe</t>
-  </si>
-  <si>
-    <t>Melina</t>
-  </si>
-  <si>
-    <t>mreyes@ipesahydro.com.pe</t>
-  </si>
-  <si>
-    <t>Manuel</t>
-  </si>
-  <si>
-    <t>palomino.alain@gmail.com</t>
-  </si>
-  <si>
-    <t>Alahin</t>
-  </si>
-  <si>
-    <t>rafael.vidal@netafim.orbia.com</t>
-  </si>
-  <si>
-    <t>Rafael</t>
-  </si>
-  <si>
-    <t>raguilera@ipesahydro.com.pe</t>
-  </si>
-  <si>
-    <t>Rocio</t>
-  </si>
-  <si>
-    <t>sistemas@colorcenter.pe</t>
-  </si>
-  <si>
-    <t>skalafatovich@inap.pe</t>
-  </si>
-  <si>
-    <t>Stefhan</t>
-  </si>
-  <si>
-    <t>tesoreria@colorcenter.pe</t>
-  </si>
-  <si>
-    <t>yeshua_486@hotmail.com</t>
-  </si>
-  <si>
-    <t>amorales@continentalperu.com</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t>crlsrmzpnc@gmail.com</t>
-  </si>
-  <si>
-    <t>daruimportaciones-e.i.r.l@hotmail.com</t>
-  </si>
-  <si>
-    <t>Felix</t>
-  </si>
-  <si>
-    <t>dchavez@taiheng.com.pe</t>
-  </si>
-  <si>
-    <t>e.llerena@distribuidoranavarrete.com.pe</t>
-  </si>
-  <si>
-    <t>Estefania</t>
-  </si>
-  <si>
-    <t>elau@brickel.com.pe</t>
-  </si>
-  <si>
-    <t>Eileen</t>
-  </si>
-  <si>
-    <t>fcabrera@faber-castell.com.pe</t>
-  </si>
-  <si>
-    <t>fchinag@taiheng.com.pe</t>
-  </si>
-  <si>
-    <t>gabrielarcarlospoma@gmail.com</t>
-  </si>
-  <si>
     <t>Gabriela</t>
   </si>
   <si>
-    <t>gerencia@remutools.com</t>
-  </si>
-  <si>
-    <t>haiteperusac@gmail.com</t>
-  </si>
-  <si>
-    <t>info@daruimportaciones.com</t>
-  </si>
-  <si>
-    <t>jc.carrillo@faber-castell.com.pe</t>
-  </si>
-  <si>
-    <t>jefe.corporativo@distribuidoranavarrete.com.pe</t>
-  </si>
-  <si>
     <t>Julia</t>
   </si>
   <si>
-    <t>jenny.12af@gmail.com</t>
-  </si>
-  <si>
     <t>Jenny</t>
   </si>
   <si>
-    <t>jkoc@tailoy.com.pe</t>
-  </si>
-  <si>
-    <t>katherine.navarrete@distribuidoranavarrete.com.pe</t>
-  </si>
-  <si>
-    <t>Hilda</t>
-  </si>
-  <si>
-    <t>lromero@tailoy.com.pe</t>
-  </si>
-  <si>
-    <t>masencios@taiheng.com.pe</t>
-  </si>
-  <si>
-    <t>Mabel</t>
-  </si>
-  <si>
-    <t>mhuarcaya@tailoy.com.pe</t>
-  </si>
-  <si>
-    <t>orojas@taiheng.com.pe</t>
-  </si>
-  <si>
-    <t>Ofelia</t>
-  </si>
-  <si>
-    <t>psilva@tailoy.com.pe</t>
-  </si>
-  <si>
-    <t>pwong@continentalperu.com</t>
-  </si>
-  <si>
     <t>Pablo</t>
   </si>
   <si>
-    <t>schung@taiheng.com.pe</t>
-  </si>
-  <si>
-    <t>Shiu</t>
-  </si>
-  <si>
-    <t>vchian@taiheng.com.pe</t>
-  </si>
-  <si>
     <t>Victor</t>
   </si>
   <si>
-    <t>ventas@daruimportaciones.com</t>
-  </si>
-  <si>
-    <t>Daniela</t>
-  </si>
-  <si>
-    <t>victorlauk@brickel.com.pe</t>
-  </si>
-  <si>
-    <t>wlopez@tailoy.com.pe</t>
-  </si>
-  <si>
-    <t>wuilmerhuichohuico@gmail.com</t>
-  </si>
-  <si>
-    <t>Wuilmer</t>
-  </si>
-  <si>
-    <t>ycapcha@brickel.com.pe</t>
-  </si>
-  <si>
-    <t>Yane</t>
-  </si>
-  <si>
-    <t>admin.conta@panguautoperu.com</t>
-  </si>
-  <si>
-    <t>Lia</t>
-  </si>
-  <si>
-    <t>aukipaliza@toyotaperu.com.pe</t>
-  </si>
-  <si>
-    <t>Auki</t>
-  </si>
-  <si>
-    <t>cbalta@grupopana.com.pe</t>
-  </si>
-  <si>
-    <t>directorgerente@grupogesa.com</t>
-  </si>
-  <si>
-    <t>dpto_personal@grupogesa.com</t>
-  </si>
-  <si>
-    <t>Aldo</t>
-  </si>
-  <si>
-    <t>dptocredito@grupogesa.com</t>
-  </si>
-  <si>
-    <t>Norma</t>
-  </si>
-  <si>
-    <t>drubio@modasa.com.pe</t>
-  </si>
-  <si>
-    <t>enrique.pagola@inchcape.com</t>
-  </si>
-  <si>
     <t>Enrique</t>
   </si>
   <si>
-    <t>ext.erika.delgado.r@astara.com</t>
-  </si>
-  <si>
-    <t>facosta@modasa.com.pe</t>
-  </si>
-  <si>
-    <t>fquiroz@autoesparcomas.com</t>
-  </si>
-  <si>
-    <t>ggarcia@modasa.com.pe</t>
-  </si>
-  <si>
-    <t>hgarcia@modasa.com.pe</t>
-  </si>
-  <si>
-    <t>hwatanabe@toyotaperu.com.pe</t>
-  </si>
-  <si>
     <t>Christian</t>
   </si>
   <si>
-    <t>imartinez@toyotaperu.com.pe</t>
-  </si>
-  <si>
-    <t>Daisuke</t>
-  </si>
-  <si>
-    <t>j.ronceros@kamazlatinoamerica.com</t>
-  </si>
-  <si>
-    <t>Jean</t>
-  </si>
-  <si>
-    <t>julia.ardiles@grupogesa.com</t>
-  </si>
-  <si>
-    <t>Josefina</t>
-  </si>
-  <si>
-    <t>karambulo@grupopana.com.pe</t>
-  </si>
-  <si>
-    <t>lnunez@dercoperu.net</t>
-  </si>
-  <si>
-    <t>Lizbeth</t>
-  </si>
-  <si>
-    <t>lorellana@autoesparfiori.com</t>
-  </si>
-  <si>
-    <t>Lina</t>
-  </si>
-  <si>
-    <t>mandy@grupopana.com.pe</t>
-  </si>
-  <si>
-    <t>mcuya@toyotaperu.com.pe</t>
-  </si>
-  <si>
-    <t>mjimenez@autoesparfiori.com</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>mschmiel@modasa.com.pe</t>
-  </si>
-  <si>
     <t>Miguel</t>
   </si>
   <si>
-    <t>ochero@toyotaperu.com.pe</t>
-  </si>
-  <si>
-    <t>ohuaman@grupogesa.com</t>
-  </si>
-  <si>
-    <t>Orestes</t>
-  </si>
-  <si>
-    <t>quanweihuang168@gmail.com</t>
-  </si>
-  <si>
-    <t>Huang</t>
-  </si>
-  <si>
-    <t>rbettocchi@modasa.com.pe</t>
-  </si>
-  <si>
-    <t>Rossana</t>
-  </si>
-  <si>
-    <t>river070717@gmail.com</t>
-  </si>
-  <si>
-    <t>Linhao</t>
-  </si>
-  <si>
-    <t>stephanie.guerra@oxyion.com</t>
-  </si>
-  <si>
-    <t>Stephanie</t>
-  </si>
-  <si>
-    <t>aepo1@yahoo.com</t>
-  </si>
-  <si>
-    <t>Alcides</t>
-  </si>
-  <si>
-    <t>alitecnoperu@alitecnoperu.com</t>
-  </si>
-  <si>
     <t>Renato</t>
   </si>
   <si>
-    <t>asistentecontable@efysisa.com.pe</t>
-  </si>
-  <si>
     <t>Marisol</t>
   </si>
   <si>
-    <t>bcarabelli@donitalo.com</t>
-  </si>
-  <si>
-    <t>Bruno</t>
-  </si>
-  <si>
-    <t>cbrescia@2cerritos.com.pe</t>
-  </si>
-  <si>
-    <t>Carla</t>
-  </si>
-  <si>
-    <t>cerritos@2cerritos.com.pe</t>
-  </si>
-  <si>
-    <t>Tulio</t>
-  </si>
-  <si>
-    <t>colnatexsac@gmail.com</t>
-  </si>
-  <si>
-    <t>Franklin</t>
-  </si>
-  <si>
-    <t>croman@rich.com</t>
-  </si>
-  <si>
-    <t>Eva</t>
-  </si>
-  <si>
-    <t>drodriguez@greenfarm.com.pe</t>
-  </si>
-  <si>
-    <t>Denisse</t>
-  </si>
-  <si>
-    <t>edgarcubas11@gmail.com</t>
-  </si>
-  <si>
-    <t>gcarabelli@donitalo.com</t>
-  </si>
-  <si>
-    <t>Giancarlo</t>
-  </si>
-  <si>
-    <t>hurlich@alejosperu.com.pe</t>
-  </si>
-  <si>
     <t>Gloria</t>
   </si>
   <si>
-    <t>isoto@rich.com</t>
-  </si>
-  <si>
-    <t>Ingrid</t>
-  </si>
-  <si>
-    <t>jcormercial@greenfarm.com.pe</t>
-  </si>
-  <si>
     <t>Gonzalo</t>
   </si>
   <si>
-    <t>jmacedo@2cerritos.com.pe</t>
-  </si>
-  <si>
-    <t>joelvt@globalinkat.com</t>
-  </si>
-  <si>
-    <t>Joel</t>
-  </si>
-  <si>
-    <t>josuevillanueva@globalinkat.com</t>
-  </si>
-  <si>
-    <t>Josue</t>
-  </si>
-  <si>
-    <t>jpalejos@alejosperu.com.pe</t>
-  </si>
-  <si>
-    <t>lulapo8@gmail.com</t>
-  </si>
-  <si>
-    <t>Lourdes</t>
-  </si>
-  <si>
-    <t>magrena.espinoza123@gmail.com</t>
-  </si>
-  <si>
-    <t>Magrena</t>
-  </si>
-  <si>
-    <t>manzovini@efysisa.com.pe</t>
-  </si>
-  <si>
-    <t>mindrisita123@gmail.com</t>
-  </si>
-  <si>
-    <t>Lisset</t>
-  </si>
-  <si>
-    <t>norma.delacruz@alitecnoperu.com</t>
-  </si>
-  <si>
-    <t>noyafuso@2cerritos.com.pe</t>
-  </si>
-  <si>
-    <t>palejo@alejosperu.com.pe</t>
-  </si>
-  <si>
-    <t>rgomez@2cerritos.com.pe</t>
-  </si>
-  <si>
     <t>Raul</t>
   </si>
   <si>
-    <t>rosario.griffin@cramer.com.pe</t>
-  </si>
-  <si>
-    <t>Rosario</t>
-  </si>
-  <si>
-    <t>sumaqagrotrade@gmail.com</t>
-  </si>
-  <si>
     <t>Sonia</t>
   </si>
   <si>
-    <t>vania.yaya@alitecnoperu.com</t>
-  </si>
-  <si>
-    <t>Vania</t>
-  </si>
-  <si>
-    <t>victor.gomez@cramer.com.pe</t>
+    <t>abasurto@empresasdispolab.com</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>admin@dpgdutyfree.com</t>
+  </si>
+  <si>
+    <t>Edson</t>
+  </si>
+  <si>
+    <t>administracion@bfs.com.pe</t>
+  </si>
+  <si>
+    <t>cblancas@beautypacificperu.com</t>
+  </si>
+  <si>
+    <t>comellesagusoz@gmail.com</t>
+  </si>
+  <si>
+    <t>Giovanna</t>
+  </si>
+  <si>
+    <t>corporacionbioformula@gmail.com</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>cramos@jenifergrund.com</t>
+  </si>
+  <si>
+    <t>Cielo</t>
+  </si>
+  <si>
+    <t>cvera@unique-yanbal.com</t>
+  </si>
+  <si>
+    <t>Carol</t>
+  </si>
+  <si>
+    <t>diego.prudencio@rsm.pe</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>echavez@eficienciacontable.com</t>
+  </si>
+  <si>
+    <t>efigueroa@cpb-abogados.com.pe</t>
+  </si>
+  <si>
+    <t>facturacionelectronica@yanbal.com</t>
+  </si>
+  <si>
+    <t>Analia</t>
+  </si>
+  <si>
+    <t>fcayo@beautypacificperu.com</t>
+  </si>
+  <si>
+    <t>finanzas@lacooper.com</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>giorgio.lazo@grupoyelave.com</t>
+  </si>
+  <si>
+    <t>Giorgio</t>
+  </si>
+  <si>
+    <t>infoperu@empresasdispolab.com</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>javier.rusca@unique-yanbal.com</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>jgrundel@jenifergrund.com</t>
+  </si>
+  <si>
+    <t>jmendoza@empresasdispolab.com</t>
+  </si>
+  <si>
+    <t>jose.bustamante@givaudan.com</t>
+  </si>
+  <si>
+    <t>laura.abanto@unilever.com</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>maribell.delapena@unique-yanbal.com</t>
+  </si>
+  <si>
+    <t>Ignacio</t>
+  </si>
+  <si>
+    <t>marisol.mata@bfs.com.pe</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>marketing@bfs.com.pe</t>
+  </si>
+  <si>
+    <t>Cathy</t>
+  </si>
+  <si>
+    <t>mbejarano@highridgebrands.com</t>
+  </si>
+  <si>
+    <t>nmontalvo@lacooper.com</t>
+  </si>
+  <si>
+    <t>Nikolai</t>
+  </si>
+  <si>
+    <t>oacosta@beautypacificperu.com</t>
+  </si>
+  <si>
+    <t>Mac</t>
+  </si>
+  <si>
+    <t>rarias@lacooper.com</t>
+  </si>
+  <si>
+    <t>robregon@lacooper.com</t>
+  </si>
+  <si>
+    <t>Roxana</t>
+  </si>
+  <si>
+    <t>sarenas@lacooper.com</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>zverastegui@unique-yanbal.com</t>
+  </si>
+  <si>
+    <t>Zoila</t>
+  </si>
+  <si>
+    <t>abonifaz@calimod.com.pe</t>
+  </si>
+  <si>
+    <t>adaines077@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ada</t>
+  </si>
+  <si>
+    <t>amejiac@peiuniqueoutfit.com</t>
+  </si>
+  <si>
+    <t>c.barretobriceno@hotmail.com</t>
+  </si>
+  <si>
+    <t>Catherine</t>
+  </si>
+  <si>
+    <t>calzadociara@hotmail.com</t>
+  </si>
+  <si>
+    <t>cintya_1998salper@hotmail.com</t>
+  </si>
+  <si>
+    <t>Deisy</t>
+  </si>
+  <si>
+    <t>commod98@gmail.com</t>
+  </si>
+  <si>
+    <t>ctoribio@calimod.com.pe</t>
+  </si>
+  <si>
+    <t>Cinthya</t>
+  </si>
+  <si>
+    <t>ehbl1@hotmail.com</t>
+  </si>
+  <si>
+    <t>Edward</t>
+  </si>
+  <si>
+    <t>epajuelo@calimod.com.pe</t>
+  </si>
+  <si>
+    <t>Elmer</t>
+  </si>
+  <si>
+    <t>erodriguez@calimod.com.pe</t>
+  </si>
+  <si>
+    <t>Eder</t>
+  </si>
+  <si>
+    <t>freddy@gruponk.pe</t>
+  </si>
+  <si>
+    <t>Freddy</t>
+  </si>
+  <si>
+    <t>freddyqp2006@gmail.com</t>
+  </si>
+  <si>
+    <t>gdavilap@peiuniqueoutfit.com</t>
+  </si>
+  <si>
+    <t>gerenciacomercial.lima@tradesandder.com</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>info@tradesandder.com</t>
+  </si>
+  <si>
+    <t>Alexi</t>
+  </si>
+  <si>
+    <t>isbelsac@hotmail.com</t>
+  </si>
+  <si>
+    <t>marketing@ciara.com.pe</t>
+  </si>
+  <si>
+    <t>Yolanda</t>
+  </si>
+  <si>
+    <t>master@calimod.com.pe</t>
+  </si>
+  <si>
+    <t>Giovana</t>
+  </si>
+  <si>
+    <t>miguel.vergara@footloose.pe</t>
+  </si>
+  <si>
+    <t>neryq200@gmail.com</t>
+  </si>
+  <si>
+    <t>Nerida</t>
+  </si>
+  <si>
+    <t>oscarcorreaalamo@hotmail.com</t>
+  </si>
+  <si>
+    <t>peru1960@hotmail.es</t>
+  </si>
+  <si>
+    <t>Elvira</t>
+  </si>
+  <si>
+    <t>peruanadepublicidad@yahoo.com</t>
+  </si>
+  <si>
+    <t>produccion@ciara.com.pe</t>
+  </si>
+  <si>
+    <t>Erick</t>
+  </si>
+  <si>
+    <t>redyzas.2023@gmail.com</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>shoeslions@hotmail.com</t>
+  </si>
+  <si>
+    <t>Lucinda</t>
+  </si>
+  <si>
+    <t>sonialuz_06@hotmail.com</t>
+  </si>
+  <si>
+    <t>ventas@calimod.com.pe</t>
+  </si>
+  <si>
+    <t>Teresa</t>
+  </si>
+  <si>
+    <t>vicguevara.23@gmail.com</t>
+  </si>
+  <si>
+    <t>zapateriabrilaz@gmail.com</t>
+  </si>
+  <si>
+    <t>Marilyn</t>
+  </si>
+  <si>
+    <t>achehab@oster.com</t>
+  </si>
+  <si>
+    <t>alan.kahn@hisense.com</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>alberto.rosas@mabe.com.pe</t>
+  </si>
+  <si>
+    <t>caroll.burgos@mabe.com.pe</t>
+  </si>
+  <si>
+    <t>edisonq@imexpomundo.com</t>
+  </si>
+  <si>
+    <t>Edison</t>
+  </si>
+  <si>
+    <t>esazalar@lge.com</t>
+  </si>
+  <si>
+    <t>fernando.novoa@lge.com</t>
+  </si>
+  <si>
+    <t>Bu</t>
+  </si>
+  <si>
+    <t>fmerinocordova@gmail.com</t>
+  </si>
+  <si>
+    <t>ggeneral@best-appliances.net</t>
+  </si>
+  <si>
+    <t>guillermo.huerta@mabe.com.pe</t>
+  </si>
+  <si>
+    <t>Guillermo</t>
+  </si>
+  <si>
+    <t>hans.beuermann@lge.com</t>
+  </si>
+  <si>
+    <t>Hans</t>
+  </si>
+  <si>
+    <t>ijimenez@tottus.com.pe</t>
+  </si>
+  <si>
+    <t>Alexandra</t>
+  </si>
+  <si>
+    <t>javier.merino@pucp.pe</t>
+  </si>
+  <si>
+    <t>jbustamantei@tottus.com.pe</t>
+  </si>
+  <si>
+    <t>jramberg@tottus.com.pe</t>
+  </si>
+  <si>
+    <t>Johann</t>
+  </si>
+  <si>
+    <t>jredondo@tottus.com.pe</t>
+  </si>
+  <si>
+    <t>julia.bustamante@mabe.com.pe</t>
+  </si>
+  <si>
+    <t>liquanzhi@hisense.com</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>lseminarioa@tottus.com.pe</t>
+  </si>
+  <si>
+    <t>mj.comitre@samsung.com</t>
+  </si>
+  <si>
+    <t>Italo</t>
+  </si>
+  <si>
+    <t>nancy.farceque@gmail.com</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>nyulit@tottus.com.pe</t>
+  </si>
+  <si>
+    <t>Joan</t>
+  </si>
+  <si>
+    <t>presidencia@imexpomundo.com</t>
+  </si>
+  <si>
+    <t>Wilman</t>
+  </si>
+  <si>
+    <t>pseminariob@tottus.com.pe</t>
+  </si>
+  <si>
+    <t>rmontes@jardencs.com</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>roberto@tcl.com</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>rosa.v.c.c@tcl.com</t>
+  </si>
+  <si>
+    <t>silvia_17_09@hotmail.com</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>t_inche@hotmail.com</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>vanessa.corcino@tcl.com</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>zhutanhui@tcl.com</t>
+  </si>
+  <si>
+    <t>Yanhui</t>
+  </si>
+  <si>
+    <t>amallqui@promelsa.com.pe</t>
+  </si>
+  <si>
+    <t>amelia.urquizo@siemens.com</t>
+  </si>
+  <si>
+    <t>Amelia</t>
+  </si>
+  <si>
+    <t>ap.pacifico.ar@siemens.com</t>
+  </si>
+  <si>
+    <t>asistente.gerencia1@promelsa.com.pe</t>
+  </si>
+  <si>
+    <t>asistente.gerencia2@promelsa.com.pe</t>
+  </si>
+  <si>
+    <t>bettymallqui@promelsa.com.pe</t>
+  </si>
+  <si>
+    <t>Betty</t>
+  </si>
+  <si>
+    <t>cobranzas@ceyesa.com.pe</t>
+  </si>
+  <si>
+    <t>Madelin</t>
+  </si>
+  <si>
+    <t>detec@detecsac.com</t>
+  </si>
+  <si>
+    <t>diego.becerra@omegapower.com.pe</t>
+  </si>
+  <si>
+    <t>erojas@ceyesa.com.pe</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>fernandez@tjh2b.com</t>
+  </si>
+  <si>
+    <t>galcalde@changcommercial.com</t>
+  </si>
+  <si>
+    <t>Glen</t>
+  </si>
+  <si>
+    <t>gcardenas@ceyesa.com.pe</t>
+  </si>
+  <si>
+    <t>gestionrrhh@promelsa.com.pe</t>
+  </si>
+  <si>
+    <t>gkp@geyer-kabel.com</t>
+  </si>
+  <si>
+    <t>inseragsrl@hotmail.com</t>
+  </si>
+  <si>
+    <t>Gladys</t>
+  </si>
+  <si>
+    <t>ire@ireingenieros.com</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>iyc-damat@hotmail.com</t>
+  </si>
+  <si>
+    <t>jgarcia@mapalsa.com</t>
+  </si>
+  <si>
+    <t>Juana</t>
+  </si>
+  <si>
+    <t>joan.alvarezp@hotmail.com</t>
+  </si>
+  <si>
+    <t>jrmsolutionsperu@gmail.com</t>
+  </si>
+  <si>
+    <t>Doris</t>
+  </si>
+  <si>
+    <t>logistica@ceyesa.com.pe</t>
+  </si>
+  <si>
+    <t>lpino@ceyesa.com.pe</t>
+  </si>
+  <si>
+    <t>maritza.rodriguez_lozano@siemens.com</t>
+  </si>
+  <si>
+    <t>Maritza</t>
+  </si>
+  <si>
+    <t>mgarcia@changcommercial.com</t>
+  </si>
+  <si>
+    <t>nlopez@omegapower.com.pe</t>
+  </si>
+  <si>
+    <t>Nelson</t>
+  </si>
+  <si>
+    <t>pburga@mapalsa.com</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>ricardoram_25@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>talmasa@talmasa.com</t>
+  </si>
+  <si>
+    <t>Andres</t>
+  </si>
+  <si>
+    <t>zreyes@changcommercial.com</t>
+  </si>
+  <si>
+    <t>Zinnia</t>
   </si>
 </sst>
 </file>
@@ -1107,819 +1119,819 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>112</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B68" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B71" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B76" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B79" t="s">
-        <v>144</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B80" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B82" t="s">
-        <v>149</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B86" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B89" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B91" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B96" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B97" t="s">
-        <v>176</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B98" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B99" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B100" t="s">
-        <v>182</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B101" t="s">
-        <v>184</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B102" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B103" t="s">
-        <v>23</v>
+        <v>189</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B104" t="s">
-        <v>189</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B105" t="s">
-        <v>191</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -1935,15 +1947,15 @@
         <v>194</v>
       </c>
       <c r="B107" t="s">
-        <v>195</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B108" t="s">
         <v>196</v>
-      </c>
-      <c r="B108" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -1951,129 +1963,144 @@
         <v>197</v>
       </c>
       <c r="B109" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B110" t="s">
-        <v>200</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B111" t="s">
-        <v>144</v>
+        <v>15</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B112" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B113" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B114" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B115" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B119" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B120" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B121" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B122" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B123" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B124" t="s">
         <v>220</v>
       </c>
-      <c r="B123" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="4"/>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="4"/>
+      <c r="A125" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B125" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="4"/>
+      <c r="A126" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B126" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="4"/>
